--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEF774C-9014-4324-A414-4BD8DCA2BF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEECCF3-21AD-44CE-9743-4C80BA997F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="132">
   <si>
     <t>Date</t>
   </si>
@@ -424,6 +424,12 @@
   </si>
   <si>
     <t>Il réclame le pot de 200g</t>
+  </si>
+  <si>
+    <t>Ibrahima DIALLO (GAMBIEN)</t>
+  </si>
+  <si>
+    <t>Il dit qu'il va exporter le café Altimo stick a gambiee</t>
   </si>
 </sst>
 </file>
@@ -491,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -511,6 +517,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -829,8 +844,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P70" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P70" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P71" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P71" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1143,7 +1158,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -1256,11 +1271,11 @@
       <c r="N2" s="10">
         <v>201000</v>
       </c>
-      <c r="O2" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P2" s="12" t="str">
+      <c r="O2" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P2" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1308,11 +1323,11 @@
       <c r="N3" s="10">
         <v>2250000</v>
       </c>
-      <c r="O3" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P3" s="12" t="str">
+      <c r="O3" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P3" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1360,11 +1375,11 @@
       <c r="N4" s="10">
         <v>225000</v>
       </c>
-      <c r="O4" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P4" s="12" t="str">
+      <c r="O4" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P4" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1412,11 +1427,11 @@
       <c r="N5" s="10">
         <v>104000</v>
       </c>
-      <c r="O5" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P5" s="12" t="str">
+      <c r="O5" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P5" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1464,11 +1479,11 @@
       <c r="N6" s="10">
         <v>30000</v>
       </c>
-      <c r="O6" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P6" s="12" t="str">
+      <c r="O6" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P6" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1516,11 +1531,11 @@
       <c r="N7" s="10">
         <v>268000</v>
       </c>
-      <c r="O7" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P7" s="12" t="str">
+      <c r="O7" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P7" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1568,11 +1583,11 @@
       <c r="N8" s="10">
         <v>270000</v>
       </c>
-      <c r="O8" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P8" s="12" t="str">
+      <c r="O8" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P8" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1620,11 +1635,11 @@
       <c r="N9" s="10">
         <v>250000</v>
       </c>
-      <c r="O9" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P9" s="12" t="str">
+      <c r="O9" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P9" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1672,11 +1687,11 @@
       <c r="N10" s="10">
         <v>277500</v>
       </c>
-      <c r="O10" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P10" s="12" t="str">
+      <c r="O10" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P10" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1724,11 +1739,11 @@
       <c r="N11" s="10">
         <v>90000</v>
       </c>
-      <c r="O11" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P11" s="12" t="str">
+      <c r="O11" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P11" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1776,11 +1791,11 @@
       <c r="N12" s="10">
         <v>134000</v>
       </c>
-      <c r="O12" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P12" s="12" t="str">
+      <c r="O12" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P12" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1828,11 +1843,11 @@
       <c r="N13" s="10">
         <v>201000</v>
       </c>
-      <c r="O13" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P13" s="12" t="str">
+      <c r="O13" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P13" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1880,11 +1895,11 @@
       <c r="N14" s="10">
         <v>92500</v>
       </c>
-      <c r="O14" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P14" s="12" t="str">
+      <c r="O14" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P14" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1932,11 +1947,11 @@
       <c r="N15" s="10">
         <v>46250</v>
       </c>
-      <c r="O15" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P15" s="12" t="str">
+      <c r="O15" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -1984,11 +1999,11 @@
       <c r="N16" s="10">
         <v>270000</v>
       </c>
-      <c r="O16" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P16" s="12" t="str">
+      <c r="O16" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2036,11 +2051,11 @@
       <c r="N17" s="10">
         <v>450000</v>
       </c>
-      <c r="O17" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P17" s="12" t="str">
+      <c r="O17" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P17" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2088,11 +2103,11 @@
       <c r="N18" s="10">
         <v>450000</v>
       </c>
-      <c r="O18" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P18" s="12" t="str">
+      <c r="O18" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P18" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2140,11 +2155,11 @@
       <c r="N19" s="10">
         <v>936000</v>
       </c>
-      <c r="O19" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P19" s="12" t="str">
+      <c r="O19" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2192,11 +2207,11 @@
       <c r="N20" s="10">
         <v>450000</v>
       </c>
-      <c r="O20" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P20" s="12" t="str">
+      <c r="O20" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2244,11 +2259,11 @@
       <c r="N21" s="10">
         <v>33500</v>
       </c>
-      <c r="O21" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P21" s="12" t="str">
+      <c r="O21" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P21" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2296,11 +2311,11 @@
       <c r="N22" s="10">
         <v>250000</v>
       </c>
-      <c r="O22" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P22" s="12" t="str">
+      <c r="O22" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P22" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2348,11 +2363,11 @@
       <c r="N23" s="10">
         <v>67000</v>
       </c>
-      <c r="O23" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P23" s="12" t="str">
+      <c r="O23" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P23" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2400,11 +2415,11 @@
       <c r="N24" s="10">
         <v>268750</v>
       </c>
-      <c r="O24" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P24" s="12" t="str">
+      <c r="O24" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P24" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2452,11 +2467,11 @@
       <c r="N25" s="10">
         <v>150000</v>
       </c>
-      <c r="O25" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P25" s="12" t="str">
+      <c r="O25" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P25" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2504,11 +2519,11 @@
       <c r="N26" s="10">
         <v>33500</v>
       </c>
-      <c r="O26" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P26" s="12" t="str">
+      <c r="O26" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P26" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2556,11 +2571,11 @@
       <c r="N27" s="10">
         <v>537500</v>
       </c>
-      <c r="O27" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P27" s="12" t="str">
+      <c r="O27" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P27" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2608,11 +2623,11 @@
       <c r="N28" s="10">
         <v>180000</v>
       </c>
-      <c r="O28" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P28" s="12" t="str">
+      <c r="O28" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P28" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2660,11 +2675,11 @@
       <c r="N29" s="10">
         <v>9250</v>
       </c>
-      <c r="O29" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P29" s="12" t="str">
+      <c r="O29" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P29" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2712,11 +2727,11 @@
       <c r="N30" s="10">
         <v>9250</v>
       </c>
-      <c r="O30" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P30" s="12" t="str">
+      <c r="O30" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P30" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2764,11 +2779,11 @@
       <c r="N31" s="10">
         <v>9250</v>
       </c>
-      <c r="O31" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P31" s="12" t="str">
+      <c r="O31" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P31" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2816,11 +2831,11 @@
       <c r="N32" s="10">
         <v>9250</v>
       </c>
-      <c r="O32" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P32" s="12" t="str">
+      <c r="O32" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P32" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2868,11 +2883,11 @@
       <c r="N33" s="10">
         <v>12000</v>
       </c>
-      <c r="O33" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P33" s="12" t="str">
+      <c r="O33" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P33" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2920,11 +2935,11 @@
       <c r="N34" s="10">
         <v>650000</v>
       </c>
-      <c r="O34" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P34" s="12" t="str">
+      <c r="O34" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P34" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -2972,11 +2987,11 @@
       <c r="N35" s="10">
         <v>650000</v>
       </c>
-      <c r="O35" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P35" s="12" t="str">
+      <c r="O35" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P35" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3024,11 +3039,11 @@
       <c r="N36" s="10">
         <v>2600000</v>
       </c>
-      <c r="O36" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P36" s="12" t="str">
+      <c r="O36" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P36" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3076,11 +3091,11 @@
       <c r="N37" s="10">
         <v>1000000</v>
       </c>
-      <c r="O37" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P37" s="12" t="str">
+      <c r="O37" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P37" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3128,11 +3143,11 @@
       <c r="N38" s="10">
         <v>22000</v>
       </c>
-      <c r="O38" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P38" s="12" t="str">
+      <c r="O38" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P38" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3180,11 +3195,11 @@
       <c r="N39" s="10">
         <v>36000</v>
       </c>
-      <c r="O39" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P39" s="12" t="str">
+      <c r="O39" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P39" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3232,11 +3247,11 @@
       <c r="N40" s="10">
         <v>36000</v>
       </c>
-      <c r="O40" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P40" s="12" t="str">
+      <c r="O40" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P40" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3284,11 +3299,11 @@
       <c r="N41" s="10">
         <v>250000</v>
       </c>
-      <c r="O41" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P41" s="12" t="str">
+      <c r="O41" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P41" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3336,11 +3351,11 @@
       <c r="N42" s="10">
         <v>520000</v>
       </c>
-      <c r="O42" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P42" s="12" t="str">
+      <c r="O42" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P42" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3388,11 +3403,11 @@
       <c r="N43" s="10">
         <v>150000</v>
       </c>
-      <c r="O43" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P43" s="12" t="str">
+      <c r="O43" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P43" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3440,11 +3455,11 @@
       <c r="N44" s="10">
         <v>60000</v>
       </c>
-      <c r="O44" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P44" s="12" t="str">
+      <c r="O44" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P44" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3492,11 +3507,11 @@
       <c r="N45" s="10">
         <v>54000</v>
       </c>
-      <c r="O45" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P45" s="12" t="str">
+      <c r="O45" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P45" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3544,11 +3559,11 @@
       <c r="N46" s="10">
         <v>2600000</v>
       </c>
-      <c r="O46" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P46" s="12" t="str">
+      <c r="O46" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P46" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3596,11 +3611,11 @@
       <c r="N47" s="10">
         <v>650000</v>
       </c>
-      <c r="O47" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P47" s="12" t="str">
+      <c r="O47" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P47" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3648,11 +3663,11 @@
       <c r="N48" s="10">
         <v>500000</v>
       </c>
-      <c r="O48" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P48" s="12" t="str">
+      <c r="O48" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P48" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3700,11 +3715,11 @@
       <c r="N49" s="10">
         <v>210000</v>
       </c>
-      <c r="O49" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P49" s="12" t="str">
+      <c r="O49" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P49" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3752,11 +3767,11 @@
       <c r="N50" s="10">
         <v>52000</v>
       </c>
-      <c r="O50" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P50" s="12" t="str">
+      <c r="O50" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P50" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3804,11 +3819,11 @@
       <c r="N51" s="10">
         <v>2600000</v>
       </c>
-      <c r="O51" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P51" s="12" t="str">
+      <c r="O51" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P51" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3856,11 +3871,11 @@
       <c r="N52" s="10">
         <v>150000</v>
       </c>
-      <c r="O52" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P52" s="12" t="str">
+      <c r="O52" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P52" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3908,11 +3923,11 @@
       <c r="N53" s="10">
         <v>243750</v>
       </c>
-      <c r="O53" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P53" s="12" t="str">
+      <c r="O53" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P53" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -3960,11 +3975,11 @@
       <c r="N54" s="10">
         <v>231250</v>
       </c>
-      <c r="O54" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P54" s="12" t="str">
+      <c r="O54" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P54" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4012,11 +4027,11 @@
       <c r="N55" s="10">
         <v>600000</v>
       </c>
-      <c r="O55" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P55" s="12" t="str">
+      <c r="O55" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P55" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4064,11 +4079,11 @@
       <c r="N56" s="10">
         <v>243750</v>
       </c>
-      <c r="O56" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P56" s="12" t="str">
+      <c r="O56" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P56" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4116,11 +4131,11 @@
       <c r="N57" s="10">
         <v>19500</v>
       </c>
-      <c r="O57" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P57" s="12" t="str">
+      <c r="O57" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P57" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4168,11 +4183,11 @@
       <c r="N58" s="10">
         <v>234500</v>
       </c>
-      <c r="O58" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P58" s="12" t="str">
+      <c r="O58" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P58" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4220,11 +4235,11 @@
       <c r="N59" s="10">
         <v>240000</v>
       </c>
-      <c r="O59" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P59" s="12" t="str">
+      <c r="O59" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P59" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4272,11 +4287,11 @@
       <c r="N60" s="10">
         <v>243750</v>
       </c>
-      <c r="O60" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P60" s="12" t="str">
+      <c r="O60" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P60" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4324,11 +4339,11 @@
       <c r="N61" s="10">
         <v>97500</v>
       </c>
-      <c r="O61" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P61" s="12" t="str">
+      <c r="O61" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P61" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4376,11 +4391,11 @@
       <c r="N62" s="10">
         <v>33500</v>
       </c>
-      <c r="O62" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P62" s="12" t="str">
+      <c r="O62" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P62" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4428,11 +4443,11 @@
       <c r="N63" s="10">
         <v>33500</v>
       </c>
-      <c r="O63" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P63" s="12" t="str">
+      <c r="O63" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P63" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4480,11 +4495,11 @@
       <c r="N64" s="10">
         <v>24000</v>
       </c>
-      <c r="O64" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P64" s="12" t="str">
+      <c r="O64" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P64" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4532,11 +4547,11 @@
       <c r="N65" s="10">
         <v>30000</v>
       </c>
-      <c r="O65" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P65" s="12" t="str">
+      <c r="O65" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P65" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4584,11 +4599,11 @@
       <c r="N66" s="10">
         <v>36000</v>
       </c>
-      <c r="O66" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P66" s="12" t="str">
+      <c r="O66" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P66" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4636,11 +4651,11 @@
       <c r="N67" s="10">
         <v>750000</v>
       </c>
-      <c r="O67" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P67" s="12" t="str">
+      <c r="O67" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P67" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4688,11 +4703,11 @@
       <c r="N68" s="10">
         <v>450000</v>
       </c>
-      <c r="O68" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P68" s="12" t="str">
+      <c r="O68" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P68" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4740,11 +4755,11 @@
       <c r="N69" s="10">
         <v>650000</v>
       </c>
-      <c r="O69" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P69" s="12" t="str">
+      <c r="O69" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P69" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
@@ -4792,11 +4807,63 @@
       <c r="N70" s="10">
         <v>750000</v>
       </c>
-      <c r="O70" s="11" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P70" s="12" t="str">
+      <c r="O70" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P70" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A71" s="11">
+        <v>46069</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F71" s="12">
+        <v>777032455</v>
+      </c>
+      <c r="G71" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="12">
+        <v>100</v>
+      </c>
+      <c r="M71" s="13">
+        <v>29500</v>
+      </c>
+      <c r="N71" s="13">
+        <v>2950000</v>
+      </c>
+      <c r="O71" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P71" s="15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEECCF3-21AD-44CE-9743-4C80BA997F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4914A678-D06E-4A21-8F58-445CB2596222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -497,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -527,19 +527,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2303,13 +2290,13 @@
         <v>56</v>
       </c>
       <c r="L22" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M22" s="10">
         <v>10000</v>
       </c>
       <c r="N22" s="10">
-        <v>250000</v>
+        <v>260000</v>
       </c>
       <c r="O22" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -2410,10 +2397,10 @@
         <v>25</v>
       </c>
       <c r="M24" s="10">
-        <v>10750</v>
+        <v>10000</v>
       </c>
       <c r="N24" s="10">
-        <v>268750</v>
+        <v>250000</v>
       </c>
       <c r="O24" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -2566,10 +2553,10 @@
         <v>50</v>
       </c>
       <c r="M27" s="10">
-        <v>10750</v>
+        <v>10000</v>
       </c>
       <c r="N27" s="10">
-        <v>537500</v>
+        <v>500000</v>
       </c>
       <c r="O27" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -4817,53 +4804,53 @@
       </c>
     </row>
     <row r="71" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A71" s="11">
+      <c r="A71" s="8">
         <v>46069</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="9">
         <v>777032455</v>
       </c>
-      <c r="G71" s="12" t="s">
+      <c r="G71" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H71" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="12" t="s">
+      <c r="H71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="K71" s="12" t="s">
+      <c r="K71" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L71" s="12">
+      <c r="L71" s="9">
         <v>100</v>
       </c>
-      <c r="M71" s="13">
+      <c r="M71" s="10">
         <v>29500</v>
       </c>
-      <c r="N71" s="13">
+      <c r="N71" s="10">
         <v>2950000</v>
       </c>
-      <c r="O71" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
-      </c>
-      <c r="P71" s="15" t="str">
+      <c r="O71" s="7" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S08</v>
+      </c>
+      <c r="P71" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4914A678-D06E-4A21-8F58-445CB2596222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FE09F3-B422-4911-8C23-8768A3B86730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="172">
   <si>
     <t>Date</t>
   </si>
@@ -430,6 +430,126 @@
   </si>
   <si>
     <t>Il dit qu'il va exporter le café Altimo stick a gambiee</t>
+  </si>
+  <si>
+    <t>PA NDIAYE</t>
+  </si>
+  <si>
+    <t>Yahya Sow Champ de courses</t>
+  </si>
+  <si>
+    <t>Moustapha BA</t>
+  </si>
+  <si>
+    <t>Elhadj</t>
+  </si>
+  <si>
+    <t>SEYDOU TALL</t>
+  </si>
+  <si>
+    <t>Yeumbeul Mbéde Sass</t>
+  </si>
+  <si>
+    <t>MAMDOU DIA</t>
+  </si>
+  <si>
+    <t>Dame Castor</t>
+  </si>
+  <si>
+    <t>Elhadj Ly</t>
+  </si>
+  <si>
+    <t>Stapro.com SARL n2</t>
+  </si>
+  <si>
+    <t>Il est satisfait de la rapidité de la livraison</t>
+  </si>
+  <si>
+    <t>Sodidalo SARL</t>
+  </si>
+  <si>
+    <t>18safar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vais essayer avec </t>
+  </si>
+  <si>
+    <t>Je vais essayer avec</t>
+  </si>
+  <si>
+    <t>Café Altimo pot 50g x 24 pcs</t>
+  </si>
+  <si>
+    <t>Mouhamed Ba</t>
+  </si>
+  <si>
+    <t>Il dit que les livraisons sont lentes</t>
+  </si>
+  <si>
+    <t>Pikine Sandika</t>
+  </si>
+  <si>
+    <t>Aliou Ba</t>
+  </si>
+  <si>
+    <t>Keur Massar Gouygui</t>
+  </si>
+  <si>
+    <t>Mountaha</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous avez retardé mon commende </t>
+  </si>
+  <si>
+    <t>Liberté 1 à 6</t>
+  </si>
+  <si>
+    <t>Djibril</t>
+  </si>
+  <si>
+    <t>Client non Partenaire</t>
+  </si>
+  <si>
+    <t>Golf</t>
+  </si>
+  <si>
+    <t>MAMADOU LAMINE DIALLO</t>
+  </si>
+  <si>
+    <t>Grand Yoff</t>
+  </si>
+  <si>
+    <t>Dame DIOP</t>
+  </si>
+  <si>
+    <t>Alassane Diallo</t>
+  </si>
+  <si>
+    <t>Siradio  Barry</t>
+  </si>
+  <si>
+    <t>Colobane</t>
+  </si>
+  <si>
+    <t>Alimentation Diallo</t>
+  </si>
+  <si>
+    <t>Livré le 26-02</t>
+  </si>
+  <si>
+    <t>Nord Foire</t>
+  </si>
+  <si>
+    <t>Livré le 26_02</t>
+  </si>
+  <si>
+    <t>Bala</t>
+  </si>
+  <si>
+    <t>Vous avez retardé mon commende</t>
   </si>
 </sst>
 </file>
@@ -497,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -527,6 +647,19 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,8 +964,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P71" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P71" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P131" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P131" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1145,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -4855,6 +4988,3126 @@
         <v>février</v>
       </c>
     </row>
+    <row r="72" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A72" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="12">
+        <v>776428218</v>
+      </c>
+      <c r="G72" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K72" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" s="12">
+        <v>20</v>
+      </c>
+      <c r="M72" s="13">
+        <v>9500</v>
+      </c>
+      <c r="N72" s="13">
+        <v>190000</v>
+      </c>
+      <c r="O72" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P72" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A73" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F73" s="12">
+        <v>774277399</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K73" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73" s="12">
+        <v>20</v>
+      </c>
+      <c r="M73" s="13">
+        <v>9500</v>
+      </c>
+      <c r="N73" s="13">
+        <v>190000</v>
+      </c>
+      <c r="O73" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P73" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A74" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F74" s="12">
+        <v>778579191</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74" s="12">
+        <v>30</v>
+      </c>
+      <c r="M74" s="13">
+        <v>9750</v>
+      </c>
+      <c r="N74" s="13">
+        <v>292500</v>
+      </c>
+      <c r="O74" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P74" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A75" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F75" s="12">
+        <v>774414059</v>
+      </c>
+      <c r="G75" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K75" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L75" s="12">
+        <v>25</v>
+      </c>
+      <c r="M75" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N75" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O75" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P75" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A76" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="12">
+        <v>779486095</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K76" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L76" s="12">
+        <v>25</v>
+      </c>
+      <c r="M76" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N76" s="13">
+        <v>450000</v>
+      </c>
+      <c r="O76" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P76" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A77" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F77" s="12">
+        <v>779676016</v>
+      </c>
+      <c r="G77" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K77" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L77" s="12">
+        <v>50</v>
+      </c>
+      <c r="M77" s="13">
+        <v>11000</v>
+      </c>
+      <c r="N77" s="13">
+        <v>550000</v>
+      </c>
+      <c r="O77" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P77" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A78" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F78" s="12">
+        <v>786323232</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K78" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L78" s="12">
+        <v>25</v>
+      </c>
+      <c r="M78" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N78" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O78" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P78" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A79" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F79" s="12">
+        <v>768059355</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K79" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79" s="12">
+        <v>60</v>
+      </c>
+      <c r="M79" s="13">
+        <v>9500</v>
+      </c>
+      <c r="N79" s="13">
+        <v>570000</v>
+      </c>
+      <c r="O79" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P79" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A80" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F80" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G80" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K80" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L80" s="12">
+        <v>1</v>
+      </c>
+      <c r="M80" s="13">
+        <v>33500</v>
+      </c>
+      <c r="N80" s="13">
+        <v>33500</v>
+      </c>
+      <c r="O80" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P80" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A81" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F81" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G81" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K81" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L81" s="12">
+        <v>7</v>
+      </c>
+      <c r="M81" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N81" s="13">
+        <v>84000</v>
+      </c>
+      <c r="O81" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P81" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A82" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" s="12">
+        <v>777096402</v>
+      </c>
+      <c r="G82" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" s="12">
+        <v>10</v>
+      </c>
+      <c r="M82" s="13">
+        <v>9750</v>
+      </c>
+      <c r="N82" s="13">
+        <v>97500</v>
+      </c>
+      <c r="O82" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P82" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A83" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" s="12">
+        <v>777096402</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K83" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83" s="12">
+        <v>10</v>
+      </c>
+      <c r="M83" s="13">
+        <v>9750</v>
+      </c>
+      <c r="N83" s="13">
+        <v>97500</v>
+      </c>
+      <c r="O83" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P83" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A84" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F84" s="12">
+        <v>777262311</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H84" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K84" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84" s="12">
+        <v>5</v>
+      </c>
+      <c r="M84" s="13">
+        <v>9750</v>
+      </c>
+      <c r="N84" s="13">
+        <v>48750</v>
+      </c>
+      <c r="O84" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P84" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A85" s="11">
+        <v>46076</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F85" s="12">
+        <v>777262311</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K85" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L85" s="12">
+        <v>5</v>
+      </c>
+      <c r="M85" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N85" s="13">
+        <v>60000</v>
+      </c>
+      <c r="O85" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P85" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A86" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F86" s="12">
+        <v>772873297</v>
+      </c>
+      <c r="G86" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L86" s="12">
+        <v>45</v>
+      </c>
+      <c r="M86" s="13">
+        <v>12500</v>
+      </c>
+      <c r="N86" s="13">
+        <v>562500</v>
+      </c>
+      <c r="O86" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P86" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A87" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F87" s="12">
+        <v>775039973</v>
+      </c>
+      <c r="G87" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="K87" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L87" s="12">
+        <v>25</v>
+      </c>
+      <c r="M87" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N87" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O87" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P87" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A88" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F88" s="12">
+        <v>778356666</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K88" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L88" s="12">
+        <v>25</v>
+      </c>
+      <c r="M88" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N88" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O88" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P88" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A89" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F89" s="12">
+        <v>780172121</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K89" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L89" s="12">
+        <v>1</v>
+      </c>
+      <c r="M89" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N89" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O89" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P89" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A90" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F90" s="12">
+        <v>777972938</v>
+      </c>
+      <c r="G90" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K90" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L90" s="12">
+        <v>3</v>
+      </c>
+      <c r="M90" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N90" s="13">
+        <v>36000</v>
+      </c>
+      <c r="O90" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P90" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A91" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F91" s="12">
+        <v>777972938</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K91" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L91" s="12">
+        <v>2</v>
+      </c>
+      <c r="M91" s="13">
+        <v>33500</v>
+      </c>
+      <c r="N91" s="13">
+        <v>67000</v>
+      </c>
+      <c r="O91" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P91" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A92" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F92" s="12">
+        <v>777972938</v>
+      </c>
+      <c r="G92" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H92" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K92" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L92" s="12">
+        <v>2</v>
+      </c>
+      <c r="M92" s="13">
+        <v>33500</v>
+      </c>
+      <c r="N92" s="13">
+        <v>67000</v>
+      </c>
+      <c r="O92" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P92" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A93" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F93" s="12">
+        <v>777972938</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H93" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K93" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="L93" s="12">
+        <v>1</v>
+      </c>
+      <c r="M93" s="13">
+        <v>17500</v>
+      </c>
+      <c r="N93" s="13">
+        <v>17500</v>
+      </c>
+      <c r="O93" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P93" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A94" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F94" s="12">
+        <v>777972938</v>
+      </c>
+      <c r="G94" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H94" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L94" s="12">
+        <v>2</v>
+      </c>
+      <c r="M94" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N94" s="13">
+        <v>52000</v>
+      </c>
+      <c r="O94" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P94" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A95" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F95" s="12">
+        <v>775894235</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K95" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L95" s="12">
+        <v>25</v>
+      </c>
+      <c r="M95" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N95" s="13">
+        <v>300000</v>
+      </c>
+      <c r="O95" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P95" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A96" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F96" s="12">
+        <v>774379845</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L96" s="12">
+        <v>25</v>
+      </c>
+      <c r="M96" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N96" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O96" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P96" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A97" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F97" s="12">
+        <v>778356666</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L97" s="12">
+        <v>5</v>
+      </c>
+      <c r="M97" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N97" s="13">
+        <v>90000</v>
+      </c>
+      <c r="O97" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P97" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A98" s="11">
+        <v>46078</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F98" s="12">
+        <v>778356666</v>
+      </c>
+      <c r="G98" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H98" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L98" s="12">
+        <v>2</v>
+      </c>
+      <c r="M98" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N98" s="13">
+        <v>36000</v>
+      </c>
+      <c r="O98" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P98" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A99" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F99" s="12">
+        <v>774061052</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K99" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L99" s="12">
+        <v>50</v>
+      </c>
+      <c r="M99" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N99" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="O99" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P99" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A100" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F100" s="12">
+        <v>774446240</v>
+      </c>
+      <c r="G100" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L100" s="12">
+        <v>25</v>
+      </c>
+      <c r="M100" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N100" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O100" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P100" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A101" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F101" s="12">
+        <v>771166914</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H101" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K101" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L101" s="12">
+        <v>1</v>
+      </c>
+      <c r="M101" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N101" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O101" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P101" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A102" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F102" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="K102" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L102" s="12">
+        <v>31</v>
+      </c>
+      <c r="M102" s="13">
+        <v>6000</v>
+      </c>
+      <c r="N102" s="13">
+        <v>186000</v>
+      </c>
+      <c r="O102" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P102" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A103" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F103" s="12">
+        <v>775079426</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K103" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L103" s="12">
+        <v>1</v>
+      </c>
+      <c r="M103" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N103" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O103" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P103" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A104" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" s="12">
+        <v>774245132</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H104" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L104" s="12">
+        <v>25</v>
+      </c>
+      <c r="M104" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N104" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O104" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P104" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A105" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F105" s="12">
+        <v>773777037</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K105" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L105" s="12">
+        <v>25</v>
+      </c>
+      <c r="M105" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N105" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O105" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P105" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A106" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F106" s="12">
+        <v>774216339</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K106" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L106" s="12">
+        <v>25</v>
+      </c>
+      <c r="M106" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N106" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O106" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P106" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A107" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F107" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K107" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L107" s="12">
+        <v>25</v>
+      </c>
+      <c r="M107" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N107" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O107" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P107" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A108" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F108" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G108" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K108" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="L108" s="12">
+        <v>1</v>
+      </c>
+      <c r="M108" s="13">
+        <v>17500</v>
+      </c>
+      <c r="N108" s="13">
+        <v>17500</v>
+      </c>
+      <c r="O108" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P108" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A109" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F109" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G109" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K109" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L109" s="12">
+        <v>3</v>
+      </c>
+      <c r="M109" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N109" s="13">
+        <v>27750</v>
+      </c>
+      <c r="O109" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P109" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A110" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F110" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G110" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K110" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L110" s="12">
+        <v>1</v>
+      </c>
+      <c r="M110" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N110" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O110" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P110" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A111" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F111" s="12">
+        <v>771355863</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K111" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L111" s="12">
+        <v>25</v>
+      </c>
+      <c r="M111" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N111" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O111" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P111" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A112" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F112" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G112" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J112" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="K112" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L112" s="12">
+        <v>4</v>
+      </c>
+      <c r="M112" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N112" s="13">
+        <v>104000</v>
+      </c>
+      <c r="O112" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P112" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A113" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F113" s="12">
+        <v>783596501</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="K113" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L113" s="12">
+        <v>1</v>
+      </c>
+      <c r="M113" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N113" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O113" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P113" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A114" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F114" s="12">
+        <v>783596501</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H114" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="K114" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L114" s="12">
+        <v>2</v>
+      </c>
+      <c r="M114" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N114" s="13">
+        <v>18500</v>
+      </c>
+      <c r="O114" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P114" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A115" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F115" s="12">
+        <v>761760410</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H115" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K115" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L115" s="12">
+        <v>1</v>
+      </c>
+      <c r="M115" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N115" s="13">
+        <v>9250</v>
+      </c>
+      <c r="O115" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P115" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A116" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F116" s="12">
+        <v>761760410</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L116" s="12">
+        <v>1</v>
+      </c>
+      <c r="M116" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N116" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O116" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P116" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A117" s="11">
+        <v>46080</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F117" s="12">
+        <v>776175166</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K117" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L117" s="12">
+        <v>100</v>
+      </c>
+      <c r="M117" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N117" s="13">
+        <v>2600000</v>
+      </c>
+      <c r="O117" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P117" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A118" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F118" s="12">
+        <v>774446240</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K118" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L118" s="12">
+        <v>25</v>
+      </c>
+      <c r="M118" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N118" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O118" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P118" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A119" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F119" s="12">
+        <v>774216339</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K119" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L119" s="12">
+        <v>25</v>
+      </c>
+      <c r="M119" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N119" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O119" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P119" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A120" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F120" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G120" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="K120" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L120" s="12">
+        <v>31</v>
+      </c>
+      <c r="M120" s="13">
+        <v>6000</v>
+      </c>
+      <c r="N120" s="13">
+        <v>186000</v>
+      </c>
+      <c r="O120" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P120" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A121" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F121" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="K121" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L121" s="12">
+        <v>3</v>
+      </c>
+      <c r="M121" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N121" s="13">
+        <v>78000</v>
+      </c>
+      <c r="O121" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P121" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A122" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F122" s="12">
+        <v>775079426</v>
+      </c>
+      <c r="G122" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I122" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="K122" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L122" s="12">
+        <v>1</v>
+      </c>
+      <c r="M122" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N122" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O122" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P122" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A123" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="F123" s="12">
+        <v>773777037</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K123" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L123" s="12">
+        <v>25</v>
+      </c>
+      <c r="M123" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N123" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O123" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P123" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A124" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F124" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G124" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H124" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K124" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L124" s="12">
+        <v>25</v>
+      </c>
+      <c r="M124" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N124" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O124" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P124" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A125" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F125" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G125" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H125" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K125" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="L125" s="12">
+        <v>1</v>
+      </c>
+      <c r="M125" s="13">
+        <v>17500</v>
+      </c>
+      <c r="N125" s="13">
+        <v>17500</v>
+      </c>
+      <c r="O125" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P125" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A126" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F126" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G126" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K126" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L126" s="12">
+        <v>3</v>
+      </c>
+      <c r="M126" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N126" s="13">
+        <v>27750</v>
+      </c>
+      <c r="O126" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P126" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A127" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F127" s="12">
+        <v>772289185</v>
+      </c>
+      <c r="G127" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H127" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I127" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K127" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L127" s="12">
+        <v>1</v>
+      </c>
+      <c r="M127" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N127" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O127" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P127" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A128" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="F128" s="12">
+        <v>771355863</v>
+      </c>
+      <c r="G128" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H128" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K128" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L128" s="12">
+        <v>25</v>
+      </c>
+      <c r="M128" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N128" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O128" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P128" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A129" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F129" s="12">
+        <v>774061052</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H129" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K129" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L129" s="12">
+        <v>50</v>
+      </c>
+      <c r="M129" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N129" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="O129" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P129" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A130" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F130" s="12">
+        <v>771166914</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H130" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I130" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K130" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L130" s="12">
+        <v>1</v>
+      </c>
+      <c r="M130" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N130" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O130" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P130" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A131" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F131" s="12">
+        <v>774245132</v>
+      </c>
+      <c r="G131" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H131" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K131" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L131" s="12">
+        <v>25</v>
+      </c>
+      <c r="M131" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N131" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O131" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P131" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FE09F3-B422-4911-8C23-8768A3B86730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DDFA74-6429-4533-AA9C-38120FC067E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="172">
   <si>
     <t>Date</t>
   </si>
@@ -456,9 +456,6 @@
     <t>Dame Castor</t>
   </si>
   <si>
-    <t>Elhadj Ly</t>
-  </si>
-  <si>
     <t>Stapro.com SARL n2</t>
   </si>
   <si>
@@ -468,9 +465,6 @@
     <t>Sodidalo SARL</t>
   </si>
   <si>
-    <t>18safar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Je vais essayer avec </t>
   </si>
   <si>
@@ -501,9 +495,6 @@
     <t>Alpha</t>
   </si>
   <si>
-    <t xml:space="preserve">Vous avez retardé mon commende </t>
-  </si>
-  <si>
     <t>Liberté 1 à 6</t>
   </si>
   <si>
@@ -550,6 +541,15 @@
   </si>
   <si>
     <t>Vous avez retardé mon commende</t>
+  </si>
+  <si>
+    <t>AMINATA NDIAYE</t>
+  </si>
+  <si>
+    <t>MAMADOU BA</t>
+  </si>
+  <si>
+    <t>AITA SARR</t>
   </si>
 </sst>
 </file>
@@ -905,16 +905,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -964,8 +964,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P131" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P131" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P115" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17">
+  <autoFilter ref="A1:P115" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1278,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P131"/>
+  <dimension ref="A1:P115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -5716,27 +5716,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A86" s="11">
         <v>46078</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E86" s="12" t="s">
         <v>140</v>
       </c>
       <c r="F86" s="12">
-        <v>772873297</v>
+        <v>775039973</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>13</v>
@@ -5745,19 +5745,19 @@
         <v>17</v>
       </c>
       <c r="J86" s="12" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="K86" s="12" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="L86" s="12">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="M86" s="13">
-        <v>12500</v>
+        <v>26000</v>
       </c>
       <c r="N86" s="13">
-        <v>562500</v>
+        <v>650000</v>
       </c>
       <c r="O86" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -5768,24 +5768,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A87" s="11">
         <v>46078</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F87" s="12">
-        <v>775039973</v>
+        <v>778356666</v>
       </c>
       <c r="G87" s="12" t="s">
         <v>16</v>
@@ -5797,7 +5797,7 @@
         <v>17</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="K87" s="12" t="s">
         <v>37</v>
@@ -5820,27 +5820,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A88" s="11">
         <v>46078</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="F88" s="12">
-        <v>778356666</v>
+        <v>777972938</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H88" s="12" t="s">
         <v>13</v>
@@ -5849,19 +5849,19 @@
         <v>17</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="K88" s="12" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="L88" s="12">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="M88" s="13">
-        <v>26000</v>
+        <v>12000</v>
       </c>
       <c r="N88" s="13">
-        <v>650000</v>
+        <v>36000</v>
       </c>
       <c r="O88" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -5883,37 +5883,37 @@
         <v>32</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E89" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F89" s="12">
+        <v>777972938</v>
+      </c>
+      <c r="G89" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F89" s="12">
-        <v>780172121</v>
-      </c>
-      <c r="G89" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="12" t="s">
-        <v>145</v>
-      </c>
       <c r="K89" s="12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L89" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M89" s="13">
-        <v>12000</v>
+        <v>33500</v>
       </c>
       <c r="N89" s="13">
-        <v>12000</v>
+        <v>67000</v>
       </c>
       <c r="O89" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -5953,19 +5953,19 @@
         <v>17</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K90" s="12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L90" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90" s="13">
-        <v>12000</v>
+        <v>33500</v>
       </c>
       <c r="N90" s="13">
-        <v>36000</v>
+        <v>67000</v>
       </c>
       <c r="O90" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6005,19 +6005,19 @@
         <v>17</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K91" s="12" t="s">
-        <v>51</v>
+        <v>145</v>
       </c>
       <c r="L91" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91" s="13">
-        <v>33500</v>
+        <v>17500</v>
       </c>
       <c r="N91" s="13">
-        <v>67000</v>
+        <v>17500</v>
       </c>
       <c r="O91" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6057,19 +6057,19 @@
         <v>17</v>
       </c>
       <c r="J92" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K92" s="12" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L92" s="12">
         <v>2</v>
       </c>
       <c r="M92" s="13">
-        <v>33500</v>
+        <v>26000</v>
       </c>
       <c r="N92" s="13">
-        <v>67000</v>
+        <v>52000</v>
       </c>
       <c r="O92" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6091,16 +6091,16 @@
         <v>32</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="F93" s="12">
-        <v>777972938</v>
+        <v>775894235</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H93" s="12" t="s">
         <v>13</v>
@@ -6109,19 +6109,19 @@
         <v>17</v>
       </c>
       <c r="J93" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K93" s="12" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="L93" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="M93" s="13">
-        <v>17500</v>
+        <v>12000</v>
       </c>
       <c r="N93" s="13">
-        <v>17500</v>
+        <v>300000</v>
       </c>
       <c r="O93" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6137,19 +6137,19 @@
         <v>46078</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F94" s="12">
-        <v>777972938</v>
+        <v>774379845</v>
       </c>
       <c r="G94" s="12" t="s">
         <v>30</v>
@@ -6161,19 +6161,19 @@
         <v>17</v>
       </c>
       <c r="J94" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K94" s="12" t="s">
         <v>37</v>
       </c>
       <c r="L94" s="12">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M94" s="13">
         <v>26000</v>
       </c>
       <c r="N94" s="13">
-        <v>52000</v>
+        <v>650000</v>
       </c>
       <c r="O94" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6184,24 +6184,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A95" s="11">
         <v>46078</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="F95" s="12">
-        <v>775894235</v>
+        <v>778356666</v>
       </c>
       <c r="G95" s="12" t="s">
         <v>16</v>
@@ -6213,19 +6213,19 @@
         <v>17</v>
       </c>
       <c r="J95" s="12" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="K95" s="12" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="L95" s="12">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="M95" s="13">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="N95" s="13">
-        <v>300000</v>
+        <v>90000</v>
       </c>
       <c r="O95" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6236,76 +6236,76 @@
         <v>février</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A96" s="11">
         <v>46078</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E96" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F96" s="12">
+        <v>778356666</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L96" s="12">
+        <v>2</v>
+      </c>
+      <c r="M96" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N96" s="13">
+        <v>36000</v>
+      </c>
+      <c r="O96" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S09</v>
+      </c>
+      <c r="P96" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A97" s="11">
+        <v>46079</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F96" s="12">
-        <v>774379845</v>
-      </c>
-      <c r="G96" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H96" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="12" t="s">
+      <c r="E97" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="K96" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L96" s="12">
-        <v>25</v>
-      </c>
-      <c r="M96" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N96" s="13">
-        <v>650000</v>
-      </c>
-      <c r="O96" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P96" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A97" s="11">
-        <v>46078</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>143</v>
-      </c>
       <c r="F97" s="12">
-        <v>778356666</v>
+        <v>774061052</v>
       </c>
       <c r="G97" s="12" t="s">
         <v>16</v>
@@ -6320,16 +6320,16 @@
         <v>21</v>
       </c>
       <c r="K97" s="12" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="L97" s="12">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="M97" s="13">
-        <v>18000</v>
+        <v>26000</v>
       </c>
       <c r="N97" s="13">
-        <v>90000</v>
+        <v>1300000</v>
       </c>
       <c r="O97" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6342,22 +6342,22 @@
     </row>
     <row r="98" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A98" s="11">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F98" s="12">
-        <v>778356666</v>
+        <v>774446240</v>
       </c>
       <c r="G98" s="12" t="s">
         <v>16</v>
@@ -6369,19 +6369,19 @@
         <v>17</v>
       </c>
       <c r="J98" s="12" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K98" s="12" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="L98" s="12">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M98" s="13">
-        <v>18000</v>
+        <v>9250</v>
       </c>
       <c r="N98" s="13">
-        <v>36000</v>
+        <v>231250</v>
       </c>
       <c r="O98" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6392,24 +6392,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A99" s="11">
         <v>46079</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="F99" s="12">
-        <v>774061052</v>
+        <v>774245132</v>
       </c>
       <c r="G99" s="12" t="s">
         <v>16</v>
@@ -6427,13 +6427,13 @@
         <v>37</v>
       </c>
       <c r="L99" s="12">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="M99" s="13">
         <v>26000</v>
       </c>
       <c r="N99" s="13">
-        <v>1300000</v>
+        <v>650000</v>
       </c>
       <c r="O99" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6449,19 +6449,19 @@
         <v>46079</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F100" s="12">
-        <v>774446240</v>
+        <v>773777037</v>
       </c>
       <c r="G100" s="12" t="s">
         <v>16</v>
@@ -6473,19 +6473,19 @@
         <v>17</v>
       </c>
       <c r="J100" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K100" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L100" s="12">
         <v>25</v>
       </c>
       <c r="M100" s="13">
-        <v>9250</v>
+        <v>26000</v>
       </c>
       <c r="N100" s="13">
-        <v>231250</v>
+        <v>650000</v>
       </c>
       <c r="O100" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6496,27 +6496,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A101" s="11">
         <v>46079</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>47</v>
+        <v>158</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F101" s="12">
-        <v>771166914</v>
+        <v>774216339</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>13</v>
@@ -6525,19 +6525,19 @@
         <v>17</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K101" s="12" t="s">
         <v>37</v>
       </c>
       <c r="L101" s="12">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="M101" s="13">
         <v>26000</v>
       </c>
       <c r="N101" s="13">
-        <v>26000</v>
+        <v>650000</v>
       </c>
       <c r="O101" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6553,19 +6553,19 @@
         <v>46079</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="F102" s="12">
-        <v>773817561</v>
+        <v>772289185</v>
       </c>
       <c r="G102" s="12" t="s">
         <v>16</v>
@@ -6577,19 +6577,19 @@
         <v>17</v>
       </c>
       <c r="J102" s="12" t="s">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="K102" s="12" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="L102" s="12">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M102" s="13">
-        <v>6000</v>
+        <v>26000</v>
       </c>
       <c r="N102" s="13">
-        <v>186000</v>
+        <v>650000</v>
       </c>
       <c r="O102" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6605,43 +6605,43 @@
         <v>46079</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F103" s="12">
-        <v>775079426</v>
+        <v>772289185</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H103" s="12" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="I103" s="12" t="s">
         <v>17</v>
       </c>
       <c r="J103" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K103" s="12" t="s">
         <v>145</v>
-      </c>
-      <c r="K103" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="L103" s="12">
         <v>1</v>
       </c>
       <c r="M103" s="13">
-        <v>12000</v>
+        <v>17500</v>
       </c>
       <c r="N103" s="13">
-        <v>12000</v>
+        <v>17500</v>
       </c>
       <c r="O103" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6652,24 +6652,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A104" s="11">
         <v>46079</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="F104" s="12">
-        <v>774245132</v>
+        <v>772289185</v>
       </c>
       <c r="G104" s="12" t="s">
         <v>16</v>
@@ -6684,16 +6684,16 @@
         <v>21</v>
       </c>
       <c r="K104" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L104" s="12">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="M104" s="13">
-        <v>26000</v>
+        <v>9250</v>
       </c>
       <c r="N104" s="13">
-        <v>650000</v>
+        <v>27750</v>
       </c>
       <c r="O104" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6704,24 +6704,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A105" s="11">
         <v>46079</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="E105" s="12" t="s">
         <v>160</v>
       </c>
       <c r="F105" s="12">
-        <v>773777037</v>
+        <v>772289185</v>
       </c>
       <c r="G105" s="12" t="s">
         <v>16</v>
@@ -6736,16 +6736,16 @@
         <v>21</v>
       </c>
       <c r="K105" s="12" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="L105" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M105" s="13">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="N105" s="13">
-        <v>650000</v>
+        <v>18000</v>
       </c>
       <c r="O105" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6756,24 +6756,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A106" s="11">
         <v>46079</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D106" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E106" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="E106" s="12" t="s">
-        <v>162</v>
-      </c>
       <c r="F106" s="12">
-        <v>774216339</v>
+        <v>771355863</v>
       </c>
       <c r="G106" s="12" t="s">
         <v>16</v>
@@ -6808,27 +6808,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A107" s="11">
         <v>46079</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="E107" s="12" t="s">
         <v>163</v>
       </c>
       <c r="F107" s="12">
-        <v>772289185</v>
+        <v>783596501</v>
       </c>
       <c r="G107" s="12" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>13</v>
@@ -6837,19 +6837,19 @@
         <v>17</v>
       </c>
       <c r="J107" s="12" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="K107" s="12" t="s">
         <v>37</v>
       </c>
       <c r="L107" s="12">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M107" s="13">
         <v>26000</v>
       </c>
       <c r="N107" s="13">
-        <v>650000</v>
+        <v>26000</v>
       </c>
       <c r="O107" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6860,27 +6860,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A108" s="11">
         <v>46079</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>163</v>
       </c>
       <c r="F108" s="12">
-        <v>772289185</v>
+        <v>783596501</v>
       </c>
       <c r="G108" s="12" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>13</v>
@@ -6889,19 +6889,19 @@
         <v>17</v>
       </c>
       <c r="J108" s="12" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="K108" s="12" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="L108" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M108" s="13">
-        <v>17500</v>
+        <v>9250</v>
       </c>
       <c r="N108" s="13">
-        <v>17500</v>
+        <v>18500</v>
       </c>
       <c r="O108" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6912,27 +6912,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A109" s="11">
         <v>46079</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="E109" s="12" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="F109" s="12">
-        <v>772289185</v>
+        <v>761760410</v>
       </c>
       <c r="G109" s="12" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>13</v>
@@ -6941,19 +6941,19 @@
         <v>17</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="K109" s="12" t="s">
         <v>34</v>
       </c>
       <c r="L109" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M109" s="13">
         <v>9250</v>
       </c>
       <c r="N109" s="13">
-        <v>27750</v>
+        <v>9250</v>
       </c>
       <c r="O109" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6964,27 +6964,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A110" s="11">
         <v>46079</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="E110" s="12" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="F110" s="12">
-        <v>772289185</v>
+        <v>761760410</v>
       </c>
       <c r="G110" s="12" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="H110" s="12" t="s">
         <v>13</v>
@@ -6993,19 +6993,19 @@
         <v>17</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="K110" s="12" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="L110" s="12">
         <v>1</v>
       </c>
       <c r="M110" s="13">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="N110" s="13">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="O110" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -7016,24 +7016,24 @@
         <v>février</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A111" s="11">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F111" s="12">
-        <v>771355863</v>
+        <v>776175166</v>
       </c>
       <c r="G111" s="12" t="s">
         <v>16</v>
@@ -7045,19 +7045,19 @@
         <v>17</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="K111" s="12" t="s">
         <v>37</v>
       </c>
       <c r="L111" s="12">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M111" s="13">
         <v>26000</v>
       </c>
       <c r="N111" s="13">
-        <v>650000</v>
+        <v>2600000</v>
       </c>
       <c r="O111" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -7097,19 +7097,19 @@
         <v>17</v>
       </c>
       <c r="J112" s="12" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="K112" s="12" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="L112" s="12">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="M112" s="13">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="N112" s="13">
-        <v>104000</v>
+        <v>186000</v>
       </c>
       <c r="O112" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -7120,27 +7120,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A113" s="11">
         <v>46079</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="F113" s="12">
-        <v>783596501</v>
+        <v>773817561</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>13</v>
@@ -7149,19 +7149,19 @@
         <v>17</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K113" s="12" t="s">
         <v>37</v>
       </c>
       <c r="L113" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M113" s="13">
         <v>26000</v>
       </c>
       <c r="N113" s="13">
-        <v>26000</v>
+        <v>78000</v>
       </c>
       <c r="O113" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -7172,48 +7172,48 @@
         <v>février</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A114" s="11">
         <v>46079</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F114" s="12">
-        <v>783596501</v>
+        <v>775079426</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="H114" s="12" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="I114" s="12" t="s">
         <v>17</v>
       </c>
       <c r="J114" s="12" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="K114" s="12" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="L114" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M114" s="13">
-        <v>9250</v>
+        <v>12000</v>
       </c>
       <c r="N114" s="13">
-        <v>18500</v>
+        <v>12000</v>
       </c>
       <c r="O114" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -7224,27 +7224,27 @@
         <v>février</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A115" s="11">
         <v>46079</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="E115" s="12" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="F115" s="12">
-        <v>761760410</v>
+        <v>771166914</v>
       </c>
       <c r="G115" s="12" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H115" s="12" t="s">
         <v>13</v>
@@ -7253,857 +7253,25 @@
         <v>17</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="K115" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L115" s="12">
         <v>1</v>
       </c>
       <c r="M115" s="13">
-        <v>9250</v>
+        <v>26000</v>
       </c>
       <c r="N115" s="13">
-        <v>9250</v>
+        <v>26000</v>
       </c>
       <c r="O115" s="14" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
       <c r="P115" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A116" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E116" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F116" s="12">
-        <v>761760410</v>
-      </c>
-      <c r="G116" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H116" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J116" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="K116" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="L116" s="12">
-        <v>1</v>
-      </c>
-      <c r="M116" s="13">
-        <v>12000</v>
-      </c>
-      <c r="N116" s="13">
-        <v>12000</v>
-      </c>
-      <c r="O116" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P116" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A117" s="11">
-        <v>46080</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E117" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F117" s="12">
-        <v>776175166</v>
-      </c>
-      <c r="G117" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H117" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I117" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J117" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="K117" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L117" s="12">
-        <v>100</v>
-      </c>
-      <c r="M117" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N117" s="13">
-        <v>2600000</v>
-      </c>
-      <c r="O117" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P117" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A118" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B118" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D118" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E118" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F118" s="12">
-        <v>774446240</v>
-      </c>
-      <c r="G118" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H118" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I118" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J118" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="K118" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L118" s="12">
-        <v>25</v>
-      </c>
-      <c r="M118" s="13">
-        <v>9250</v>
-      </c>
-      <c r="N118" s="13">
-        <v>231250</v>
-      </c>
-      <c r="O118" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P118" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A119" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="F119" s="12">
-        <v>774216339</v>
-      </c>
-      <c r="G119" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H119" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I119" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J119" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K119" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L119" s="12">
-        <v>25</v>
-      </c>
-      <c r="M119" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N119" s="13">
-        <v>650000</v>
-      </c>
-      <c r="O119" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P119" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A120" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E120" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="F120" s="12">
-        <v>773817561</v>
-      </c>
-      <c r="G120" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I120" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J120" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="K120" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="L120" s="12">
-        <v>31</v>
-      </c>
-      <c r="M120" s="13">
-        <v>6000</v>
-      </c>
-      <c r="N120" s="13">
-        <v>186000</v>
-      </c>
-      <c r="O120" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P120" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A121" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B121" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E121" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="F121" s="12">
-        <v>773817561</v>
-      </c>
-      <c r="G121" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I121" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J121" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="K121" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L121" s="12">
-        <v>3</v>
-      </c>
-      <c r="M121" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N121" s="13">
-        <v>78000</v>
-      </c>
-      <c r="O121" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P121" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A122" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B122" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="E122" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="F122" s="12">
-        <v>775079426</v>
-      </c>
-      <c r="G122" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H122" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="I122" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J122" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="K122" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="L122" s="12">
-        <v>1</v>
-      </c>
-      <c r="M122" s="13">
-        <v>12000</v>
-      </c>
-      <c r="N122" s="13">
-        <v>12000</v>
-      </c>
-      <c r="O122" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P122" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A123" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B123" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="F123" s="12">
-        <v>773777037</v>
-      </c>
-      <c r="G123" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H123" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I123" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J123" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K123" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L123" s="12">
-        <v>25</v>
-      </c>
-      <c r="M123" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N123" s="13">
-        <v>650000</v>
-      </c>
-      <c r="O123" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P123" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A124" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B124" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C124" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D124" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E124" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F124" s="12">
-        <v>772289185</v>
-      </c>
-      <c r="G124" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H124" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I124" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J124" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K124" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L124" s="12">
-        <v>25</v>
-      </c>
-      <c r="M124" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N124" s="13">
-        <v>650000</v>
-      </c>
-      <c r="O124" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P124" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A125" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B125" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C125" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E125" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F125" s="12">
-        <v>772289185</v>
-      </c>
-      <c r="G125" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H125" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I125" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J125" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K125" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="L125" s="12">
-        <v>1</v>
-      </c>
-      <c r="M125" s="13">
-        <v>17500</v>
-      </c>
-      <c r="N125" s="13">
-        <v>17500</v>
-      </c>
-      <c r="O125" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P125" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A126" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B126" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D126" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E126" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F126" s="12">
-        <v>772289185</v>
-      </c>
-      <c r="G126" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H126" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I126" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J126" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K126" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="L126" s="12">
-        <v>3</v>
-      </c>
-      <c r="M126" s="13">
-        <v>9250</v>
-      </c>
-      <c r="N126" s="13">
-        <v>27750</v>
-      </c>
-      <c r="O126" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P126" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A127" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B127" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E127" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F127" s="12">
-        <v>772289185</v>
-      </c>
-      <c r="G127" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H127" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I127" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J127" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K127" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="L127" s="12">
-        <v>1</v>
-      </c>
-      <c r="M127" s="13">
-        <v>18000</v>
-      </c>
-      <c r="N127" s="13">
-        <v>18000</v>
-      </c>
-      <c r="O127" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P127" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A128" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C128" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E128" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="F128" s="12">
-        <v>771355863</v>
-      </c>
-      <c r="G128" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H128" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I128" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J128" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K128" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L128" s="12">
-        <v>25</v>
-      </c>
-      <c r="M128" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N128" s="13">
-        <v>650000</v>
-      </c>
-      <c r="O128" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P128" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A129" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E129" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="F129" s="12">
-        <v>774061052</v>
-      </c>
-      <c r="G129" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I129" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J129" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K129" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L129" s="12">
-        <v>50</v>
-      </c>
-      <c r="M129" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N129" s="13">
-        <v>1300000</v>
-      </c>
-      <c r="O129" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P129" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A130" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B130" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C130" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E130" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="F130" s="12">
-        <v>771166914</v>
-      </c>
-      <c r="G130" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H130" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I130" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J130" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="K130" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L130" s="12">
-        <v>1</v>
-      </c>
-      <c r="M130" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N130" s="13">
-        <v>26000</v>
-      </c>
-      <c r="O130" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P130" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A131" s="11">
-        <v>46079</v>
-      </c>
-      <c r="B131" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C131" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E131" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F131" s="12">
-        <v>774245132</v>
-      </c>
-      <c r="G131" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H131" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I131" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J131" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K131" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L131" s="12">
-        <v>25</v>
-      </c>
-      <c r="M131" s="13">
-        <v>26000</v>
-      </c>
-      <c r="N131" s="13">
-        <v>650000</v>
-      </c>
-      <c r="O131" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
-      </c>
-      <c r="P131" s="15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DDFA74-6429-4533-AA9C-38120FC067E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E5B0F0-AB3B-4131-A0C0-092A21B3668F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="185">
   <si>
     <t>Date</t>
   </si>
@@ -550,6 +550,45 @@
   </si>
   <si>
     <t>AITA SARR</t>
+  </si>
+  <si>
+    <t>Boubacar BA</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA DIALLO</t>
+  </si>
+  <si>
+    <t>ABLAYE DIALLO</t>
+  </si>
+  <si>
+    <t>Dalifort</t>
+  </si>
+  <si>
+    <t>Sow</t>
+  </si>
+  <si>
+    <t>Grand Dakar</t>
+  </si>
+  <si>
+    <t>Wane</t>
+  </si>
+  <si>
+    <t>HLM</t>
+  </si>
+  <si>
+    <t>Baye sy</t>
+  </si>
+  <si>
+    <t>Moustapha Mbaye</t>
+  </si>
+  <si>
+    <t>Bassirou NDAO</t>
+  </si>
+  <si>
+    <t>Demain stp</t>
+  </si>
+  <si>
+    <t>Moussa</t>
   </si>
 </sst>
 </file>
@@ -905,16 +944,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -964,8 +1003,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P115" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17">
-  <autoFilter ref="A1:P115" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P136" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P136" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1278,7 +1317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P115"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -4989,2291 +5028,3383 @@
       </c>
     </row>
     <row r="72" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A72" s="11">
+      <c r="A72" s="8">
         <v>46076</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="9">
         <v>776428218</v>
       </c>
-      <c r="G72" s="12" t="s">
+      <c r="G72" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="12" t="s">
+      <c r="H72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K72" s="12" t="s">
+      <c r="K72" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L72" s="12">
+      <c r="L72" s="9">
         <v>20</v>
       </c>
-      <c r="M72" s="13">
+      <c r="M72" s="10">
         <v>9500</v>
       </c>
-      <c r="N72" s="13">
+      <c r="N72" s="10">
         <v>190000</v>
       </c>
-      <c r="O72" s="14" t="str">
+      <c r="O72" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P72" s="15" t="str">
+      <c r="P72" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A73" s="11">
+      <c r="A73" s="8">
         <v>46076</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="9">
         <v>774277399</v>
       </c>
-      <c r="G73" s="12" t="s">
+      <c r="G73" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H73" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="12" t="s">
+      <c r="H73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K73" s="12" t="s">
+      <c r="K73" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L73" s="12">
+      <c r="L73" s="9">
         <v>20</v>
       </c>
-      <c r="M73" s="13">
+      <c r="M73" s="10">
         <v>9500</v>
       </c>
-      <c r="N73" s="13">
+      <c r="N73" s="10">
         <v>190000</v>
       </c>
-      <c r="O73" s="14" t="str">
+      <c r="O73" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P73" s="15" t="str">
+      <c r="P73" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A74" s="11">
+      <c r="A74" s="8">
         <v>46076</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E74" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="9">
         <v>778579191</v>
       </c>
-      <c r="G74" s="12" t="s">
+      <c r="G74" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K74" s="12" t="s">
+      <c r="H74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L74" s="12">
+      <c r="L74" s="9">
         <v>30</v>
       </c>
-      <c r="M74" s="13">
+      <c r="M74" s="10">
         <v>9750</v>
       </c>
-      <c r="N74" s="13">
+      <c r="N74" s="10">
         <v>292500</v>
       </c>
-      <c r="O74" s="14" t="str">
+      <c r="O74" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P74" s="15" t="str">
+      <c r="P74" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A75" s="11">
+      <c r="A75" s="8">
         <v>46076</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="E75" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="9">
         <v>774414059</v>
       </c>
-      <c r="G75" s="12" t="s">
+      <c r="G75" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H75" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="12" t="s">
+      <c r="H75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K75" s="12" t="s">
+      <c r="K75" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L75" s="12">
+      <c r="L75" s="9">
         <v>25</v>
       </c>
-      <c r="M75" s="13">
+      <c r="M75" s="10">
         <v>9250</v>
       </c>
-      <c r="N75" s="13">
+      <c r="N75" s="10">
         <v>231250</v>
       </c>
-      <c r="O75" s="14" t="str">
+      <c r="O75" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P75" s="15" t="str">
+      <c r="P75" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A76" s="11">
+      <c r="A76" s="8">
         <v>46076</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F76" s="12">
+      <c r="F76" s="9">
         <v>779486095</v>
       </c>
-      <c r="G76" s="12" t="s">
+      <c r="G76" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="12" t="s">
+      <c r="H76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K76" s="12" t="s">
+      <c r="K76" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L76" s="12">
+      <c r="L76" s="9">
         <v>25</v>
       </c>
-      <c r="M76" s="13">
+      <c r="M76" s="10">
         <v>18000</v>
       </c>
-      <c r="N76" s="13">
+      <c r="N76" s="10">
         <v>450000</v>
       </c>
-      <c r="O76" s="14" t="str">
+      <c r="O76" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P76" s="15" t="str">
+      <c r="P76" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A77" s="11">
+      <c r="A77" s="8">
         <v>46076</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="9">
         <v>779676016</v>
       </c>
-      <c r="G77" s="12" t="s">
+      <c r="G77" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H77" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="12" t="s">
+      <c r="H77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K77" s="12" t="s">
+      <c r="K77" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L77" s="12">
+      <c r="L77" s="9">
         <v>50</v>
       </c>
-      <c r="M77" s="13">
+      <c r="M77" s="10">
         <v>11000</v>
       </c>
-      <c r="N77" s="13">
+      <c r="N77" s="10">
         <v>550000</v>
       </c>
-      <c r="O77" s="14" t="str">
+      <c r="O77" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P77" s="15" t="str">
+      <c r="P77" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A78" s="11">
+      <c r="A78" s="8">
         <v>46076</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="9">
         <v>786323232</v>
       </c>
-      <c r="G78" s="12" t="s">
+      <c r="G78" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="12" t="s">
+      <c r="H78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K78" s="12" t="s">
+      <c r="K78" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L78" s="12">
+      <c r="L78" s="9">
         <v>25</v>
       </c>
-      <c r="M78" s="13">
+      <c r="M78" s="10">
         <v>9250</v>
       </c>
-      <c r="N78" s="13">
+      <c r="N78" s="10">
         <v>231250</v>
       </c>
-      <c r="O78" s="14" t="str">
+      <c r="O78" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P78" s="15" t="str">
+      <c r="P78" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A79" s="11">
+      <c r="A79" s="8">
         <v>46076</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F79" s="12">
+      <c r="F79" s="9">
         <v>768059355</v>
       </c>
-      <c r="G79" s="12" t="s">
+      <c r="G79" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H79" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="12" t="s">
+      <c r="H79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K79" s="12" t="s">
+      <c r="K79" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="12">
+      <c r="L79" s="9">
         <v>60</v>
       </c>
-      <c r="M79" s="13">
+      <c r="M79" s="10">
         <v>9500</v>
       </c>
-      <c r="N79" s="13">
+      <c r="N79" s="10">
         <v>570000</v>
       </c>
-      <c r="O79" s="14" t="str">
+      <c r="O79" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P79" s="15" t="str">
+      <c r="P79" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A80" s="11">
+      <c r="A80" s="8">
         <v>46076</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F80" s="12">
+      <c r="F80" s="9">
         <v>773817561</v>
       </c>
-      <c r="G80" s="12" t="s">
+      <c r="G80" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I80" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="12" t="s">
+      <c r="H80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K80" s="12" t="s">
+      <c r="K80" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L80" s="12">
+      <c r="L80" s="9">
         <v>1</v>
       </c>
-      <c r="M80" s="13">
+      <c r="M80" s="10">
         <v>33500</v>
       </c>
-      <c r="N80" s="13">
+      <c r="N80" s="10">
         <v>33500</v>
       </c>
-      <c r="O80" s="14" t="str">
+      <c r="O80" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P80" s="15" t="str">
+      <c r="P80" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A81" s="11">
+      <c r="A81" s="8">
         <v>46076</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F81" s="12">
+      <c r="F81" s="9">
         <v>773817561</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="G81" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H81" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I81" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="12" t="s">
+      <c r="H81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K81" s="12" t="s">
+      <c r="K81" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L81" s="12">
+      <c r="L81" s="9">
         <v>7</v>
       </c>
-      <c r="M81" s="13">
+      <c r="M81" s="10">
         <v>12000</v>
       </c>
-      <c r="N81" s="13">
+      <c r="N81" s="10">
         <v>84000</v>
       </c>
-      <c r="O81" s="14" t="str">
+      <c r="O81" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P81" s="15" t="str">
+      <c r="P81" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A82" s="11">
+      <c r="A82" s="8">
         <v>46076</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E82" s="12" t="s">
+      <c r="E82" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F82" s="9">
         <v>777096402</v>
       </c>
-      <c r="G82" s="12" t="s">
+      <c r="G82" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="12" t="s">
+      <c r="H82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K82" s="12" t="s">
+      <c r="K82" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L82" s="12">
+      <c r="L82" s="9">
         <v>10</v>
       </c>
-      <c r="M82" s="13">
+      <c r="M82" s="10">
         <v>9750</v>
       </c>
-      <c r="N82" s="13">
+      <c r="N82" s="10">
         <v>97500</v>
       </c>
-      <c r="O82" s="14" t="str">
+      <c r="O82" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P82" s="15" t="str">
+      <c r="P82" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A83" s="11">
+      <c r="A83" s="8">
         <v>46076</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="E83" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="9">
         <v>777096402</v>
       </c>
-      <c r="G83" s="12" t="s">
+      <c r="G83" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H83" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I83" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="12" t="s">
+      <c r="H83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K83" s="12" t="s">
+      <c r="K83" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L83" s="12">
+      <c r="L83" s="9">
         <v>10</v>
       </c>
-      <c r="M83" s="13">
+      <c r="M83" s="10">
         <v>9750</v>
       </c>
-      <c r="N83" s="13">
+      <c r="N83" s="10">
         <v>97500</v>
       </c>
-      <c r="O83" s="14" t="str">
+      <c r="O83" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P83" s="15" t="str">
+      <c r="P83" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A84" s="11">
+      <c r="A84" s="8">
         <v>46076</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="9">
         <v>777262311</v>
       </c>
-      <c r="G84" s="12" t="s">
+      <c r="G84" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I84" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" s="12" t="s">
+      <c r="H84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K84" s="12" t="s">
+      <c r="K84" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L84" s="12">
+      <c r="L84" s="9">
         <v>5</v>
       </c>
-      <c r="M84" s="13">
+      <c r="M84" s="10">
         <v>9750</v>
       </c>
-      <c r="N84" s="13">
+      <c r="N84" s="10">
         <v>48750</v>
       </c>
-      <c r="O84" s="14" t="str">
+      <c r="O84" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P84" s="15" t="str">
+      <c r="P84" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A85" s="11">
+      <c r="A85" s="8">
         <v>46076</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="9">
         <v>777262311</v>
       </c>
-      <c r="G85" s="12" t="s">
+      <c r="G85" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H85" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I85" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="12" t="s">
+      <c r="H85" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K85" s="12" t="s">
+      <c r="K85" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L85" s="12">
+      <c r="L85" s="9">
         <v>5</v>
       </c>
-      <c r="M85" s="13">
+      <c r="M85" s="10">
         <v>12000</v>
       </c>
-      <c r="N85" s="13">
+      <c r="N85" s="10">
         <v>60000</v>
       </c>
-      <c r="O85" s="14" t="str">
+      <c r="O85" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P85" s="15" t="str">
+      <c r="P85" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A86" s="11">
+      <c r="A86" s="8">
         <v>46078</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F86" s="12">
+      <c r="F86" s="9">
         <v>775039973</v>
       </c>
-      <c r="G86" s="12" t="s">
+      <c r="G86" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="12" t="s">
+      <c r="H86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="K86" s="12" t="s">
+      <c r="K86" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L86" s="12">
+      <c r="L86" s="9">
         <v>25</v>
       </c>
-      <c r="M86" s="13">
+      <c r="M86" s="10">
         <v>26000</v>
       </c>
-      <c r="N86" s="13">
+      <c r="N86" s="10">
         <v>650000</v>
       </c>
-      <c r="O86" s="14" t="str">
+      <c r="O86" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P86" s="15" t="str">
+      <c r="P86" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A87" s="11">
+      <c r="A87" s="8">
         <v>46078</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F87" s="12">
+      <c r="F87" s="9">
         <v>778356666</v>
       </c>
-      <c r="G87" s="12" t="s">
+      <c r="G87" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H87" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I87" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J87" s="12" t="s">
+      <c r="H87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K87" s="12" t="s">
+      <c r="K87" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L87" s="12">
+      <c r="L87" s="9">
         <v>25</v>
       </c>
-      <c r="M87" s="13">
+      <c r="M87" s="10">
         <v>26000</v>
       </c>
-      <c r="N87" s="13">
+      <c r="N87" s="10">
         <v>650000</v>
       </c>
-      <c r="O87" s="14" t="str">
+      <c r="O87" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P87" s="15" t="str">
+      <c r="P87" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A88" s="11">
+      <c r="A88" s="8">
         <v>46078</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E88" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F88" s="12">
+      <c r="F88" s="9">
         <v>777972938</v>
       </c>
-      <c r="G88" s="12" t="s">
+      <c r="G88" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H88" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I88" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J88" s="12" t="s">
+      <c r="H88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K88" s="12" t="s">
+      <c r="K88" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L88" s="12">
+      <c r="L88" s="9">
         <v>3</v>
       </c>
-      <c r="M88" s="13">
+      <c r="M88" s="10">
         <v>12000</v>
       </c>
-      <c r="N88" s="13">
+      <c r="N88" s="10">
         <v>36000</v>
       </c>
-      <c r="O88" s="14" t="str">
+      <c r="O88" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P88" s="15" t="str">
+      <c r="P88" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A89" s="11">
+      <c r="A89" s="8">
         <v>46078</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E89" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F89" s="12">
+      <c r="F89" s="9">
         <v>777972938</v>
       </c>
-      <c r="G89" s="12" t="s">
+      <c r="G89" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H89" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I89" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" s="12" t="s">
+      <c r="H89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K89" s="12" t="s">
+      <c r="K89" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L89" s="12">
+      <c r="L89" s="9">
         <v>2</v>
       </c>
-      <c r="M89" s="13">
+      <c r="M89" s="10">
         <v>33500</v>
       </c>
-      <c r="N89" s="13">
+      <c r="N89" s="10">
         <v>67000</v>
       </c>
-      <c r="O89" s="14" t="str">
+      <c r="O89" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P89" s="15" t="str">
+      <c r="P89" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A90" s="11">
+      <c r="A90" s="8">
         <v>46078</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="E90" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F90" s="12">
+      <c r="F90" s="9">
         <v>777972938</v>
       </c>
-      <c r="G90" s="12" t="s">
+      <c r="G90" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I90" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J90" s="12" t="s">
+      <c r="H90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K90" s="12" t="s">
+      <c r="K90" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="L90" s="12">
+      <c r="L90" s="9">
         <v>2</v>
       </c>
-      <c r="M90" s="13">
+      <c r="M90" s="10">
         <v>33500</v>
       </c>
-      <c r="N90" s="13">
+      <c r="N90" s="10">
         <v>67000</v>
       </c>
-      <c r="O90" s="14" t="str">
+      <c r="O90" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P90" s="15" t="str">
+      <c r="P90" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A91" s="11">
+      <c r="A91" s="8">
         <v>46078</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="E91" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F91" s="12">
+      <c r="F91" s="9">
         <v>777972938</v>
       </c>
-      <c r="G91" s="12" t="s">
+      <c r="G91" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H91" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I91" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" s="12" t="s">
+      <c r="H91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K91" s="12" t="s">
+      <c r="K91" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L91" s="12">
+      <c r="L91" s="9">
         <v>1</v>
       </c>
-      <c r="M91" s="13">
+      <c r="M91" s="10">
         <v>17500</v>
       </c>
-      <c r="N91" s="13">
+      <c r="N91" s="10">
         <v>17500</v>
       </c>
-      <c r="O91" s="14" t="str">
+      <c r="O91" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P91" s="15" t="str">
+      <c r="P91" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A92" s="11">
+      <c r="A92" s="8">
         <v>46078</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="E92" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F92" s="12">
+      <c r="F92" s="9">
         <v>777972938</v>
       </c>
-      <c r="G92" s="12" t="s">
+      <c r="G92" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H92" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J92" s="12" t="s">
+      <c r="H92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K92" s="12" t="s">
+      <c r="K92" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L92" s="12">
+      <c r="L92" s="9">
         <v>2</v>
       </c>
-      <c r="M92" s="13">
+      <c r="M92" s="10">
         <v>26000</v>
       </c>
-      <c r="N92" s="13">
+      <c r="N92" s="10">
         <v>52000</v>
       </c>
-      <c r="O92" s="14" t="str">
+      <c r="O92" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P92" s="15" t="str">
+      <c r="P92" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A93" s="11">
+      <c r="A93" s="8">
         <v>46078</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="E93" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F93" s="12">
+      <c r="F93" s="9">
         <v>775894235</v>
       </c>
-      <c r="G93" s="12" t="s">
+      <c r="G93" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H93" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I93" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" s="12" t="s">
+      <c r="H93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="K93" s="12" t="s">
+      <c r="K93" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L93" s="12">
+      <c r="L93" s="9">
         <v>25</v>
       </c>
-      <c r="M93" s="13">
+      <c r="M93" s="10">
         <v>12000</v>
       </c>
-      <c r="N93" s="13">
+      <c r="N93" s="10">
         <v>300000</v>
       </c>
-      <c r="O93" s="14" t="str">
+      <c r="O93" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P93" s="15" t="str">
+      <c r="P93" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A94" s="11">
+      <c r="A94" s="8">
         <v>46078</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C94" s="12" t="s">
+      <c r="C94" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="E94" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F94" s="12">
+      <c r="F94" s="9">
         <v>774379845</v>
       </c>
-      <c r="G94" s="12" t="s">
+      <c r="G94" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H94" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I94" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J94" s="12" t="s">
+      <c r="H94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="K94" s="12" t="s">
+      <c r="K94" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L94" s="12">
+      <c r="L94" s="9">
         <v>25</v>
       </c>
-      <c r="M94" s="13">
+      <c r="M94" s="10">
         <v>26000</v>
       </c>
-      <c r="N94" s="13">
+      <c r="N94" s="10">
         <v>650000</v>
       </c>
-      <c r="O94" s="14" t="str">
+      <c r="O94" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P94" s="15" t="str">
+      <c r="P94" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A95" s="11">
+      <c r="A95" s="8">
         <v>46078</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C95" s="12" t="s">
+      <c r="C95" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E95" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F95" s="12">
+      <c r="F95" s="9">
         <v>778356666</v>
       </c>
-      <c r="G95" s="12" t="s">
+      <c r="G95" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H95" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I95" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" s="12" t="s">
+      <c r="H95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K95" s="12" t="s">
+      <c r="K95" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L95" s="12">
+      <c r="L95" s="9">
         <v>5</v>
       </c>
-      <c r="M95" s="13">
+      <c r="M95" s="10">
         <v>18000</v>
       </c>
-      <c r="N95" s="13">
+      <c r="N95" s="10">
         <v>90000</v>
       </c>
-      <c r="O95" s="14" t="str">
+      <c r="O95" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P95" s="15" t="str">
+      <c r="P95" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A96" s="11">
+      <c r="A96" s="8">
         <v>46078</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E96" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F96" s="12">
+      <c r="F96" s="9">
         <v>778356666</v>
       </c>
-      <c r="G96" s="12" t="s">
+      <c r="G96" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H96" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I96" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J96" s="12" t="s">
+      <c r="H96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K96" s="12" t="s">
+      <c r="K96" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="L96" s="12">
+      <c r="L96" s="9">
         <v>2</v>
       </c>
-      <c r="M96" s="13">
+      <c r="M96" s="10">
         <v>18000</v>
       </c>
-      <c r="N96" s="13">
+      <c r="N96" s="10">
         <v>36000</v>
       </c>
-      <c r="O96" s="14" t="str">
+      <c r="O96" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P96" s="15" t="str">
+      <c r="P96" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A97" s="11">
+      <c r="A97" s="8">
         <v>46079</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="E97" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="F97" s="12">
+      <c r="F97" s="9">
         <v>774061052</v>
       </c>
-      <c r="G97" s="12" t="s">
+      <c r="G97" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H97" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I97" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J97" s="12" t="s">
+      <c r="H97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K97" s="12" t="s">
+      <c r="K97" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L97" s="12">
+      <c r="L97" s="9">
         <v>50</v>
       </c>
-      <c r="M97" s="13">
+      <c r="M97" s="10">
         <v>26000</v>
       </c>
-      <c r="N97" s="13">
+      <c r="N97" s="10">
         <v>1300000</v>
       </c>
-      <c r="O97" s="14" t="str">
+      <c r="O97" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P97" s="15" t="str">
+      <c r="P97" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A98" s="11">
+      <c r="A98" s="8">
         <v>46079</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="E98" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F98" s="9">
         <v>774446240</v>
       </c>
-      <c r="G98" s="12" t="s">
+      <c r="G98" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H98" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I98" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J98" s="12" t="s">
+      <c r="H98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K98" s="12" t="s">
+      <c r="K98" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L98" s="12">
+      <c r="L98" s="9">
         <v>25</v>
       </c>
-      <c r="M98" s="13">
+      <c r="M98" s="10">
         <v>9250</v>
       </c>
-      <c r="N98" s="13">
+      <c r="N98" s="10">
         <v>231250</v>
       </c>
-      <c r="O98" s="14" t="str">
+      <c r="O98" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P98" s="15" t="str">
+      <c r="P98" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A99" s="11">
+      <c r="A99" s="8">
         <v>46079</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="E99" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F99" s="12">
+      <c r="F99" s="9">
         <v>774245132</v>
       </c>
-      <c r="G99" s="12" t="s">
+      <c r="G99" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H99" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I99" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J99" s="12" t="s">
+      <c r="H99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K99" s="12" t="s">
+      <c r="K99" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L99" s="12">
+      <c r="L99" s="9">
         <v>25</v>
       </c>
-      <c r="M99" s="13">
+      <c r="M99" s="10">
         <v>26000</v>
       </c>
-      <c r="N99" s="13">
+      <c r="N99" s="10">
         <v>650000</v>
       </c>
-      <c r="O99" s="14" t="str">
+      <c r="O99" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P99" s="15" t="str">
+      <c r="P99" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A100" s="11">
+      <c r="A100" s="8">
         <v>46079</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="E100" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="9">
         <v>773777037</v>
       </c>
-      <c r="G100" s="12" t="s">
+      <c r="G100" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H100" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I100" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J100" s="12" t="s">
+      <c r="H100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K100" s="12" t="s">
+      <c r="K100" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L100" s="12">
+      <c r="L100" s="9">
         <v>25</v>
       </c>
-      <c r="M100" s="13">
+      <c r="M100" s="10">
         <v>26000</v>
       </c>
-      <c r="N100" s="13">
+      <c r="N100" s="10">
         <v>650000</v>
       </c>
-      <c r="O100" s="14" t="str">
+      <c r="O100" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P100" s="15" t="str">
+      <c r="P100" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A101" s="11">
+      <c r="A101" s="8">
         <v>46079</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E101" s="12" t="s">
+      <c r="E101" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F101" s="12">
+      <c r="F101" s="9">
         <v>774216339</v>
       </c>
-      <c r="G101" s="12" t="s">
+      <c r="G101" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H101" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I101" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" s="12" t="s">
+      <c r="H101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K101" s="12" t="s">
+      <c r="K101" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L101" s="12">
+      <c r="L101" s="9">
         <v>25</v>
       </c>
-      <c r="M101" s="13">
+      <c r="M101" s="10">
         <v>26000</v>
       </c>
-      <c r="N101" s="13">
+      <c r="N101" s="10">
         <v>650000</v>
       </c>
-      <c r="O101" s="14" t="str">
+      <c r="O101" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P101" s="15" t="str">
+      <c r="P101" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A102" s="11">
+      <c r="A102" s="8">
         <v>46079</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E102" s="12" t="s">
+      <c r="E102" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F102" s="12">
+      <c r="F102" s="9">
         <v>772289185</v>
       </c>
-      <c r="G102" s="12" t="s">
+      <c r="G102" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H102" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I102" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" s="12" t="s">
+      <c r="H102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K102" s="12" t="s">
+      <c r="K102" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L102" s="12">
+      <c r="L102" s="9">
         <v>25</v>
       </c>
-      <c r="M102" s="13">
+      <c r="M102" s="10">
         <v>26000</v>
       </c>
-      <c r="N102" s="13">
+      <c r="N102" s="10">
         <v>650000</v>
       </c>
-      <c r="O102" s="14" t="str">
+      <c r="O102" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P102" s="15" t="str">
+      <c r="P102" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A103" s="11">
+      <c r="A103" s="8">
         <v>46079</v>
       </c>
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E103" s="12" t="s">
+      <c r="E103" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F103" s="12">
+      <c r="F103" s="9">
         <v>772289185</v>
       </c>
-      <c r="G103" s="12" t="s">
+      <c r="G103" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H103" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I103" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" s="12" t="s">
+      <c r="H103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K103" s="12" t="s">
+      <c r="K103" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L103" s="12">
+      <c r="L103" s="9">
         <v>1</v>
       </c>
-      <c r="M103" s="13">
+      <c r="M103" s="10">
         <v>17500</v>
       </c>
-      <c r="N103" s="13">
+      <c r="N103" s="10">
         <v>17500</v>
       </c>
-      <c r="O103" s="14" t="str">
+      <c r="O103" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P103" s="15" t="str">
+      <c r="P103" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A104" s="11">
+      <c r="A104" s="8">
         <v>46079</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F104" s="12">
+      <c r="F104" s="9">
         <v>772289185</v>
       </c>
-      <c r="G104" s="12" t="s">
+      <c r="G104" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H104" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I104" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J104" s="12" t="s">
+      <c r="H104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K104" s="12" t="s">
+      <c r="K104" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L104" s="12">
+      <c r="L104" s="9">
         <v>3</v>
       </c>
-      <c r="M104" s="13">
+      <c r="M104" s="10">
         <v>9250</v>
       </c>
-      <c r="N104" s="13">
+      <c r="N104" s="10">
         <v>27750</v>
       </c>
-      <c r="O104" s="14" t="str">
+      <c r="O104" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P104" s="15" t="str">
+      <c r="P104" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A105" s="11">
+      <c r="A105" s="8">
         <v>46079</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C105" s="12" t="s">
+      <c r="C105" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D105" s="12" t="s">
+      <c r="D105" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E105" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F105" s="12">
+      <c r="F105" s="9">
         <v>772289185</v>
       </c>
-      <c r="G105" s="12" t="s">
+      <c r="G105" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H105" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I105" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="12" t="s">
+      <c r="H105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K105" s="12" t="s">
+      <c r="K105" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L105" s="12">
+      <c r="L105" s="9">
         <v>1</v>
       </c>
-      <c r="M105" s="13">
+      <c r="M105" s="10">
         <v>18000</v>
       </c>
-      <c r="N105" s="13">
+      <c r="N105" s="10">
         <v>18000</v>
       </c>
-      <c r="O105" s="14" t="str">
+      <c r="O105" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P105" s="15" t="str">
+      <c r="P105" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A106" s="11">
+      <c r="A106" s="8">
         <v>46079</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D106" s="12" t="s">
+      <c r="D106" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E106" s="12" t="s">
+      <c r="E106" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F106" s="12">
+      <c r="F106" s="9">
         <v>771355863</v>
       </c>
-      <c r="G106" s="12" t="s">
+      <c r="G106" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H106" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I106" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J106" s="12" t="s">
+      <c r="H106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K106" s="12" t="s">
+      <c r="K106" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L106" s="12">
+      <c r="L106" s="9">
         <v>25</v>
       </c>
-      <c r="M106" s="13">
+      <c r="M106" s="10">
         <v>26000</v>
       </c>
-      <c r="N106" s="13">
+      <c r="N106" s="10">
         <v>650000</v>
       </c>
-      <c r="O106" s="14" t="str">
+      <c r="O106" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P106" s="15" t="str">
+      <c r="P106" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A107" s="11">
+      <c r="A107" s="8">
         <v>46079</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E107" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F107" s="12">
+      <c r="F107" s="9">
         <v>783596501</v>
       </c>
-      <c r="G107" s="12" t="s">
+      <c r="G107" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H107" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I107" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J107" s="12" t="s">
+      <c r="H107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K107" s="12" t="s">
+      <c r="K107" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L107" s="12">
+      <c r="L107" s="9">
         <v>1</v>
       </c>
-      <c r="M107" s="13">
+      <c r="M107" s="10">
         <v>26000</v>
       </c>
-      <c r="N107" s="13">
+      <c r="N107" s="10">
         <v>26000</v>
       </c>
-      <c r="O107" s="14" t="str">
+      <c r="O107" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P107" s="15" t="str">
+      <c r="P107" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="108" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A108" s="11">
+      <c r="A108" s="8">
         <v>46079</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D108" s="12" t="s">
+      <c r="D108" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E108" s="12" t="s">
+      <c r="E108" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F108" s="12">
+      <c r="F108" s="9">
         <v>783596501</v>
       </c>
-      <c r="G108" s="12" t="s">
+      <c r="G108" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H108" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I108" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J108" s="12" t="s">
+      <c r="H108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K108" s="12" t="s">
+      <c r="K108" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L108" s="12">
+      <c r="L108" s="9">
         <v>2</v>
       </c>
-      <c r="M108" s="13">
+      <c r="M108" s="10">
         <v>9250</v>
       </c>
-      <c r="N108" s="13">
+      <c r="N108" s="10">
         <v>18500</v>
       </c>
-      <c r="O108" s="14" t="str">
+      <c r="O108" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P108" s="15" t="str">
+      <c r="P108" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A109" s="11">
+      <c r="A109" s="8">
         <v>46079</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D109" s="12" t="s">
+      <c r="D109" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E109" s="12" t="s">
+      <c r="E109" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F109" s="12">
+      <c r="F109" s="9">
         <v>761760410</v>
       </c>
-      <c r="G109" s="12" t="s">
+      <c r="G109" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H109" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I109" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J109" s="12" t="s">
+      <c r="H109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="K109" s="12" t="s">
+      <c r="K109" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L109" s="12">
+      <c r="L109" s="9">
         <v>1</v>
       </c>
-      <c r="M109" s="13">
+      <c r="M109" s="10">
         <v>9250</v>
       </c>
-      <c r="N109" s="13">
+      <c r="N109" s="10">
         <v>9250</v>
       </c>
-      <c r="O109" s="14" t="str">
+      <c r="O109" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P109" s="15" t="str">
+      <c r="P109" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A110" s="11">
+      <c r="A110" s="8">
         <v>46079</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D110" s="12" t="s">
+      <c r="D110" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E110" s="12" t="s">
+      <c r="E110" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F110" s="12">
+      <c r="F110" s="9">
         <v>761760410</v>
       </c>
-      <c r="G110" s="12" t="s">
+      <c r="G110" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H110" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I110" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J110" s="12" t="s">
+      <c r="H110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="K110" s="12" t="s">
+      <c r="K110" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L110" s="12">
+      <c r="L110" s="9">
         <v>1</v>
       </c>
-      <c r="M110" s="13">
+      <c r="M110" s="10">
         <v>12000</v>
       </c>
-      <c r="N110" s="13">
+      <c r="N110" s="10">
         <v>12000</v>
       </c>
-      <c r="O110" s="14" t="str">
+      <c r="O110" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P110" s="15" t="str">
+      <c r="P110" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="111" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A111" s="11">
+      <c r="A111" s="8">
         <v>46080</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C111" s="12" t="s">
+      <c r="C111" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="D111" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E111" s="12" t="s">
+      <c r="E111" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F111" s="9">
         <v>776175166</v>
       </c>
-      <c r="G111" s="12" t="s">
+      <c r="G111" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H111" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I111" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J111" s="12" t="s">
+      <c r="H111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J111" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K111" s="12" t="s">
+      <c r="K111" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L111" s="12">
+      <c r="L111" s="9">
         <v>100</v>
       </c>
-      <c r="M111" s="13">
+      <c r="M111" s="10">
         <v>26000</v>
       </c>
-      <c r="N111" s="13">
+      <c r="N111" s="10">
         <v>2600000</v>
       </c>
-      <c r="O111" s="14" t="str">
+      <c r="O111" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P111" s="15" t="str">
+      <c r="P111" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A112" s="11">
+      <c r="A112" s="8">
         <v>46079</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="D112" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E112" s="12" t="s">
+      <c r="E112" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F112" s="12">
+      <c r="F112" s="9">
         <v>773817561</v>
       </c>
-      <c r="G112" s="12" t="s">
+      <c r="G112" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H112" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I112" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J112" s="12" t="s">
+      <c r="H112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J112" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K112" s="12" t="s">
+      <c r="K112" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L112" s="12">
+      <c r="L112" s="9">
         <v>31</v>
       </c>
-      <c r="M112" s="13">
+      <c r="M112" s="10">
         <v>6000</v>
       </c>
-      <c r="N112" s="13">
+      <c r="N112" s="10">
         <v>186000</v>
       </c>
-      <c r="O112" s="14" t="str">
+      <c r="O112" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P112" s="15" t="str">
+      <c r="P112" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A113" s="11">
+      <c r="A113" s="8">
         <v>46079</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C113" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E113" s="12" t="s">
+      <c r="E113" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F113" s="12">
+      <c r="F113" s="9">
         <v>773817561</v>
       </c>
-      <c r="G113" s="12" t="s">
+      <c r="G113" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H113" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I113" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J113" s="12" t="s">
+      <c r="H113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K113" s="12" t="s">
+      <c r="K113" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L113" s="12">
+      <c r="L113" s="9">
         <v>3</v>
       </c>
-      <c r="M113" s="13">
+      <c r="M113" s="10">
         <v>26000</v>
       </c>
-      <c r="N113" s="13">
+      <c r="N113" s="10">
         <v>78000</v>
       </c>
-      <c r="O113" s="14" t="str">
+      <c r="O113" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P113" s="15" t="str">
+      <c r="P113" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A114" s="11">
+      <c r="A114" s="8">
         <v>46079</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D114" s="12" t="s">
+      <c r="D114" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E114" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F114" s="12">
+      <c r="F114" s="9">
         <v>775079426</v>
       </c>
-      <c r="G114" s="12" t="s">
+      <c r="G114" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H114" s="12" t="s">
+      <c r="H114" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I114" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J114" s="12" t="s">
+      <c r="I114" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="K114" s="12" t="s">
+      <c r="K114" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L114" s="12">
+      <c r="L114" s="9">
         <v>1</v>
       </c>
-      <c r="M114" s="13">
+      <c r="M114" s="10">
         <v>12000</v>
       </c>
-      <c r="N114" s="13">
+      <c r="N114" s="10">
         <v>12000</v>
       </c>
-      <c r="O114" s="14" t="str">
+      <c r="O114" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P114" s="15" t="str">
+      <c r="P114" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>février</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A115" s="11">
+      <c r="A115" s="8">
         <v>46079</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="C115" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D115" s="12" t="s">
+      <c r="D115" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F115" s="12">
+      <c r="F115" s="9">
         <v>771166914</v>
       </c>
-      <c r="G115" s="12" t="s">
+      <c r="G115" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H115" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I115" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J115" s="12" t="s">
+      <c r="H115" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J115" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K115" s="12" t="s">
+      <c r="K115" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L115" s="12">
+      <c r="L115" s="9">
         <v>1</v>
       </c>
-      <c r="M115" s="13">
+      <c r="M115" s="10">
         <v>26000</v>
       </c>
-      <c r="N115" s="13">
+      <c r="N115" s="10">
         <v>26000</v>
       </c>
-      <c r="O115" s="14" t="str">
+      <c r="O115" s="7" t="str">
         <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S09</v>
       </c>
-      <c r="P115" s="15" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>février</v>
+      <c r="P115" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>février</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A116" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F116" s="12">
+        <v>776712564</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L116" s="12">
+        <v>7</v>
+      </c>
+      <c r="M116" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N116" s="13">
+        <v>126000</v>
+      </c>
+      <c r="O116" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P116" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A117" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F117" s="12">
+        <v>776712564</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H117" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K117" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L117" s="12">
+        <v>3</v>
+      </c>
+      <c r="M117" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N117" s="13">
+        <v>54000</v>
+      </c>
+      <c r="O117" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P117" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A118" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F118" s="12">
+        <v>776712564</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K118" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L118" s="12">
+        <v>1</v>
+      </c>
+      <c r="M118" s="13">
+        <v>9750</v>
+      </c>
+      <c r="N118" s="13">
+        <v>9750</v>
+      </c>
+      <c r="O118" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P118" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A119" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F119" s="12">
+        <v>779676016</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K119" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L119" s="12">
+        <v>25</v>
+      </c>
+      <c r="M119" s="13">
+        <v>11000</v>
+      </c>
+      <c r="N119" s="13">
+        <v>275000</v>
+      </c>
+      <c r="O119" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P119" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A120" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F120" s="12">
+        <v>778976507</v>
+      </c>
+      <c r="G120" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K120" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L120" s="12">
+        <v>25</v>
+      </c>
+      <c r="M120" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N120" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O120" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P120" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A121" s="11">
+        <v>46083</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F121" s="12">
+        <v>771010134</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="K121" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L121" s="12">
+        <v>100</v>
+      </c>
+      <c r="M121" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N121" s="13">
+        <v>2600000</v>
+      </c>
+      <c r="O121" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P121" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A122" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F122" s="12">
+        <v>784537895</v>
+      </c>
+      <c r="G122" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K122" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L122" s="12">
+        <v>50</v>
+      </c>
+      <c r="M122" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N122" s="13">
+        <v>450000</v>
+      </c>
+      <c r="O122" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P122" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A123" s="11">
+        <v>46084</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F123" s="12">
+        <v>775586604</v>
+      </c>
+      <c r="G123" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K123" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L123" s="12">
+        <v>50</v>
+      </c>
+      <c r="M123" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N123" s="13">
+        <v>450000</v>
+      </c>
+      <c r="O123" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P123" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A124" s="11">
+        <v>46088</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F124" s="12">
+        <v>776172529</v>
+      </c>
+      <c r="G124" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H124" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K124" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L124" s="12">
+        <v>1</v>
+      </c>
+      <c r="M124" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N124" s="13">
+        <v>9250</v>
+      </c>
+      <c r="O124" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P124" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A125" s="11">
+        <v>46088</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F125" s="12">
+        <v>776172529</v>
+      </c>
+      <c r="G125" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H125" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K125" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="L125" s="12">
+        <v>1</v>
+      </c>
+      <c r="M125" s="13">
+        <v>17500</v>
+      </c>
+      <c r="N125" s="13">
+        <v>17500</v>
+      </c>
+      <c r="O125" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P125" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A126" s="11">
+        <v>46088</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F126" s="12">
+        <v>776172529</v>
+      </c>
+      <c r="G126" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K126" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L126" s="12">
+        <v>11</v>
+      </c>
+      <c r="M126" s="13">
+        <v>29000</v>
+      </c>
+      <c r="N126" s="13">
+        <v>319000</v>
+      </c>
+      <c r="O126" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P126" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A127" s="11">
+        <v>46088</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="F127" s="12">
+        <v>776172529</v>
+      </c>
+      <c r="G127" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H127" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I127" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K127" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L127" s="12">
+        <v>14</v>
+      </c>
+      <c r="M127" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N127" s="13">
+        <v>364000</v>
+      </c>
+      <c r="O127" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P127" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A128" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F128" s="12">
+        <v>775273147</v>
+      </c>
+      <c r="G128" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H128" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K128" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L128" s="12">
+        <v>1</v>
+      </c>
+      <c r="M128" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N128" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O128" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P128" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A129" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F129" s="12">
+        <v>775273147</v>
+      </c>
+      <c r="G129" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H129" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K129" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L129" s="12">
+        <v>25</v>
+      </c>
+      <c r="M129" s="13">
+        <v>6000</v>
+      </c>
+      <c r="N129" s="13">
+        <v>150000</v>
+      </c>
+      <c r="O129" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P129" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A130" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F130" s="12">
+        <v>775411988</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H130" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I130" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K130" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L130" s="12">
+        <v>4</v>
+      </c>
+      <c r="M130" s="13">
+        <v>33500</v>
+      </c>
+      <c r="N130" s="13">
+        <v>134000</v>
+      </c>
+      <c r="O130" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P130" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A131" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F131" s="12">
+        <v>775079426</v>
+      </c>
+      <c r="G131" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H131" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K131" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L131" s="12">
+        <v>1</v>
+      </c>
+      <c r="M131" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N131" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O131" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P131" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A132" s="11">
+        <v>46087</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="F132" s="12">
+        <v>775014335</v>
+      </c>
+      <c r="G132" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H132" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I132" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K132" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L132" s="12">
+        <v>1</v>
+      </c>
+      <c r="M132" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N132" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O132" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P132" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A133" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="F133" s="12">
+        <v>772899294</v>
+      </c>
+      <c r="G133" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H133" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I133" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J133" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K133" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L133" s="12">
+        <v>25</v>
+      </c>
+      <c r="M133" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N133" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O133" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P133" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A134" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F134" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G134" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I134" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="K134" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L134" s="12">
+        <v>24</v>
+      </c>
+      <c r="M134" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N134" s="13">
+        <v>624000</v>
+      </c>
+      <c r="O134" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P134" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A135" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F135" s="12">
+        <v>771837885</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H135" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K135" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L135" s="12">
+        <v>1</v>
+      </c>
+      <c r="M135" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N135" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O135" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P135" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A136" s="11">
+        <v>46086</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F136" s="12">
+        <v>771837885</v>
+      </c>
+      <c r="G136" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H136" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K136" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L136" s="12">
+        <v>3</v>
+      </c>
+      <c r="M136" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N136" s="13">
+        <v>36000</v>
+      </c>
+      <c r="O136" s="14" t="str">
+        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S010</v>
+      </c>
+      <c r="P136" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E5B0F0-AB3B-4131-A0C0-092A21B3668F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF331F09-4FB0-497D-A76C-554F17F00071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -656,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -686,19 +686,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -712,6 +699,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -721,7 +709,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1020,10 +1007,10 @@
     <tableColumn id="14" xr3:uid="{8DD706C4-BCF7-47C0-9913-F482F7A2F321}" name="Quantites" dataDxfId="4"/>
     <tableColumn id="15" xr3:uid="{D96EE09E-B22B-4D75-AABE-AEBF7CE286A6}" name="Prix_Unitaire" dataDxfId="3"/>
     <tableColumn id="16" xr3:uid="{B1727D51-96B6-4015-83C5-EBCAD96E9834}" name="Prix Total" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="1">
-      <calculatedColumnFormula>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</calculatedColumnFormula>
+    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="0">
+      <calculatedColumnFormula>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="0">
+    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="1">
       <calculatedColumnFormula>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1431,8 +1418,8 @@
         <v>201000</v>
       </c>
       <c r="O2" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P2" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1483,8 +1470,8 @@
         <v>2250000</v>
       </c>
       <c r="O3" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P3" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1535,8 +1522,8 @@
         <v>225000</v>
       </c>
       <c r="O4" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P4" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1587,8 +1574,8 @@
         <v>104000</v>
       </c>
       <c r="O5" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P5" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1639,8 +1626,8 @@
         <v>30000</v>
       </c>
       <c r="O6" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P6" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1691,8 +1678,8 @@
         <v>268000</v>
       </c>
       <c r="O7" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P7" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1743,8 +1730,8 @@
         <v>270000</v>
       </c>
       <c r="O8" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P8" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1795,8 +1782,8 @@
         <v>250000</v>
       </c>
       <c r="O9" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P9" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1847,8 +1834,8 @@
         <v>277500</v>
       </c>
       <c r="O10" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P10" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1899,8 +1886,8 @@
         <v>90000</v>
       </c>
       <c r="O11" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P11" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1951,8 +1938,8 @@
         <v>134000</v>
       </c>
       <c r="O12" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P12" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2003,8 +1990,8 @@
         <v>201000</v>
       </c>
       <c r="O13" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P13" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2055,8 +2042,8 @@
         <v>92500</v>
       </c>
       <c r="O14" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P14" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2107,8 +2094,8 @@
         <v>46250</v>
       </c>
       <c r="O15" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2159,8 +2146,8 @@
         <v>270000</v>
       </c>
       <c r="O16" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2211,8 +2198,8 @@
         <v>450000</v>
       </c>
       <c r="O17" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P17" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2263,8 +2250,8 @@
         <v>450000</v>
       </c>
       <c r="O18" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P18" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2315,8 +2302,8 @@
         <v>936000</v>
       </c>
       <c r="O19" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2367,8 +2354,8 @@
         <v>450000</v>
       </c>
       <c r="O20" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2419,8 +2406,8 @@
         <v>33500</v>
       </c>
       <c r="O21" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P21" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2471,8 +2458,8 @@
         <v>260000</v>
       </c>
       <c r="O22" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P22" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2523,8 +2510,8 @@
         <v>67000</v>
       </c>
       <c r="O23" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P23" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2575,8 +2562,8 @@
         <v>250000</v>
       </c>
       <c r="O24" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P24" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2627,8 +2614,8 @@
         <v>150000</v>
       </c>
       <c r="O25" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P25" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2679,8 +2666,8 @@
         <v>33500</v>
       </c>
       <c r="O26" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P26" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2731,8 +2718,8 @@
         <v>500000</v>
       </c>
       <c r="O27" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P27" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2783,8 +2770,8 @@
         <v>180000</v>
       </c>
       <c r="O28" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P28" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2835,8 +2822,8 @@
         <v>9250</v>
       </c>
       <c r="O29" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P29" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2887,8 +2874,8 @@
         <v>9250</v>
       </c>
       <c r="O30" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P30" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2939,8 +2926,8 @@
         <v>9250</v>
       </c>
       <c r="O31" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P31" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -2991,8 +2978,8 @@
         <v>9250</v>
       </c>
       <c r="O32" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P32" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3043,8 +3030,8 @@
         <v>12000</v>
       </c>
       <c r="O33" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P33" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3095,8 +3082,8 @@
         <v>650000</v>
       </c>
       <c r="O34" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P34" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3147,8 +3134,8 @@
         <v>650000</v>
       </c>
       <c r="O35" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P35" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3199,8 +3186,8 @@
         <v>2600000</v>
       </c>
       <c r="O36" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P36" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3251,8 +3238,8 @@
         <v>1000000</v>
       </c>
       <c r="O37" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P37" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3303,8 +3290,8 @@
         <v>22000</v>
       </c>
       <c r="O38" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P38" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3355,8 +3342,8 @@
         <v>36000</v>
       </c>
       <c r="O39" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P39" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3407,8 +3394,8 @@
         <v>36000</v>
       </c>
       <c r="O40" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P40" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3459,8 +3446,8 @@
         <v>250000</v>
       </c>
       <c r="O41" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P41" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3511,8 +3498,8 @@
         <v>520000</v>
       </c>
       <c r="O42" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P42" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3563,8 +3550,8 @@
         <v>150000</v>
       </c>
       <c r="O43" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P43" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3615,8 +3602,8 @@
         <v>60000</v>
       </c>
       <c r="O44" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P44" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3667,8 +3654,8 @@
         <v>54000</v>
       </c>
       <c r="O45" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P45" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3719,8 +3706,8 @@
         <v>2600000</v>
       </c>
       <c r="O46" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P46" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3771,8 +3758,8 @@
         <v>650000</v>
       </c>
       <c r="O47" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P47" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3823,8 +3810,8 @@
         <v>500000</v>
       </c>
       <c r="O48" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P48" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3875,8 +3862,8 @@
         <v>210000</v>
       </c>
       <c r="O49" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P49" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3927,8 +3914,8 @@
         <v>52000</v>
       </c>
       <c r="O50" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P50" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -3979,8 +3966,8 @@
         <v>2600000</v>
       </c>
       <c r="O51" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P51" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4031,8 +4018,8 @@
         <v>150000</v>
       </c>
       <c r="O52" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P52" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4083,8 +4070,8 @@
         <v>243750</v>
       </c>
       <c r="O53" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P53" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4135,8 +4122,8 @@
         <v>231250</v>
       </c>
       <c r="O54" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P54" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4187,8 +4174,8 @@
         <v>600000</v>
       </c>
       <c r="O55" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P55" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4239,8 +4226,8 @@
         <v>243750</v>
       </c>
       <c r="O56" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P56" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4291,8 +4278,8 @@
         <v>19500</v>
       </c>
       <c r="O57" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P57" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4343,8 +4330,8 @@
         <v>234500</v>
       </c>
       <c r="O58" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P58" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4395,8 +4382,8 @@
         <v>240000</v>
       </c>
       <c r="O59" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P59" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4447,8 +4434,8 @@
         <v>243750</v>
       </c>
       <c r="O60" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P60" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4499,8 +4486,8 @@
         <v>97500</v>
       </c>
       <c r="O61" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P61" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4551,8 +4538,8 @@
         <v>33500</v>
       </c>
       <c r="O62" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P62" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4603,8 +4590,8 @@
         <v>33500</v>
       </c>
       <c r="O63" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P63" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4655,8 +4642,8 @@
         <v>24000</v>
       </c>
       <c r="O64" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P64" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4707,8 +4694,8 @@
         <v>30000</v>
       </c>
       <c r="O65" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P65" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4759,8 +4746,8 @@
         <v>36000</v>
       </c>
       <c r="O66" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P66" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4811,8 +4798,8 @@
         <v>750000</v>
       </c>
       <c r="O67" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P67" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4863,8 +4850,8 @@
         <v>450000</v>
       </c>
       <c r="O68" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P68" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4915,8 +4902,8 @@
         <v>650000</v>
       </c>
       <c r="O69" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P69" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -4967,8 +4954,8 @@
         <v>750000</v>
       </c>
       <c r="O70" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P70" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5019,8 +5006,8 @@
         <v>2950000</v>
       </c>
       <c r="O71" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S08</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S8</v>
       </c>
       <c r="P71" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5071,8 +5058,8 @@
         <v>190000</v>
       </c>
       <c r="O72" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P72" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5123,8 +5110,8 @@
         <v>190000</v>
       </c>
       <c r="O73" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P73" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5175,8 +5162,8 @@
         <v>292500</v>
       </c>
       <c r="O74" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P74" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5227,8 +5214,8 @@
         <v>231250</v>
       </c>
       <c r="O75" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P75" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5279,8 +5266,8 @@
         <v>450000</v>
       </c>
       <c r="O76" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P76" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5331,8 +5318,8 @@
         <v>550000</v>
       </c>
       <c r="O77" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P77" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5383,8 +5370,8 @@
         <v>231250</v>
       </c>
       <c r="O78" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P78" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5435,8 +5422,8 @@
         <v>570000</v>
       </c>
       <c r="O79" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P79" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5487,8 +5474,8 @@
         <v>33500</v>
       </c>
       <c r="O80" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P80" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5539,8 +5526,8 @@
         <v>84000</v>
       </c>
       <c r="O81" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P81" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5591,8 +5578,8 @@
         <v>97500</v>
       </c>
       <c r="O82" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P82" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5643,8 +5630,8 @@
         <v>97500</v>
       </c>
       <c r="O83" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P83" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5695,8 +5682,8 @@
         <v>48750</v>
       </c>
       <c r="O84" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P84" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5747,8 +5734,8 @@
         <v>60000</v>
       </c>
       <c r="O85" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P85" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5799,8 +5786,8 @@
         <v>650000</v>
       </c>
       <c r="O86" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P86" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5851,8 +5838,8 @@
         <v>650000</v>
       </c>
       <c r="O87" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P87" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5903,8 +5890,8 @@
         <v>36000</v>
       </c>
       <c r="O88" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P88" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -5955,8 +5942,8 @@
         <v>67000</v>
       </c>
       <c r="O89" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P89" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6007,8 +5994,8 @@
         <v>67000</v>
       </c>
       <c r="O90" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P90" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6059,8 +6046,8 @@
         <v>17500</v>
       </c>
       <c r="O91" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P91" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6111,8 +6098,8 @@
         <v>52000</v>
       </c>
       <c r="O92" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P92" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6163,8 +6150,8 @@
         <v>300000</v>
       </c>
       <c r="O93" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P93" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6215,8 +6202,8 @@
         <v>650000</v>
       </c>
       <c r="O94" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P94" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6267,8 +6254,8 @@
         <v>90000</v>
       </c>
       <c r="O95" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P95" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6319,8 +6306,8 @@
         <v>36000</v>
       </c>
       <c r="O96" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P96" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6371,8 +6358,8 @@
         <v>1300000</v>
       </c>
       <c r="O97" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P97" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6423,8 +6410,8 @@
         <v>231250</v>
       </c>
       <c r="O98" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P98" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6475,8 +6462,8 @@
         <v>650000</v>
       </c>
       <c r="O99" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P99" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6527,8 +6514,8 @@
         <v>650000</v>
       </c>
       <c r="O100" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P100" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6579,8 +6566,8 @@
         <v>650000</v>
       </c>
       <c r="O101" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P101" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6631,8 +6618,8 @@
         <v>650000</v>
       </c>
       <c r="O102" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P102" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6683,8 +6670,8 @@
         <v>17500</v>
       </c>
       <c r="O103" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P103" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6735,8 +6722,8 @@
         <v>27750</v>
       </c>
       <c r="O104" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P104" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6787,8 +6774,8 @@
         <v>18000</v>
       </c>
       <c r="O105" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P105" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6839,8 +6826,8 @@
         <v>650000</v>
       </c>
       <c r="O106" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P106" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6891,8 +6878,8 @@
         <v>26000</v>
       </c>
       <c r="O107" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P107" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6943,8 +6930,8 @@
         <v>18500</v>
       </c>
       <c r="O108" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P108" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -6995,8 +6982,8 @@
         <v>9250</v>
       </c>
       <c r="O109" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P109" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7047,8 +7034,8 @@
         <v>12000</v>
       </c>
       <c r="O110" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P110" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7099,8 +7086,8 @@
         <v>2600000</v>
       </c>
       <c r="O111" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P111" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7151,8 +7138,8 @@
         <v>186000</v>
       </c>
       <c r="O112" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P112" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7203,8 +7190,8 @@
         <v>78000</v>
       </c>
       <c r="O113" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P113" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7255,8 +7242,8 @@
         <v>12000</v>
       </c>
       <c r="O114" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P114" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7307,8 +7294,8 @@
         <v>26000</v>
       </c>
       <c r="O115" s="7" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S09</v>
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S9</v>
       </c>
       <c r="P115" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -7316,1093 +7303,1093 @@
       </c>
     </row>
     <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A116" s="11">
+      <c r="A116" s="8">
         <v>46083</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D116" s="12" t="s">
+      <c r="D116" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E116" s="12" t="s">
+      <c r="E116" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F116" s="12">
+      <c r="F116" s="9">
         <v>776712564</v>
       </c>
-      <c r="G116" s="12" t="s">
+      <c r="G116" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H116" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J116" s="12" t="s">
+      <c r="H116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K116" s="12" t="s">
+      <c r="K116" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="L116" s="12">
+      <c r="L116" s="9">
         <v>7</v>
       </c>
-      <c r="M116" s="13">
+      <c r="M116" s="10">
         <v>18000</v>
       </c>
-      <c r="N116" s="13">
+      <c r="N116" s="10">
         <v>126000</v>
       </c>
-      <c r="O116" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P116" s="15" t="str">
+      <c r="O116" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P116" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A117" s="11">
+      <c r="A117" s="8">
         <v>46083</v>
       </c>
-      <c r="B117" s="12" t="s">
+      <c r="B117" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="D117" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E117" s="12" t="s">
+      <c r="E117" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F117" s="12">
+      <c r="F117" s="9">
         <v>776712564</v>
       </c>
-      <c r="G117" s="12" t="s">
+      <c r="G117" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H117" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I117" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J117" s="12" t="s">
+      <c r="H117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K117" s="12" t="s">
+      <c r="K117" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L117" s="12">
+      <c r="L117" s="9">
         <v>3</v>
       </c>
-      <c r="M117" s="13">
+      <c r="M117" s="10">
         <v>18000</v>
       </c>
-      <c r="N117" s="13">
+      <c r="N117" s="10">
         <v>54000</v>
       </c>
-      <c r="O117" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P117" s="15" t="str">
+      <c r="O117" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P117" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A118" s="11">
+      <c r="A118" s="8">
         <v>46083</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B118" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D118" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E118" s="12" t="s">
+      <c r="E118" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F118" s="12">
+      <c r="F118" s="9">
         <v>776712564</v>
       </c>
-      <c r="G118" s="12" t="s">
+      <c r="G118" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H118" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I118" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J118" s="12" t="s">
+      <c r="H118" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K118" s="12" t="s">
+      <c r="K118" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L118" s="12">
+      <c r="L118" s="9">
         <v>1</v>
       </c>
-      <c r="M118" s="13">
+      <c r="M118" s="10">
         <v>9750</v>
       </c>
-      <c r="N118" s="13">
+      <c r="N118" s="10">
         <v>9750</v>
       </c>
-      <c r="O118" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P118" s="15" t="str">
+      <c r="O118" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P118" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A119" s="11">
+      <c r="A119" s="8">
         <v>46083</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C119" s="12" t="s">
+      <c r="C119" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E119" s="12" t="s">
+      <c r="E119" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F119" s="12">
+      <c r="F119" s="9">
         <v>779676016</v>
       </c>
-      <c r="G119" s="12" t="s">
+      <c r="G119" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H119" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I119" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J119" s="12" t="s">
+      <c r="H119" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K119" s="12" t="s">
+      <c r="K119" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L119" s="12">
+      <c r="L119" s="9">
         <v>25</v>
       </c>
-      <c r="M119" s="13">
+      <c r="M119" s="10">
         <v>11000</v>
       </c>
-      <c r="N119" s="13">
+      <c r="N119" s="10">
         <v>275000</v>
       </c>
-      <c r="O119" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P119" s="15" t="str">
+      <c r="O119" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P119" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A120" s="11">
+      <c r="A120" s="8">
         <v>46083</v>
       </c>
-      <c r="B120" s="12" t="s">
+      <c r="B120" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D120" s="12" t="s">
+      <c r="D120" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E120" s="12" t="s">
+      <c r="E120" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F120" s="12">
+      <c r="F120" s="9">
         <v>778976507</v>
       </c>
-      <c r="G120" s="12" t="s">
+      <c r="G120" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H120" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I120" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J120" s="12" t="s">
+      <c r="H120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K120" s="12" t="s">
+      <c r="K120" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L120" s="12">
+      <c r="L120" s="9">
         <v>25</v>
       </c>
-      <c r="M120" s="13">
+      <c r="M120" s="10">
         <v>26000</v>
       </c>
-      <c r="N120" s="13">
+      <c r="N120" s="10">
         <v>650000</v>
       </c>
-      <c r="O120" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P120" s="15" t="str">
+      <c r="O120" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P120" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A121" s="11">
+      <c r="A121" s="8">
         <v>46083</v>
       </c>
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D121" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E121" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F121" s="12">
+      <c r="F121" s="9">
         <v>771010134</v>
       </c>
-      <c r="G121" s="12" t="s">
+      <c r="G121" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H121" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I121" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J121" s="12" t="s">
+      <c r="H121" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="K121" s="12" t="s">
+      <c r="K121" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L121" s="12">
+      <c r="L121" s="9">
         <v>100</v>
       </c>
-      <c r="M121" s="13">
+      <c r="M121" s="10">
         <v>26000</v>
       </c>
-      <c r="N121" s="13">
+      <c r="N121" s="10">
         <v>2600000</v>
       </c>
-      <c r="O121" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P121" s="15" t="str">
+      <c r="O121" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P121" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A122" s="11">
+      <c r="A122" s="8">
         <v>46084</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D122" s="12" t="s">
+      <c r="D122" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E122" s="12" t="s">
+      <c r="E122" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F122" s="12">
+      <c r="F122" s="9">
         <v>784537895</v>
       </c>
-      <c r="G122" s="12" t="s">
+      <c r="G122" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H122" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I122" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J122" s="12" t="s">
+      <c r="H122" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K122" s="12" t="s">
+      <c r="K122" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L122" s="12">
+      <c r="L122" s="9">
         <v>50</v>
       </c>
-      <c r="M122" s="13">
+      <c r="M122" s="10">
         <v>9000</v>
       </c>
-      <c r="N122" s="13">
+      <c r="N122" s="10">
         <v>450000</v>
       </c>
-      <c r="O122" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P122" s="15" t="str">
+      <c r="O122" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P122" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A123" s="11">
+      <c r="A123" s="8">
         <v>46084</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E123" s="12" t="s">
+      <c r="E123" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F123" s="12">
+      <c r="F123" s="9">
         <v>775586604</v>
       </c>
-      <c r="G123" s="12" t="s">
+      <c r="G123" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H123" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I123" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J123" s="12" t="s">
+      <c r="H123" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K123" s="12" t="s">
+      <c r="K123" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L123" s="12">
+      <c r="L123" s="9">
         <v>50</v>
       </c>
-      <c r="M123" s="13">
+      <c r="M123" s="10">
         <v>9000</v>
       </c>
-      <c r="N123" s="13">
+      <c r="N123" s="10">
         <v>450000</v>
       </c>
-      <c r="O123" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P123" s="15" t="str">
+      <c r="O123" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P123" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A124" s="11">
+      <c r="A124" s="8">
         <v>46088</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D124" s="12" t="s">
+      <c r="D124" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E124" s="12" t="s">
+      <c r="E124" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F124" s="12">
+      <c r="F124" s="9">
         <v>776172529</v>
       </c>
-      <c r="G124" s="12" t="s">
+      <c r="G124" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H124" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I124" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J124" s="12" t="s">
+      <c r="H124" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K124" s="12" t="s">
+      <c r="K124" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L124" s="12">
+      <c r="L124" s="9">
         <v>1</v>
       </c>
-      <c r="M124" s="13">
+      <c r="M124" s="10">
         <v>9250</v>
       </c>
-      <c r="N124" s="13">
+      <c r="N124" s="10">
         <v>9250</v>
       </c>
-      <c r="O124" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P124" s="15" t="str">
+      <c r="O124" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P124" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A125" s="11">
+      <c r="A125" s="8">
         <v>46088</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B125" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C125" s="12" t="s">
+      <c r="C125" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E125" s="12" t="s">
+      <c r="E125" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F125" s="12">
+      <c r="F125" s="9">
         <v>776172529</v>
       </c>
-      <c r="G125" s="12" t="s">
+      <c r="G125" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H125" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I125" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J125" s="12" t="s">
+      <c r="H125" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K125" s="12" t="s">
+      <c r="K125" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L125" s="12">
+      <c r="L125" s="9">
         <v>1</v>
       </c>
-      <c r="M125" s="13">
+      <c r="M125" s="10">
         <v>17500</v>
       </c>
-      <c r="N125" s="13">
+      <c r="N125" s="10">
         <v>17500</v>
       </c>
-      <c r="O125" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P125" s="15" t="str">
+      <c r="O125" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P125" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A126" s="11">
+      <c r="A126" s="8">
         <v>46088</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="C126" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E126" s="12" t="s">
+      <c r="E126" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F126" s="12">
+      <c r="F126" s="9">
         <v>776172529</v>
       </c>
-      <c r="G126" s="12" t="s">
+      <c r="G126" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H126" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I126" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J126" s="12" t="s">
+      <c r="H126" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K126" s="12" t="s">
+      <c r="K126" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L126" s="12">
+      <c r="L126" s="9">
         <v>11</v>
       </c>
-      <c r="M126" s="13">
+      <c r="M126" s="10">
         <v>29000</v>
       </c>
-      <c r="N126" s="13">
+      <c r="N126" s="10">
         <v>319000</v>
       </c>
-      <c r="O126" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P126" s="15" t="str">
+      <c r="O126" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P126" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A127" s="11">
+      <c r="A127" s="8">
         <v>46088</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E127" s="12" t="s">
+      <c r="E127" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F127" s="12">
+      <c r="F127" s="9">
         <v>776172529</v>
       </c>
-      <c r="G127" s="12" t="s">
+      <c r="G127" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H127" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I127" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J127" s="12" t="s">
+      <c r="H127" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K127" s="12" t="s">
+      <c r="K127" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L127" s="12">
+      <c r="L127" s="9">
         <v>14</v>
       </c>
-      <c r="M127" s="13">
+      <c r="M127" s="10">
         <v>26000</v>
       </c>
-      <c r="N127" s="13">
+      <c r="N127" s="10">
         <v>364000</v>
       </c>
-      <c r="O127" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P127" s="15" t="str">
+      <c r="O127" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P127" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A128" s="11">
+      <c r="A128" s="8">
         <v>46087</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E128" s="12" t="s">
+      <c r="E128" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F128" s="12">
+      <c r="F128" s="9">
         <v>775273147</v>
       </c>
-      <c r="G128" s="12" t="s">
+      <c r="G128" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H128" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I128" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J128" s="12" t="s">
+      <c r="H128" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K128" s="12" t="s">
+      <c r="K128" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L128" s="12">
+      <c r="L128" s="9">
         <v>1</v>
       </c>
-      <c r="M128" s="13">
+      <c r="M128" s="10">
         <v>26000</v>
       </c>
-      <c r="N128" s="13">
+      <c r="N128" s="10">
         <v>26000</v>
       </c>
-      <c r="O128" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P128" s="15" t="str">
+      <c r="O128" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P128" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A129" s="11">
+      <c r="A129" s="8">
         <v>46087</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C129" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E129" s="12" t="s">
+      <c r="E129" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F129" s="12">
+      <c r="F129" s="9">
         <v>775273147</v>
       </c>
-      <c r="G129" s="12" t="s">
+      <c r="G129" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I129" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J129" s="12" t="s">
+      <c r="H129" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K129" s="12" t="s">
+      <c r="K129" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L129" s="12">
+      <c r="L129" s="9">
         <v>25</v>
       </c>
-      <c r="M129" s="13">
+      <c r="M129" s="10">
         <v>6000</v>
       </c>
-      <c r="N129" s="13">
+      <c r="N129" s="10">
         <v>150000</v>
       </c>
-      <c r="O129" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P129" s="15" t="str">
+      <c r="O129" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P129" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A130" s="11">
+      <c r="A130" s="8">
         <v>46087</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E130" s="12" t="s">
+      <c r="E130" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F130" s="12">
+      <c r="F130" s="9">
         <v>775411988</v>
       </c>
-      <c r="G130" s="12" t="s">
+      <c r="G130" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H130" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I130" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J130" s="12" t="s">
+      <c r="H130" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K130" s="12" t="s">
+      <c r="K130" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="L130" s="12">
+      <c r="L130" s="9">
         <v>4</v>
       </c>
-      <c r="M130" s="13">
+      <c r="M130" s="10">
         <v>33500</v>
       </c>
-      <c r="N130" s="13">
+      <c r="N130" s="10">
         <v>134000</v>
       </c>
-      <c r="O130" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P130" s="15" t="str">
+      <c r="O130" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P130" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A131" s="11">
+      <c r="A131" s="8">
         <v>46087</v>
       </c>
-      <c r="B131" s="12" t="s">
+      <c r="B131" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="C131" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D131" s="12" t="s">
+      <c r="D131" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E131" s="12" t="s">
+      <c r="E131" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F131" s="12">
+      <c r="F131" s="9">
         <v>775079426</v>
       </c>
-      <c r="G131" s="12" t="s">
+      <c r="G131" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H131" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I131" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J131" s="12" t="s">
+      <c r="H131" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K131" s="12" t="s">
+      <c r="K131" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L131" s="12">
+      <c r="L131" s="9">
         <v>1</v>
       </c>
-      <c r="M131" s="13">
+      <c r="M131" s="10">
         <v>12000</v>
       </c>
-      <c r="N131" s="13">
+      <c r="N131" s="10">
         <v>12000</v>
       </c>
-      <c r="O131" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P131" s="15" t="str">
+      <c r="O131" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P131" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A132" s="11">
+      <c r="A132" s="8">
         <v>46087</v>
       </c>
-      <c r="B132" s="12" t="s">
+      <c r="B132" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D132" s="12" t="s">
+      <c r="D132" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="E132" s="12" t="s">
+      <c r="E132" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F132" s="12">
+      <c r="F132" s="9">
         <v>775014335</v>
       </c>
-      <c r="G132" s="12" t="s">
+      <c r="G132" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H132" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I132" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J132" s="12" t="s">
+      <c r="H132" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K132" s="12" t="s">
+      <c r="K132" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L132" s="12">
+      <c r="L132" s="9">
         <v>1</v>
       </c>
-      <c r="M132" s="13">
+      <c r="M132" s="10">
         <v>12000</v>
       </c>
-      <c r="N132" s="13">
+      <c r="N132" s="10">
         <v>12000</v>
       </c>
-      <c r="O132" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P132" s="15" t="str">
+      <c r="O132" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P132" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A133" s="11">
+      <c r="A133" s="8">
         <v>46086</v>
       </c>
-      <c r="B133" s="12" t="s">
+      <c r="B133" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C133" s="12" t="s">
+      <c r="C133" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D133" s="12" t="s">
+      <c r="D133" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E133" s="12" t="s">
+      <c r="E133" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F133" s="12">
+      <c r="F133" s="9">
         <v>772899294</v>
       </c>
-      <c r="G133" s="12" t="s">
+      <c r="G133" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H133" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I133" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J133" s="12" t="s">
+      <c r="H133" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J133" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K133" s="12" t="s">
+      <c r="K133" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L133" s="12">
+      <c r="L133" s="9">
         <v>25</v>
       </c>
-      <c r="M133" s="13">
+      <c r="M133" s="10">
         <v>26000</v>
       </c>
-      <c r="N133" s="13">
+      <c r="N133" s="10">
         <v>650000</v>
       </c>
-      <c r="O133" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P133" s="15" t="str">
+      <c r="O133" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P133" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A134" s="11">
+      <c r="A134" s="8">
         <v>46086</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E134" s="12" t="s">
+      <c r="E134" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F134" s="12">
+      <c r="F134" s="9">
         <v>775544532</v>
       </c>
-      <c r="G134" s="12" t="s">
+      <c r="G134" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H134" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I134" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J134" s="12" t="s">
+      <c r="H134" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="K134" s="12" t="s">
+      <c r="K134" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L134" s="12">
+      <c r="L134" s="9">
         <v>24</v>
       </c>
-      <c r="M134" s="13">
+      <c r="M134" s="10">
         <v>26000</v>
       </c>
-      <c r="N134" s="13">
+      <c r="N134" s="10">
         <v>624000</v>
       </c>
-      <c r="O134" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P134" s="15" t="str">
+      <c r="O134" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P134" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A135" s="11">
+      <c r="A135" s="8">
         <v>46086</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C135" s="12" t="s">
+      <c r="C135" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E135" s="12" t="s">
+      <c r="E135" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F135" s="12">
+      <c r="F135" s="9">
         <v>771837885</v>
       </c>
-      <c r="G135" s="12" t="s">
+      <c r="G135" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H135" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I135" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J135" s="12" t="s">
+      <c r="H135" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K135" s="12" t="s">
+      <c r="K135" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L135" s="12">
+      <c r="L135" s="9">
         <v>1</v>
       </c>
-      <c r="M135" s="13">
+      <c r="M135" s="10">
         <v>26000</v>
       </c>
-      <c r="N135" s="13">
+      <c r="N135" s="10">
         <v>26000</v>
       </c>
-      <c r="O135" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P135" s="15" t="str">
+      <c r="O135" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P135" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A136" s="11">
+      <c r="A136" s="8">
         <v>46086</v>
       </c>
-      <c r="B136" s="12" t="s">
+      <c r="B136" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D136" s="12" t="s">
+      <c r="D136" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E136" s="12" t="s">
+      <c r="E136" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F136" s="12">
+      <c r="F136" s="9">
         <v>771837885</v>
       </c>
-      <c r="G136" s="12" t="s">
+      <c r="G136" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H136" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I136" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J136" s="12" t="s">
+      <c r="H136" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K136" s="12" t="s">
+      <c r="K136" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L136" s="12">
+      <c r="L136" s="9">
         <v>3</v>
       </c>
-      <c r="M136" s="13">
+      <c r="M136" s="10">
         <v>12000</v>
       </c>
-      <c r="N136" s="13">
+      <c r="N136" s="10">
         <v>36000</v>
       </c>
-      <c r="O136" s="14" t="str">
-        <f>"S0"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S010</v>
-      </c>
-      <c r="P136" s="15" t="str">
+      <c r="O136" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S10</v>
+      </c>
+      <c r="P136" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF331F09-4FB0-497D-A76C-554F17F00071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E75397-3000-4DCE-A8E9-2BC56C7D94CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="215">
   <si>
     <t>Date</t>
   </si>
@@ -589,6 +589,96 @@
   </si>
   <si>
     <t>Moussa</t>
+  </si>
+  <si>
+    <t>Lamine Diallo</t>
+  </si>
+  <si>
+    <t>Guinaw Rail</t>
+  </si>
+  <si>
+    <t>Khadime FALL</t>
+  </si>
+  <si>
+    <t>Mame Serigne</t>
+  </si>
+  <si>
+    <t>Galle GOLLE</t>
+  </si>
+  <si>
+    <t>Café pot Refraish 200g</t>
+  </si>
+  <si>
+    <t>Abdou Diallo</t>
+  </si>
+  <si>
+    <t>Pikine Rue 10</t>
+  </si>
+  <si>
+    <t>Moustapha  Daow</t>
+  </si>
+  <si>
+    <t>Jaxaay</t>
+  </si>
+  <si>
+    <t>Momodou Salif</t>
+  </si>
+  <si>
+    <t>Aladji</t>
+  </si>
+  <si>
+    <t>Makhtar</t>
+  </si>
+  <si>
+    <t>Ndioguou</t>
+  </si>
+  <si>
+    <t>Diamniadio</t>
+  </si>
+  <si>
+    <t>Serigne Touré</t>
+  </si>
+  <si>
+    <t>Seye et Frère</t>
+  </si>
+  <si>
+    <t>Il dit que le produit est cher par rapport aux prix du marché</t>
+  </si>
+  <si>
+    <t>Amadou</t>
+  </si>
+  <si>
+    <t>Khalifa</t>
+  </si>
+  <si>
+    <t>Ousseynou diop</t>
+  </si>
+  <si>
+    <t>Livré le 12-03</t>
+  </si>
+  <si>
+    <t>Diouf Alimentation</t>
+  </si>
+  <si>
+    <t>Massaer</t>
+  </si>
+  <si>
+    <t>Diallo</t>
+  </si>
+  <si>
+    <t>Cheikh Bara</t>
+  </si>
+  <si>
+    <t>Baldé et frère</t>
+  </si>
+  <si>
+    <t>MACTAR</t>
+  </si>
+  <si>
+    <t>El Hadji</t>
+  </si>
+  <si>
+    <t>Alioune</t>
   </si>
 </sst>
 </file>
@@ -656,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -686,6 +776,19 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +802,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -709,6 +811,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -990,8 +1093,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P136" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P136" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P178" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P178" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1007,10 +1110,10 @@
     <tableColumn id="14" xr3:uid="{8DD706C4-BCF7-47C0-9913-F482F7A2F321}" name="Quantites" dataDxfId="4"/>
     <tableColumn id="15" xr3:uid="{D96EE09E-B22B-4D75-AABE-AEBF7CE286A6}" name="Prix_Unitaire" dataDxfId="3"/>
     <tableColumn id="16" xr3:uid="{B1727D51-96B6-4015-83C5-EBCAD96E9834}" name="Prix Total" dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="0">
+    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="1">
       <calculatedColumnFormula>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="1">
+    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="0">
       <calculatedColumnFormula>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1304,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -8394,6 +8497,2190 @@
         <v>mars</v>
       </c>
     </row>
+    <row r="137" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A137" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F137" s="12">
+        <v>779676016</v>
+      </c>
+      <c r="G137" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H137" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K137" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L137" s="12">
+        <v>5</v>
+      </c>
+      <c r="M137" s="13">
+        <v>6000</v>
+      </c>
+      <c r="N137" s="13">
+        <v>30000</v>
+      </c>
+      <c r="O137" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P137" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A138" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F138" s="12">
+        <v>779676016</v>
+      </c>
+      <c r="G138" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K138" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L138" s="12">
+        <v>75</v>
+      </c>
+      <c r="M138" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N138" s="13">
+        <v>693750</v>
+      </c>
+      <c r="O138" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P138" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A139" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F139" s="12">
+        <v>781297575</v>
+      </c>
+      <c r="G139" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H139" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K139" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L139" s="12">
+        <v>25</v>
+      </c>
+      <c r="M139" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N139" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O139" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P139" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A140" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="F140" s="12">
+        <v>771952687</v>
+      </c>
+      <c r="G140" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H140" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I140" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K140" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L140" s="12">
+        <v>50</v>
+      </c>
+      <c r="M140" s="13">
+        <v>29000</v>
+      </c>
+      <c r="N140" s="13">
+        <v>1450000</v>
+      </c>
+      <c r="O140" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P140" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A141" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="F141" s="12">
+        <v>777772248</v>
+      </c>
+      <c r="G141" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H141" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K141" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L141" s="12">
+        <v>20</v>
+      </c>
+      <c r="M141" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N141" s="13">
+        <v>185000</v>
+      </c>
+      <c r="O141" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P141" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A142" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F142" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G142" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H142" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K142" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L142" s="12">
+        <v>25</v>
+      </c>
+      <c r="M142" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N142" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O142" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P142" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A143" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F143" s="12">
+        <v>775586819</v>
+      </c>
+      <c r="G143" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H143" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K143" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L143" s="12">
+        <v>4</v>
+      </c>
+      <c r="M143" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N143" s="13">
+        <v>78000</v>
+      </c>
+      <c r="O143" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P143" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A144" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F144" s="12">
+        <v>775250570</v>
+      </c>
+      <c r="G144" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I144" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K144" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L144" s="12">
+        <v>25</v>
+      </c>
+      <c r="M144" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N144" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O144" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P144" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A145" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F145" s="12">
+        <v>775586819</v>
+      </c>
+      <c r="G145" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H145" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K145" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L145" s="12">
+        <v>27</v>
+      </c>
+      <c r="M145" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N145" s="13">
+        <v>702000</v>
+      </c>
+      <c r="O145" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P145" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A146" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F146" s="12">
+        <v>784537895</v>
+      </c>
+      <c r="G146" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K146" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L146" s="12">
+        <v>25</v>
+      </c>
+      <c r="M146" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N146" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O146" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P146" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A147" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F147" s="12">
+        <v>784537895</v>
+      </c>
+      <c r="G147" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J147" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K147" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L147" s="12">
+        <v>25</v>
+      </c>
+      <c r="M147" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N147" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O147" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P147" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A148" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F148" s="12">
+        <v>776428218</v>
+      </c>
+      <c r="G148" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K148" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L148" s="12">
+        <v>25</v>
+      </c>
+      <c r="M148" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N148" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O148" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P148" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A149" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D149" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F149" s="12">
+        <v>775467226</v>
+      </c>
+      <c r="G149" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J149" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K149" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L149" s="12">
+        <v>1</v>
+      </c>
+      <c r="M149" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N149" s="13">
+        <v>19500</v>
+      </c>
+      <c r="O149" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P149" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A150" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D150" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F150" s="12">
+        <v>775467226</v>
+      </c>
+      <c r="G150" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K150" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L150" s="12">
+        <v>20</v>
+      </c>
+      <c r="M150" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N150" s="13">
+        <v>185000</v>
+      </c>
+      <c r="O150" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P150" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A151" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B151" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F151" s="12">
+        <v>775467226</v>
+      </c>
+      <c r="G151" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J151" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K151" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="L151" s="12">
+        <v>1</v>
+      </c>
+      <c r="M151" s="13">
+        <v>11000</v>
+      </c>
+      <c r="N151" s="13">
+        <v>11000</v>
+      </c>
+      <c r="O151" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P151" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A152" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D152" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F152" s="12">
+        <v>775426848</v>
+      </c>
+      <c r="G152" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H152" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I152" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K152" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L152" s="12">
+        <v>25</v>
+      </c>
+      <c r="M152" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N152" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O152" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P152" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A153" s="11">
+        <v>46092</v>
+      </c>
+      <c r="B153" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F153" s="12">
+        <v>771040904</v>
+      </c>
+      <c r="G153" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I153" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J153" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K153" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L153" s="12">
+        <v>25</v>
+      </c>
+      <c r="M153" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N153" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O153" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P153" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A154" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F154" s="12">
+        <v>772377240</v>
+      </c>
+      <c r="G154" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I154" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K154" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L154" s="12">
+        <v>50</v>
+      </c>
+      <c r="M154" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N154" s="13">
+        <v>975000</v>
+      </c>
+      <c r="O154" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P154" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A155" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="F155" s="12">
+        <v>771078008</v>
+      </c>
+      <c r="G155" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J155" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K155" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L155" s="12">
+        <v>10</v>
+      </c>
+      <c r="M155" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N155" s="13">
+        <v>92500</v>
+      </c>
+      <c r="O155" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P155" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A156" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D156" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F156" s="12">
+        <v>776634479</v>
+      </c>
+      <c r="G156" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H156" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K156" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L156" s="12">
+        <v>21</v>
+      </c>
+      <c r="M156" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N156" s="13">
+        <v>1134000</v>
+      </c>
+      <c r="O156" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P156" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A157" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F157" s="12">
+        <v>776634479</v>
+      </c>
+      <c r="G157" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J157" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K157" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L157" s="12">
+        <v>5</v>
+      </c>
+      <c r="M157" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N157" s="13">
+        <v>97500</v>
+      </c>
+      <c r="O157" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P157" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A158" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F158" s="12">
+        <v>775602589</v>
+      </c>
+      <c r="G158" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H158" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I158" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K158" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L158" s="12">
+        <v>5</v>
+      </c>
+      <c r="M158" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N158" s="13">
+        <v>130000</v>
+      </c>
+      <c r="O158" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P158" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A159" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F159" s="12">
+        <v>788217757</v>
+      </c>
+      <c r="G159" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I159" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J159" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K159" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L159" s="12">
+        <v>25</v>
+      </c>
+      <c r="M159" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N159" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O159" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P159" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A160" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F160" s="12">
+        <v>775485563</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K160" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L160" s="12">
+        <v>5</v>
+      </c>
+      <c r="M160" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N160" s="13">
+        <v>97500</v>
+      </c>
+      <c r="O160" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P160" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A161" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B161" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F161" s="12">
+        <v>779486095</v>
+      </c>
+      <c r="G161" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I161" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K161" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L161" s="12">
+        <v>27</v>
+      </c>
+      <c r="M161" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N161" s="13">
+        <v>486000</v>
+      </c>
+      <c r="O161" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P161" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A162" s="11">
+        <v>46091</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F162" s="12">
+        <v>786323232</v>
+      </c>
+      <c r="G162" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I162" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K162" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L162" s="12">
+        <v>100</v>
+      </c>
+      <c r="M162" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N162" s="13">
+        <v>1950000</v>
+      </c>
+      <c r="O162" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P162" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A163" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F163" s="12">
+        <v>772038792</v>
+      </c>
+      <c r="G163" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I163" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J163" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="K163" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L163" s="12">
+        <v>10</v>
+      </c>
+      <c r="M163" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N163" s="13">
+        <v>92500</v>
+      </c>
+      <c r="O163" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P163" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A164" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F164" s="12">
+        <v>776256670</v>
+      </c>
+      <c r="G164" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I164" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J164" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K164" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L164" s="12">
+        <v>25</v>
+      </c>
+      <c r="M164" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N164" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O164" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P164" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A165" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F165" s="12">
+        <v>776414102</v>
+      </c>
+      <c r="G165" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I165" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J165" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K165" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L165" s="12">
+        <v>25</v>
+      </c>
+      <c r="M165" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N165" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O165" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P165" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A166" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F166" s="12">
+        <v>776952210</v>
+      </c>
+      <c r="G166" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I166" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K166" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L166" s="12">
+        <v>2</v>
+      </c>
+      <c r="M166" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N166" s="13">
+        <v>36000</v>
+      </c>
+      <c r="O166" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P166" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A167" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B167" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F167" s="12">
+        <v>765667743</v>
+      </c>
+      <c r="G167" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J167" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K167" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L167" s="12">
+        <v>1</v>
+      </c>
+      <c r="M167" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N167" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O167" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P167" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A168" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F168" s="12">
+        <v>765667743</v>
+      </c>
+      <c r="G168" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I168" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J168" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K168" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L168" s="12">
+        <v>1</v>
+      </c>
+      <c r="M168" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N168" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O168" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P168" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A169" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B169" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F169" s="12">
+        <v>761760419</v>
+      </c>
+      <c r="G169" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J169" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K169" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L169" s="12">
+        <v>1</v>
+      </c>
+      <c r="M169" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N169" s="13">
+        <v>12000</v>
+      </c>
+      <c r="O169" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P169" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A170" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="F170" s="12">
+        <v>761760419</v>
+      </c>
+      <c r="G170" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K170" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L170" s="12">
+        <v>3</v>
+      </c>
+      <c r="M170" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N170" s="13">
+        <v>27750</v>
+      </c>
+      <c r="O170" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P170" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A171" s="11">
+        <v>46093</v>
+      </c>
+      <c r="B171" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="F171" s="12">
+        <v>783596501</v>
+      </c>
+      <c r="G171" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J171" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K171" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L171" s="12">
+        <v>2</v>
+      </c>
+      <c r="M171" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N171" s="13">
+        <v>39000</v>
+      </c>
+      <c r="O171" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P171" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A172" s="11">
+        <v>46095</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F172" s="12">
+        <v>777262311</v>
+      </c>
+      <c r="G172" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K172" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L172" s="12">
+        <v>4</v>
+      </c>
+      <c r="M172" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N172" s="13">
+        <v>78000</v>
+      </c>
+      <c r="O172" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P172" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A173" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D173" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="F173" s="12">
+        <v>779661523</v>
+      </c>
+      <c r="G173" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H173" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J173" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K173" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L173" s="12">
+        <v>25</v>
+      </c>
+      <c r="M173" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N173" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O173" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P173" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A174" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D174" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F174" s="12">
+        <v>773482683</v>
+      </c>
+      <c r="G174" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J174" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K174" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L174" s="12">
+        <v>25</v>
+      </c>
+      <c r="M174" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N174" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O174" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P174" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A175" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F175" s="12">
+        <v>775740574</v>
+      </c>
+      <c r="G175" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J175" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K175" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L175" s="12">
+        <v>25</v>
+      </c>
+      <c r="M175" s="13">
+        <v>30000</v>
+      </c>
+      <c r="N175" s="13">
+        <v>750000</v>
+      </c>
+      <c r="O175" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P175" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A176" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D176" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F176" s="12">
+        <v>775987400</v>
+      </c>
+      <c r="G176" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H176" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J176" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K176" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L176" s="12">
+        <v>2</v>
+      </c>
+      <c r="M176" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N176" s="13">
+        <v>39000</v>
+      </c>
+      <c r="O176" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P176" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A177" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D177" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F177" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G177" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H177" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I177" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J177" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K177" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L177" s="12">
+        <v>25</v>
+      </c>
+      <c r="M177" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N177" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O177" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P177" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A178" s="11">
+        <v>46094</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D178" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="F178" s="12">
+        <v>775538380</v>
+      </c>
+      <c r="G178" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J178" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K178" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L178" s="12">
+        <v>2</v>
+      </c>
+      <c r="M178" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N178" s="13">
+        <v>39000</v>
+      </c>
+      <c r="O178" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P178" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E75397-3000-4DCE-A8E9-2BC56C7D94CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CCB021-430F-4459-812E-3C029D8C21C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="215">
   <si>
     <t>Date</t>
   </si>
@@ -1093,8 +1093,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P178" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P178" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P179" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P179" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1407,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P178"/>
+  <dimension ref="A1:P179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -8498,2185 +8498,2237 @@
       </c>
     </row>
     <row r="137" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A137" s="11">
+      <c r="A137" s="8">
         <v>46090</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="B137" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C137" s="12" t="s">
+      <c r="C137" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D137" s="12" t="s">
+      <c r="D137" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E137" s="12" t="s">
+      <c r="E137" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F137" s="12">
+      <c r="F137" s="9">
         <v>779676016</v>
       </c>
-      <c r="G137" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H137" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I137" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J137" s="12" t="s">
+      <c r="G137" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K137" s="12" t="s">
+      <c r="K137" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L137" s="12">
+      <c r="L137" s="9">
         <v>5</v>
       </c>
-      <c r="M137" s="13">
+      <c r="M137" s="10">
         <v>6000</v>
       </c>
-      <c r="N137" s="13">
+      <c r="N137" s="10">
         <v>30000</v>
       </c>
-      <c r="O137" s="14" t="str">
+      <c r="O137" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P137" s="15" t="str">
+      <c r="P137" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="138" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A138" s="11">
+      <c r="A138" s="8">
         <v>46090</v>
       </c>
-      <c r="B138" s="12" t="s">
+      <c r="B138" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D138" s="12" t="s">
+      <c r="D138" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E138" s="12" t="s">
+      <c r="E138" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F138" s="12">
+      <c r="F138" s="9">
         <v>779676016</v>
       </c>
-      <c r="G138" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H138" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I138" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J138" s="12" t="s">
+      <c r="G138" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K138" s="12" t="s">
+      <c r="K138" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L138" s="12">
+      <c r="L138" s="9">
         <v>75</v>
       </c>
-      <c r="M138" s="13">
+      <c r="M138" s="10">
         <v>9250</v>
       </c>
-      <c r="N138" s="13">
+      <c r="N138" s="10">
         <v>693750</v>
       </c>
-      <c r="O138" s="14" t="str">
+      <c r="O138" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P138" s="15" t="str">
+      <c r="P138" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A139" s="11">
+      <c r="A139" s="8">
         <v>46090</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C139" s="12" t="s">
+      <c r="C139" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D139" s="12" t="s">
+      <c r="D139" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E139" s="12" t="s">
+      <c r="E139" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F139" s="12">
+      <c r="F139" s="9">
         <v>781297575</v>
       </c>
-      <c r="G139" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H139" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I139" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J139" s="12" t="s">
+      <c r="G139" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K139" s="12" t="s">
+      <c r="K139" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L139" s="12">
+      <c r="L139" s="9">
         <v>25</v>
       </c>
-      <c r="M139" s="13">
+      <c r="M139" s="10">
         <v>26000</v>
       </c>
-      <c r="N139" s="13">
+      <c r="N139" s="10">
         <v>650000</v>
       </c>
-      <c r="O139" s="14" t="str">
+      <c r="O139" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P139" s="15" t="str">
+      <c r="P139" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="140" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A140" s="11">
+      <c r="A140" s="8">
         <v>46090</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D140" s="12" t="s">
+      <c r="D140" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E140" s="12" t="s">
+      <c r="E140" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F140" s="12">
+      <c r="F140" s="9">
         <v>771952687</v>
       </c>
-      <c r="G140" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H140" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I140" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J140" s="12" t="s">
+      <c r="G140" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K140" s="12" t="s">
+      <c r="K140" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L140" s="12">
+      <c r="L140" s="9">
         <v>50</v>
       </c>
-      <c r="M140" s="13">
+      <c r="M140" s="10">
         <v>29000</v>
       </c>
-      <c r="N140" s="13">
+      <c r="N140" s="10">
         <v>1450000</v>
       </c>
-      <c r="O140" s="14" t="str">
+      <c r="O140" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P140" s="15" t="str">
+      <c r="P140" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A141" s="11">
+      <c r="A141" s="8">
         <v>46090</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C141" s="12" t="s">
+      <c r="C141" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D141" s="12" t="s">
+      <c r="D141" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E141" s="12" t="s">
+      <c r="E141" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F141" s="12">
+      <c r="F141" s="9">
         <v>777772248</v>
       </c>
-      <c r="G141" s="12" t="s">
+      <c r="G141" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H141" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I141" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J141" s="12" t="s">
+      <c r="H141" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K141" s="12" t="s">
+      <c r="K141" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L141" s="12">
+      <c r="L141" s="9">
         <v>20</v>
       </c>
-      <c r="M141" s="13">
+      <c r="M141" s="10">
         <v>9250</v>
       </c>
-      <c r="N141" s="13">
+      <c r="N141" s="10">
         <v>185000</v>
       </c>
-      <c r="O141" s="14" t="str">
+      <c r="O141" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P141" s="15" t="str">
+      <c r="P141" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A142" s="11">
+      <c r="A142" s="8">
         <v>46090</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="B142" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C142" s="12" t="s">
+      <c r="C142" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="D142" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E142" s="12" t="s">
+      <c r="E142" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F142" s="12">
+      <c r="F142" s="9">
         <v>775544532</v>
       </c>
-      <c r="G142" s="12" t="s">
+      <c r="G142" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H142" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I142" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J142" s="12" t="s">
+      <c r="H142" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K142" s="12" t="s">
+      <c r="K142" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L142" s="12">
+      <c r="L142" s="9">
         <v>25</v>
       </c>
-      <c r="M142" s="13">
+      <c r="M142" s="10">
         <v>26000</v>
       </c>
-      <c r="N142" s="13">
+      <c r="N142" s="10">
         <v>650000</v>
       </c>
-      <c r="O142" s="14" t="str">
+      <c r="O142" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P142" s="15" t="str">
+      <c r="P142" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A143" s="11">
+      <c r="A143" s="8">
         <v>46092</v>
       </c>
-      <c r="B143" s="12" t="s">
+      <c r="B143" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C143" s="12" t="s">
+      <c r="C143" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D143" s="12" t="s">
+      <c r="D143" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E143" s="12" t="s">
+      <c r="E143" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F143" s="12">
+      <c r="F143" s="9">
         <v>775586819</v>
       </c>
-      <c r="G143" s="12" t="s">
+      <c r="G143" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H143" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I143" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J143" s="12" t="s">
+      <c r="H143" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K143" s="12" t="s">
+      <c r="K143" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L143" s="12">
+      <c r="L143" s="9">
         <v>4</v>
       </c>
-      <c r="M143" s="13">
+      <c r="M143" s="10">
         <v>19500</v>
       </c>
-      <c r="N143" s="13">
+      <c r="N143" s="10">
         <v>78000</v>
       </c>
-      <c r="O143" s="14" t="str">
+      <c r="O143" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P143" s="15" t="str">
+      <c r="P143" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="144" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A144" s="11">
+      <c r="A144" s="8">
         <v>46092</v>
       </c>
-      <c r="B144" s="12" t="s">
+      <c r="B144" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C144" s="12" t="s">
+      <c r="C144" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D144" s="12" t="s">
+      <c r="D144" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E144" s="12" t="s">
+      <c r="E144" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="F144" s="12">
+      <c r="F144" s="9">
         <v>775250570</v>
       </c>
-      <c r="G144" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I144" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J144" s="12" t="s">
+      <c r="G144" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K144" s="12" t="s">
+      <c r="K144" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L144" s="12">
+      <c r="L144" s="9">
         <v>25</v>
       </c>
-      <c r="M144" s="13">
+      <c r="M144" s="10">
         <v>19500</v>
       </c>
-      <c r="N144" s="13">
+      <c r="N144" s="10">
         <v>487500</v>
       </c>
-      <c r="O144" s="14" t="str">
+      <c r="O144" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P144" s="15" t="str">
+      <c r="P144" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A145" s="11">
+      <c r="A145" s="8">
         <v>46092</v>
       </c>
-      <c r="B145" s="12" t="s">
+      <c r="B145" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C145" s="12" t="s">
+      <c r="C145" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D145" s="12" t="s">
+      <c r="D145" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E145" s="12" t="s">
+      <c r="E145" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F145" s="12">
+      <c r="F145" s="9">
         <v>775586819</v>
       </c>
-      <c r="G145" s="12" t="s">
+      <c r="G145" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H145" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I145" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J145" s="12" t="s">
+      <c r="H145" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K145" s="12" t="s">
+      <c r="K145" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L145" s="12">
+      <c r="L145" s="9">
         <v>27</v>
       </c>
-      <c r="M145" s="13">
+      <c r="M145" s="10">
         <v>26000</v>
       </c>
-      <c r="N145" s="13">
+      <c r="N145" s="10">
         <v>702000</v>
       </c>
-      <c r="O145" s="14" t="str">
+      <c r="O145" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P145" s="15" t="str">
+      <c r="P145" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A146" s="11">
+      <c r="A146" s="8">
         <v>46092</v>
       </c>
-      <c r="B146" s="12" t="s">
+      <c r="B146" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D146" s="12" t="s">
+      <c r="D146" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E146" s="12" t="s">
+      <c r="E146" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F146" s="12">
+      <c r="F146" s="9">
         <v>784537895</v>
       </c>
-      <c r="G146" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I146" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J146" s="12" t="s">
+      <c r="G146" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K146" s="12" t="s">
+      <c r="K146" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L146" s="12">
+      <c r="L146" s="9">
         <v>25</v>
       </c>
-      <c r="M146" s="13">
+      <c r="M146" s="10">
         <v>26000</v>
       </c>
-      <c r="N146" s="13">
+      <c r="N146" s="10">
         <v>650000</v>
       </c>
-      <c r="O146" s="14" t="str">
+      <c r="O146" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P146" s="15" t="str">
+      <c r="P146" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A147" s="11">
+      <c r="A147" s="8">
         <v>46092</v>
       </c>
-      <c r="B147" s="12" t="s">
+      <c r="B147" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C147" s="12" t="s">
+      <c r="C147" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D147" s="12" t="s">
+      <c r="D147" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E147" s="12" t="s">
+      <c r="E147" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F147" s="12">
+      <c r="F147" s="9">
         <v>784537895</v>
       </c>
-      <c r="G147" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H147" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I147" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J147" s="12" t="s">
+      <c r="G147" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J147" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K147" s="12" t="s">
+      <c r="K147" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L147" s="12">
+      <c r="L147" s="9">
         <v>25</v>
       </c>
-      <c r="M147" s="13">
+      <c r="M147" s="10">
         <v>19500</v>
       </c>
-      <c r="N147" s="13">
+      <c r="N147" s="10">
         <v>487500</v>
       </c>
-      <c r="O147" s="14" t="str">
+      <c r="O147" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P147" s="15" t="str">
+      <c r="P147" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A148" s="11">
+      <c r="A148" s="8">
         <v>46092</v>
       </c>
-      <c r="B148" s="12" t="s">
+      <c r="B148" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C148" s="12" t="s">
+      <c r="C148" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D148" s="12" t="s">
+      <c r="D148" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E148" s="12" t="s">
+      <c r="E148" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F148" s="12">
+      <c r="F148" s="9">
         <v>776428218</v>
       </c>
-      <c r="G148" s="12" t="s">
+      <c r="G148" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H148" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I148" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J148" s="12" t="s">
+      <c r="H148" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J148" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K148" s="12" t="s">
+      <c r="K148" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L148" s="12">
+      <c r="L148" s="9">
         <v>25</v>
       </c>
-      <c r="M148" s="13">
+      <c r="M148" s="10">
         <v>19500</v>
       </c>
-      <c r="N148" s="13">
+      <c r="N148" s="10">
         <v>487500</v>
       </c>
-      <c r="O148" s="14" t="str">
+      <c r="O148" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P148" s="15" t="str">
+      <c r="P148" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A149" s="11">
+      <c r="A149" s="8">
         <v>46092</v>
       </c>
-      <c r="B149" s="12" t="s">
+      <c r="B149" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C149" s="12" t="s">
+      <c r="C149" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D149" s="12" t="s">
+      <c r="D149" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E149" s="12" t="s">
+      <c r="E149" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F149" s="12">
+      <c r="F149" s="9">
         <v>775467226</v>
       </c>
-      <c r="G149" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H149" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I149" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J149" s="12" t="s">
+      <c r="G149" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J149" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K149" s="12" t="s">
+      <c r="K149" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L149" s="12">
+      <c r="L149" s="9">
         <v>1</v>
       </c>
-      <c r="M149" s="13">
+      <c r="M149" s="10">
         <v>19500</v>
       </c>
-      <c r="N149" s="13">
+      <c r="N149" s="10">
         <v>19500</v>
       </c>
-      <c r="O149" s="14" t="str">
+      <c r="O149" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P149" s="15" t="str">
+      <c r="P149" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A150" s="11">
+      <c r="A150" s="8">
         <v>46092</v>
       </c>
-      <c r="B150" s="12" t="s">
+      <c r="B150" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C150" s="12" t="s">
+      <c r="C150" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D150" s="12" t="s">
+      <c r="D150" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E150" s="12" t="s">
+      <c r="E150" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F150" s="12">
+      <c r="F150" s="9">
         <v>775467226</v>
       </c>
-      <c r="G150" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H150" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I150" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J150" s="12" t="s">
+      <c r="G150" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K150" s="12" t="s">
+      <c r="K150" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L150" s="12">
+      <c r="L150" s="9">
         <v>20</v>
       </c>
-      <c r="M150" s="13">
+      <c r="M150" s="10">
         <v>9250</v>
       </c>
-      <c r="N150" s="13">
+      <c r="N150" s="10">
         <v>185000</v>
       </c>
-      <c r="O150" s="14" t="str">
+      <c r="O150" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P150" s="15" t="str">
+      <c r="P150" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A151" s="11">
+      <c r="A151" s="8">
         <v>46092</v>
       </c>
-      <c r="B151" s="12" t="s">
+      <c r="B151" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C151" s="12" t="s">
+      <c r="C151" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="D151" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="E151" s="12" t="s">
+      <c r="E151" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F151" s="12">
+      <c r="F151" s="9">
         <v>775467226</v>
       </c>
-      <c r="G151" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H151" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I151" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J151" s="12" t="s">
+      <c r="G151" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J151" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K151" s="12" t="s">
+      <c r="K151" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L151" s="12">
+      <c r="L151" s="9">
         <v>1</v>
       </c>
-      <c r="M151" s="13">
+      <c r="M151" s="10">
         <v>11000</v>
       </c>
-      <c r="N151" s="13">
+      <c r="N151" s="10">
         <v>11000</v>
       </c>
-      <c r="O151" s="14" t="str">
+      <c r="O151" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P151" s="15" t="str">
+      <c r="P151" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A152" s="11">
+      <c r="A152" s="8">
         <v>46092</v>
       </c>
-      <c r="B152" s="12" t="s">
+      <c r="B152" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C152" s="12" t="s">
+      <c r="C152" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D152" s="12" t="s">
+      <c r="D152" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E152" s="12" t="s">
+      <c r="E152" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F152" s="12">
+      <c r="F152" s="9">
         <v>775426848</v>
       </c>
-      <c r="G152" s="12" t="s">
+      <c r="G152" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H152" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I152" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J152" s="12" t="s">
+      <c r="H152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K152" s="12" t="s">
+      <c r="K152" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L152" s="12">
+      <c r="L152" s="9">
         <v>25</v>
       </c>
-      <c r="M152" s="13">
+      <c r="M152" s="10">
         <v>19500</v>
       </c>
-      <c r="N152" s="13">
+      <c r="N152" s="10">
         <v>487500</v>
       </c>
-      <c r="O152" s="14" t="str">
+      <c r="O152" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P152" s="15" t="str">
+      <c r="P152" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A153" s="11">
+      <c r="A153" s="8">
         <v>46092</v>
       </c>
-      <c r="B153" s="12" t="s">
+      <c r="B153" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C153" s="12" t="s">
+      <c r="C153" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D153" s="12" t="s">
+      <c r="D153" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E153" s="12" t="s">
+      <c r="E153" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="F153" s="12">
+      <c r="F153" s="9">
         <v>771040904</v>
       </c>
-      <c r="G153" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H153" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I153" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J153" s="12" t="s">
+      <c r="G153" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J153" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K153" s="12" t="s">
+      <c r="K153" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L153" s="12">
+      <c r="L153" s="9">
         <v>25</v>
       </c>
-      <c r="M153" s="13">
+      <c r="M153" s="10">
         <v>26000</v>
       </c>
-      <c r="N153" s="13">
+      <c r="N153" s="10">
         <v>650000</v>
       </c>
-      <c r="O153" s="14" t="str">
+      <c r="O153" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P153" s="15" t="str">
+      <c r="P153" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A154" s="11">
+      <c r="A154" s="8">
         <v>46091</v>
       </c>
-      <c r="B154" s="12" t="s">
+      <c r="B154" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C154" s="12" t="s">
+      <c r="C154" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D154" s="12" t="s">
+      <c r="D154" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E154" s="12" t="s">
+      <c r="E154" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F154" s="12">
+      <c r="F154" s="9">
         <v>772377240</v>
       </c>
-      <c r="G154" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H154" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I154" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J154" s="12" t="s">
+      <c r="G154" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J154" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K154" s="12" t="s">
+      <c r="K154" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L154" s="12">
+      <c r="L154" s="9">
         <v>50</v>
       </c>
-      <c r="M154" s="13">
+      <c r="M154" s="10">
         <v>19500</v>
       </c>
-      <c r="N154" s="13">
+      <c r="N154" s="10">
         <v>975000</v>
       </c>
-      <c r="O154" s="14" t="str">
+      <c r="O154" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P154" s="15" t="str">
+      <c r="P154" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A155" s="11">
+      <c r="A155" s="8">
         <v>46091</v>
       </c>
-      <c r="B155" s="12" t="s">
+      <c r="B155" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C155" s="12" t="s">
+      <c r="C155" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D155" s="12" t="s">
+      <c r="D155" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E155" s="12" t="s">
+      <c r="E155" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="F155" s="12">
+      <c r="F155" s="9">
         <v>771078008</v>
       </c>
-      <c r="G155" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H155" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I155" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J155" s="12" t="s">
+      <c r="G155" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J155" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K155" s="12" t="s">
+      <c r="K155" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L155" s="12">
+      <c r="L155" s="9">
         <v>10</v>
       </c>
-      <c r="M155" s="13">
+      <c r="M155" s="10">
         <v>9250</v>
       </c>
-      <c r="N155" s="13">
+      <c r="N155" s="10">
         <v>92500</v>
       </c>
-      <c r="O155" s="14" t="str">
+      <c r="O155" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P155" s="15" t="str">
+      <c r="P155" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A156" s="11">
+      <c r="A156" s="8">
         <v>46091</v>
       </c>
-      <c r="B156" s="12" t="s">
+      <c r="B156" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E156" s="12" t="s">
+      <c r="E156" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F156" s="12">
+      <c r="F156" s="9">
         <v>776634479</v>
       </c>
-      <c r="G156" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H156" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I156" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J156" s="12" t="s">
+      <c r="G156" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J156" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K156" s="12" t="s">
+      <c r="K156" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L156" s="12">
+      <c r="L156" s="9">
         <v>21</v>
       </c>
-      <c r="M156" s="13">
+      <c r="M156" s="10">
         <v>54000</v>
       </c>
-      <c r="N156" s="13">
+      <c r="N156" s="10">
         <v>1134000</v>
       </c>
-      <c r="O156" s="14" t="str">
+      <c r="O156" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P156" s="15" t="str">
+      <c r="P156" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A157" s="11">
+      <c r="A157" s="8">
         <v>46091</v>
       </c>
-      <c r="B157" s="12" t="s">
+      <c r="B157" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C157" s="12" t="s">
+      <c r="C157" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D157" s="12" t="s">
+      <c r="D157" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E157" s="12" t="s">
+      <c r="E157" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F157" s="12">
+      <c r="F157" s="9">
         <v>776634479</v>
       </c>
-      <c r="G157" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H157" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I157" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J157" s="12" t="s">
+      <c r="G157" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H157" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J157" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K157" s="12" t="s">
+      <c r="K157" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L157" s="12">
+      <c r="L157" s="9">
         <v>5</v>
       </c>
-      <c r="M157" s="13">
+      <c r="M157" s="10">
         <v>19500</v>
       </c>
-      <c r="N157" s="13">
+      <c r="N157" s="10">
         <v>97500</v>
       </c>
-      <c r="O157" s="14" t="str">
+      <c r="O157" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P157" s="15" t="str">
+      <c r="P157" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A158" s="11">
+      <c r="A158" s="8">
         <v>46091</v>
       </c>
-      <c r="B158" s="12" t="s">
+      <c r="B158" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C158" s="12" t="s">
+      <c r="C158" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D158" s="12" t="s">
+      <c r="D158" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E158" s="12" t="s">
+      <c r="E158" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="F158" s="12">
+      <c r="F158" s="9">
         <v>775602589</v>
       </c>
-      <c r="G158" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H158" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I158" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J158" s="12" t="s">
+      <c r="G158" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J158" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K158" s="12" t="s">
+      <c r="K158" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L158" s="12">
+      <c r="L158" s="9">
         <v>5</v>
       </c>
-      <c r="M158" s="13">
+      <c r="M158" s="10">
         <v>26000</v>
       </c>
-      <c r="N158" s="13">
+      <c r="N158" s="10">
         <v>130000</v>
       </c>
-      <c r="O158" s="14" t="str">
+      <c r="O158" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P158" s="15" t="str">
+      <c r="P158" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A159" s="11">
+      <c r="A159" s="8">
         <v>46091</v>
       </c>
-      <c r="B159" s="12" t="s">
+      <c r="B159" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C159" s="12" t="s">
+      <c r="C159" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D159" s="12" t="s">
+      <c r="D159" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E159" s="12" t="s">
+      <c r="E159" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F159" s="12">
+      <c r="F159" s="9">
         <v>788217757</v>
       </c>
-      <c r="G159" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H159" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I159" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J159" s="12" t="s">
+      <c r="G159" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J159" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K159" s="12" t="s">
+      <c r="K159" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L159" s="12">
+      <c r="L159" s="9">
         <v>25</v>
       </c>
-      <c r="M159" s="13">
+      <c r="M159" s="10">
         <v>19500</v>
       </c>
-      <c r="N159" s="13">
+      <c r="N159" s="10">
         <v>487500</v>
       </c>
-      <c r="O159" s="14" t="str">
+      <c r="O159" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P159" s="15" t="str">
+      <c r="P159" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A160" s="11">
+      <c r="A160" s="8">
         <v>46091</v>
       </c>
-      <c r="B160" s="12" t="s">
+      <c r="B160" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C160" s="12" t="s">
+      <c r="C160" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D160" s="12" t="s">
+      <c r="D160" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E160" s="12" t="s">
+      <c r="E160" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F160" s="12">
+      <c r="F160" s="9">
         <v>775485563</v>
       </c>
-      <c r="G160" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H160" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I160" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J160" s="12" t="s">
+      <c r="G160" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J160" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K160" s="12" t="s">
+      <c r="K160" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L160" s="12">
+      <c r="L160" s="9">
         <v>5</v>
       </c>
-      <c r="M160" s="13">
+      <c r="M160" s="10">
         <v>19500</v>
       </c>
-      <c r="N160" s="13">
+      <c r="N160" s="10">
         <v>97500</v>
       </c>
-      <c r="O160" s="14" t="str">
+      <c r="O160" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P160" s="15" t="str">
+      <c r="P160" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A161" s="11">
+      <c r="A161" s="8">
         <v>46091</v>
       </c>
-      <c r="B161" s="12" t="s">
+      <c r="B161" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C161" s="12" t="s">
+      <c r="C161" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D161" s="12" t="s">
+      <c r="D161" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E161" s="12" t="s">
+      <c r="E161" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F161" s="12">
+      <c r="F161" s="9">
         <v>779486095</v>
       </c>
-      <c r="G161" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H161" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I161" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J161" s="12" t="s">
+      <c r="G161" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J161" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K161" s="12" t="s">
+      <c r="K161" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L161" s="12">
+      <c r="L161" s="9">
         <v>27</v>
       </c>
-      <c r="M161" s="13">
+      <c r="M161" s="10">
         <v>18000</v>
       </c>
-      <c r="N161" s="13">
+      <c r="N161" s="10">
         <v>486000</v>
       </c>
-      <c r="O161" s="14" t="str">
+      <c r="O161" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P161" s="15" t="str">
+      <c r="P161" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="162" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A162" s="11">
+      <c r="A162" s="8">
         <v>46091</v>
       </c>
-      <c r="B162" s="12" t="s">
+      <c r="B162" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D162" s="12" t="s">
+      <c r="D162" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E162" s="12" t="s">
+      <c r="E162" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="F162" s="12">
+      <c r="F162" s="9">
         <v>786323232</v>
       </c>
-      <c r="G162" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H162" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I162" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J162" s="12" t="s">
+      <c r="G162" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J162" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K162" s="12" t="s">
+      <c r="K162" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L162" s="12">
+      <c r="L162" s="9">
         <v>100</v>
       </c>
-      <c r="M162" s="13">
+      <c r="M162" s="10">
         <v>19500</v>
       </c>
-      <c r="N162" s="13">
+      <c r="N162" s="10">
         <v>1950000</v>
       </c>
-      <c r="O162" s="14" t="str">
+      <c r="O162" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P162" s="15" t="str">
+      <c r="P162" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="163" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A163" s="11">
+      <c r="A163" s="8">
         <v>46093</v>
       </c>
-      <c r="B163" s="12" t="s">
+      <c r="B163" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C163" s="12" t="s">
+      <c r="C163" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D163" s="12" t="s">
+      <c r="D163" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E163" s="12" t="s">
+      <c r="E163" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F163" s="12">
+      <c r="F163" s="9">
         <v>772038792</v>
       </c>
-      <c r="G163" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H163" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I163" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J163" s="12" t="s">
+      <c r="G163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J163" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="K163" s="12" t="s">
+      <c r="K163" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L163" s="12">
+      <c r="L163" s="9">
         <v>10</v>
       </c>
-      <c r="M163" s="13">
+      <c r="M163" s="10">
         <v>9250</v>
       </c>
-      <c r="N163" s="13">
+      <c r="N163" s="10">
         <v>92500</v>
       </c>
-      <c r="O163" s="14" t="str">
+      <c r="O163" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P163" s="15" t="str">
+      <c r="P163" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="164" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A164" s="11">
+      <c r="A164" s="8">
         <v>46093</v>
       </c>
-      <c r="B164" s="12" t="s">
+      <c r="B164" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C164" s="12" t="s">
+      <c r="C164" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D164" s="12" t="s">
+      <c r="D164" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E164" s="12" t="s">
+      <c r="E164" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="F164" s="12">
+      <c r="F164" s="9">
         <v>776256670</v>
       </c>
-      <c r="G164" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H164" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I164" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J164" s="12" t="s">
+      <c r="G164" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J164" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K164" s="12" t="s">
+      <c r="K164" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L164" s="12">
+      <c r="L164" s="9">
         <v>25</v>
       </c>
-      <c r="M164" s="13">
+      <c r="M164" s="10">
         <v>19500</v>
       </c>
-      <c r="N164" s="13">
+      <c r="N164" s="10">
         <v>487500</v>
       </c>
-      <c r="O164" s="14" t="str">
+      <c r="O164" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P164" s="15" t="str">
+      <c r="P164" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="165" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A165" s="11">
+      <c r="A165" s="8">
         <v>46093</v>
       </c>
-      <c r="B165" s="12" t="s">
+      <c r="B165" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C165" s="12" t="s">
+      <c r="C165" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D165" s="12" t="s">
+      <c r="D165" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E165" s="12" t="s">
+      <c r="E165" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F165" s="12">
+      <c r="F165" s="9">
         <v>776414102</v>
       </c>
-      <c r="G165" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H165" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I165" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J165" s="12" t="s">
+      <c r="G165" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H165" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J165" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K165" s="12" t="s">
+      <c r="K165" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L165" s="12">
+      <c r="L165" s="9">
         <v>25</v>
       </c>
-      <c r="M165" s="13">
+      <c r="M165" s="10">
         <v>19500</v>
       </c>
-      <c r="N165" s="13">
+      <c r="N165" s="10">
         <v>487500</v>
       </c>
-      <c r="O165" s="14" t="str">
+      <c r="O165" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P165" s="15" t="str">
+      <c r="P165" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="166" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A166" s="11">
+      <c r="A166" s="8">
         <v>46093</v>
       </c>
-      <c r="B166" s="12" t="s">
+      <c r="B166" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C166" s="12" t="s">
+      <c r="C166" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D166" s="12" t="s">
+      <c r="D166" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E166" s="12" t="s">
+      <c r="E166" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F166" s="12">
+      <c r="F166" s="9">
         <v>776952210</v>
       </c>
-      <c r="G166" s="12" t="s">
+      <c r="G166" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H166" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I166" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J166" s="12" t="s">
+      <c r="H166" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J166" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K166" s="12" t="s">
+      <c r="K166" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L166" s="12">
+      <c r="L166" s="9">
         <v>2</v>
       </c>
-      <c r="M166" s="13">
+      <c r="M166" s="10">
         <v>18000</v>
       </c>
-      <c r="N166" s="13">
+      <c r="N166" s="10">
         <v>36000</v>
       </c>
-      <c r="O166" s="14" t="str">
+      <c r="O166" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P166" s="15" t="str">
+      <c r="P166" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A167" s="11">
+      <c r="A167" s="8">
         <v>46093</v>
       </c>
-      <c r="B167" s="12" t="s">
+      <c r="B167" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C167" s="12" t="s">
+      <c r="C167" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D167" s="12" t="s">
+      <c r="D167" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E167" s="12" t="s">
+      <c r="E167" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F167" s="12">
+      <c r="F167" s="9">
         <v>765667743</v>
       </c>
-      <c r="G167" s="12" t="s">
+      <c r="G167" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H167" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I167" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J167" s="12" t="s">
+      <c r="H167" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J167" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K167" s="12" t="s">
+      <c r="K167" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="L167" s="12">
+      <c r="L167" s="9">
         <v>1</v>
       </c>
-      <c r="M167" s="13">
+      <c r="M167" s="10">
         <v>18000</v>
       </c>
-      <c r="N167" s="13">
+      <c r="N167" s="10">
         <v>18000</v>
       </c>
-      <c r="O167" s="14" t="str">
+      <c r="O167" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P167" s="15" t="str">
+      <c r="P167" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="168" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A168" s="11">
+      <c r="A168" s="8">
         <v>46093</v>
       </c>
-      <c r="B168" s="12" t="s">
+      <c r="B168" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C168" s="12" t="s">
+      <c r="C168" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D168" s="12" t="s">
+      <c r="D168" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E168" s="12" t="s">
+      <c r="E168" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="F168" s="12">
+      <c r="F168" s="9">
         <v>765667743</v>
       </c>
-      <c r="G168" s="12" t="s">
+      <c r="G168" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="H168" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I168" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J168" s="12" t="s">
+      <c r="H168" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J168" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K168" s="12" t="s">
+      <c r="K168" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L168" s="12">
+      <c r="L168" s="9">
         <v>1</v>
       </c>
-      <c r="M168" s="13">
+      <c r="M168" s="10">
         <v>18000</v>
       </c>
-      <c r="N168" s="13">
+      <c r="N168" s="10">
         <v>18000</v>
       </c>
-      <c r="O168" s="14" t="str">
+      <c r="O168" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P168" s="15" t="str">
+      <c r="P168" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="169" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A169" s="11">
+      <c r="A169" s="8">
         <v>46093</v>
       </c>
-      <c r="B169" s="12" t="s">
+      <c r="B169" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C169" s="12" t="s">
+      <c r="C169" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D169" s="12" t="s">
+      <c r="D169" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E169" s="12" t="s">
+      <c r="E169" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="F169" s="12">
+      <c r="F169" s="9">
         <v>761760419</v>
       </c>
-      <c r="G169" s="12" t="s">
+      <c r="G169" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H169" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I169" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J169" s="12" t="s">
+      <c r="H169" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J169" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K169" s="12" t="s">
+      <c r="K169" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L169" s="12">
+      <c r="L169" s="9">
         <v>1</v>
       </c>
-      <c r="M169" s="13">
+      <c r="M169" s="10">
         <v>12000</v>
       </c>
-      <c r="N169" s="13">
+      <c r="N169" s="10">
         <v>12000</v>
       </c>
-      <c r="O169" s="14" t="str">
+      <c r="O169" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P169" s="15" t="str">
+      <c r="P169" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="170" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A170" s="11">
+      <c r="A170" s="8">
         <v>46093</v>
       </c>
-      <c r="B170" s="12" t="s">
+      <c r="B170" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C170" s="12" t="s">
+      <c r="C170" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D170" s="12" t="s">
+      <c r="D170" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E170" s="12" t="s">
+      <c r="E170" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="F170" s="12">
+      <c r="F170" s="9">
         <v>761760419</v>
       </c>
-      <c r="G170" s="12" t="s">
+      <c r="G170" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H170" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I170" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J170" s="12" t="s">
+      <c r="H170" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J170" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K170" s="12" t="s">
+      <c r="K170" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L170" s="12">
+      <c r="L170" s="9">
         <v>3</v>
       </c>
-      <c r="M170" s="13">
+      <c r="M170" s="10">
         <v>9250</v>
       </c>
-      <c r="N170" s="13">
+      <c r="N170" s="10">
         <v>27750</v>
       </c>
-      <c r="O170" s="14" t="str">
+      <c r="O170" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P170" s="15" t="str">
+      <c r="P170" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A171" s="11">
+      <c r="A171" s="8">
         <v>46093</v>
       </c>
-      <c r="B171" s="12" t="s">
+      <c r="B171" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C171" s="12" t="s">
+      <c r="C171" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D171" s="12" t="s">
+      <c r="D171" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E171" s="12" t="s">
+      <c r="E171" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="F171" s="12">
+      <c r="F171" s="9">
         <v>783596501</v>
       </c>
-      <c r="G171" s="12" t="s">
+      <c r="G171" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H171" s="12" t="s">
+      <c r="H171" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I171" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J171" s="12" t="s">
+      <c r="I171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J171" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="K171" s="12" t="s">
+      <c r="K171" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L171" s="12">
+      <c r="L171" s="9">
         <v>2</v>
       </c>
-      <c r="M171" s="13">
+      <c r="M171" s="10">
         <v>19500</v>
       </c>
-      <c r="N171" s="13">
+      <c r="N171" s="10">
         <v>39000</v>
       </c>
-      <c r="O171" s="14" t="str">
+      <c r="O171" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P171" s="15" t="str">
+      <c r="P171" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="172" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A172" s="11">
+      <c r="A172" s="8">
         <v>46095</v>
       </c>
-      <c r="B172" s="12" t="s">
+      <c r="B172" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C172" s="12" t="s">
+      <c r="C172" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D172" s="12" t="s">
+      <c r="D172" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E172" s="12" t="s">
+      <c r="E172" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F172" s="12">
+      <c r="F172" s="9">
         <v>777262311</v>
       </c>
-      <c r="G172" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H172" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I172" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J172" s="12" t="s">
+      <c r="G172" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H172" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J172" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K172" s="12" t="s">
+      <c r="K172" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L172" s="12">
+      <c r="L172" s="9">
         <v>4</v>
       </c>
-      <c r="M172" s="13">
+      <c r="M172" s="10">
         <v>19500</v>
       </c>
-      <c r="N172" s="13">
+      <c r="N172" s="10">
         <v>78000</v>
       </c>
-      <c r="O172" s="14" t="str">
+      <c r="O172" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P172" s="15" t="str">
+      <c r="P172" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="173" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A173" s="11">
+      <c r="A173" s="8">
         <v>46094</v>
       </c>
-      <c r="B173" s="12" t="s">
+      <c r="B173" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C173" s="12" t="s">
+      <c r="C173" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D173" s="12" t="s">
+      <c r="D173" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E173" s="12" t="s">
+      <c r="E173" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F173" s="12">
+      <c r="F173" s="9">
         <v>779661523</v>
       </c>
-      <c r="G173" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I173" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J173" s="12" t="s">
+      <c r="G173" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J173" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K173" s="12" t="s">
+      <c r="K173" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L173" s="12">
+      <c r="L173" s="9">
         <v>25</v>
       </c>
-      <c r="M173" s="13">
+      <c r="M173" s="10">
         <v>26000</v>
       </c>
-      <c r="N173" s="13">
+      <c r="N173" s="10">
         <v>650000</v>
       </c>
-      <c r="O173" s="14" t="str">
+      <c r="O173" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P173" s="15" t="str">
+      <c r="P173" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A174" s="11">
+      <c r="A174" s="8">
         <v>46094</v>
       </c>
-      <c r="B174" s="12" t="s">
+      <c r="B174" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D174" s="12" t="s">
+      <c r="D174" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E174" s="12" t="s">
+      <c r="E174" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F174" s="12">
+      <c r="F174" s="9">
         <v>773482683</v>
       </c>
-      <c r="G174" s="12" t="s">
+      <c r="G174" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H174" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I174" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J174" s="12" t="s">
+      <c r="H174" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J174" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K174" s="12" t="s">
+      <c r="K174" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L174" s="12">
+      <c r="L174" s="9">
         <v>25</v>
       </c>
-      <c r="M174" s="13">
+      <c r="M174" s="10">
         <v>26000</v>
       </c>
-      <c r="N174" s="13">
+      <c r="N174" s="10">
         <v>650000</v>
       </c>
-      <c r="O174" s="14" t="str">
+      <c r="O174" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P174" s="15" t="str">
+      <c r="P174" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="175" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A175" s="11">
+      <c r="A175" s="8">
         <v>46094</v>
       </c>
-      <c r="B175" s="12" t="s">
+      <c r="B175" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C175" s="12" t="s">
+      <c r="C175" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D175" s="12" t="s">
+      <c r="D175" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E175" s="12" t="s">
+      <c r="E175" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F175" s="12">
+      <c r="F175" s="9">
         <v>775740574</v>
       </c>
-      <c r="G175" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H175" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I175" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J175" s="12" t="s">
+      <c r="G175" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H175" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J175" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K175" s="12" t="s">
+      <c r="K175" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L175" s="12">
+      <c r="L175" s="9">
         <v>25</v>
       </c>
-      <c r="M175" s="13">
+      <c r="M175" s="10">
         <v>30000</v>
       </c>
-      <c r="N175" s="13">
+      <c r="N175" s="10">
         <v>750000</v>
       </c>
-      <c r="O175" s="14" t="str">
+      <c r="O175" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P175" s="15" t="str">
+      <c r="P175" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="176" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A176" s="11">
+      <c r="A176" s="8">
         <v>46094</v>
       </c>
-      <c r="B176" s="12" t="s">
+      <c r="B176" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C176" s="12" t="s">
+      <c r="C176" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D176" s="12" t="s">
+      <c r="D176" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E176" s="12" t="s">
+      <c r="E176" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F176" s="12">
+      <c r="F176" s="9">
         <v>775987400</v>
       </c>
-      <c r="G176" s="12" t="s">
+      <c r="G176" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H176" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I176" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J176" s="12" t="s">
+      <c r="H176" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J176" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K176" s="12" t="s">
+      <c r="K176" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L176" s="12">
+      <c r="L176" s="9">
         <v>2</v>
       </c>
-      <c r="M176" s="13">
+      <c r="M176" s="10">
         <v>19500</v>
       </c>
-      <c r="N176" s="13">
+      <c r="N176" s="10">
         <v>39000</v>
       </c>
-      <c r="O176" s="14" t="str">
+      <c r="O176" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P176" s="15" t="str">
+      <c r="P176" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A177" s="11">
+      <c r="A177" s="8">
         <v>46094</v>
       </c>
-      <c r="B177" s="12" t="s">
+      <c r="B177" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C177" s="12" t="s">
+      <c r="C177" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D177" s="12" t="s">
+      <c r="D177" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E177" s="12" t="s">
+      <c r="E177" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F177" s="12">
+      <c r="F177" s="9">
         <v>775544532</v>
       </c>
-      <c r="G177" s="12" t="s">
+      <c r="G177" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H177" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I177" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J177" s="12" t="s">
+      <c r="H177" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J177" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K177" s="12" t="s">
+      <c r="K177" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L177" s="12">
+      <c r="L177" s="9">
         <v>25</v>
       </c>
-      <c r="M177" s="13">
+      <c r="M177" s="10">
         <v>26000</v>
       </c>
-      <c r="N177" s="13">
+      <c r="N177" s="10">
         <v>650000</v>
       </c>
-      <c r="O177" s="14" t="str">
+      <c r="O177" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P177" s="15" t="str">
+      <c r="P177" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="178" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A178" s="11">
+      <c r="A178" s="8">
         <v>46094</v>
       </c>
-      <c r="B178" s="12" t="s">
+      <c r="B178" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C178" s="12" t="s">
+      <c r="C178" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D178" s="12" t="s">
+      <c r="D178" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E178" s="12" t="s">
+      <c r="E178" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F178" s="12">
+      <c r="F178" s="9">
         <v>775538380</v>
       </c>
-      <c r="G178" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H178" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I178" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J178" s="12" t="s">
+      <c r="G178" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H178" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J178" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K178" s="12" t="s">
+      <c r="K178" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L178" s="12">
+      <c r="L178" s="9">
         <v>2</v>
       </c>
-      <c r="M178" s="13">
+      <c r="M178" s="10">
         <v>19500</v>
       </c>
-      <c r="N178" s="13">
+      <c r="N178" s="10">
         <v>39000</v>
       </c>
-      <c r="O178" s="14" t="str">
+      <c r="O178" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P178" s="15" t="str">
+      <c r="P178" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A179" s="11">
+        <v>46090</v>
+      </c>
+      <c r="B179" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E179" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="F179" s="12">
+        <v>781297576</v>
+      </c>
+      <c r="G179" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H179" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J179" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K179" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L179" s="12">
+        <v>100</v>
+      </c>
+      <c r="M179" s="13">
+        <v>5750</v>
+      </c>
+      <c r="N179" s="13">
+        <v>575000</v>
+      </c>
+      <c r="O179" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S11</v>
+      </c>
+      <c r="P179" s="15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CCB021-430F-4459-812E-3C029D8C21C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4794A7E9-7137-4013-805A-B62EA94FC78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="228">
   <si>
     <t>Date</t>
   </si>
@@ -679,6 +679,45 @@
   </si>
   <si>
     <t>Alioune</t>
+  </si>
+  <si>
+    <t>Keur Massar Sotrac</t>
+  </si>
+  <si>
+    <t>Amadou Diallo</t>
+  </si>
+  <si>
+    <t>Ouakam</t>
+  </si>
+  <si>
+    <t>Sonké Global Distribution Suarl</t>
+  </si>
+  <si>
+    <t>Gueule Tapée</t>
+  </si>
+  <si>
+    <t>Baye FALL</t>
+  </si>
+  <si>
+    <t>Grand Boutique</t>
+  </si>
+  <si>
+    <t>Mbao</t>
+  </si>
+  <si>
+    <t>Elhadj Thiaw</t>
+  </si>
+  <si>
+    <t>Zac Mbao</t>
+  </si>
+  <si>
+    <t>Ibrahima Tahirou</t>
+  </si>
+  <si>
+    <t>Ablaye</t>
+  </si>
+  <si>
+    <t>Abdou Rakhmane Baldé</t>
   </si>
 </sst>
 </file>
@@ -1093,8 +1132,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P179" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P179" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P194" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P194" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1407,7 +1446,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P179"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -10682,53 +10721,833 @@
       </c>
     </row>
     <row r="179" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A179" s="11">
+      <c r="A179" s="8">
         <v>46090</v>
       </c>
-      <c r="B179" s="12" t="s">
+      <c r="B179" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C179" s="12" t="s">
+      <c r="C179" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D179" s="12" t="s">
+      <c r="D179" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E179" s="12" t="s">
+      <c r="E179" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F179" s="12">
+      <c r="F179" s="9">
         <v>781297576</v>
       </c>
-      <c r="G179" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H179" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I179" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J179" s="12" t="s">
+      <c r="G179" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H179" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J179" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K179" s="12" t="s">
+      <c r="K179" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L179" s="12">
+      <c r="L179" s="9">
         <v>100</v>
       </c>
-      <c r="M179" s="13">
+      <c r="M179" s="10">
         <v>5750</v>
       </c>
-      <c r="N179" s="13">
+      <c r="N179" s="10">
         <v>575000</v>
       </c>
-      <c r="O179" s="14" t="str">
+      <c r="O179" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S11</v>
       </c>
-      <c r="P179" s="15" t="str">
+      <c r="P179" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A180" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D180" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F180" s="12">
+        <v>775113886</v>
+      </c>
+      <c r="G180" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H180" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I180" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K180" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L180" s="12">
+        <v>25</v>
+      </c>
+      <c r="M180" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N180" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O180" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P180" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A181" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B181" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D181" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F181" s="12">
+        <v>775626425</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H181" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J181" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K181" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L181" s="12">
+        <v>3</v>
+      </c>
+      <c r="M181" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N181" s="13">
+        <v>54000</v>
+      </c>
+      <c r="O181" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P181" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A182" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D182" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E182" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F182" s="12">
+        <v>786361148</v>
+      </c>
+      <c r="G182" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I182" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J182" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K182" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L182" s="12">
+        <v>2</v>
+      </c>
+      <c r="M182" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N182" s="13">
+        <v>36000</v>
+      </c>
+      <c r="O182" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P182" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A183" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B183" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F183" s="12">
+        <v>770158721</v>
+      </c>
+      <c r="G183" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H183" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I183" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J183" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K183" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L183" s="12">
+        <v>25</v>
+      </c>
+      <c r="M183" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N183" s="13">
+        <v>450000</v>
+      </c>
+      <c r="O183" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P183" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A184" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D184" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F184" s="12">
+        <v>770158721</v>
+      </c>
+      <c r="G184" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H184" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K184" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L184" s="12">
+        <v>25</v>
+      </c>
+      <c r="M184" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N184" s="13">
+        <v>450000</v>
+      </c>
+      <c r="O184" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P184" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A185" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D185" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E185" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="F185" s="12">
+        <v>775649041</v>
+      </c>
+      <c r="G185" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H185" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J185" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K185" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L185" s="12">
+        <v>1</v>
+      </c>
+      <c r="M185" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N185" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O185" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P185" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A186" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D186" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F186" s="12">
+        <v>784785900</v>
+      </c>
+      <c r="G186" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H186" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I186" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K186" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L186" s="12">
+        <v>9</v>
+      </c>
+      <c r="M186" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N186" s="13">
+        <v>83250</v>
+      </c>
+      <c r="O186" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P186" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A187" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B187" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D187" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F187" s="12">
+        <v>784785900</v>
+      </c>
+      <c r="G187" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H187" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I187" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J187" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K187" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L187" s="12">
+        <v>7</v>
+      </c>
+      <c r="M187" s="13">
+        <v>30000</v>
+      </c>
+      <c r="N187" s="13">
+        <v>210000</v>
+      </c>
+      <c r="O187" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P187" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A188" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D188" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F188" s="12">
+        <v>784785900</v>
+      </c>
+      <c r="G188" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H188" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K188" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L188" s="12">
+        <v>4</v>
+      </c>
+      <c r="M188" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N188" s="13">
+        <v>78000</v>
+      </c>
+      <c r="O188" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P188" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A189" s="11">
+        <v>46098</v>
+      </c>
+      <c r="B189" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D189" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F189" s="12">
+        <v>784785900</v>
+      </c>
+      <c r="G189" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H189" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I189" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J189" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K189" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L189" s="12">
+        <v>33</v>
+      </c>
+      <c r="M189" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N189" s="13">
+        <v>858000</v>
+      </c>
+      <c r="O189" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P189" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A190" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D190" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F190" s="12">
+        <v>773122246</v>
+      </c>
+      <c r="G190" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H190" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I190" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K190" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L190" s="12">
+        <v>25</v>
+      </c>
+      <c r="M190" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N190" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O190" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P190" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A191" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B191" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D191" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F191" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G191" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H191" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J191" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K191" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L191" s="12">
+        <v>25</v>
+      </c>
+      <c r="M191" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N191" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O191" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P191" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A192" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D192" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="F192" s="12">
+        <v>775079426</v>
+      </c>
+      <c r="G192" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H192" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J192" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K192" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L192" s="12">
+        <v>1</v>
+      </c>
+      <c r="M192" s="13">
+        <v>6000</v>
+      </c>
+      <c r="N192" s="13">
+        <v>6000</v>
+      </c>
+      <c r="O192" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P192" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A193" s="11">
+        <v>46097</v>
+      </c>
+      <c r="B193" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D193" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F193" s="12">
+        <v>776634479</v>
+      </c>
+      <c r="G193" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H193" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I193" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J193" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K193" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L193" s="12">
+        <v>30</v>
+      </c>
+      <c r="M193" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N193" s="13">
+        <v>1620000</v>
+      </c>
+      <c r="O193" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P193" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A194" s="11">
+        <v>46099</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E194" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F194" s="12">
+        <v>774993694</v>
+      </c>
+      <c r="G194" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H194" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I194" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J194" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K194" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L194" s="12">
+        <v>50</v>
+      </c>
+      <c r="M194" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N194" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="O194" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
+      </c>
+      <c r="P194" s="15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4794A7E9-7137-4013-805A-B62EA94FC78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B71F2A-85B4-4BB3-BC52-CF6D7EE9E694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="237">
   <si>
     <t>Date</t>
   </si>
@@ -718,6 +718,33 @@
   </si>
   <si>
     <t>Abdou Rakhmane Baldé</t>
+  </si>
+  <si>
+    <t>18safar</t>
+  </si>
+  <si>
+    <t>Je vais essayer avec les 10</t>
+  </si>
+  <si>
+    <t>Khadim Lo</t>
+  </si>
+  <si>
+    <t>Khdime sylla</t>
+  </si>
+  <si>
+    <t>Kamlac Junior BLE cereal 50g x 10 x 8 sachet</t>
+  </si>
+  <si>
+    <t>Chocolat Jaune 10gx60pcsx6 boites</t>
+  </si>
+  <si>
+    <t>Aziz</t>
+  </si>
+  <si>
+    <t>Matar Gaye</t>
+  </si>
+  <si>
+    <t>Ndiaye &amp; Frère</t>
   </si>
 </sst>
 </file>
@@ -1132,8 +1159,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P194" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P194" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P211" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P211" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1446,7 +1473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P194"/>
+  <dimension ref="A1:P211"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -10773,781 +10800,1665 @@
       </c>
     </row>
     <row r="180" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A180" s="11">
+      <c r="A180" s="8">
         <v>46098</v>
       </c>
-      <c r="B180" s="12" t="s">
+      <c r="B180" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C180" s="12" t="s">
+      <c r="C180" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D180" s="12" t="s">
+      <c r="D180" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E180" s="12" t="s">
+      <c r="E180" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="F180" s="12">
+      <c r="F180" s="9">
         <v>775113886</v>
       </c>
-      <c r="G180" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H180" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I180" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J180" s="12" t="s">
+      <c r="G180" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H180" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J180" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K180" s="12" t="s">
+      <c r="K180" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L180" s="12">
+      <c r="L180" s="9">
         <v>25</v>
       </c>
-      <c r="M180" s="13">
+      <c r="M180" s="10">
         <v>9250</v>
       </c>
-      <c r="N180" s="13">
+      <c r="N180" s="10">
         <v>231250</v>
       </c>
-      <c r="O180" s="14" t="str">
+      <c r="O180" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P180" s="15" t="str">
+      <c r="P180" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A181" s="11">
+      <c r="A181" s="8">
         <v>46098</v>
       </c>
-      <c r="B181" s="12" t="s">
+      <c r="B181" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C181" s="12" t="s">
+      <c r="C181" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D181" s="12" t="s">
+      <c r="D181" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="E181" s="12" t="s">
+      <c r="E181" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F181" s="12">
+      <c r="F181" s="9">
         <v>775626425</v>
       </c>
-      <c r="G181" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H181" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I181" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J181" s="12" t="s">
+      <c r="G181" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H181" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J181" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K181" s="12" t="s">
+      <c r="K181" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L181" s="12">
+      <c r="L181" s="9">
         <v>3</v>
       </c>
-      <c r="M181" s="13">
+      <c r="M181" s="10">
         <v>18000</v>
       </c>
-      <c r="N181" s="13">
+      <c r="N181" s="10">
         <v>54000</v>
       </c>
-      <c r="O181" s="14" t="str">
+      <c r="O181" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P181" s="15" t="str">
+      <c r="P181" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="182" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A182" s="11">
+      <c r="A182" s="8">
         <v>46098</v>
       </c>
-      <c r="B182" s="12" t="s">
+      <c r="B182" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C182" s="12" t="s">
+      <c r="C182" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D182" s="12" t="s">
+      <c r="D182" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E182" s="12" t="s">
+      <c r="E182" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="F182" s="12">
+      <c r="F182" s="9">
         <v>786361148</v>
       </c>
-      <c r="G182" s="12" t="s">
+      <c r="G182" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="H182" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I182" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J182" s="12" t="s">
+      <c r="H182" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J182" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K182" s="12" t="s">
+      <c r="K182" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L182" s="12">
+      <c r="L182" s="9">
         <v>2</v>
       </c>
-      <c r="M182" s="13">
+      <c r="M182" s="10">
         <v>18000</v>
       </c>
-      <c r="N182" s="13">
+      <c r="N182" s="10">
         <v>36000</v>
       </c>
-      <c r="O182" s="14" t="str">
+      <c r="O182" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P182" s="15" t="str">
+      <c r="P182" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="183" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A183" s="11">
+      <c r="A183" s="8">
         <v>46098</v>
       </c>
-      <c r="B183" s="12" t="s">
+      <c r="B183" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C183" s="12" t="s">
+      <c r="C183" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D183" s="12" t="s">
+      <c r="D183" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E183" s="12" t="s">
+      <c r="E183" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F183" s="12">
+      <c r="F183" s="9">
         <v>770158721</v>
       </c>
-      <c r="G183" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H183" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I183" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J183" s="12" t="s">
+      <c r="G183" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H183" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J183" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K183" s="12" t="s">
+      <c r="K183" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="L183" s="12">
+      <c r="L183" s="9">
         <v>25</v>
       </c>
-      <c r="M183" s="13">
+      <c r="M183" s="10">
         <v>18000</v>
       </c>
-      <c r="N183" s="13">
+      <c r="N183" s="10">
         <v>450000</v>
       </c>
-      <c r="O183" s="14" t="str">
+      <c r="O183" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P183" s="15" t="str">
+      <c r="P183" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="184" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A184" s="11">
+      <c r="A184" s="8">
         <v>46098</v>
       </c>
-      <c r="B184" s="12" t="s">
+      <c r="B184" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C184" s="12" t="s">
+      <c r="C184" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D184" s="12" t="s">
+      <c r="D184" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E184" s="12" t="s">
+      <c r="E184" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F184" s="12">
+      <c r="F184" s="9">
         <v>770158721</v>
       </c>
-      <c r="G184" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H184" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I184" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J184" s="12" t="s">
+      <c r="G184" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J184" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K184" s="12" t="s">
+      <c r="K184" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L184" s="12">
+      <c r="L184" s="9">
         <v>25</v>
       </c>
-      <c r="M184" s="13">
+      <c r="M184" s="10">
         <v>18000</v>
       </c>
-      <c r="N184" s="13">
+      <c r="N184" s="10">
         <v>450000</v>
       </c>
-      <c r="O184" s="14" t="str">
+      <c r="O184" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P184" s="15" t="str">
+      <c r="P184" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="185" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A185" s="11">
+      <c r="A185" s="8">
         <v>46098</v>
       </c>
-      <c r="B185" s="12" t="s">
+      <c r="B185" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C185" s="12" t="s">
+      <c r="C185" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D185" s="12" t="s">
+      <c r="D185" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E185" s="12" t="s">
+      <c r="E185" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="F185" s="12">
+      <c r="F185" s="9">
         <v>775649041</v>
       </c>
-      <c r="G185" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H185" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I185" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J185" s="12" t="s">
+      <c r="G185" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H185" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J185" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K185" s="12" t="s">
+      <c r="K185" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L185" s="12">
+      <c r="L185" s="9">
         <v>1</v>
       </c>
-      <c r="M185" s="13">
+      <c r="M185" s="10">
         <v>18000</v>
       </c>
-      <c r="N185" s="13">
+      <c r="N185" s="10">
         <v>18000</v>
       </c>
-      <c r="O185" s="14" t="str">
+      <c r="O185" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P185" s="15" t="str">
+      <c r="P185" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="186" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A186" s="11">
+      <c r="A186" s="8">
         <v>46098</v>
       </c>
-      <c r="B186" s="12" t="s">
+      <c r="B186" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C186" s="12" t="s">
+      <c r="C186" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D186" s="12" t="s">
+      <c r="D186" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E186" s="12" t="s">
+      <c r="E186" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F186" s="12">
+      <c r="F186" s="9">
         <v>784785900</v>
       </c>
-      <c r="G186" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H186" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I186" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J186" s="12" t="s">
+      <c r="G186" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H186" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J186" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K186" s="12" t="s">
+      <c r="K186" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L186" s="12">
+      <c r="L186" s="9">
         <v>9</v>
       </c>
-      <c r="M186" s="13">
+      <c r="M186" s="10">
         <v>9250</v>
       </c>
-      <c r="N186" s="13">
+      <c r="N186" s="10">
         <v>83250</v>
       </c>
-      <c r="O186" s="14" t="str">
+      <c r="O186" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P186" s="15" t="str">
+      <c r="P186" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="187" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A187" s="11">
+      <c r="A187" s="8">
         <v>46098</v>
       </c>
-      <c r="B187" s="12" t="s">
+      <c r="B187" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C187" s="12" t="s">
+      <c r="C187" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D187" s="12" t="s">
+      <c r="D187" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E187" s="12" t="s">
+      <c r="E187" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F187" s="12">
+      <c r="F187" s="9">
         <v>784785900</v>
       </c>
-      <c r="G187" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H187" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I187" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J187" s="12" t="s">
+      <c r="G187" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H187" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J187" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K187" s="12" t="s">
+      <c r="K187" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L187" s="12">
+      <c r="L187" s="9">
         <v>7</v>
       </c>
-      <c r="M187" s="13">
+      <c r="M187" s="10">
         <v>30000</v>
       </c>
-      <c r="N187" s="13">
+      <c r="N187" s="10">
         <v>210000</v>
       </c>
-      <c r="O187" s="14" t="str">
+      <c r="O187" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P187" s="15" t="str">
+      <c r="P187" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="188" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A188" s="11">
+      <c r="A188" s="8">
         <v>46098</v>
       </c>
-      <c r="B188" s="12" t="s">
+      <c r="B188" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C188" s="12" t="s">
+      <c r="C188" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D188" s="12" t="s">
+      <c r="D188" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E188" s="12" t="s">
+      <c r="E188" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F188" s="12">
+      <c r="F188" s="9">
         <v>784785900</v>
       </c>
-      <c r="G188" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H188" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I188" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J188" s="12" t="s">
+      <c r="G188" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H188" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J188" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K188" s="12" t="s">
+      <c r="K188" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L188" s="12">
+      <c r="L188" s="9">
         <v>4</v>
       </c>
-      <c r="M188" s="13">
+      <c r="M188" s="10">
         <v>19500</v>
       </c>
-      <c r="N188" s="13">
+      <c r="N188" s="10">
         <v>78000</v>
       </c>
-      <c r="O188" s="14" t="str">
+      <c r="O188" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P188" s="15" t="str">
+      <c r="P188" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="189" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A189" s="11">
+      <c r="A189" s="8">
         <v>46098</v>
       </c>
-      <c r="B189" s="12" t="s">
+      <c r="B189" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C189" s="12" t="s">
+      <c r="C189" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D189" s="12" t="s">
+      <c r="D189" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E189" s="12" t="s">
+      <c r="E189" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F189" s="12">
+      <c r="F189" s="9">
         <v>784785900</v>
       </c>
-      <c r="G189" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H189" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I189" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J189" s="12" t="s">
+      <c r="G189" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J189" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K189" s="12" t="s">
+      <c r="K189" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L189" s="12">
+      <c r="L189" s="9">
         <v>33</v>
       </c>
-      <c r="M189" s="13">
+      <c r="M189" s="10">
         <v>26000</v>
       </c>
-      <c r="N189" s="13">
+      <c r="N189" s="10">
         <v>858000</v>
       </c>
-      <c r="O189" s="14" t="str">
+      <c r="O189" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P189" s="15" t="str">
+      <c r="P189" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="190" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A190" s="11">
+      <c r="A190" s="8">
         <v>46097</v>
       </c>
-      <c r="B190" s="12" t="s">
+      <c r="B190" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C190" s="12" t="s">
+      <c r="C190" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D190" s="12" t="s">
+      <c r="D190" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E190" s="12" t="s">
+      <c r="E190" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F190" s="12">
+      <c r="F190" s="9">
         <v>773122246</v>
       </c>
-      <c r="G190" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H190" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I190" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J190" s="12" t="s">
+      <c r="G190" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H190" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J190" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K190" s="12" t="s">
+      <c r="K190" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L190" s="12">
+      <c r="L190" s="9">
         <v>25</v>
       </c>
-      <c r="M190" s="13">
+      <c r="M190" s="10">
         <v>9250</v>
       </c>
-      <c r="N190" s="13">
+      <c r="N190" s="10">
         <v>231250</v>
       </c>
-      <c r="O190" s="14" t="str">
+      <c r="O190" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P190" s="15" t="str">
+      <c r="P190" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="191" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A191" s="11">
+      <c r="A191" s="8">
         <v>46097</v>
       </c>
-      <c r="B191" s="12" t="s">
+      <c r="B191" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C191" s="12" t="s">
+      <c r="C191" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D191" s="12" t="s">
+      <c r="D191" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E191" s="12" t="s">
+      <c r="E191" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F191" s="12">
+      <c r="F191" s="9">
         <v>775544532</v>
       </c>
-      <c r="G191" s="12" t="s">
+      <c r="G191" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H191" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I191" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J191" s="12" t="s">
+      <c r="H191" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J191" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K191" s="12" t="s">
+      <c r="K191" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L191" s="12">
+      <c r="L191" s="9">
         <v>25</v>
       </c>
-      <c r="M191" s="13">
+      <c r="M191" s="10">
         <v>26000</v>
       </c>
-      <c r="N191" s="13">
+      <c r="N191" s="10">
         <v>650000</v>
       </c>
-      <c r="O191" s="14" t="str">
+      <c r="O191" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P191" s="15" t="str">
+      <c r="P191" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="192" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A192" s="11">
+      <c r="A192" s="8">
         <v>46097</v>
       </c>
-      <c r="B192" s="12" t="s">
+      <c r="B192" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C192" s="12" t="s">
+      <c r="C192" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D192" s="12" t="s">
+      <c r="D192" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E192" s="12" t="s">
+      <c r="E192" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F192" s="12">
+      <c r="F192" s="9">
         <v>775079426</v>
       </c>
-      <c r="G192" s="12" t="s">
+      <c r="G192" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H192" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I192" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J192" s="12" t="s">
+      <c r="H192" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J192" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K192" s="12" t="s">
+      <c r="K192" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L192" s="12">
+      <c r="L192" s="9">
         <v>1</v>
       </c>
-      <c r="M192" s="13">
+      <c r="M192" s="10">
         <v>6000</v>
       </c>
-      <c r="N192" s="13">
+      <c r="N192" s="10">
         <v>6000</v>
       </c>
-      <c r="O192" s="14" t="str">
+      <c r="O192" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P192" s="15" t="str">
+      <c r="P192" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="193" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A193" s="11">
+      <c r="A193" s="8">
         <v>46097</v>
       </c>
-      <c r="B193" s="12" t="s">
+      <c r="B193" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C193" s="12" t="s">
+      <c r="C193" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D193" s="12" t="s">
+      <c r="D193" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E193" s="12" t="s">
+      <c r="E193" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F193" s="12">
+      <c r="F193" s="9">
         <v>776634479</v>
       </c>
-      <c r="G193" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H193" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I193" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J193" s="12" t="s">
+      <c r="G193" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H193" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J193" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K193" s="12" t="s">
+      <c r="K193" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L193" s="12">
+      <c r="L193" s="9">
         <v>30</v>
       </c>
-      <c r="M193" s="13">
+      <c r="M193" s="10">
         <v>54000</v>
       </c>
-      <c r="N193" s="13">
+      <c r="N193" s="10">
         <v>1620000</v>
       </c>
-      <c r="O193" s="14" t="str">
+      <c r="O193" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P193" s="15" t="str">
+      <c r="P193" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A194" s="11">
+      <c r="A194" s="8">
         <v>46099</v>
       </c>
-      <c r="B194" s="12" t="s">
+      <c r="B194" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C194" s="12" t="s">
+      <c r="C194" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D194" s="12" t="s">
+      <c r="D194" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E194" s="12" t="s">
+      <c r="E194" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="F194" s="12">
+      <c r="F194" s="9">
         <v>774993694</v>
       </c>
-      <c r="G194" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H194" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I194" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J194" s="12" t="s">
+      <c r="G194" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H194" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J194" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K194" s="12" t="s">
+      <c r="K194" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L194" s="12">
+      <c r="L194" s="9">
         <v>50</v>
       </c>
-      <c r="M194" s="13">
+      <c r="M194" s="10">
         <v>26000</v>
       </c>
-      <c r="N194" s="13">
+      <c r="N194" s="10">
         <v>1300000</v>
       </c>
-      <c r="O194" s="14" t="str">
+      <c r="O194" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S12</v>
       </c>
-      <c r="P194" s="15" t="str">
+      <c r="P194" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A195" s="11">
+        <v>46106</v>
+      </c>
+      <c r="B195" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D195" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E195" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F195" s="12">
+        <v>773531341</v>
+      </c>
+      <c r="G195" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I195" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J195" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K195" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L195" s="12">
+        <v>200</v>
+      </c>
+      <c r="M195" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N195" s="13">
+        <v>5200000</v>
+      </c>
+      <c r="O195" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P195" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A196" s="11">
+        <v>46106</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F196" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G196" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H196" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J196" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K196" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L196" s="12">
+        <v>25</v>
+      </c>
+      <c r="M196" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N196" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O196" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P196" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A197" s="11">
+        <v>46106</v>
+      </c>
+      <c r="B197" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F197" s="12">
+        <v>780172121</v>
+      </c>
+      <c r="G197" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H197" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J197" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="K197" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L197" s="12">
+        <v>10</v>
+      </c>
+      <c r="M197" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N197" s="13">
+        <v>540000</v>
+      </c>
+      <c r="O197" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P197" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A198" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="F198" s="12">
+        <v>770217868</v>
+      </c>
+      <c r="G198" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H198" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I198" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J198" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K198" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L198" s="12">
+        <v>25</v>
+      </c>
+      <c r="M198" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N198" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O198" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P198" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A199" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B199" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E199" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="F199" s="12">
+        <v>776317469</v>
+      </c>
+      <c r="G199" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H199" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I199" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J199" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K199" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L199" s="12">
+        <v>25</v>
+      </c>
+      <c r="M199" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N199" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O199" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P199" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A200" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E200" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F200" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G200" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H200" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K200" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L200" s="12">
+        <v>25</v>
+      </c>
+      <c r="M200" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N200" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O200" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P200" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A201" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B201" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F201" s="12">
+        <v>776634479</v>
+      </c>
+      <c r="G201" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H201" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I201" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J201" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K201" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L201" s="12">
+        <v>1</v>
+      </c>
+      <c r="M201" s="13">
+        <v>15000</v>
+      </c>
+      <c r="N201" s="13">
+        <v>15000</v>
+      </c>
+      <c r="O201" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P201" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A202" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D202" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E202" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F202" s="12">
+        <v>776634479</v>
+      </c>
+      <c r="G202" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H202" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I202" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J202" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K202" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="L202" s="12">
+        <v>1</v>
+      </c>
+      <c r="M202" s="13">
+        <v>10000</v>
+      </c>
+      <c r="N202" s="13">
+        <v>10000</v>
+      </c>
+      <c r="O202" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P202" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A203" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B203" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D203" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E203" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F203" s="12">
+        <v>777262311</v>
+      </c>
+      <c r="G203" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H203" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I203" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J203" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K203" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L203" s="12">
+        <v>2</v>
+      </c>
+      <c r="M203" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N203" s="13">
+        <v>108000</v>
+      </c>
+      <c r="O203" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P203" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A204" s="11">
+        <v>46108</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D204" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E204" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F204" s="12">
+        <v>776634479</v>
+      </c>
+      <c r="G204" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H204" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K204" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L204" s="12">
+        <v>2</v>
+      </c>
+      <c r="M204" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N204" s="13">
+        <v>108000</v>
+      </c>
+      <c r="O204" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P204" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A205" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B205" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D205" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E205" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F205" s="12">
+        <v>766657313</v>
+      </c>
+      <c r="G205" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H205" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J205" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K205" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L205" s="12">
+        <v>30</v>
+      </c>
+      <c r="M205" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N205" s="13">
+        <v>780000</v>
+      </c>
+      <c r="O205" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P205" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A206" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D206" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F206" s="12">
+        <v>766657313</v>
+      </c>
+      <c r="G206" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H206" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I206" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K206" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L206" s="12">
+        <v>1</v>
+      </c>
+      <c r="M206" s="13">
+        <v>28000</v>
+      </c>
+      <c r="N206" s="13">
+        <v>28000</v>
+      </c>
+      <c r="O206" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P206" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A207" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B207" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E207" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F207" s="12">
+        <v>773199049</v>
+      </c>
+      <c r="G207" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H207" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I207" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J207" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K207" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L207" s="12">
+        <v>25</v>
+      </c>
+      <c r="M207" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N207" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O207" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P207" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A208" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D208" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E208" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F208" s="12">
+        <v>773817561</v>
+      </c>
+      <c r="G208" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H208" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I208" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K208" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L208" s="12">
+        <v>3</v>
+      </c>
+      <c r="M208" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N208" s="13">
+        <v>162000</v>
+      </c>
+      <c r="O208" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P208" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A209" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B209" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F209" s="12">
+        <v>775894235</v>
+      </c>
+      <c r="G209" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H209" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I209" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J209" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K209" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L209" s="12">
+        <v>3</v>
+      </c>
+      <c r="M209" s="13">
+        <v>54000</v>
+      </c>
+      <c r="N209" s="13">
+        <v>162000</v>
+      </c>
+      <c r="O209" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P209" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A210" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D210" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E210" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F210" s="12">
+        <v>773122246</v>
+      </c>
+      <c r="G210" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H210" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I210" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K210" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L210" s="12">
+        <v>25</v>
+      </c>
+      <c r="M210" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N210" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O210" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P210" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A211" s="11">
+        <v>46107</v>
+      </c>
+      <c r="B211" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D211" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="F211" s="12">
+        <v>772313191</v>
+      </c>
+      <c r="G211" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H211" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J211" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K211" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L211" s="12">
+        <v>300</v>
+      </c>
+      <c r="M211" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N211" s="13">
+        <v>7800000</v>
+      </c>
+      <c r="O211" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S13</v>
+      </c>
+      <c r="P211" s="15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B71F2A-85B4-4BB3-BC52-CF6D7EE9E694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1B2E42-3CE7-4B7B-94E2-79DC1891F0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="238">
   <si>
     <t>Date</t>
   </si>
@@ -745,6 +745,9 @@
   </si>
   <si>
     <t>Ndiaye &amp; Frère</t>
+  </si>
+  <si>
+    <t>S13</t>
   </si>
 </sst>
 </file>
@@ -812,7 +815,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -842,19 +845,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10842,9 +10832,8 @@
       <c r="N180" s="10">
         <v>231250</v>
       </c>
-      <c r="O180" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O180" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P180" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -10894,9 +10883,8 @@
       <c r="N181" s="10">
         <v>54000</v>
       </c>
-      <c r="O181" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O181" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P181" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -10946,9 +10934,8 @@
       <c r="N182" s="10">
         <v>36000</v>
       </c>
-      <c r="O182" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O182" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P182" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -10998,9 +10985,8 @@
       <c r="N183" s="10">
         <v>450000</v>
       </c>
-      <c r="O183" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O183" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P183" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11050,9 +11036,8 @@
       <c r="N184" s="10">
         <v>450000</v>
       </c>
-      <c r="O184" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O184" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P184" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11102,9 +11087,8 @@
       <c r="N185" s="10">
         <v>18000</v>
       </c>
-      <c r="O185" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O185" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P185" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11154,9 +11138,8 @@
       <c r="N186" s="10">
         <v>83250</v>
       </c>
-      <c r="O186" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O186" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P186" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11206,9 +11189,8 @@
       <c r="N187" s="10">
         <v>210000</v>
       </c>
-      <c r="O187" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O187" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P187" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11258,9 +11240,8 @@
       <c r="N188" s="10">
         <v>78000</v>
       </c>
-      <c r="O188" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O188" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P188" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11310,9 +11291,8 @@
       <c r="N189" s="10">
         <v>858000</v>
       </c>
-      <c r="O189" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O189" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P189" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11362,9 +11342,8 @@
       <c r="N190" s="10">
         <v>231250</v>
       </c>
-      <c r="O190" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O190" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P190" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11414,9 +11393,8 @@
       <c r="N191" s="10">
         <v>650000</v>
       </c>
-      <c r="O191" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O191" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P191" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11466,9 +11444,8 @@
       <c r="N192" s="10">
         <v>6000</v>
       </c>
-      <c r="O192" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O192" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P192" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11518,9 +11495,8 @@
       <c r="N193" s="10">
         <v>1620000</v>
       </c>
-      <c r="O193" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O193" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P193" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11570,9 +11546,8 @@
       <c r="N194" s="10">
         <v>1300000</v>
       </c>
-      <c r="O194" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S12</v>
+      <c r="O194" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="P194" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11580,885 +11555,885 @@
       </c>
     </row>
     <row r="195" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A195" s="11">
+      <c r="A195" s="8">
         <v>46106</v>
       </c>
-      <c r="B195" s="12" t="s">
+      <c r="B195" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C195" s="12" t="s">
+      <c r="C195" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D195" s="12" t="s">
+      <c r="D195" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E195" s="12" t="s">
+      <c r="E195" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F195" s="12">
+      <c r="F195" s="9">
         <v>773531341</v>
       </c>
-      <c r="G195" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H195" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I195" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J195" s="12" t="s">
+      <c r="G195" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J195" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K195" s="12" t="s">
+      <c r="K195" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L195" s="12">
+      <c r="L195" s="9">
         <v>200</v>
       </c>
-      <c r="M195" s="13">
+      <c r="M195" s="10">
         <v>26000</v>
       </c>
-      <c r="N195" s="13">
+      <c r="N195" s="10">
         <v>5200000</v>
       </c>
-      <c r="O195" s="14" t="str">
+      <c r="O195" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P195" s="15" t="str">
+      <c r="P195" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="196" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A196" s="11">
+      <c r="A196" s="8">
         <v>46106</v>
       </c>
-      <c r="B196" s="12" t="s">
+      <c r="B196" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C196" s="12" t="s">
+      <c r="C196" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D196" s="12" t="s">
+      <c r="D196" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E196" s="12" t="s">
+      <c r="E196" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F196" s="12">
+      <c r="F196" s="9">
         <v>775544532</v>
       </c>
-      <c r="G196" s="12" t="s">
+      <c r="G196" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H196" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I196" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J196" s="12" t="s">
+      <c r="H196" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J196" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K196" s="12" t="s">
+      <c r="K196" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L196" s="12">
+      <c r="L196" s="9">
         <v>25</v>
       </c>
-      <c r="M196" s="13">
+      <c r="M196" s="10">
         <v>26000</v>
       </c>
-      <c r="N196" s="13">
+      <c r="N196" s="10">
         <v>650000</v>
       </c>
-      <c r="O196" s="14" t="str">
+      <c r="O196" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P196" s="15" t="str">
+      <c r="P196" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="197" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A197" s="11">
+      <c r="A197" s="8">
         <v>46106</v>
       </c>
-      <c r="B197" s="12" t="s">
+      <c r="B197" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C197" s="12" t="s">
+      <c r="C197" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D197" s="12" t="s">
+      <c r="D197" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E197" s="12" t="s">
+      <c r="E197" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="F197" s="12">
+      <c r="F197" s="9">
         <v>780172121</v>
       </c>
-      <c r="G197" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H197" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I197" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J197" s="12" t="s">
+      <c r="G197" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H197" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J197" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="K197" s="12" t="s">
+      <c r="K197" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L197" s="12">
+      <c r="L197" s="9">
         <v>10</v>
       </c>
-      <c r="M197" s="13">
+      <c r="M197" s="10">
         <v>54000</v>
       </c>
-      <c r="N197" s="13">
+      <c r="N197" s="10">
         <v>540000</v>
       </c>
-      <c r="O197" s="14" t="str">
+      <c r="O197" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P197" s="15" t="str">
+      <c r="P197" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="198" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A198" s="11">
+      <c r="A198" s="8">
         <v>46108</v>
       </c>
-      <c r="B198" s="12" t="s">
+      <c r="B198" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C198" s="12" t="s">
+      <c r="C198" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D198" s="12" t="s">
+      <c r="D198" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E198" s="12" t="s">
+      <c r="E198" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="F198" s="12">
+      <c r="F198" s="9">
         <v>770217868</v>
       </c>
-      <c r="G198" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H198" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I198" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J198" s="12" t="s">
+      <c r="G198" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H198" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J198" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K198" s="12" t="s">
+      <c r="K198" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L198" s="12">
+      <c r="L198" s="9">
         <v>25</v>
       </c>
-      <c r="M198" s="13">
+      <c r="M198" s="10">
         <v>19500</v>
       </c>
-      <c r="N198" s="13">
+      <c r="N198" s="10">
         <v>487500</v>
       </c>
-      <c r="O198" s="14" t="str">
+      <c r="O198" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P198" s="15" t="str">
+      <c r="P198" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="199" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A199" s="11">
+      <c r="A199" s="8">
         <v>46108</v>
       </c>
-      <c r="B199" s="12" t="s">
+      <c r="B199" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C199" s="12" t="s">
+      <c r="C199" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D199" s="12" t="s">
+      <c r="D199" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E199" s="12" t="s">
+      <c r="E199" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="F199" s="12">
+      <c r="F199" s="9">
         <v>776317469</v>
       </c>
-      <c r="G199" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H199" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I199" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J199" s="12" t="s">
+      <c r="G199" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H199" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J199" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K199" s="12" t="s">
+      <c r="K199" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L199" s="12">
+      <c r="L199" s="9">
         <v>25</v>
       </c>
-      <c r="M199" s="13">
+      <c r="M199" s="10">
         <v>19500</v>
       </c>
-      <c r="N199" s="13">
+      <c r="N199" s="10">
         <v>487500</v>
       </c>
-      <c r="O199" s="14" t="str">
+      <c r="O199" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P199" s="15" t="str">
+      <c r="P199" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="200" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A200" s="11">
+      <c r="A200" s="8">
         <v>46108</v>
       </c>
-      <c r="B200" s="12" t="s">
+      <c r="B200" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C200" s="12" t="s">
+      <c r="C200" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D200" s="12" t="s">
+      <c r="D200" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E200" s="12" t="s">
+      <c r="E200" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F200" s="12">
+      <c r="F200" s="9">
         <v>775544532</v>
       </c>
-      <c r="G200" s="12" t="s">
+      <c r="G200" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H200" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I200" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J200" s="12" t="s">
+      <c r="H200" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J200" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K200" s="12" t="s">
+      <c r="K200" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L200" s="12">
+      <c r="L200" s="9">
         <v>25</v>
       </c>
-      <c r="M200" s="13">
+      <c r="M200" s="10">
         <v>26000</v>
       </c>
-      <c r="N200" s="13">
+      <c r="N200" s="10">
         <v>650000</v>
       </c>
-      <c r="O200" s="14" t="str">
+      <c r="O200" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P200" s="15" t="str">
+      <c r="P200" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="201" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A201" s="11">
+      <c r="A201" s="8">
         <v>46108</v>
       </c>
-      <c r="B201" s="12" t="s">
+      <c r="B201" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C201" s="12" t="s">
+      <c r="C201" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D201" s="12" t="s">
+      <c r="D201" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E201" s="12" t="s">
+      <c r="E201" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F201" s="12">
+      <c r="F201" s="9">
         <v>776634479</v>
       </c>
-      <c r="G201" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H201" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I201" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J201" s="12" t="s">
+      <c r="G201" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H201" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J201" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K201" s="12" t="s">
+      <c r="K201" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="L201" s="12">
+      <c r="L201" s="9">
         <v>1</v>
       </c>
-      <c r="M201" s="13">
+      <c r="M201" s="10">
         <v>15000</v>
       </c>
-      <c r="N201" s="13">
+      <c r="N201" s="10">
         <v>15000</v>
       </c>
-      <c r="O201" s="14" t="str">
+      <c r="O201" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P201" s="15" t="str">
+      <c r="P201" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="202" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A202" s="11">
+      <c r="A202" s="8">
         <v>46108</v>
       </c>
-      <c r="B202" s="12" t="s">
+      <c r="B202" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C202" s="12" t="s">
+      <c r="C202" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D202" s="12" t="s">
+      <c r="D202" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E202" s="12" t="s">
+      <c r="E202" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F202" s="12">
+      <c r="F202" s="9">
         <v>776634479</v>
       </c>
-      <c r="G202" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H202" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I202" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J202" s="12" t="s">
+      <c r="G202" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H202" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J202" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K202" s="12" t="s">
+      <c r="K202" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="L202" s="12">
+      <c r="L202" s="9">
         <v>1</v>
       </c>
-      <c r="M202" s="13">
+      <c r="M202" s="10">
         <v>10000</v>
       </c>
-      <c r="N202" s="13">
+      <c r="N202" s="10">
         <v>10000</v>
       </c>
-      <c r="O202" s="14" t="str">
+      <c r="O202" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P202" s="15" t="str">
+      <c r="P202" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="203" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A203" s="11">
+      <c r="A203" s="8">
         <v>46108</v>
       </c>
-      <c r="B203" s="12" t="s">
+      <c r="B203" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C203" s="12" t="s">
+      <c r="C203" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D203" s="12" t="s">
+      <c r="D203" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E203" s="12" t="s">
+      <c r="E203" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F203" s="12">
+      <c r="F203" s="9">
         <v>777262311</v>
       </c>
-      <c r="G203" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H203" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I203" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J203" s="12" t="s">
+      <c r="G203" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H203" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J203" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K203" s="12" t="s">
+      <c r="K203" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L203" s="12">
+      <c r="L203" s="9">
         <v>2</v>
       </c>
-      <c r="M203" s="13">
+      <c r="M203" s="10">
         <v>54000</v>
       </c>
-      <c r="N203" s="13">
+      <c r="N203" s="10">
         <v>108000</v>
       </c>
-      <c r="O203" s="14" t="str">
+      <c r="O203" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P203" s="15" t="str">
+      <c r="P203" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="204" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A204" s="11">
+      <c r="A204" s="8">
         <v>46108</v>
       </c>
-      <c r="B204" s="12" t="s">
+      <c r="B204" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C204" s="12" t="s">
+      <c r="C204" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D204" s="12" t="s">
+      <c r="D204" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E204" s="12" t="s">
+      <c r="E204" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F204" s="12">
+      <c r="F204" s="9">
         <v>776634479</v>
       </c>
-      <c r="G204" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H204" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I204" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J204" s="12" t="s">
+      <c r="G204" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H204" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J204" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K204" s="12" t="s">
+      <c r="K204" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L204" s="12">
+      <c r="L204" s="9">
         <v>2</v>
       </c>
-      <c r="M204" s="13">
+      <c r="M204" s="10">
         <v>54000</v>
       </c>
-      <c r="N204" s="13">
+      <c r="N204" s="10">
         <v>108000</v>
       </c>
-      <c r="O204" s="14" t="str">
+      <c r="O204" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P204" s="15" t="str">
+      <c r="P204" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A205" s="11">
+      <c r="A205" s="8">
         <v>46107</v>
       </c>
-      <c r="B205" s="12" t="s">
+      <c r="B205" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C205" s="12" t="s">
+      <c r="C205" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D205" s="12" t="s">
+      <c r="D205" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E205" s="12" t="s">
+      <c r="E205" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="F205" s="12">
+      <c r="F205" s="9">
         <v>766657313</v>
       </c>
-      <c r="G205" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H205" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I205" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J205" s="12" t="s">
+      <c r="G205" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H205" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J205" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K205" s="12" t="s">
+      <c r="K205" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L205" s="12">
+      <c r="L205" s="9">
         <v>30</v>
       </c>
-      <c r="M205" s="13">
+      <c r="M205" s="10">
         <v>26000</v>
       </c>
-      <c r="N205" s="13">
+      <c r="N205" s="10">
         <v>780000</v>
       </c>
-      <c r="O205" s="14" t="str">
+      <c r="O205" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P205" s="15" t="str">
+      <c r="P205" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="206" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A206" s="11">
+      <c r="A206" s="8">
         <v>46107</v>
       </c>
-      <c r="B206" s="12" t="s">
+      <c r="B206" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C206" s="12" t="s">
+      <c r="C206" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D206" s="12" t="s">
+      <c r="D206" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E206" s="12" t="s">
+      <c r="E206" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="F206" s="12">
+      <c r="F206" s="9">
         <v>766657313</v>
       </c>
-      <c r="G206" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H206" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I206" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J206" s="12" t="s">
+      <c r="G206" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H206" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J206" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K206" s="12" t="s">
+      <c r="K206" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L206" s="12">
+      <c r="L206" s="9">
         <v>1</v>
       </c>
-      <c r="M206" s="13">
+      <c r="M206" s="10">
         <v>28000</v>
       </c>
-      <c r="N206" s="13">
+      <c r="N206" s="10">
         <v>28000</v>
       </c>
-      <c r="O206" s="14" t="str">
+      <c r="O206" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P206" s="15" t="str">
+      <c r="P206" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="207" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A207" s="11">
+      <c r="A207" s="8">
         <v>46107</v>
       </c>
-      <c r="B207" s="12" t="s">
+      <c r="B207" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C207" s="12" t="s">
+      <c r="C207" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D207" s="12" t="s">
+      <c r="D207" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E207" s="12" t="s">
+      <c r="E207" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="F207" s="12">
+      <c r="F207" s="9">
         <v>773199049</v>
       </c>
-      <c r="G207" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H207" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I207" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J207" s="12" t="s">
+      <c r="G207" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H207" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J207" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K207" s="12" t="s">
+      <c r="K207" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L207" s="12">
+      <c r="L207" s="9">
         <v>25</v>
       </c>
-      <c r="M207" s="13">
+      <c r="M207" s="10">
         <v>19500</v>
       </c>
-      <c r="N207" s="13">
+      <c r="N207" s="10">
         <v>487500</v>
       </c>
-      <c r="O207" s="14" t="str">
+      <c r="O207" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P207" s="15" t="str">
+      <c r="P207" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A208" s="11">
+      <c r="A208" s="8">
         <v>46107</v>
       </c>
-      <c r="B208" s="12" t="s">
+      <c r="B208" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C208" s="12" t="s">
+      <c r="C208" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D208" s="12" t="s">
+      <c r="D208" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E208" s="12" t="s">
+      <c r="E208" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F208" s="12">
+      <c r="F208" s="9">
         <v>773817561</v>
       </c>
-      <c r="G208" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H208" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I208" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J208" s="12" t="s">
+      <c r="G208" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H208" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J208" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K208" s="12" t="s">
+      <c r="K208" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L208" s="12">
+      <c r="L208" s="9">
         <v>3</v>
       </c>
-      <c r="M208" s="13">
+      <c r="M208" s="10">
         <v>54000</v>
       </c>
-      <c r="N208" s="13">
+      <c r="N208" s="10">
         <v>162000</v>
       </c>
-      <c r="O208" s="14" t="str">
+      <c r="O208" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P208" s="15" t="str">
+      <c r="P208" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A209" s="11">
+      <c r="A209" s="8">
         <v>46107</v>
       </c>
-      <c r="B209" s="12" t="s">
+      <c r="B209" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C209" s="12" t="s">
+      <c r="C209" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D209" s="12" t="s">
+      <c r="D209" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E209" s="12" t="s">
+      <c r="E209" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F209" s="12">
+      <c r="F209" s="9">
         <v>775894235</v>
       </c>
-      <c r="G209" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H209" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I209" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J209" s="12" t="s">
+      <c r="G209" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H209" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J209" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K209" s="12" t="s">
+      <c r="K209" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L209" s="12">
+      <c r="L209" s="9">
         <v>3</v>
       </c>
-      <c r="M209" s="13">
+      <c r="M209" s="10">
         <v>54000</v>
       </c>
-      <c r="N209" s="13">
+      <c r="N209" s="10">
         <v>162000</v>
       </c>
-      <c r="O209" s="14" t="str">
+      <c r="O209" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P209" s="15" t="str">
+      <c r="P209" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A210" s="11">
+      <c r="A210" s="8">
         <v>46107</v>
       </c>
-      <c r="B210" s="12" t="s">
+      <c r="B210" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C210" s="12" t="s">
+      <c r="C210" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D210" s="12" t="s">
+      <c r="D210" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E210" s="12" t="s">
+      <c r="E210" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F210" s="12">
+      <c r="F210" s="9">
         <v>773122246</v>
       </c>
-      <c r="G210" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H210" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I210" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J210" s="12" t="s">
+      <c r="G210" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H210" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J210" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K210" s="12" t="s">
+      <c r="K210" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L210" s="12">
+      <c r="L210" s="9">
         <v>25</v>
       </c>
-      <c r="M210" s="13">
+      <c r="M210" s="10">
         <v>26000</v>
       </c>
-      <c r="N210" s="13">
+      <c r="N210" s="10">
         <v>650000</v>
       </c>
-      <c r="O210" s="14" t="str">
+      <c r="O210" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P210" s="15" t="str">
+      <c r="P210" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A211" s="11">
+      <c r="A211" s="8">
         <v>46107</v>
       </c>
-      <c r="B211" s="12" t="s">
+      <c r="B211" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C211" s="12" t="s">
+      <c r="C211" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D211" s="12" t="s">
+      <c r="D211" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E211" s="12" t="s">
+      <c r="E211" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="F211" s="12">
+      <c r="F211" s="9">
         <v>772313191</v>
       </c>
-      <c r="G211" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H211" s="12" t="s">
+      <c r="G211" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H211" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I211" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J211" s="12" t="s">
+      <c r="I211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J211" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K211" s="12" t="s">
+      <c r="K211" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L211" s="12">
+      <c r="L211" s="9">
         <v>300</v>
       </c>
-      <c r="M211" s="13">
+      <c r="M211" s="10">
         <v>26000</v>
       </c>
-      <c r="N211" s="13">
+      <c r="N211" s="10">
         <v>7800000</v>
       </c>
-      <c r="O211" s="14" t="str">
+      <c r="O211" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S13</v>
       </c>
-      <c r="P211" s="15" t="str">
+      <c r="P211" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1B2E42-3CE7-4B7B-94E2-79DC1891F0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F21E8A9-8B2B-46A9-B791-0ECF88833503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="237">
   <si>
     <t>Date</t>
   </si>
@@ -745,9 +745,6 @@
   </si>
   <si>
     <t>Ndiaye &amp; Frère</t>
-  </si>
-  <si>
-    <t>S13</t>
   </si>
 </sst>
 </file>
@@ -10832,8 +10829,9 @@
       <c r="N180" s="10">
         <v>231250</v>
       </c>
-      <c r="O180" s="7" t="s">
-        <v>237</v>
+      <c r="O180" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P180" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -10883,8 +10881,9 @@
       <c r="N181" s="10">
         <v>54000</v>
       </c>
-      <c r="O181" s="7" t="s">
-        <v>237</v>
+      <c r="O181" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P181" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -10934,8 +10933,9 @@
       <c r="N182" s="10">
         <v>36000</v>
       </c>
-      <c r="O182" s="7" t="s">
-        <v>237</v>
+      <c r="O182" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P182" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -10985,8 +10985,9 @@
       <c r="N183" s="10">
         <v>450000</v>
       </c>
-      <c r="O183" s="7" t="s">
-        <v>237</v>
+      <c r="O183" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P183" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11036,8 +11037,9 @@
       <c r="N184" s="10">
         <v>450000</v>
       </c>
-      <c r="O184" s="7" t="s">
-        <v>237</v>
+      <c r="O184" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P184" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11087,8 +11089,9 @@
       <c r="N185" s="10">
         <v>18000</v>
       </c>
-      <c r="O185" s="7" t="s">
-        <v>237</v>
+      <c r="O185" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P185" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11138,8 +11141,9 @@
       <c r="N186" s="10">
         <v>83250</v>
       </c>
-      <c r="O186" s="7" t="s">
-        <v>237</v>
+      <c r="O186" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P186" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11189,8 +11193,9 @@
       <c r="N187" s="10">
         <v>210000</v>
       </c>
-      <c r="O187" s="7" t="s">
-        <v>237</v>
+      <c r="O187" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P187" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11240,8 +11245,9 @@
       <c r="N188" s="10">
         <v>78000</v>
       </c>
-      <c r="O188" s="7" t="s">
-        <v>237</v>
+      <c r="O188" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P188" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11291,8 +11297,9 @@
       <c r="N189" s="10">
         <v>858000</v>
       </c>
-      <c r="O189" s="7" t="s">
-        <v>237</v>
+      <c r="O189" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P189" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11342,8 +11349,9 @@
       <c r="N190" s="10">
         <v>231250</v>
       </c>
-      <c r="O190" s="7" t="s">
-        <v>237</v>
+      <c r="O190" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P190" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11393,8 +11401,9 @@
       <c r="N191" s="10">
         <v>650000</v>
       </c>
-      <c r="O191" s="7" t="s">
-        <v>237</v>
+      <c r="O191" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P191" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11444,8 +11453,9 @@
       <c r="N192" s="10">
         <v>6000</v>
       </c>
-      <c r="O192" s="7" t="s">
-        <v>237</v>
+      <c r="O192" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P192" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11495,8 +11505,9 @@
       <c r="N193" s="10">
         <v>1620000</v>
       </c>
-      <c r="O193" s="7" t="s">
-        <v>237</v>
+      <c r="O193" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P193" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -11546,8 +11557,9 @@
       <c r="N194" s="10">
         <v>1300000</v>
       </c>
-      <c r="O194" s="7" t="s">
-        <v>237</v>
+      <c r="O194" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S12</v>
       </c>
       <c r="P194" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F21E8A9-8B2B-46A9-B791-0ECF88833503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BA7BC2-38C8-4A74-A49A-928D603584B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="255">
   <si>
     <t>Date</t>
   </si>
@@ -745,6 +745,60 @@
   </si>
   <si>
     <t>Ndiaye &amp; Frère</t>
+  </si>
+  <si>
+    <t>Ousmane</t>
+  </si>
+  <si>
+    <t>Refraish Evapore</t>
+  </si>
+  <si>
+    <t>Khadime SYLLA</t>
+  </si>
+  <si>
+    <t>Abdallah Aïdara</t>
+  </si>
+  <si>
+    <t>Il dit dit que le produit est lente</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je lui est livré le 30 lundi </t>
+  </si>
+  <si>
+    <t>Abdourahmane</t>
+  </si>
+  <si>
+    <t>Livré le lundi 30</t>
+  </si>
+  <si>
+    <t>Niacrobe</t>
+  </si>
+  <si>
+    <t>Momodou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je lui ai livré le mardi 31 </t>
+  </si>
+  <si>
+    <t>TBC SARL</t>
+  </si>
+  <si>
+    <t>LAMP</t>
+  </si>
+  <si>
+    <t>Il apprécie la baisse des prix du produit</t>
+  </si>
+  <si>
+    <t>Abdoulakhate SAMB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il voulait essayer </t>
+  </si>
+  <si>
+    <t>Mballo Séye</t>
   </si>
 </sst>
 </file>
@@ -812,7 +866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -842,6 +896,19 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1146,8 +1213,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P211" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P211" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P242" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P242" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1460,7 +1527,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P211"/>
+  <dimension ref="A1:P242"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -12450,6 +12517,1618 @@
         <v>mars</v>
       </c>
     </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A212" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E212" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F212" s="12">
+        <v>771166914</v>
+      </c>
+      <c r="G212" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H212" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K212" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="L212" s="12">
+        <v>1</v>
+      </c>
+      <c r="M212" s="13">
+        <v>17500</v>
+      </c>
+      <c r="N212" s="13">
+        <v>17500</v>
+      </c>
+      <c r="O212" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P212" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A213" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B213" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="F213" s="12">
+        <v>775276149</v>
+      </c>
+      <c r="G213" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H213" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J213" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K213" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L213" s="12">
+        <v>50</v>
+      </c>
+      <c r="M213" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N213" s="13">
+        <v>437500</v>
+      </c>
+      <c r="O213" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P213" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A214" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F214" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G214" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H214" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I214" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J214" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K214" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L214" s="12">
+        <v>24</v>
+      </c>
+      <c r="M214" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N214" s="13">
+        <v>624000</v>
+      </c>
+      <c r="O214" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P214" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A215" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B215" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="F215" s="12">
+        <v>776317469</v>
+      </c>
+      <c r="G215" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H215" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J215" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K215" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L215" s="12">
+        <v>25</v>
+      </c>
+      <c r="M215" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N215" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O215" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P215" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A216" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F216" s="12">
+        <v>775273147</v>
+      </c>
+      <c r="G216" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H216" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K216" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L216" s="12">
+        <v>25</v>
+      </c>
+      <c r="M216" s="13">
+        <v>5750</v>
+      </c>
+      <c r="N216" s="13">
+        <v>143750</v>
+      </c>
+      <c r="O216" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P216" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A217" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D217" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F217" s="12">
+        <v>775485563</v>
+      </c>
+      <c r="G217" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H217" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I217" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J217" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K217" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L217" s="12">
+        <v>10</v>
+      </c>
+      <c r="M217" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N217" s="13">
+        <v>87500</v>
+      </c>
+      <c r="O217" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P217" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A218" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D218" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="F218" s="12">
+        <v>785923657</v>
+      </c>
+      <c r="G218" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H218" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I218" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="K218" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L218" s="12">
+        <v>5</v>
+      </c>
+      <c r="M218" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N218" s="13">
+        <v>130000</v>
+      </c>
+      <c r="O218" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P218" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A219" s="11">
+        <v>46115</v>
+      </c>
+      <c r="B219" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D219" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F219" s="12">
+        <v>782357233</v>
+      </c>
+      <c r="G219" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H219" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I219" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J219" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K219" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L219" s="12">
+        <v>5</v>
+      </c>
+      <c r="M219" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N219" s="13">
+        <v>43750</v>
+      </c>
+      <c r="O219" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P219" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A220" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D220" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E220" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F220" s="12">
+        <v>766657313</v>
+      </c>
+      <c r="G220" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H220" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I220" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="K220" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L220" s="12">
+        <v>25</v>
+      </c>
+      <c r="M220" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N220" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O220" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P220" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A221" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B221" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D221" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E221" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F221" s="12">
+        <v>781142243</v>
+      </c>
+      <c r="G221" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H221" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I221" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J221" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="K221" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L221" s="12">
+        <v>50</v>
+      </c>
+      <c r="M221" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N221" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="O221" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P221" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A222" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D222" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F222" s="12">
+        <v>783682649</v>
+      </c>
+      <c r="G222" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I222" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J222" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K222" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L222" s="12">
+        <v>25</v>
+      </c>
+      <c r="M222" s="13">
+        <v>9250</v>
+      </c>
+      <c r="N222" s="13">
+        <v>231250</v>
+      </c>
+      <c r="O222" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P222" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A223" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B223" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D223" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="F223" s="12">
+        <v>775772788</v>
+      </c>
+      <c r="G223" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H223" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I223" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J223" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="K223" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L223" s="12">
+        <v>50</v>
+      </c>
+      <c r="M223" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N223" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="O223" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P223" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A224" s="11">
+        <v>46114</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D224" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="F224" s="12">
+        <v>774624747</v>
+      </c>
+      <c r="G224" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H224" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I224" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J224" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K224" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L224" s="12">
+        <v>10</v>
+      </c>
+      <c r="M224" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N224" s="13">
+        <v>87500</v>
+      </c>
+      <c r="O224" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P224" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A225" s="11">
+        <v>46113</v>
+      </c>
+      <c r="B225" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E225" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F225" s="12">
+        <v>775586604</v>
+      </c>
+      <c r="G225" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H225" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I225" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J225" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K225" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L225" s="12">
+        <v>50</v>
+      </c>
+      <c r="M225" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N225" s="13">
+        <v>437500</v>
+      </c>
+      <c r="O225" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P225" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A226" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B226" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D226" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E226" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F226" s="12">
+        <v>773546192</v>
+      </c>
+      <c r="G226" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H226" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I226" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K226" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L226" s="12">
+        <v>2</v>
+      </c>
+      <c r="M226" s="13">
+        <v>33500</v>
+      </c>
+      <c r="N226" s="13">
+        <v>67000</v>
+      </c>
+      <c r="O226" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P226" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A227" s="11">
+        <v>46113</v>
+      </c>
+      <c r="B227" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F227" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G227" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H227" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I227" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J227" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K227" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L227" s="12">
+        <v>25</v>
+      </c>
+      <c r="M227" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N227" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O227" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P227" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A228" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D228" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F228" s="12">
+        <v>775197108</v>
+      </c>
+      <c r="G228" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H228" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I228" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J228" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K228" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L228" s="12">
+        <v>1</v>
+      </c>
+      <c r="M228" s="13">
+        <v>6000</v>
+      </c>
+      <c r="N228" s="13">
+        <v>6000</v>
+      </c>
+      <c r="O228" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P228" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A229" s="11">
+        <v>46113</v>
+      </c>
+      <c r="B229" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D229" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F229" s="12">
+        <v>775987400</v>
+      </c>
+      <c r="G229" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H229" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I229" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J229" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K229" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L229" s="12">
+        <v>5</v>
+      </c>
+      <c r="M229" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N229" s="13">
+        <v>97500</v>
+      </c>
+      <c r="O229" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P229" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A230" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D230" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="F230" s="12">
+        <v>775987400</v>
+      </c>
+      <c r="G230" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H230" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J230" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K230" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L230" s="12">
+        <v>1</v>
+      </c>
+      <c r="M230" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N230" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O230" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P230" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A231" s="11">
+        <v>46113</v>
+      </c>
+      <c r="B231" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D231" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E231" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F231" s="12">
+        <v>775894235</v>
+      </c>
+      <c r="G231" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H231" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I231" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J231" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K231" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L231" s="12">
+        <v>2</v>
+      </c>
+      <c r="M231" s="13">
+        <v>15000</v>
+      </c>
+      <c r="N231" s="13">
+        <v>30000</v>
+      </c>
+      <c r="O231" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P231" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A232" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B232" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D232" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E232" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="F232" s="12">
+        <v>782990477</v>
+      </c>
+      <c r="G232" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I232" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J232" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="K232" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L232" s="12">
+        <v>25</v>
+      </c>
+      <c r="M232" s="13">
+        <v>28000</v>
+      </c>
+      <c r="N232" s="13">
+        <v>700000</v>
+      </c>
+      <c r="O232" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P232" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A233" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B233" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D233" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E233" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F233" s="12">
+        <v>772990477</v>
+      </c>
+      <c r="G233" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H233" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I233" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J233" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K233" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L233" s="12">
+        <v>25</v>
+      </c>
+      <c r="M233" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N233" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O233" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P233" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A234" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D234" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E234" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F234" s="12">
+        <v>784537895</v>
+      </c>
+      <c r="G234" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H234" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I234" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J234" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K234" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L234" s="12">
+        <v>50</v>
+      </c>
+      <c r="M234" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N234" s="13">
+        <v>437500</v>
+      </c>
+      <c r="O234" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P234" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A235" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B235" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D235" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E235" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F235" s="12">
+        <v>784537895</v>
+      </c>
+      <c r="G235" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H235" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I235" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J235" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K235" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L235" s="12">
+        <v>50</v>
+      </c>
+      <c r="M235" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N235" s="13">
+        <v>437500</v>
+      </c>
+      <c r="O235" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P235" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A236" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D236" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E236" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F236" s="12">
+        <v>777096402</v>
+      </c>
+      <c r="G236" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H236" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I236" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J236" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K236" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L236" s="12">
+        <v>10</v>
+      </c>
+      <c r="M236" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N236" s="13">
+        <v>87500</v>
+      </c>
+      <c r="O236" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P236" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A237" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B237" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D237" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E237" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F237" s="12">
+        <v>777096402</v>
+      </c>
+      <c r="G237" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H237" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I237" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J237" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K237" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L237" s="12">
+        <v>1</v>
+      </c>
+      <c r="M237" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N237" s="13">
+        <v>26000</v>
+      </c>
+      <c r="O237" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P237" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A238" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D238" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E238" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F238" s="12">
+        <v>777096402</v>
+      </c>
+      <c r="G238" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H238" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I238" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J238" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K238" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L238" s="12">
+        <v>55</v>
+      </c>
+      <c r="M238" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N238" s="13">
+        <v>481250</v>
+      </c>
+      <c r="O238" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P238" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A239" s="11">
+        <v>46112</v>
+      </c>
+      <c r="B239" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D239" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E239" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F239" s="12">
+        <v>774414059</v>
+      </c>
+      <c r="G239" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H239" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I239" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J239" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K239" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L239" s="12">
+        <v>50</v>
+      </c>
+      <c r="M239" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N239" s="13">
+        <v>437500</v>
+      </c>
+      <c r="O239" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P239" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A240" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D240" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E240" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F240" s="12">
+        <v>774993694</v>
+      </c>
+      <c r="G240" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H240" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I240" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J240" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="K240" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L240" s="12">
+        <v>25</v>
+      </c>
+      <c r="M240" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N240" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O240" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P240" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A241" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B241" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D241" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E241" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="F241" s="12">
+        <v>765434141</v>
+      </c>
+      <c r="G241" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H241" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I241" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J241" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K241" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L241" s="12">
+        <v>25</v>
+      </c>
+      <c r="M241" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N241" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O241" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P241" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A242" s="11">
+        <v>46111</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D242" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E242" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F242" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G242" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H242" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I242" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J242" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K242" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L242" s="12">
+        <v>25</v>
+      </c>
+      <c r="M242" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N242" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O242" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S14</v>
+      </c>
+      <c r="P242" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mars</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BA7BC2-38C8-4A74-A49A-928D603584B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BD0B66-C108-4B5C-9CA6-13039A0163AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="218" yWindow="720" windowWidth="18982" windowHeight="10080" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="272">
   <si>
     <t>Date</t>
   </si>
@@ -799,6 +799,57 @@
   </si>
   <si>
     <t>Mballo Séye</t>
+  </si>
+  <si>
+    <t>mame_mareme_ndiaye</t>
+  </si>
+  <si>
+    <t>Abdou DIALLO</t>
+  </si>
+  <si>
+    <t>TAPAHA GAYE</t>
+  </si>
+  <si>
+    <t>ndiaye_ngouye</t>
+  </si>
+  <si>
+    <t>Kayar</t>
+  </si>
+  <si>
+    <t>Babacar</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA BAKHDAD</t>
+  </si>
+  <si>
+    <t>MOUHAMED DAYEL</t>
+  </si>
+  <si>
+    <t>Modou Ndiaye</t>
+  </si>
+  <si>
+    <t>sow_seynabou</t>
+  </si>
+  <si>
+    <t>fatoumata_traore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il demande nos chemises </t>
+  </si>
+  <si>
+    <t>Sylla</t>
+  </si>
+  <si>
+    <t>DJIBRIL laye</t>
+  </si>
+  <si>
+    <t>J'ai fait la livraison le mardi mais il est venu à 19h moins</t>
+  </si>
+  <si>
+    <t>Madiama SYLLA</t>
+  </si>
+  <si>
+    <t>Client satisfait</t>
   </si>
 </sst>
 </file>
@@ -1154,16 +1205,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -1213,8 +1264,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P242" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P242" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P273" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17">
+  <autoFilter ref="A1:P273" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1527,7 +1578,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P242"/>
+  <dimension ref="A1:P273"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -12518,1615 +12569,3227 @@
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A212" s="11">
+      <c r="A212" s="8">
         <v>46115</v>
       </c>
-      <c r="B212" s="12" t="s">
+      <c r="B212" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C212" s="12" t="s">
+      <c r="C212" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D212" s="12" t="s">
+      <c r="D212" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E212" s="12" t="s">
+      <c r="E212" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F212" s="12">
+      <c r="F212" s="9">
         <v>771166914</v>
       </c>
-      <c r="G212" s="12" t="s">
+      <c r="G212" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H212" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I212" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J212" s="12" t="s">
+      <c r="H212" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J212" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K212" s="12" t="s">
+      <c r="K212" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L212" s="12">
+      <c r="L212" s="9">
         <v>1</v>
       </c>
-      <c r="M212" s="13">
+      <c r="M212" s="10">
         <v>17500</v>
       </c>
-      <c r="N212" s="13">
+      <c r="N212" s="10">
         <v>17500</v>
       </c>
-      <c r="O212" s="14" t="str">
+      <c r="O212" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P212" s="15" t="str">
+      <c r="P212" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A213" s="11">
+      <c r="A213" s="8">
         <v>46115</v>
       </c>
-      <c r="B213" s="12" t="s">
+      <c r="B213" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C213" s="12" t="s">
+      <c r="C213" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D213" s="12" t="s">
+      <c r="D213" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E213" s="12" t="s">
+      <c r="E213" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="F213" s="12">
+      <c r="F213" s="9">
         <v>775276149</v>
       </c>
-      <c r="G213" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H213" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I213" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J213" s="12" t="s">
+      <c r="G213" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H213" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J213" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K213" s="12" t="s">
+      <c r="K213" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L213" s="12">
+      <c r="L213" s="9">
         <v>50</v>
       </c>
-      <c r="M213" s="13">
+      <c r="M213" s="10">
         <v>8750</v>
       </c>
-      <c r="N213" s="13">
+      <c r="N213" s="10">
         <v>437500</v>
       </c>
-      <c r="O213" s="14" t="str">
+      <c r="O213" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P213" s="15" t="str">
+      <c r="P213" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A214" s="11">
+      <c r="A214" s="8">
         <v>46115</v>
       </c>
-      <c r="B214" s="12" t="s">
+      <c r="B214" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C214" s="12" t="s">
+      <c r="C214" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D214" s="12" t="s">
+      <c r="D214" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E214" s="12" t="s">
+      <c r="E214" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F214" s="12">
+      <c r="F214" s="9">
         <v>775544532</v>
       </c>
-      <c r="G214" s="12" t="s">
+      <c r="G214" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H214" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I214" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J214" s="12" t="s">
+      <c r="H214" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J214" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K214" s="12" t="s">
+      <c r="K214" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L214" s="12">
+      <c r="L214" s="9">
         <v>24</v>
       </c>
-      <c r="M214" s="13">
+      <c r="M214" s="10">
         <v>26000</v>
       </c>
-      <c r="N214" s="13">
+      <c r="N214" s="10">
         <v>624000</v>
       </c>
-      <c r="O214" s="14" t="str">
+      <c r="O214" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P214" s="15" t="str">
+      <c r="P214" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="215" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A215" s="11">
+      <c r="A215" s="8">
         <v>46112</v>
       </c>
-      <c r="B215" s="12" t="s">
+      <c r="B215" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C215" s="12" t="s">
+      <c r="C215" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D215" s="12" t="s">
+      <c r="D215" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E215" s="12" t="s">
+      <c r="E215" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="F215" s="12">
+      <c r="F215" s="9">
         <v>776317469</v>
       </c>
-      <c r="G215" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H215" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I215" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J215" s="12" t="s">
+      <c r="G215" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H215" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J215" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K215" s="12" t="s">
+      <c r="K215" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L215" s="12">
+      <c r="L215" s="9">
         <v>25</v>
       </c>
-      <c r="M215" s="13">
+      <c r="M215" s="10">
         <v>19500</v>
       </c>
-      <c r="N215" s="13">
+      <c r="N215" s="10">
         <v>487500</v>
       </c>
-      <c r="O215" s="14" t="str">
+      <c r="O215" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P215" s="15" t="str">
+      <c r="P215" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A216" s="11">
+      <c r="A216" s="8">
         <v>46115</v>
       </c>
-      <c r="B216" s="12" t="s">
+      <c r="B216" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C216" s="12" t="s">
+      <c r="C216" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D216" s="12" t="s">
+      <c r="D216" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E216" s="12" t="s">
+      <c r="E216" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F216" s="12">
+      <c r="F216" s="9">
         <v>775273147</v>
       </c>
-      <c r="G216" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H216" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I216" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J216" s="12" t="s">
+      <c r="G216" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H216" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J216" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K216" s="12" t="s">
+      <c r="K216" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L216" s="12">
+      <c r="L216" s="9">
         <v>25</v>
       </c>
-      <c r="M216" s="13">
+      <c r="M216" s="10">
         <v>5750</v>
       </c>
-      <c r="N216" s="13">
+      <c r="N216" s="10">
         <v>143750</v>
       </c>
-      <c r="O216" s="14" t="str">
+      <c r="O216" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P216" s="15" t="str">
+      <c r="P216" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A217" s="11">
+      <c r="A217" s="8">
         <v>46115</v>
       </c>
-      <c r="B217" s="12" t="s">
+      <c r="B217" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C217" s="12" t="s">
+      <c r="C217" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D217" s="12" t="s">
+      <c r="D217" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E217" s="12" t="s">
+      <c r="E217" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F217" s="12">
+      <c r="F217" s="9">
         <v>775485563</v>
       </c>
-      <c r="G217" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H217" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I217" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J217" s="12" t="s">
+      <c r="G217" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H217" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J217" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K217" s="12" t="s">
+      <c r="K217" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L217" s="12">
+      <c r="L217" s="9">
         <v>10</v>
       </c>
-      <c r="M217" s="13">
+      <c r="M217" s="10">
         <v>8750</v>
       </c>
-      <c r="N217" s="13">
+      <c r="N217" s="10">
         <v>87500</v>
       </c>
-      <c r="O217" s="14" t="str">
+      <c r="O217" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P217" s="15" t="str">
+      <c r="P217" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A218" s="11">
+      <c r="A218" s="8">
         <v>46115</v>
       </c>
-      <c r="B218" s="12" t="s">
+      <c r="B218" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C218" s="12" t="s">
+      <c r="C218" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D218" s="12" t="s">
+      <c r="D218" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E218" s="12" t="s">
+      <c r="E218" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F218" s="12">
+      <c r="F218" s="9">
         <v>785923657</v>
       </c>
-      <c r="G218" s="12" t="s">
+      <c r="G218" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H218" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I218" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J218" s="12" t="s">
+      <c r="H218" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J218" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="K218" s="12" t="s">
+      <c r="K218" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L218" s="12">
+      <c r="L218" s="9">
         <v>5</v>
       </c>
-      <c r="M218" s="13">
+      <c r="M218" s="10">
         <v>26000</v>
       </c>
-      <c r="N218" s="13">
+      <c r="N218" s="10">
         <v>130000</v>
       </c>
-      <c r="O218" s="14" t="str">
+      <c r="O218" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P218" s="15" t="str">
+      <c r="P218" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A219" s="11">
+      <c r="A219" s="8">
         <v>46115</v>
       </c>
-      <c r="B219" s="12" t="s">
+      <c r="B219" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C219" s="12" t="s">
+      <c r="C219" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D219" s="12" t="s">
+      <c r="D219" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E219" s="12" t="s">
+      <c r="E219" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F219" s="12">
+      <c r="F219" s="9">
         <v>782357233</v>
       </c>
-      <c r="G219" s="12" t="s">
+      <c r="G219" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="H219" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I219" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J219" s="12" t="s">
+      <c r="H219" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J219" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K219" s="12" t="s">
+      <c r="K219" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L219" s="12">
+      <c r="L219" s="9">
         <v>5</v>
       </c>
-      <c r="M219" s="13">
+      <c r="M219" s="10">
         <v>8750</v>
       </c>
-      <c r="N219" s="13">
+      <c r="N219" s="10">
         <v>43750</v>
       </c>
-      <c r="O219" s="14" t="str">
+      <c r="O219" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P219" s="15" t="str">
+      <c r="P219" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A220" s="11">
+      <c r="A220" s="8">
         <v>46111</v>
       </c>
-      <c r="B220" s="12" t="s">
+      <c r="B220" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C220" s="12" t="s">
+      <c r="C220" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D220" s="12" t="s">
+      <c r="D220" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E220" s="12" t="s">
+      <c r="E220" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="F220" s="12">
+      <c r="F220" s="9">
         <v>766657313</v>
       </c>
-      <c r="G220" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H220" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I220" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J220" s="12" t="s">
+      <c r="G220" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H220" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J220" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="K220" s="12" t="s">
+      <c r="K220" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L220" s="12">
+      <c r="L220" s="9">
         <v>25</v>
       </c>
-      <c r="M220" s="13">
+      <c r="M220" s="10">
         <v>19500</v>
       </c>
-      <c r="N220" s="13">
+      <c r="N220" s="10">
         <v>487500</v>
       </c>
-      <c r="O220" s="14" t="str">
+      <c r="O220" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P220" s="15" t="str">
+      <c r="P220" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A221" s="11">
+      <c r="A221" s="8">
         <v>46112</v>
       </c>
-      <c r="B221" s="12" t="s">
+      <c r="B221" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C221" s="12" t="s">
+      <c r="C221" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D221" s="12" t="s">
+      <c r="D221" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E221" s="12" t="s">
+      <c r="E221" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="F221" s="12">
+      <c r="F221" s="9">
         <v>781142243</v>
       </c>
-      <c r="G221" s="12" t="s">
+      <c r="G221" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H221" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I221" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J221" s="12" t="s">
+      <c r="H221" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J221" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="K221" s="12" t="s">
+      <c r="K221" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L221" s="12">
+      <c r="L221" s="9">
         <v>50</v>
       </c>
-      <c r="M221" s="13">
+      <c r="M221" s="10">
         <v>26000</v>
       </c>
-      <c r="N221" s="13">
+      <c r="N221" s="10">
         <v>1300000</v>
       </c>
-      <c r="O221" s="14" t="str">
+      <c r="O221" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P221" s="15" t="str">
+      <c r="P221" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="222" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A222" s="11">
+      <c r="A222" s="8">
         <v>46111</v>
       </c>
-      <c r="B222" s="12" t="s">
+      <c r="B222" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C222" s="12" t="s">
+      <c r="C222" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D222" s="12" t="s">
+      <c r="D222" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E222" s="12" t="s">
+      <c r="E222" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F222" s="12">
+      <c r="F222" s="9">
         <v>783682649</v>
       </c>
-      <c r="G222" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H222" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I222" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J222" s="12" t="s">
+      <c r="G222" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J222" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K222" s="12" t="s">
+      <c r="K222" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L222" s="12">
+      <c r="L222" s="9">
         <v>25</v>
       </c>
-      <c r="M222" s="13">
+      <c r="M222" s="10">
         <v>9250</v>
       </c>
-      <c r="N222" s="13">
+      <c r="N222" s="10">
         <v>231250</v>
       </c>
-      <c r="O222" s="14" t="str">
+      <c r="O222" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P222" s="15" t="str">
+      <c r="P222" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="223" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A223" s="11">
+      <c r="A223" s="8">
         <v>46111</v>
       </c>
-      <c r="B223" s="12" t="s">
+      <c r="B223" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C223" s="12" t="s">
+      <c r="C223" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D223" s="12" t="s">
+      <c r="D223" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="E223" s="12" t="s">
+      <c r="E223" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="F223" s="12">
+      <c r="F223" s="9">
         <v>775772788</v>
       </c>
-      <c r="G223" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H223" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I223" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J223" s="12" t="s">
+      <c r="G223" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H223" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J223" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="K223" s="12" t="s">
+      <c r="K223" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L223" s="12">
+      <c r="L223" s="9">
         <v>50</v>
       </c>
-      <c r="M223" s="13">
+      <c r="M223" s="10">
         <v>26000</v>
       </c>
-      <c r="N223" s="13">
+      <c r="N223" s="10">
         <v>1300000</v>
       </c>
-      <c r="O223" s="14" t="str">
+      <c r="O223" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P223" s="15" t="str">
+      <c r="P223" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A224" s="11">
+      <c r="A224" s="8">
         <v>46114</v>
       </c>
-      <c r="B224" s="12" t="s">
+      <c r="B224" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C224" s="12" t="s">
+      <c r="C224" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D224" s="12" t="s">
+      <c r="D224" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E224" s="12" t="s">
+      <c r="E224" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="F224" s="12">
+      <c r="F224" s="9">
         <v>774624747</v>
       </c>
-      <c r="G224" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H224" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I224" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J224" s="12" t="s">
+      <c r="G224" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H224" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J224" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K224" s="12" t="s">
+      <c r="K224" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L224" s="12">
+      <c r="L224" s="9">
         <v>10</v>
       </c>
-      <c r="M224" s="13">
+      <c r="M224" s="10">
         <v>8750</v>
       </c>
-      <c r="N224" s="13">
+      <c r="N224" s="10">
         <v>87500</v>
       </c>
-      <c r="O224" s="14" t="str">
+      <c r="O224" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P224" s="15" t="str">
+      <c r="P224" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="225" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A225" s="11">
+      <c r="A225" s="8">
         <v>46113</v>
       </c>
-      <c r="B225" s="12" t="s">
+      <c r="B225" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C225" s="12" t="s">
+      <c r="C225" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D225" s="12" t="s">
+      <c r="D225" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E225" s="12" t="s">
+      <c r="E225" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F225" s="12">
+      <c r="F225" s="9">
         <v>775586604</v>
       </c>
-      <c r="G225" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H225" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I225" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J225" s="12" t="s">
+      <c r="G225" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H225" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J225" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K225" s="12" t="s">
+      <c r="K225" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L225" s="12">
+      <c r="L225" s="9">
         <v>50</v>
       </c>
-      <c r="M225" s="13">
+      <c r="M225" s="10">
         <v>8750</v>
       </c>
-      <c r="N225" s="13">
+      <c r="N225" s="10">
         <v>437500</v>
       </c>
-      <c r="O225" s="14" t="str">
+      <c r="O225" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P225" s="15" t="str">
+      <c r="P225" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A226" s="11">
+      <c r="A226" s="8">
         <v>46112</v>
       </c>
-      <c r="B226" s="12" t="s">
+      <c r="B226" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C226" s="12" t="s">
+      <c r="C226" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D226" s="12" t="s">
+      <c r="D226" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E226" s="12" t="s">
+      <c r="E226" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F226" s="12">
+      <c r="F226" s="9">
         <v>773546192</v>
       </c>
-      <c r="G226" s="12" t="s">
+      <c r="G226" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H226" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I226" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J226" s="12" t="s">
+      <c r="H226" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J226" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K226" s="12" t="s">
+      <c r="K226" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="L226" s="12">
+      <c r="L226" s="9">
         <v>2</v>
       </c>
-      <c r="M226" s="13">
+      <c r="M226" s="10">
         <v>33500</v>
       </c>
-      <c r="N226" s="13">
+      <c r="N226" s="10">
         <v>67000</v>
       </c>
-      <c r="O226" s="14" t="str">
+      <c r="O226" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P226" s="15" t="str">
+      <c r="P226" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A227" s="11">
+      <c r="A227" s="8">
         <v>46113</v>
       </c>
-      <c r="B227" s="12" t="s">
+      <c r="B227" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C227" s="12" t="s">
+      <c r="C227" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D227" s="12" t="s">
+      <c r="D227" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E227" s="12" t="s">
+      <c r="E227" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F227" s="12">
+      <c r="F227" s="9">
         <v>775544532</v>
       </c>
-      <c r="G227" s="12" t="s">
+      <c r="G227" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H227" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I227" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J227" s="12" t="s">
+      <c r="H227" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J227" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K227" s="12" t="s">
+      <c r="K227" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L227" s="12">
+      <c r="L227" s="9">
         <v>25</v>
       </c>
-      <c r="M227" s="13">
+      <c r="M227" s="10">
         <v>26000</v>
       </c>
-      <c r="N227" s="13">
+      <c r="N227" s="10">
         <v>650000</v>
       </c>
-      <c r="O227" s="14" t="str">
+      <c r="O227" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P227" s="15" t="str">
+      <c r="P227" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A228" s="11">
+      <c r="A228" s="8">
         <v>46111</v>
       </c>
-      <c r="B228" s="12" t="s">
+      <c r="B228" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C228" s="12" t="s">
+      <c r="C228" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D228" s="12" t="s">
+      <c r="D228" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E228" s="12" t="s">
+      <c r="E228" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F228" s="12">
+      <c r="F228" s="9">
         <v>775197108</v>
       </c>
-      <c r="G228" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H228" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I228" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J228" s="12" t="s">
+      <c r="G228" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H228" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J228" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K228" s="12" t="s">
+      <c r="K228" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L228" s="12">
+      <c r="L228" s="9">
         <v>1</v>
       </c>
-      <c r="M228" s="13">
+      <c r="M228" s="10">
         <v>6000</v>
       </c>
-      <c r="N228" s="13">
+      <c r="N228" s="10">
         <v>6000</v>
       </c>
-      <c r="O228" s="14" t="str">
+      <c r="O228" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P228" s="15" t="str">
+      <c r="P228" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A229" s="11">
+      <c r="A229" s="8">
         <v>46113</v>
       </c>
-      <c r="B229" s="12" t="s">
+      <c r="B229" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C229" s="12" t="s">
+      <c r="C229" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D229" s="12" t="s">
+      <c r="D229" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E229" s="12" t="s">
+      <c r="E229" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F229" s="12">
+      <c r="F229" s="9">
         <v>775987400</v>
       </c>
-      <c r="G229" s="12" t="s">
+      <c r="G229" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H229" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I229" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J229" s="12" t="s">
+      <c r="H229" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J229" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K229" s="12" t="s">
+      <c r="K229" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L229" s="12">
+      <c r="L229" s="9">
         <v>5</v>
       </c>
-      <c r="M229" s="13">
+      <c r="M229" s="10">
         <v>19500</v>
       </c>
-      <c r="N229" s="13">
+      <c r="N229" s="10">
         <v>97500</v>
       </c>
-      <c r="O229" s="14" t="str">
+      <c r="O229" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P229" s="15" t="str">
+      <c r="P229" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A230" s="11">
+      <c r="A230" s="8">
         <v>46111</v>
       </c>
-      <c r="B230" s="12" t="s">
+      <c r="B230" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C230" s="12" t="s">
+      <c r="C230" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D230" s="12" t="s">
+      <c r="D230" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E230" s="12" t="s">
+      <c r="E230" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F230" s="12">
+      <c r="F230" s="9">
         <v>775987400</v>
       </c>
-      <c r="G230" s="12" t="s">
+      <c r="G230" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H230" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I230" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J230" s="12" t="s">
+      <c r="H230" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J230" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K230" s="12" t="s">
+      <c r="K230" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L230" s="12">
+      <c r="L230" s="9">
         <v>1</v>
       </c>
-      <c r="M230" s="13">
+      <c r="M230" s="10">
         <v>26000</v>
       </c>
-      <c r="N230" s="13">
+      <c r="N230" s="10">
         <v>26000</v>
       </c>
-      <c r="O230" s="14" t="str">
+      <c r="O230" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P230" s="15" t="str">
+      <c r="P230" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A231" s="11">
+      <c r="A231" s="8">
         <v>46113</v>
       </c>
-      <c r="B231" s="12" t="s">
+      <c r="B231" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C231" s="12" t="s">
+      <c r="C231" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D231" s="12" t="s">
+      <c r="D231" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E231" s="12" t="s">
+      <c r="E231" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F231" s="12">
+      <c r="F231" s="9">
         <v>775894235</v>
       </c>
-      <c r="G231" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H231" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I231" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J231" s="12" t="s">
+      <c r="G231" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H231" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J231" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K231" s="12" t="s">
+      <c r="K231" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="L231" s="12">
+      <c r="L231" s="9">
         <v>2</v>
       </c>
-      <c r="M231" s="13">
+      <c r="M231" s="10">
         <v>15000</v>
       </c>
-      <c r="N231" s="13">
+      <c r="N231" s="10">
         <v>30000</v>
       </c>
-      <c r="O231" s="14" t="str">
+      <c r="O231" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P231" s="15" t="str">
+      <c r="P231" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="232" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A232" s="11">
+      <c r="A232" s="8">
         <v>46112</v>
       </c>
-      <c r="B232" s="12" t="s">
+      <c r="B232" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C232" s="12" t="s">
+      <c r="C232" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D232" s="12" t="s">
+      <c r="D232" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E232" s="12" t="s">
+      <c r="E232" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="F232" s="12">
+      <c r="F232" s="9">
         <v>782990477</v>
       </c>
-      <c r="G232" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H232" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I232" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J232" s="12" t="s">
+      <c r="G232" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J232" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="K232" s="12" t="s">
+      <c r="K232" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L232" s="12">
+      <c r="L232" s="9">
         <v>25</v>
       </c>
-      <c r="M232" s="13">
+      <c r="M232" s="10">
         <v>28000</v>
       </c>
-      <c r="N232" s="13">
+      <c r="N232" s="10">
         <v>700000</v>
       </c>
-      <c r="O232" s="14" t="str">
+      <c r="O232" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P232" s="15" t="str">
+      <c r="P232" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A233" s="11">
+      <c r="A233" s="8">
         <v>46112</v>
       </c>
-      <c r="B233" s="12" t="s">
+      <c r="B233" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C233" s="12" t="s">
+      <c r="C233" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D233" s="12" t="s">
+      <c r="D233" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E233" s="12" t="s">
+      <c r="E233" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="F233" s="12">
+      <c r="F233" s="9">
         <v>772990477</v>
       </c>
-      <c r="G233" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H233" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I233" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J233" s="12" t="s">
+      <c r="G233" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H233" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J233" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K233" s="12" t="s">
+      <c r="K233" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L233" s="12">
+      <c r="L233" s="9">
         <v>25</v>
       </c>
-      <c r="M233" s="13">
+      <c r="M233" s="10">
         <v>26000</v>
       </c>
-      <c r="N233" s="13">
+      <c r="N233" s="10">
         <v>650000</v>
       </c>
-      <c r="O233" s="14" t="str">
+      <c r="O233" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P233" s="15" t="str">
+      <c r="P233" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A234" s="11">
+      <c r="A234" s="8">
         <v>46112</v>
       </c>
-      <c r="B234" s="12" t="s">
+      <c r="B234" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C234" s="12" t="s">
+      <c r="C234" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D234" s="12" t="s">
+      <c r="D234" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E234" s="12" t="s">
+      <c r="E234" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F234" s="12">
+      <c r="F234" s="9">
         <v>784537895</v>
       </c>
-      <c r="G234" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H234" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I234" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J234" s="12" t="s">
+      <c r="G234" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H234" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J234" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K234" s="12" t="s">
+      <c r="K234" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L234" s="12">
+      <c r="L234" s="9">
         <v>50</v>
       </c>
-      <c r="M234" s="13">
+      <c r="M234" s="10">
         <v>8750</v>
       </c>
-      <c r="N234" s="13">
+      <c r="N234" s="10">
         <v>437500</v>
       </c>
-      <c r="O234" s="14" t="str">
+      <c r="O234" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P234" s="15" t="str">
+      <c r="P234" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="235" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A235" s="11">
+      <c r="A235" s="8">
         <v>46112</v>
       </c>
-      <c r="B235" s="12" t="s">
+      <c r="B235" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C235" s="12" t="s">
+      <c r="C235" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D235" s="12" t="s">
+      <c r="D235" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E235" s="12" t="s">
+      <c r="E235" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F235" s="12">
+      <c r="F235" s="9">
         <v>784537895</v>
       </c>
-      <c r="G235" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H235" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I235" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J235" s="12" t="s">
+      <c r="G235" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H235" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J235" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K235" s="12" t="s">
+      <c r="K235" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L235" s="12">
+      <c r="L235" s="9">
         <v>50</v>
       </c>
-      <c r="M235" s="13">
+      <c r="M235" s="10">
         <v>8750</v>
       </c>
-      <c r="N235" s="13">
+      <c r="N235" s="10">
         <v>437500</v>
       </c>
-      <c r="O235" s="14" t="str">
+      <c r="O235" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P235" s="15" t="str">
+      <c r="P235" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A236" s="11">
+      <c r="A236" s="8">
         <v>46112</v>
       </c>
-      <c r="B236" s="12" t="s">
+      <c r="B236" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C236" s="12" t="s">
+      <c r="C236" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D236" s="12" t="s">
+      <c r="D236" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E236" s="12" t="s">
+      <c r="E236" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F236" s="12">
+      <c r="F236" s="9">
         <v>777096402</v>
       </c>
-      <c r="G236" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H236" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I236" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J236" s="12" t="s">
+      <c r="G236" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H236" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J236" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K236" s="12" t="s">
+      <c r="K236" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L236" s="12">
+      <c r="L236" s="9">
         <v>10</v>
       </c>
-      <c r="M236" s="13">
+      <c r="M236" s="10">
         <v>8750</v>
       </c>
-      <c r="N236" s="13">
+      <c r="N236" s="10">
         <v>87500</v>
       </c>
-      <c r="O236" s="14" t="str">
+      <c r="O236" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P236" s="15" t="str">
+      <c r="P236" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="237" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A237" s="11">
+      <c r="A237" s="8">
         <v>46112</v>
       </c>
-      <c r="B237" s="12" t="s">
+      <c r="B237" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C237" s="12" t="s">
+      <c r="C237" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D237" s="12" t="s">
+      <c r="D237" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E237" s="12" t="s">
+      <c r="E237" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F237" s="12">
+      <c r="F237" s="9">
         <v>777096402</v>
       </c>
-      <c r="G237" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H237" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I237" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J237" s="12" t="s">
+      <c r="G237" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H237" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J237" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K237" s="12" t="s">
+      <c r="K237" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L237" s="12">
+      <c r="L237" s="9">
         <v>1</v>
       </c>
-      <c r="M237" s="13">
+      <c r="M237" s="10">
         <v>26000</v>
       </c>
-      <c r="N237" s="13">
+      <c r="N237" s="10">
         <v>26000</v>
       </c>
-      <c r="O237" s="14" t="str">
+      <c r="O237" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P237" s="15" t="str">
+      <c r="P237" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="238" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A238" s="11">
+      <c r="A238" s="8">
         <v>46112</v>
       </c>
-      <c r="B238" s="12" t="s">
+      <c r="B238" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C238" s="12" t="s">
+      <c r="C238" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D238" s="12" t="s">
+      <c r="D238" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E238" s="12" t="s">
+      <c r="E238" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F238" s="12">
+      <c r="F238" s="9">
         <v>777096402</v>
       </c>
-      <c r="G238" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H238" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I238" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J238" s="12" t="s">
+      <c r="G238" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H238" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J238" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K238" s="12" t="s">
+      <c r="K238" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L238" s="12">
+      <c r="L238" s="9">
         <v>55</v>
       </c>
-      <c r="M238" s="13">
+      <c r="M238" s="10">
         <v>8750</v>
       </c>
-      <c r="N238" s="13">
+      <c r="N238" s="10">
         <v>481250</v>
       </c>
-      <c r="O238" s="14" t="str">
+      <c r="O238" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P238" s="15" t="str">
+      <c r="P238" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="239" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A239" s="11">
+      <c r="A239" s="8">
         <v>46112</v>
       </c>
-      <c r="B239" s="12" t="s">
+      <c r="B239" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C239" s="12" t="s">
+      <c r="C239" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D239" s="12" t="s">
+      <c r="D239" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E239" s="12" t="s">
+      <c r="E239" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F239" s="12">
+      <c r="F239" s="9">
         <v>774414059</v>
       </c>
-      <c r="G239" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H239" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I239" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J239" s="12" t="s">
+      <c r="G239" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J239" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K239" s="12" t="s">
+      <c r="K239" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L239" s="12">
+      <c r="L239" s="9">
         <v>50</v>
       </c>
-      <c r="M239" s="13">
+      <c r="M239" s="10">
         <v>8750</v>
       </c>
-      <c r="N239" s="13">
+      <c r="N239" s="10">
         <v>437500</v>
       </c>
-      <c r="O239" s="14" t="str">
+      <c r="O239" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P239" s="15" t="str">
+      <c r="P239" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="240" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A240" s="11">
+      <c r="A240" s="8">
         <v>46111</v>
       </c>
-      <c r="B240" s="12" t="s">
+      <c r="B240" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C240" s="12" t="s">
+      <c r="C240" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D240" s="12" t="s">
+      <c r="D240" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E240" s="12" t="s">
+      <c r="E240" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="F240" s="12">
+      <c r="F240" s="9">
         <v>774993694</v>
       </c>
-      <c r="G240" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H240" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I240" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J240" s="12" t="s">
+      <c r="G240" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H240" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J240" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="K240" s="12" t="s">
+      <c r="K240" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L240" s="12">
+      <c r="L240" s="9">
         <v>25</v>
       </c>
-      <c r="M240" s="13">
+      <c r="M240" s="10">
         <v>19500</v>
       </c>
-      <c r="N240" s="13">
+      <c r="N240" s="10">
         <v>487500</v>
       </c>
-      <c r="O240" s="14" t="str">
+      <c r="O240" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P240" s="15" t="str">
+      <c r="P240" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A241" s="11">
+      <c r="A241" s="8">
         <v>46111</v>
       </c>
-      <c r="B241" s="12" t="s">
+      <c r="B241" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C241" s="12" t="s">
+      <c r="C241" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D241" s="12" t="s">
+      <c r="D241" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E241" s="12" t="s">
+      <c r="E241" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="F241" s="12">
+      <c r="F241" s="9">
         <v>765434141</v>
       </c>
-      <c r="G241" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H241" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I241" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J241" s="12" t="s">
+      <c r="G241" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H241" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I241" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J241" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="K241" s="12" t="s">
+      <c r="K241" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L241" s="12">
+      <c r="L241" s="9">
         <v>25</v>
       </c>
-      <c r="M241" s="13">
+      <c r="M241" s="10">
         <v>26000</v>
       </c>
-      <c r="N241" s="13">
+      <c r="N241" s="10">
         <v>650000</v>
       </c>
-      <c r="O241" s="14" t="str">
+      <c r="O241" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P241" s="15" t="str">
+      <c r="P241" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A242" s="11">
+      <c r="A242" s="8">
         <v>46111</v>
       </c>
-      <c r="B242" s="12" t="s">
+      <c r="B242" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C242" s="12" t="s">
+      <c r="C242" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D242" s="12" t="s">
+      <c r="D242" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E242" s="12" t="s">
+      <c r="E242" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F242" s="12">
+      <c r="F242" s="9">
         <v>775544532</v>
       </c>
-      <c r="G242" s="12" t="s">
+      <c r="G242" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H242" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I242" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J242" s="12" t="s">
+      <c r="H242" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I242" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J242" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K242" s="12" t="s">
+      <c r="K242" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L242" s="12">
+      <c r="L242" s="9">
         <v>25</v>
       </c>
-      <c r="M242" s="13">
+      <c r="M242" s="10">
         <v>26000</v>
       </c>
-      <c r="N242" s="13">
+      <c r="N242" s="10">
         <v>650000</v>
       </c>
-      <c r="O242" s="14" t="str">
+      <c r="O242" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S14</v>
       </c>
-      <c r="P242" s="15" t="str">
+      <c r="P242" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mars</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A243" s="11">
+        <v>46122</v>
+      </c>
+      <c r="B243" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D243" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E243" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F243" s="12">
+        <v>773757278</v>
+      </c>
+      <c r="G243" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H243" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I243" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J243" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K243" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L243" s="12">
+        <v>25</v>
+      </c>
+      <c r="M243" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N243" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O243" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P243" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A244" s="11">
+        <v>46119</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C244" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D244" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E244" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F244" s="12">
+        <v>781282357</v>
+      </c>
+      <c r="G244" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H244" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I244" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J244" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K244" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L244" s="12">
+        <v>50</v>
+      </c>
+      <c r="M244" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N244" s="13">
+        <v>1300000</v>
+      </c>
+      <c r="O244" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P244" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A245" s="11">
+        <v>46119</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D245" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E245" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F245" s="12">
+        <v>775541532</v>
+      </c>
+      <c r="G245" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H245" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I245" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J245" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K245" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L245" s="12">
+        <v>25</v>
+      </c>
+      <c r="M245" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N245" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O245" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P245" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A246" s="11">
+        <v>46124</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D246" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E246" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="F246" s="12">
+        <v>773012416</v>
+      </c>
+      <c r="G246" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H246" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I246" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J246" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K246" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L246" s="12">
+        <v>10</v>
+      </c>
+      <c r="M246" s="13">
+        <v>12000</v>
+      </c>
+      <c r="N246" s="13">
+        <v>120000</v>
+      </c>
+      <c r="O246" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P246" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A247" s="11">
+        <v>46124</v>
+      </c>
+      <c r="B247" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D247" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E247" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="F247" s="12">
+        <v>773012416</v>
+      </c>
+      <c r="G247" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H247" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I247" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J247" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K247" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L247" s="12">
+        <v>10</v>
+      </c>
+      <c r="M247" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N247" s="13">
+        <v>90000</v>
+      </c>
+      <c r="O247" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P247" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A248" s="11">
+        <v>46124</v>
+      </c>
+      <c r="B248" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C248" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D248" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E248" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="F248" s="12">
+        <v>773012416</v>
+      </c>
+      <c r="G248" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H248" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I248" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J248" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K248" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="L248" s="12">
+        <v>2</v>
+      </c>
+      <c r="M248" s="13">
+        <v>17500</v>
+      </c>
+      <c r="N248" s="13">
+        <v>35000</v>
+      </c>
+      <c r="O248" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P248" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A249" s="11">
+        <v>46124</v>
+      </c>
+      <c r="B249" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D249" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E249" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="F249" s="12">
+        <v>773012416</v>
+      </c>
+      <c r="G249" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H249" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I249" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J249" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K249" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L249" s="12">
+        <v>7</v>
+      </c>
+      <c r="M249" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N249" s="13">
+        <v>182000</v>
+      </c>
+      <c r="O249" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P249" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A250" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C250" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D250" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E250" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F250" s="12">
+        <v>776180875</v>
+      </c>
+      <c r="G250" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H250" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I250" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J250" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K250" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L250" s="12">
+        <v>10</v>
+      </c>
+      <c r="M250" s="13">
+        <v>28000</v>
+      </c>
+      <c r="N250" s="13">
+        <v>280000</v>
+      </c>
+      <c r="O250" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P250" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A251" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B251" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C251" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D251" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E251" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F251" s="12">
+        <v>776180875</v>
+      </c>
+      <c r="G251" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H251" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I251" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J251" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K251" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L251" s="12">
+        <v>15</v>
+      </c>
+      <c r="M251" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N251" s="13">
+        <v>390000</v>
+      </c>
+      <c r="O251" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P251" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A252" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C252" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D252" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E252" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="F252" s="12">
+        <v>775411094</v>
+      </c>
+      <c r="G252" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H252" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I252" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J252" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K252" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L252" s="12">
+        <v>25</v>
+      </c>
+      <c r="M252" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N252" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O252" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P252" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A253" s="11">
+        <v>46119</v>
+      </c>
+      <c r="B253" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C253" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D253" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E253" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F253" s="12">
+        <v>776428218</v>
+      </c>
+      <c r="G253" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H253" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I253" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J253" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K253" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L253" s="12">
+        <v>1</v>
+      </c>
+      <c r="M253" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N253" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O253" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P253" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A254" s="11">
+        <v>46119</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C254" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D254" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E254" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F254" s="12">
+        <v>776428218</v>
+      </c>
+      <c r="G254" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H254" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I254" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J254" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K254" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="L254" s="12">
+        <v>1</v>
+      </c>
+      <c r="M254" s="13">
+        <v>18000</v>
+      </c>
+      <c r="N254" s="13">
+        <v>18000</v>
+      </c>
+      <c r="O254" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P254" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A255" s="11">
+        <v>46119</v>
+      </c>
+      <c r="B255" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C255" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D255" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E255" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F255" s="12">
+        <v>776428218</v>
+      </c>
+      <c r="G255" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H255" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I255" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J255" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K255" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L255" s="12">
+        <v>50</v>
+      </c>
+      <c r="M255" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N255" s="13">
+        <v>437500</v>
+      </c>
+      <c r="O255" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P255" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A256" s="11">
+        <v>46122</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D256" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E256" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="F256" s="12">
+        <v>774415358</v>
+      </c>
+      <c r="G256" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H256" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I256" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J256" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K256" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L256" s="12">
+        <v>30</v>
+      </c>
+      <c r="M256" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N256" s="13">
+        <v>270000</v>
+      </c>
+      <c r="O256" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P256" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A257" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B257" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D257" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E257" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F257" s="12">
+        <v>771166914</v>
+      </c>
+      <c r="G257" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H257" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I257" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J257" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K257" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L257" s="12">
+        <v>1</v>
+      </c>
+      <c r="M257" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N257" s="13">
+        <v>9000</v>
+      </c>
+      <c r="O257" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P257" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A258" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D258" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E258" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F258" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G258" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H258" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I258" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J258" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K258" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L258" s="12">
+        <v>25</v>
+      </c>
+      <c r="M258" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N258" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O258" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P258" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A259" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B259" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C259" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D259" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E259" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F259" s="12">
+        <v>775544532</v>
+      </c>
+      <c r="G259" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H259" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I259" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J259" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K259" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L259" s="12">
+        <v>1</v>
+      </c>
+      <c r="M259" s="13">
+        <v>15000</v>
+      </c>
+      <c r="N259" s="13">
+        <v>15000</v>
+      </c>
+      <c r="O259" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P259" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A260" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B260" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C260" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D260" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E260" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F260" s="12">
+        <v>776536527</v>
+      </c>
+      <c r="G260" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H260" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I260" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J260" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="K260" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L260" s="12">
+        <v>20</v>
+      </c>
+      <c r="M260" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N260" s="13">
+        <v>180000</v>
+      </c>
+      <c r="O260" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P260" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A261" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B261" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C261" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D261" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E261" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="F261" s="12">
+        <v>773546663</v>
+      </c>
+      <c r="G261" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H261" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I261" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J261" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K261" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L261" s="12">
+        <v>25</v>
+      </c>
+      <c r="M261" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N261" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O261" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P261" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A262" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B262" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C262" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D262" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E262" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F262" s="12">
+        <v>776536527</v>
+      </c>
+      <c r="G262" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H262" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I262" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J262" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="K262" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L262" s="12">
+        <v>10</v>
+      </c>
+      <c r="M262" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N262" s="13">
+        <v>90000</v>
+      </c>
+      <c r="O262" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P262" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A263" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B263" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C263" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D263" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E263" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F263" s="12">
+        <v>778657940</v>
+      </c>
+      <c r="G263" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H263" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I263" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J263" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="K263" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L263" s="12">
+        <v>25</v>
+      </c>
+      <c r="M263" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N263" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O263" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P263" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A264" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D264" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E264" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F264" s="12">
+        <v>778657940</v>
+      </c>
+      <c r="G264" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H264" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I264" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J264" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="K264" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L264" s="12">
+        <v>25</v>
+      </c>
+      <c r="M264" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N264" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O264" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P264" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A265" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B265" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D265" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E265" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="F265" s="12">
+        <v>776414102</v>
+      </c>
+      <c r="G265" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H265" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I265" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J265" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K265" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L265" s="12">
+        <v>75</v>
+      </c>
+      <c r="M265" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N265" s="13">
+        <v>675000</v>
+      </c>
+      <c r="O265" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P265" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A266" s="11">
+        <v>46121</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D266" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E266" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F266" s="12">
+        <v>773199049</v>
+      </c>
+      <c r="G266" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H266" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I266" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J266" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K266" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L266" s="12">
+        <v>15</v>
+      </c>
+      <c r="M266" s="13">
+        <v>53000</v>
+      </c>
+      <c r="N266" s="13">
+        <v>795000</v>
+      </c>
+      <c r="O266" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P266" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A267" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B267" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D267" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E267" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F267" s="12">
+        <v>775411988</v>
+      </c>
+      <c r="G267" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H267" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I267" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J267" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K267" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L267" s="12">
+        <v>1</v>
+      </c>
+      <c r="M267" s="13">
+        <v>33500</v>
+      </c>
+      <c r="N267" s="13">
+        <v>33500</v>
+      </c>
+      <c r="O267" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P267" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A268" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D268" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E268" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F268" s="12">
+        <v>775411988</v>
+      </c>
+      <c r="G268" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H268" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I268" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J268" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K268" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L268" s="12">
+        <v>25</v>
+      </c>
+      <c r="M268" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N268" s="13">
+        <v>650000</v>
+      </c>
+      <c r="O268" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P268" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A269" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B269" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D269" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E269" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F269" s="12">
+        <v>775411988</v>
+      </c>
+      <c r="G269" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H269" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I269" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J269" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K269" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L269" s="12">
+        <v>25</v>
+      </c>
+      <c r="M269" s="13">
+        <v>19500</v>
+      </c>
+      <c r="N269" s="13">
+        <v>487500</v>
+      </c>
+      <c r="O269" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P269" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A270" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C270" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D270" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E270" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F270" s="12">
+        <v>775411988</v>
+      </c>
+      <c r="G270" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H270" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I270" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J270" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K270" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L270" s="12">
+        <v>1</v>
+      </c>
+      <c r="M270" s="13">
+        <v>9000</v>
+      </c>
+      <c r="N270" s="13">
+        <v>9000</v>
+      </c>
+      <c r="O270" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P270" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A271" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B271" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D271" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E271" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="F271" s="12">
+        <v>776121781</v>
+      </c>
+      <c r="G271" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H271" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I271" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J271" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="K271" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L271" s="12">
+        <v>30</v>
+      </c>
+      <c r="M271" s="13">
+        <v>8750</v>
+      </c>
+      <c r="N271" s="13">
+        <v>262500</v>
+      </c>
+      <c r="O271" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P271" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A272" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C272" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D272" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E272" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="F272" s="12">
+        <v>776121781</v>
+      </c>
+      <c r="G272" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H272" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I272" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J272" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="K272" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L272" s="12">
+        <v>177</v>
+      </c>
+      <c r="M272" s="13">
+        <v>5500</v>
+      </c>
+      <c r="N272" s="13">
+        <v>973500</v>
+      </c>
+      <c r="O272" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P272" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A273" s="11">
+        <v>46120</v>
+      </c>
+      <c r="B273" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C273" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D273" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E273" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="F273" s="12">
+        <v>776121781</v>
+      </c>
+      <c r="G273" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H273" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I273" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J273" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="K273" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L273" s="12">
+        <v>100</v>
+      </c>
+      <c r="M273" s="13">
+        <v>26000</v>
+      </c>
+      <c r="N273" s="13">
+        <v>2600000</v>
+      </c>
+      <c r="O273" s="14" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P273" s="15" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BD0B66-C108-4B5C-9CA6-13039A0163AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266CE197-01D9-4798-BD59-DC365CBDD749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="218" yWindow="720" windowWidth="18982" windowHeight="10080" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="272">
   <si>
     <t>Date</t>
   </si>
@@ -917,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -947,19 +947,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1205,16 +1192,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1264,8 +1251,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P273" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17">
-  <autoFilter ref="A1:P273" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P275" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P275" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1578,7 +1565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P273"/>
+  <dimension ref="A1:P275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -14181,1613 +14168,1717 @@
       </c>
     </row>
     <row r="243" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A243" s="11">
+      <c r="A243" s="8">
         <v>46122</v>
       </c>
-      <c r="B243" s="12" t="s">
+      <c r="B243" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C243" s="12" t="s">
+      <c r="C243" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D243" s="12" t="s">
+      <c r="D243" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E243" s="12" t="s">
+      <c r="E243" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="F243" s="12">
+      <c r="F243" s="9">
         <v>773757278</v>
       </c>
-      <c r="G243" s="12" t="s">
+      <c r="G243" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="H243" s="12" t="s">
+      <c r="H243" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I243" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J243" s="12" t="s">
+      <c r="I243" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J243" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K243" s="12" t="s">
+      <c r="K243" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L243" s="12">
+      <c r="L243" s="9">
         <v>25</v>
       </c>
-      <c r="M243" s="13">
+      <c r="M243" s="10">
         <v>19500</v>
       </c>
-      <c r="N243" s="13">
+      <c r="N243" s="10">
         <v>487500</v>
       </c>
-      <c r="O243" s="14" t="str">
+      <c r="O243" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P243" s="15" t="str">
+      <c r="P243" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A244" s="11">
+      <c r="A244" s="8">
         <v>46119</v>
       </c>
-      <c r="B244" s="12" t="s">
+      <c r="B244" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C244" s="12" t="s">
+      <c r="C244" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D244" s="12" t="s">
+      <c r="D244" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E244" s="12" t="s">
+      <c r="E244" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="F244" s="12">
+      <c r="F244" s="9">
         <v>781282357</v>
       </c>
-      <c r="G244" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H244" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I244" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J244" s="12" t="s">
+      <c r="G244" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H244" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I244" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J244" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K244" s="12" t="s">
+      <c r="K244" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L244" s="12">
+      <c r="L244" s="9">
         <v>50</v>
       </c>
-      <c r="M244" s="13">
+      <c r="M244" s="10">
         <v>26000</v>
       </c>
-      <c r="N244" s="13">
+      <c r="N244" s="10">
         <v>1300000</v>
       </c>
-      <c r="O244" s="14" t="str">
+      <c r="O244" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P244" s="15" t="str">
+      <c r="P244" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A245" s="11">
+      <c r="A245" s="8">
         <v>46119</v>
       </c>
-      <c r="B245" s="12" t="s">
+      <c r="B245" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C245" s="12" t="s">
+      <c r="C245" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D245" s="12" t="s">
+      <c r="D245" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E245" s="12" t="s">
+      <c r="E245" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F245" s="12">
+      <c r="F245" s="9">
         <v>775541532</v>
       </c>
-      <c r="G245" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H245" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I245" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J245" s="12" t="s">
+      <c r="G245" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H245" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I245" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J245" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K245" s="12" t="s">
+      <c r="K245" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L245" s="12">
+      <c r="L245" s="9">
         <v>25</v>
       </c>
-      <c r="M245" s="13">
+      <c r="M245" s="10">
         <v>26000</v>
       </c>
-      <c r="N245" s="13">
+      <c r="N245" s="10">
         <v>650000</v>
       </c>
-      <c r="O245" s="14" t="str">
+      <c r="O245" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P245" s="15" t="str">
+      <c r="P245" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A246" s="11">
+      <c r="A246" s="8">
         <v>46124</v>
       </c>
-      <c r="B246" s="12" t="s">
+      <c r="B246" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C246" s="12" t="s">
+      <c r="C246" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D246" s="12" t="s">
+      <c r="D246" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E246" s="12" t="s">
+      <c r="E246" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F246" s="12">
+      <c r="F246" s="9">
         <v>773012416</v>
       </c>
-      <c r="G246" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H246" s="12" t="s">
+      <c r="G246" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H246" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I246" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J246" s="12" t="s">
+      <c r="I246" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J246" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K246" s="12" t="s">
+      <c r="K246" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L246" s="12">
+      <c r="L246" s="9">
         <v>10</v>
       </c>
-      <c r="M246" s="13">
+      <c r="M246" s="10">
         <v>12000</v>
       </c>
-      <c r="N246" s="13">
+      <c r="N246" s="10">
         <v>120000</v>
       </c>
-      <c r="O246" s="14" t="str">
+      <c r="O246" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P246" s="15" t="str">
+      <c r="P246" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A247" s="11">
+      <c r="A247" s="8">
         <v>46124</v>
       </c>
-      <c r="B247" s="12" t="s">
+      <c r="B247" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C247" s="12" t="s">
+      <c r="C247" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D247" s="12" t="s">
+      <c r="D247" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E247" s="12" t="s">
+      <c r="E247" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F247" s="12">
+      <c r="F247" s="9">
         <v>773012416</v>
       </c>
-      <c r="G247" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H247" s="12" t="s">
+      <c r="G247" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H247" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I247" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J247" s="12" t="s">
+      <c r="I247" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J247" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K247" s="12" t="s">
+      <c r="K247" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L247" s="12">
+      <c r="L247" s="9">
         <v>10</v>
       </c>
-      <c r="M247" s="13">
+      <c r="M247" s="10">
         <v>9000</v>
       </c>
-      <c r="N247" s="13">
+      <c r="N247" s="10">
         <v>90000</v>
       </c>
-      <c r="O247" s="14" t="str">
+      <c r="O247" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P247" s="15" t="str">
+      <c r="P247" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A248" s="11">
+      <c r="A248" s="8">
         <v>46124</v>
       </c>
-      <c r="B248" s="12" t="s">
+      <c r="B248" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C248" s="12" t="s">
+      <c r="C248" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D248" s="12" t="s">
+      <c r="D248" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E248" s="12" t="s">
+      <c r="E248" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F248" s="12">
+      <c r="F248" s="9">
         <v>773012416</v>
       </c>
-      <c r="G248" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H248" s="12" t="s">
+      <c r="G248" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H248" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I248" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J248" s="12" t="s">
+      <c r="I248" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J248" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K248" s="12" t="s">
+      <c r="K248" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L248" s="12">
+      <c r="L248" s="9">
         <v>2</v>
       </c>
-      <c r="M248" s="13">
+      <c r="M248" s="10">
         <v>17500</v>
       </c>
-      <c r="N248" s="13">
+      <c r="N248" s="10">
         <v>35000</v>
       </c>
-      <c r="O248" s="14" t="str">
+      <c r="O248" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P248" s="15" t="str">
+      <c r="P248" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A249" s="11">
+      <c r="A249" s="8">
         <v>46124</v>
       </c>
-      <c r="B249" s="12" t="s">
+      <c r="B249" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C249" s="12" t="s">
+      <c r="C249" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D249" s="12" t="s">
+      <c r="D249" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="E249" s="12" t="s">
+      <c r="E249" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F249" s="12">
+      <c r="F249" s="9">
         <v>773012416</v>
       </c>
-      <c r="G249" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H249" s="12" t="s">
+      <c r="G249" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H249" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I249" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J249" s="12" t="s">
+      <c r="I249" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J249" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K249" s="12" t="s">
+      <c r="K249" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L249" s="12">
+      <c r="L249" s="9">
         <v>7</v>
       </c>
-      <c r="M249" s="13">
+      <c r="M249" s="10">
         <v>26000</v>
       </c>
-      <c r="N249" s="13">
+      <c r="N249" s="10">
         <v>182000</v>
       </c>
-      <c r="O249" s="14" t="str">
+      <c r="O249" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P249" s="15" t="str">
+      <c r="P249" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="250" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A250" s="11">
+      <c r="A250" s="8">
         <v>46121</v>
       </c>
-      <c r="B250" s="12" t="s">
+      <c r="B250" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C250" s="12" t="s">
+      <c r="C250" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D250" s="12" t="s">
+      <c r="D250" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E250" s="12" t="s">
+      <c r="E250" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F250" s="12">
+      <c r="F250" s="9">
         <v>776180875</v>
       </c>
-      <c r="G250" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H250" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I250" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J250" s="12" t="s">
+      <c r="G250" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H250" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I250" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J250" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K250" s="12" t="s">
+      <c r="K250" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L250" s="12">
+      <c r="L250" s="9">
         <v>10</v>
       </c>
-      <c r="M250" s="13">
+      <c r="M250" s="10">
         <v>28000</v>
       </c>
-      <c r="N250" s="13">
+      <c r="N250" s="10">
         <v>280000</v>
       </c>
-      <c r="O250" s="14" t="str">
+      <c r="O250" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P250" s="15" t="str">
+      <c r="P250" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="251" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A251" s="11">
+      <c r="A251" s="8">
         <v>46121</v>
       </c>
-      <c r="B251" s="12" t="s">
+      <c r="B251" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C251" s="12" t="s">
+      <c r="C251" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D251" s="12" t="s">
+      <c r="D251" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E251" s="12" t="s">
+      <c r="E251" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F251" s="12">
+      <c r="F251" s="9">
         <v>776180875</v>
       </c>
-      <c r="G251" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H251" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I251" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J251" s="12" t="s">
+      <c r="G251" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H251" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I251" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J251" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K251" s="12" t="s">
+      <c r="K251" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L251" s="12">
+      <c r="L251" s="9">
         <v>15</v>
       </c>
-      <c r="M251" s="13">
+      <c r="M251" s="10">
         <v>26000</v>
       </c>
-      <c r="N251" s="13">
+      <c r="N251" s="10">
         <v>390000</v>
       </c>
-      <c r="O251" s="14" t="str">
+      <c r="O251" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P251" s="15" t="str">
+      <c r="P251" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A252" s="11">
+      <c r="A252" s="8">
         <v>46121</v>
       </c>
-      <c r="B252" s="12" t="s">
+      <c r="B252" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C252" s="12" t="s">
+      <c r="C252" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D252" s="12" t="s">
+      <c r="D252" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E252" s="12" t="s">
+      <c r="E252" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="F252" s="12">
+      <c r="F252" s="9">
         <v>775411094</v>
       </c>
-      <c r="G252" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H252" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I252" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J252" s="12" t="s">
+      <c r="G252" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H252" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I252" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J252" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K252" s="12" t="s">
+      <c r="K252" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L252" s="12">
+      <c r="L252" s="9">
         <v>25</v>
       </c>
-      <c r="M252" s="13">
+      <c r="M252" s="10">
         <v>26000</v>
       </c>
-      <c r="N252" s="13">
+      <c r="N252" s="10">
         <v>650000</v>
       </c>
-      <c r="O252" s="14" t="str">
+      <c r="O252" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P252" s="15" t="str">
+      <c r="P252" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="253" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A253" s="11">
+      <c r="A253" s="8">
         <v>46119</v>
       </c>
-      <c r="B253" s="12" t="s">
+      <c r="B253" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C253" s="12" t="s">
+      <c r="C253" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D253" s="12" t="s">
+      <c r="D253" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E253" s="12" t="s">
+      <c r="E253" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F253" s="12">
+      <c r="F253" s="9">
         <v>776428218</v>
       </c>
-      <c r="G253" s="12" t="s">
+      <c r="G253" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H253" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I253" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J253" s="12" t="s">
+      <c r="H253" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I253" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J253" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K253" s="12" t="s">
+      <c r="K253" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L253" s="12">
+      <c r="L253" s="9">
         <v>1</v>
       </c>
-      <c r="M253" s="13">
+      <c r="M253" s="10">
         <v>18000</v>
       </c>
-      <c r="N253" s="13">
+      <c r="N253" s="10">
         <v>18000</v>
       </c>
-      <c r="O253" s="14" t="str">
+      <c r="O253" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P253" s="15" t="str">
+      <c r="P253" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="254" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A254" s="11">
+      <c r="A254" s="8">
         <v>46119</v>
       </c>
-      <c r="B254" s="12" t="s">
+      <c r="B254" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C254" s="12" t="s">
+      <c r="C254" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D254" s="12" t="s">
+      <c r="D254" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E254" s="12" t="s">
+      <c r="E254" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F254" s="12">
+      <c r="F254" s="9">
         <v>776428218</v>
       </c>
-      <c r="G254" s="12" t="s">
+      <c r="G254" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H254" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I254" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J254" s="12" t="s">
+      <c r="H254" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I254" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J254" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K254" s="12" t="s">
+      <c r="K254" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="L254" s="12">
+      <c r="L254" s="9">
         <v>1</v>
       </c>
-      <c r="M254" s="13">
+      <c r="M254" s="10">
         <v>18000</v>
       </c>
-      <c r="N254" s="13">
+      <c r="N254" s="10">
         <v>18000</v>
       </c>
-      <c r="O254" s="14" t="str">
+      <c r="O254" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P254" s="15" t="str">
+      <c r="P254" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="255" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A255" s="11">
+      <c r="A255" s="8">
         <v>46119</v>
       </c>
-      <c r="B255" s="12" t="s">
+      <c r="B255" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C255" s="12" t="s">
+      <c r="C255" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D255" s="12" t="s">
+      <c r="D255" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E255" s="12" t="s">
+      <c r="E255" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F255" s="12">
+      <c r="F255" s="9">
         <v>776428218</v>
       </c>
-      <c r="G255" s="12" t="s">
+      <c r="G255" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H255" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I255" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J255" s="12" t="s">
+      <c r="H255" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I255" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J255" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K255" s="12" t="s">
+      <c r="K255" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L255" s="12">
+      <c r="L255" s="9">
         <v>50</v>
       </c>
-      <c r="M255" s="13">
+      <c r="M255" s="10">
         <v>8750</v>
       </c>
-      <c r="N255" s="13">
+      <c r="N255" s="10">
         <v>437500</v>
       </c>
-      <c r="O255" s="14" t="str">
+      <c r="O255" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P255" s="15" t="str">
+      <c r="P255" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A256" s="11">
+      <c r="A256" s="8">
         <v>46122</v>
       </c>
-      <c r="B256" s="12" t="s">
+      <c r="B256" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C256" s="12" t="s">
+      <c r="C256" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D256" s="12" t="s">
+      <c r="D256" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E256" s="12" t="s">
+      <c r="E256" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="F256" s="12">
+      <c r="F256" s="9">
         <v>774415358</v>
       </c>
-      <c r="G256" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H256" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I256" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J256" s="12" t="s">
+      <c r="G256" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H256" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I256" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J256" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K256" s="12" t="s">
+      <c r="K256" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L256" s="12">
+      <c r="L256" s="9">
         <v>30</v>
       </c>
-      <c r="M256" s="13">
+      <c r="M256" s="10">
         <v>9000</v>
       </c>
-      <c r="N256" s="13">
+      <c r="N256" s="10">
         <v>270000</v>
       </c>
-      <c r="O256" s="14" t="str">
+      <c r="O256" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P256" s="15" t="str">
+      <c r="P256" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A257" s="11">
+      <c r="A257" s="8">
         <v>46121</v>
       </c>
-      <c r="B257" s="12" t="s">
+      <c r="B257" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C257" s="12" t="s">
+      <c r="C257" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D257" s="12" t="s">
+      <c r="D257" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E257" s="12" t="s">
+      <c r="E257" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F257" s="12">
+      <c r="F257" s="9">
         <v>771166914</v>
       </c>
-      <c r="G257" s="12" t="s">
+      <c r="G257" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H257" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I257" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J257" s="12" t="s">
+      <c r="H257" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I257" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J257" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K257" s="12" t="s">
+      <c r="K257" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L257" s="12">
+      <c r="L257" s="9">
         <v>1</v>
       </c>
-      <c r="M257" s="13">
+      <c r="M257" s="10">
         <v>9000</v>
       </c>
-      <c r="N257" s="13">
+      <c r="N257" s="10">
         <v>9000</v>
       </c>
-      <c r="O257" s="14" t="str">
+      <c r="O257" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P257" s="15" t="str">
+      <c r="P257" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A258" s="11">
+      <c r="A258" s="8">
         <v>46121</v>
       </c>
-      <c r="B258" s="12" t="s">
+      <c r="B258" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C258" s="12" t="s">
+      <c r="C258" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D258" s="12" t="s">
+      <c r="D258" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E258" s="12" t="s">
+      <c r="E258" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F258" s="12">
+      <c r="F258" s="9">
         <v>775544532</v>
       </c>
-      <c r="G258" s="12" t="s">
+      <c r="G258" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H258" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I258" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J258" s="12" t="s">
+      <c r="H258" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I258" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J258" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K258" s="12" t="s">
+      <c r="K258" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L258" s="12">
+      <c r="L258" s="9">
         <v>25</v>
       </c>
-      <c r="M258" s="13">
+      <c r="M258" s="10">
         <v>26000</v>
       </c>
-      <c r="N258" s="13">
+      <c r="N258" s="10">
         <v>650000</v>
       </c>
-      <c r="O258" s="14" t="str">
+      <c r="O258" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P258" s="15" t="str">
+      <c r="P258" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="259" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A259" s="11">
+      <c r="A259" s="8">
         <v>46121</v>
       </c>
-      <c r="B259" s="12" t="s">
+      <c r="B259" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C259" s="12" t="s">
+      <c r="C259" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D259" s="12" t="s">
+      <c r="D259" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E259" s="12" t="s">
+      <c r="E259" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F259" s="12">
+      <c r="F259" s="9">
         <v>775544532</v>
       </c>
-      <c r="G259" s="12" t="s">
+      <c r="G259" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H259" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I259" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J259" s="12" t="s">
+      <c r="H259" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I259" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J259" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K259" s="12" t="s">
+      <c r="K259" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="L259" s="12">
+      <c r="L259" s="9">
         <v>1</v>
       </c>
-      <c r="M259" s="13">
+      <c r="M259" s="10">
         <v>15000</v>
       </c>
-      <c r="N259" s="13">
+      <c r="N259" s="10">
         <v>15000</v>
       </c>
-      <c r="O259" s="14" t="str">
+      <c r="O259" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P259" s="15" t="str">
+      <c r="P259" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A260" s="11">
+      <c r="A260" s="8">
         <v>46121</v>
       </c>
-      <c r="B260" s="12" t="s">
+      <c r="B260" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C260" s="12" t="s">
+      <c r="C260" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D260" s="12" t="s">
+      <c r="D260" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E260" s="12" t="s">
+      <c r="E260" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F260" s="12">
+      <c r="F260" s="9">
         <v>776536527</v>
       </c>
-      <c r="G260" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H260" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I260" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J260" s="12" t="s">
+      <c r="G260" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H260" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I260" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J260" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="K260" s="12" t="s">
+      <c r="K260" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L260" s="12">
+      <c r="L260" s="9">
         <v>20</v>
       </c>
-      <c r="M260" s="13">
+      <c r="M260" s="10">
         <v>9000</v>
       </c>
-      <c r="N260" s="13">
+      <c r="N260" s="10">
         <v>180000</v>
       </c>
-      <c r="O260" s="14" t="str">
+      <c r="O260" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P260" s="15" t="str">
+      <c r="P260" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="261" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A261" s="11">
+      <c r="A261" s="8">
         <v>46121</v>
       </c>
-      <c r="B261" s="12" t="s">
+      <c r="B261" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C261" s="12" t="s">
+      <c r="C261" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D261" s="12" t="s">
+      <c r="D261" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E261" s="12" t="s">
+      <c r="E261" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="F261" s="12">
+      <c r="F261" s="9">
         <v>773546663</v>
       </c>
-      <c r="G261" s="12" t="s">
+      <c r="G261" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H261" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I261" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J261" s="12" t="s">
+      <c r="H261" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I261" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J261" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K261" s="12" t="s">
+      <c r="K261" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L261" s="12">
+      <c r="L261" s="9">
         <v>25</v>
       </c>
-      <c r="M261" s="13">
+      <c r="M261" s="10">
         <v>26000</v>
       </c>
-      <c r="N261" s="13">
+      <c r="N261" s="10">
         <v>650000</v>
       </c>
-      <c r="O261" s="14" t="str">
+      <c r="O261" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P261" s="15" t="str">
+      <c r="P261" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="262" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A262" s="11">
+      <c r="A262" s="8">
         <v>46121</v>
       </c>
-      <c r="B262" s="12" t="s">
+      <c r="B262" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C262" s="12" t="s">
+      <c r="C262" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D262" s="12" t="s">
+      <c r="D262" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E262" s="12" t="s">
+      <c r="E262" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F262" s="12">
+      <c r="F262" s="9">
         <v>776536527</v>
       </c>
-      <c r="G262" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H262" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I262" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J262" s="12" t="s">
+      <c r="G262" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H262" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I262" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J262" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="K262" s="12" t="s">
+      <c r="K262" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L262" s="12">
+      <c r="L262" s="9">
         <v>10</v>
       </c>
-      <c r="M262" s="13">
+      <c r="M262" s="10">
         <v>9000</v>
       </c>
-      <c r="N262" s="13">
+      <c r="N262" s="10">
         <v>90000</v>
       </c>
-      <c r="O262" s="14" t="str">
+      <c r="O262" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P262" s="15" t="str">
+      <c r="P262" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="263" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A263" s="11">
+      <c r="A263" s="8">
         <v>46121</v>
       </c>
-      <c r="B263" s="12" t="s">
+      <c r="B263" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C263" s="12" t="s">
+      <c r="C263" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D263" s="12" t="s">
+      <c r="D263" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E263" s="12" t="s">
+      <c r="E263" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F263" s="12">
+      <c r="F263" s="9">
         <v>778657940</v>
       </c>
-      <c r="G263" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H263" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I263" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J263" s="12" t="s">
+      <c r="G263" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H263" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I263" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J263" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="K263" s="12" t="s">
+      <c r="K263" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L263" s="12">
+      <c r="L263" s="9">
         <v>25</v>
       </c>
-      <c r="M263" s="13">
+      <c r="M263" s="10">
         <v>26000</v>
       </c>
-      <c r="N263" s="13">
+      <c r="N263" s="10">
         <v>650000</v>
       </c>
-      <c r="O263" s="14" t="str">
+      <c r="O263" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P263" s="15" t="str">
+      <c r="P263" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="264" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A264" s="11">
+      <c r="A264" s="8">
         <v>46121</v>
       </c>
-      <c r="B264" s="12" t="s">
+      <c r="B264" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C264" s="12" t="s">
+      <c r="C264" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D264" s="12" t="s">
+      <c r="D264" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E264" s="12" t="s">
+      <c r="E264" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F264" s="12">
+      <c r="F264" s="9">
         <v>778657940</v>
       </c>
-      <c r="G264" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H264" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I264" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J264" s="12" t="s">
+      <c r="G264" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H264" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I264" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J264" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="K264" s="12" t="s">
+      <c r="K264" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L264" s="12">
+      <c r="L264" s="9">
         <v>25</v>
       </c>
-      <c r="M264" s="13">
+      <c r="M264" s="10">
         <v>19500</v>
       </c>
-      <c r="N264" s="13">
+      <c r="N264" s="10">
         <v>487500</v>
       </c>
-      <c r="O264" s="14" t="str">
+      <c r="O264" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P264" s="15" t="str">
+      <c r="P264" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A265" s="11">
+      <c r="A265" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F265" s="9">
+        <v>778657940</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H265" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I265" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J265" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="K265" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L265" s="9">
+        <v>25</v>
+      </c>
+      <c r="M265" s="10">
+        <v>26000</v>
+      </c>
+      <c r="N265" s="10">
+        <v>650000</v>
+      </c>
+      <c r="O265" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P265" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A266" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C266" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D266" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E266" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="F266" s="9">
+        <v>778657940</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H266" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I266" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J266" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="K266" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L266" s="9">
+        <v>25</v>
+      </c>
+      <c r="M266" s="10">
+        <v>32000</v>
+      </c>
+      <c r="N266" s="10">
+        <v>800000</v>
+      </c>
+      <c r="O266" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S15</v>
+      </c>
+      <c r="P266" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A267" s="8">
         <v>46121</v>
       </c>
-      <c r="B265" s="12" t="s">
+      <c r="B267" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C265" s="12" t="s">
+      <c r="C267" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D265" s="12" t="s">
+      <c r="D267" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E265" s="12" t="s">
+      <c r="E267" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F265" s="12">
+      <c r="F267" s="9">
         <v>776414102</v>
       </c>
-      <c r="G265" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H265" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I265" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J265" s="12" t="s">
+      <c r="G267" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H267" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I267" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J267" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K265" s="12" t="s">
+      <c r="K267" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L265" s="12">
+      <c r="L267" s="9">
         <v>75</v>
       </c>
-      <c r="M265" s="13">
+      <c r="M267" s="10">
         <v>9000</v>
       </c>
-      <c r="N265" s="13">
+      <c r="N267" s="10">
         <v>675000</v>
       </c>
-      <c r="O265" s="14" t="str">
+      <c r="O267" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P265" s="15" t="str">
+      <c r="P267" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="266" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A266" s="11">
+    <row r="268" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A268" s="8">
         <v>46121</v>
       </c>
-      <c r="B266" s="12" t="s">
+      <c r="B268" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C266" s="12" t="s">
+      <c r="C268" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D266" s="12" t="s">
+      <c r="D268" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E266" s="12" t="s">
+      <c r="E268" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="F266" s="12">
+      <c r="F268" s="9">
         <v>773199049</v>
       </c>
-      <c r="G266" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H266" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I266" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J266" s="12" t="s">
+      <c r="G268" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H268" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I268" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J268" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K266" s="12" t="s">
+      <c r="K268" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L266" s="12">
+      <c r="L268" s="9">
         <v>15</v>
       </c>
-      <c r="M266" s="13">
+      <c r="M268" s="10">
         <v>53000</v>
       </c>
-      <c r="N266" s="13">
+      <c r="N268" s="10">
         <v>795000</v>
       </c>
-      <c r="O266" s="14" t="str">
+      <c r="O268" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P266" s="15" t="str">
+      <c r="P268" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="267" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A267" s="11">
+    <row r="269" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A269" s="8">
         <v>46120</v>
       </c>
-      <c r="B267" s="12" t="s">
+      <c r="B269" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C267" s="12" t="s">
+      <c r="C269" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D267" s="12" t="s">
+      <c r="D269" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E267" s="12" t="s">
+      <c r="E269" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F267" s="12">
+      <c r="F269" s="9">
         <v>775411988</v>
       </c>
-      <c r="G267" s="12" t="s">
+      <c r="G269" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H267" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I267" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J267" s="12" t="s">
+      <c r="H269" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I269" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J269" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K267" s="12" t="s">
+      <c r="K269" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="L267" s="12">
+      <c r="L269" s="9">
         <v>1</v>
       </c>
-      <c r="M267" s="13">
+      <c r="M269" s="10">
         <v>33500</v>
       </c>
-      <c r="N267" s="13">
+      <c r="N269" s="10">
         <v>33500</v>
       </c>
-      <c r="O267" s="14" t="str">
+      <c r="O269" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P267" s="15" t="str">
+      <c r="P269" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="268" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A268" s="11">
+    <row r="270" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A270" s="8">
         <v>46120</v>
       </c>
-      <c r="B268" s="12" t="s">
+      <c r="B270" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C268" s="12" t="s">
+      <c r="C270" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D268" s="12" t="s">
+      <c r="D270" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E268" s="12" t="s">
+      <c r="E270" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F268" s="12">
+      <c r="F270" s="9">
         <v>775411988</v>
       </c>
-      <c r="G268" s="12" t="s">
+      <c r="G270" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H268" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I268" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J268" s="12" t="s">
+      <c r="H270" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I270" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J270" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K268" s="12" t="s">
+      <c r="K270" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L268" s="12">
+      <c r="L270" s="9">
         <v>25</v>
       </c>
-      <c r="M268" s="13">
+      <c r="M270" s="10">
         <v>26000</v>
       </c>
-      <c r="N268" s="13">
+      <c r="N270" s="10">
         <v>650000</v>
       </c>
-      <c r="O268" s="14" t="str">
+      <c r="O270" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P268" s="15" t="str">
+      <c r="P270" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="269" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A269" s="11">
+    <row r="271" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A271" s="8">
         <v>46120</v>
       </c>
-      <c r="B269" s="12" t="s">
+      <c r="B271" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C269" s="12" t="s">
+      <c r="C271" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D269" s="12" t="s">
+      <c r="D271" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E269" s="12" t="s">
+      <c r="E271" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F269" s="12">
+      <c r="F271" s="9">
         <v>775411988</v>
       </c>
-      <c r="G269" s="12" t="s">
+      <c r="G271" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H269" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I269" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J269" s="12" t="s">
+      <c r="H271" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I271" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J271" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K269" s="12" t="s">
+      <c r="K271" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L269" s="12">
+      <c r="L271" s="9">
         <v>25</v>
       </c>
-      <c r="M269" s="13">
+      <c r="M271" s="10">
         <v>19500</v>
       </c>
-      <c r="N269" s="13">
+      <c r="N271" s="10">
         <v>487500</v>
       </c>
-      <c r="O269" s="14" t="str">
+      <c r="O271" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P269" s="15" t="str">
+      <c r="P271" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="270" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A270" s="11">
+    <row r="272" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A272" s="8">
         <v>46120</v>
       </c>
-      <c r="B270" s="12" t="s">
+      <c r="B272" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C270" s="12" t="s">
+      <c r="C272" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D270" s="12" t="s">
+      <c r="D272" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E270" s="12" t="s">
+      <c r="E272" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F270" s="12">
+      <c r="F272" s="9">
         <v>775411988</v>
       </c>
-      <c r="G270" s="12" t="s">
+      <c r="G272" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H270" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I270" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J270" s="12" t="s">
+      <c r="H272" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I272" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J272" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K270" s="12" t="s">
+      <c r="K272" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L270" s="12">
+      <c r="L272" s="9">
         <v>1</v>
       </c>
-      <c r="M270" s="13">
+      <c r="M272" s="10">
         <v>9000</v>
       </c>
-      <c r="N270" s="13">
+      <c r="N272" s="10">
         <v>9000</v>
       </c>
-      <c r="O270" s="14" t="str">
+      <c r="O272" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P270" s="15" t="str">
+      <c r="P272" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="271" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A271" s="11">
+    <row r="273" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A273" s="8">
         <v>46120</v>
       </c>
-      <c r="B271" s="12" t="s">
+      <c r="B273" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C271" s="12" t="s">
+      <c r="C273" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D271" s="12" t="s">
+      <c r="D273" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E271" s="12" t="s">
+      <c r="E273" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F271" s="12">
+      <c r="F273" s="9">
         <v>776121781</v>
       </c>
-      <c r="G271" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H271" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I271" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J271" s="12" t="s">
+      <c r="G273" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H273" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I273" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J273" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="K271" s="12" t="s">
+      <c r="K273" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L271" s="12">
+      <c r="L273" s="9">
         <v>30</v>
       </c>
-      <c r="M271" s="13">
+      <c r="M273" s="10">
         <v>8750</v>
       </c>
-      <c r="N271" s="13">
+      <c r="N273" s="10">
         <v>262500</v>
       </c>
-      <c r="O271" s="14" t="str">
+      <c r="O273" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P271" s="15" t="str">
+      <c r="P273" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="272" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A272" s="11">
+    <row r="274" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A274" s="8">
         <v>46120</v>
       </c>
-      <c r="B272" s="12" t="s">
+      <c r="B274" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C272" s="12" t="s">
+      <c r="C274" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D272" s="12" t="s">
+      <c r="D274" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E272" s="12" t="s">
+      <c r="E274" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F272" s="12">
+      <c r="F274" s="9">
         <v>776121781</v>
       </c>
-      <c r="G272" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H272" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I272" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J272" s="12" t="s">
+      <c r="G274" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H274" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I274" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J274" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="K272" s="12" t="s">
+      <c r="K274" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L272" s="12">
+      <c r="L274" s="9">
         <v>177</v>
       </c>
-      <c r="M272" s="13">
+      <c r="M274" s="10">
         <v>5500</v>
       </c>
-      <c r="N272" s="13">
+      <c r="N274" s="10">
         <v>973500</v>
       </c>
-      <c r="O272" s="14" t="str">
+      <c r="O274" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P272" s="15" t="str">
+      <c r="P274" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
-    <row r="273" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A273" s="11">
+    <row r="275" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A275" s="8">
         <v>46120</v>
       </c>
-      <c r="B273" s="12" t="s">
+      <c r="B275" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C273" s="12" t="s">
+      <c r="C275" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D273" s="12" t="s">
+      <c r="D275" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E273" s="12" t="s">
+      <c r="E275" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F273" s="12">
+      <c r="F275" s="9">
         <v>776121781</v>
       </c>
-      <c r="G273" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H273" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I273" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J273" s="12" t="s">
+      <c r="G275" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H275" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I275" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J275" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="K273" s="12" t="s">
+      <c r="K275" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L273" s="12">
+      <c r="L275" s="9">
         <v>100</v>
       </c>
-      <c r="M273" s="13">
+      <c r="M275" s="10">
         <v>26000</v>
       </c>
-      <c r="N273" s="13">
+      <c r="N275" s="10">
         <v>2600000</v>
       </c>
-      <c r="O273" s="14" t="str">
+      <c r="O275" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S15</v>
       </c>
-      <c r="P273" s="15" t="str">
+      <c r="P275" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266CE197-01D9-4798-BD59-DC365CBDD749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F39375-4229-4139-892F-2CA51F4F8D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="300">
   <si>
     <t>Date</t>
   </si>
@@ -850,6 +850,90 @@
   </si>
   <si>
     <t>Client satisfait</t>
+  </si>
+  <si>
+    <t>Ibrahima</t>
+  </si>
+  <si>
+    <t>Chocolat transparent 200gx24pcs</t>
+  </si>
+  <si>
+    <t>Chocolat transparent 400gx12pcs</t>
+  </si>
+  <si>
+    <t>Meadowlite 25Kg</t>
+  </si>
+  <si>
+    <t>Souhaibou</t>
+  </si>
+  <si>
+    <t>KEUR MASSAR N°2</t>
+  </si>
+  <si>
+    <t>Bayakh</t>
+  </si>
+  <si>
+    <t>Bada THIAW</t>
+  </si>
+  <si>
+    <t>Tournal Yeumbeul</t>
+  </si>
+  <si>
+    <t>ALPHA DIALLO</t>
+  </si>
+  <si>
+    <t>SEYNABOU BA</t>
+  </si>
+  <si>
+    <t>Matar Ndaiye</t>
+  </si>
+  <si>
+    <t>Fallou</t>
+  </si>
+  <si>
+    <t>Chocolat jaune 200g x 24 pcs</t>
+  </si>
+  <si>
+    <t>Khassa Diop</t>
+  </si>
+  <si>
+    <t>Mame  Gor</t>
+  </si>
+  <si>
+    <t>Korka</t>
+  </si>
+  <si>
+    <t>Pa Sylla</t>
+  </si>
+  <si>
+    <t>Idrissa</t>
+  </si>
+  <si>
+    <t>Modou</t>
+  </si>
+  <si>
+    <t>Darro TOURE</t>
+  </si>
+  <si>
+    <t>Tapha</t>
+  </si>
+  <si>
+    <t>Mamodou DIALLO</t>
+  </si>
+  <si>
+    <t>Mactar Diallo</t>
+  </si>
+  <si>
+    <t>Supermarché le cayor</t>
+  </si>
+  <si>
+    <t>Gueye et frère</t>
+  </si>
+  <si>
+    <t>Mamadou DIBA</t>
+  </si>
+  <si>
+    <t>Supermarché</t>
   </si>
 </sst>
 </file>
@@ -917,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -947,6 +1031,22 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1251,8 +1351,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P275" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P275" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P329" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P329" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1565,7 +1665,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P275"/>
+  <dimension ref="A1:P329"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -15883,6 +15983,2814 @@
         <v>avril</v>
       </c>
     </row>
+    <row r="276" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A276" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D276" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E276" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F276" s="13">
+        <v>777739323</v>
+      </c>
+      <c r="G276" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H276" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I276" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J276" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K276" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L276" s="12">
+        <v>30</v>
+      </c>
+      <c r="M276" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N276" s="14">
+        <v>270000</v>
+      </c>
+      <c r="O276" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P276" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A277" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B277" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C277" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D277" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E277" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F277" s="13">
+        <v>777739323</v>
+      </c>
+      <c r="G277" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H277" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I277" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J277" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K277" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L277" s="12">
+        <v>3</v>
+      </c>
+      <c r="M277" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N277" s="14">
+        <v>84000</v>
+      </c>
+      <c r="O277" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P277" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A278" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C278" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D278" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E278" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F278" s="13">
+        <v>779486095</v>
+      </c>
+      <c r="G278" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H278" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I278" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J278" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K278" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="L278" s="12">
+        <v>15</v>
+      </c>
+      <c r="M278" s="14">
+        <v>12500</v>
+      </c>
+      <c r="N278" s="14">
+        <v>187500</v>
+      </c>
+      <c r="O278" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P278" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A279" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B279" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="C279" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D279" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E279" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F279" s="13">
+        <v>779486095</v>
+      </c>
+      <c r="G279" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H279" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I279" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J279" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K279" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="L279" s="12">
+        <v>10</v>
+      </c>
+      <c r="M279" s="14">
+        <v>12500</v>
+      </c>
+      <c r="N279" s="14">
+        <v>125000</v>
+      </c>
+      <c r="O279" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P279" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A280" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C280" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D280" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E280" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F280" s="13">
+        <v>778356666</v>
+      </c>
+      <c r="G280" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H280" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I280" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J280" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K280" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L280" s="12">
+        <v>25</v>
+      </c>
+      <c r="M280" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N280" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O280" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P280" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A281" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B281" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C281" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D281" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E281" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F281" s="13">
+        <v>774216339</v>
+      </c>
+      <c r="G281" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H281" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I281" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J281" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="K281" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L281" s="12">
+        <v>50</v>
+      </c>
+      <c r="M281" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N281" s="14">
+        <v>1300000</v>
+      </c>
+      <c r="O281" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P281" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A282" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C282" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D282" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E282" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F282" s="13">
+        <v>774216339</v>
+      </c>
+      <c r="G282" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H282" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I282" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J282" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="K282" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L282" s="12">
+        <v>5</v>
+      </c>
+      <c r="M282" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N282" s="14">
+        <v>97500</v>
+      </c>
+      <c r="O282" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P282" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A283" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B283" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C283" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D283" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E283" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F283" s="13">
+        <v>776634479</v>
+      </c>
+      <c r="G283" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H283" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I283" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J283" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K283" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L283" s="12">
+        <v>25</v>
+      </c>
+      <c r="M283" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N283" s="14">
+        <v>1325000</v>
+      </c>
+      <c r="O283" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P283" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A284" s="11">
+        <v>46125</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C284" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D284" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E284" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="F284" s="13">
+        <v>774624747</v>
+      </c>
+      <c r="G284" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H284" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I284" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J284" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K284" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L284" s="12">
+        <v>20</v>
+      </c>
+      <c r="M284" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N284" s="14">
+        <v>180000</v>
+      </c>
+      <c r="O284" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P284" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A285" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B285" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C285" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D285" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="E285" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F285" s="13">
+        <v>779598695</v>
+      </c>
+      <c r="G285" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H285" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I285" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J285" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K285" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L285" s="12">
+        <v>25</v>
+      </c>
+      <c r="M285" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N285" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O285" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P285" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A286" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C286" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D286" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E286" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F286" s="13">
+        <v>773531341</v>
+      </c>
+      <c r="G286" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H286" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I286" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J286" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K286" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L286" s="12">
+        <v>1</v>
+      </c>
+      <c r="M286" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N286" s="14">
+        <v>53000</v>
+      </c>
+      <c r="O286" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P286" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A287" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B287" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C287" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D287" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E287" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F287" s="13">
+        <v>775586819</v>
+      </c>
+      <c r="G287" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H287" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I287" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J287" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K287" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L287" s="12">
+        <v>25</v>
+      </c>
+      <c r="M287" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N287" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O287" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P287" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A288" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C288" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D288" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E288" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F288" s="13">
+        <v>768059355</v>
+      </c>
+      <c r="G288" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H288" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I288" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J288" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K288" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L288" s="12">
+        <v>50</v>
+      </c>
+      <c r="M288" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N288" s="14">
+        <v>1400000</v>
+      </c>
+      <c r="O288" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P288" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A289" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B289" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C289" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D289" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E289" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F289" s="13">
+        <v>763639555</v>
+      </c>
+      <c r="G289" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H289" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I289" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J289" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K289" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="L289" s="12">
+        <v>1</v>
+      </c>
+      <c r="M289" s="14">
+        <v>17500</v>
+      </c>
+      <c r="N289" s="14">
+        <v>17500</v>
+      </c>
+      <c r="O289" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P289" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A290" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C290" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D290" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F290" s="13">
+        <v>763639555</v>
+      </c>
+      <c r="G290" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H290" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I290" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J290" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K290" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L290" s="12">
+        <v>26</v>
+      </c>
+      <c r="M290" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N290" s="14">
+        <v>234000</v>
+      </c>
+      <c r="O290" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P290" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A291" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B291" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C291" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D291" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E291" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F291" s="13">
+        <v>763639555</v>
+      </c>
+      <c r="G291" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H291" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I291" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J291" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K291" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L291" s="12">
+        <v>9</v>
+      </c>
+      <c r="M291" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N291" s="14">
+        <v>234000</v>
+      </c>
+      <c r="O291" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P291" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A292" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C292" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D292" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E292" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F292" s="13">
+        <v>778650281</v>
+      </c>
+      <c r="G292" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H292" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I292" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J292" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K292" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L292" s="12">
+        <v>25</v>
+      </c>
+      <c r="M292" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N292" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O292" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P292" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A293" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B293" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C293" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D293" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E293" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F293" s="13">
+        <v>773340367</v>
+      </c>
+      <c r="G293" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H293" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I293" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J293" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K293" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L293" s="12">
+        <v>12</v>
+      </c>
+      <c r="M293" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N293" s="14">
+        <v>312000</v>
+      </c>
+      <c r="O293" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P293" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A294" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C294" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D294" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E294" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F294" s="13">
+        <v>779420909</v>
+      </c>
+      <c r="G294" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H294" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I294" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J294" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K294" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L294" s="12">
+        <v>13</v>
+      </c>
+      <c r="M294" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N294" s="14">
+        <v>338000</v>
+      </c>
+      <c r="O294" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P294" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A295" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B295" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C295" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D295" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E295" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F295" s="13">
+        <v>768059355</v>
+      </c>
+      <c r="G295" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H295" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I295" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J295" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K295" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L295" s="12">
+        <v>50</v>
+      </c>
+      <c r="M295" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N295" s="14">
+        <v>1400000</v>
+      </c>
+      <c r="O295" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P295" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A296" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C296" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D296" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E296" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="F296" s="13">
+        <v>771165277</v>
+      </c>
+      <c r="G296" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H296" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I296" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J296" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K296" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L296" s="12">
+        <v>2</v>
+      </c>
+      <c r="M296" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N296" s="14">
+        <v>106000</v>
+      </c>
+      <c r="O296" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P296" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A297" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B297" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C297" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D297" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E297" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F297" s="13">
+        <v>763469670</v>
+      </c>
+      <c r="G297" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H297" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I297" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J297" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K297" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L297" s="12">
+        <v>100</v>
+      </c>
+      <c r="M297" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N297" s="14">
+        <v>5300000</v>
+      </c>
+      <c r="O297" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P297" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A298" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C298" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D298" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E298" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="F298" s="13">
+        <v>771786135</v>
+      </c>
+      <c r="G298" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H298" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I298" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J298" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K298" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="L298" s="12">
+        <v>2</v>
+      </c>
+      <c r="M298" s="14">
+        <v>12500</v>
+      </c>
+      <c r="N298" s="14">
+        <v>25000</v>
+      </c>
+      <c r="O298" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P298" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A299" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B299" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C299" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D299" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E299" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="F299" s="13">
+        <v>771786135</v>
+      </c>
+      <c r="G299" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H299" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I299" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J299" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K299" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="L299" s="12">
+        <v>2</v>
+      </c>
+      <c r="M299" s="14">
+        <v>15500</v>
+      </c>
+      <c r="N299" s="14">
+        <v>31000</v>
+      </c>
+      <c r="O299" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P299" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A300" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C300" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D300" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E300" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="F300" s="13">
+        <v>778852859</v>
+      </c>
+      <c r="G300" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H300" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I300" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J300" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K300" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L300" s="12">
+        <v>25</v>
+      </c>
+      <c r="M300" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N300" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O300" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P300" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A301" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B301" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C301" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D301" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E301" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F301" s="13">
+        <v>708015391</v>
+      </c>
+      <c r="G301" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H301" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I301" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J301" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K301" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L301" s="12">
+        <v>1</v>
+      </c>
+      <c r="M301" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N301" s="14">
+        <v>53000</v>
+      </c>
+      <c r="O301" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P301" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A302" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C302" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D302" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E302" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F302" s="13">
+        <v>772131614</v>
+      </c>
+      <c r="G302" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H302" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I302" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J302" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K302" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L302" s="12">
+        <v>10</v>
+      </c>
+      <c r="M302" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N302" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O302" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P302" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A303" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B303" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C303" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D303" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E303" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="F303" s="13">
+        <v>778276533</v>
+      </c>
+      <c r="G303" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H303" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I303" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J303" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K303" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L303" s="12">
+        <v>1</v>
+      </c>
+      <c r="M303" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N303" s="14">
+        <v>26000</v>
+      </c>
+      <c r="O303" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P303" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="304" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A304" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C304" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D304" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E304" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="F304" s="13">
+        <v>775544532</v>
+      </c>
+      <c r="G304" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H304" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I304" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J304" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K304" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L304" s="12">
+        <v>24</v>
+      </c>
+      <c r="M304" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N304" s="14">
+        <v>624000</v>
+      </c>
+      <c r="O304" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P304" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A305" s="11">
+        <v>46129</v>
+      </c>
+      <c r="B305" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C305" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D305" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E305" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F305" s="13">
+        <v>772131614</v>
+      </c>
+      <c r="G305" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H305" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I305" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J305" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K305" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L305" s="12">
+        <v>1</v>
+      </c>
+      <c r="M305" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N305" s="14">
+        <v>53000</v>
+      </c>
+      <c r="O305" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P305" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A306" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B306" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C306" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D306" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E306" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F306" s="13">
+        <v>779865100</v>
+      </c>
+      <c r="G306" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H306" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I306" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J306" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K306" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L306" s="12">
+        <v>10</v>
+      </c>
+      <c r="M306" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N306" s="14">
+        <v>195000</v>
+      </c>
+      <c r="O306" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P306" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A307" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B307" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C307" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D307" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E307" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F307" s="13">
+        <v>779865100</v>
+      </c>
+      <c r="G307" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H307" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I307" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J307" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K307" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L307" s="12">
+        <v>20</v>
+      </c>
+      <c r="M307" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N307" s="14">
+        <v>180000</v>
+      </c>
+      <c r="O307" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P307" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A308" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C308" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D308" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E308" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F308" s="13">
+        <v>771871533</v>
+      </c>
+      <c r="G308" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H308" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I308" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J308" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K308" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L308" s="12">
+        <v>1</v>
+      </c>
+      <c r="M308" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N308" s="14">
+        <v>9000</v>
+      </c>
+      <c r="O308" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P308" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A309" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B309" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C309" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D309" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E309" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F309" s="13">
+        <v>771871533</v>
+      </c>
+      <c r="G309" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H309" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I309" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J309" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K309" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L309" s="12">
+        <v>5</v>
+      </c>
+      <c r="M309" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N309" s="14">
+        <v>130000</v>
+      </c>
+      <c r="O309" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P309" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A310" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B310" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C310" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D310" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E310" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F310" s="13">
+        <v>773501029</v>
+      </c>
+      <c r="G310" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H310" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I310" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J310" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K310" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L310" s="12">
+        <v>1</v>
+      </c>
+      <c r="M310" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N310" s="14">
+        <v>9000</v>
+      </c>
+      <c r="O310" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P310" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A311" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B311" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C311" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D311" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E311" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F311" s="13">
+        <v>773501029</v>
+      </c>
+      <c r="G311" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H311" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I311" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J311" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K311" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L311" s="12">
+        <v>5</v>
+      </c>
+      <c r="M311" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N311" s="14">
+        <v>130000</v>
+      </c>
+      <c r="O311" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P311" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A312" s="11">
+        <v>46127</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C312" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D312" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E312" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="F312" s="13">
+        <v>784464768</v>
+      </c>
+      <c r="G312" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H312" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I312" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J312" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K312" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L312" s="12">
+        <v>16</v>
+      </c>
+      <c r="M312" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N312" s="14">
+        <v>416000</v>
+      </c>
+      <c r="O312" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P312" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A313" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B313" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C313" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D313" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E313" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F313" s="13">
+        <v>781316258</v>
+      </c>
+      <c r="G313" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H313" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I313" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J313" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K313" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L313" s="12">
+        <v>5</v>
+      </c>
+      <c r="M313" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N313" s="14">
+        <v>130000</v>
+      </c>
+      <c r="O313" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P313" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="314" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A314" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B314" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C314" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D314" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E314" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F314" s="13">
+        <v>775378651</v>
+      </c>
+      <c r="G314" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H314" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I314" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J314" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K314" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L314" s="12">
+        <v>25</v>
+      </c>
+      <c r="M314" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N314" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O314" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P314" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="315" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A315" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B315" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C315" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D315" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E315" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F315" s="13">
+        <v>781316258</v>
+      </c>
+      <c r="G315" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H315" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I315" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J315" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K315" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L315" s="12">
+        <v>5</v>
+      </c>
+      <c r="M315" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N315" s="14">
+        <v>97500</v>
+      </c>
+      <c r="O315" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P315" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A316" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B316" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C316" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D316" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E316" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F316" s="13">
+        <v>781316258</v>
+      </c>
+      <c r="G316" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H316" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I316" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J316" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K316" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="L316" s="12">
+        <v>10</v>
+      </c>
+      <c r="M316" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N316" s="14">
+        <v>280000</v>
+      </c>
+      <c r="O316" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P316" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="317" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A317" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B317" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C317" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D317" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E317" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F317" s="13">
+        <v>775378651</v>
+      </c>
+      <c r="G317" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H317" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I317" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J317" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K317" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L317" s="12">
+        <v>3</v>
+      </c>
+      <c r="M317" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N317" s="14">
+        <v>58500</v>
+      </c>
+      <c r="O317" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P317" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="318" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A318" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B318" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C318" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D318" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E318" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F318" s="13">
+        <v>775378651</v>
+      </c>
+      <c r="G318" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H318" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I318" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J318" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K318" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="L318" s="12">
+        <v>5</v>
+      </c>
+      <c r="M318" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N318" s="14">
+        <v>45000</v>
+      </c>
+      <c r="O318" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P318" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="319" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A319" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B319" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C319" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D319" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E319" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F319" s="13">
+        <v>775378651</v>
+      </c>
+      <c r="G319" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H319" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I319" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J319" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K319" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L319" s="12">
+        <v>10</v>
+      </c>
+      <c r="M319" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N319" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O319" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P319" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="320" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A320" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B320" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C320" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D320" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E320" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F320" s="13">
+        <v>776367168</v>
+      </c>
+      <c r="G320" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H320" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I320" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J320" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K320" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L320" s="12">
+        <v>25</v>
+      </c>
+      <c r="M320" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N320" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O320" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P320" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="321" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A321" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B321" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C321" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D321" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E321" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="F321" s="13">
+        <v>773248259</v>
+      </c>
+      <c r="G321" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H321" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I321" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J321" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K321" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L321" s="12">
+        <v>2</v>
+      </c>
+      <c r="M321" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N321" s="14">
+        <v>39000</v>
+      </c>
+      <c r="O321" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P321" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="322" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A322" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B322" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C322" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D322" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E322" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F322" s="13">
+        <v>774446616</v>
+      </c>
+      <c r="G322" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H322" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I322" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J322" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K322" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="L322" s="12">
+        <v>4</v>
+      </c>
+      <c r="M322" s="14">
+        <v>12500</v>
+      </c>
+      <c r="N322" s="14">
+        <v>50000</v>
+      </c>
+      <c r="O322" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P322" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="323" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A323" s="11">
+        <v>46126</v>
+      </c>
+      <c r="B323" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="C323" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D323" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E323" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F323" s="13">
+        <v>774446616</v>
+      </c>
+      <c r="G323" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H323" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I323" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J323" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K323" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="L323" s="12">
+        <v>1</v>
+      </c>
+      <c r="M323" s="14">
+        <v>15500</v>
+      </c>
+      <c r="N323" s="14">
+        <v>15500</v>
+      </c>
+      <c r="O323" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P323" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="324" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A324" s="11">
+        <v>46130</v>
+      </c>
+      <c r="B324" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C324" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D324" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E324" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F324" s="13">
+        <v>762951288</v>
+      </c>
+      <c r="G324" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H324" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I324" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J324" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K324" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L324" s="12">
+        <v>1</v>
+      </c>
+      <c r="M324" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N324" s="14">
+        <v>26000</v>
+      </c>
+      <c r="O324" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P324" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="325" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A325" s="11">
+        <v>46130</v>
+      </c>
+      <c r="B325" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C325" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D325" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E325" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F325" s="13">
+        <v>772038792</v>
+      </c>
+      <c r="G325" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H325" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I325" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J325" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K325" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L325" s="12">
+        <v>1</v>
+      </c>
+      <c r="M325" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N325" s="14">
+        <v>53000</v>
+      </c>
+      <c r="O325" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P325" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="326" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A326" s="11">
+        <v>46130</v>
+      </c>
+      <c r="B326" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C326" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D326" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E326" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F326" s="13">
+        <v>772038792</v>
+      </c>
+      <c r="G326" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H326" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I326" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J326" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K326" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="L326" s="12">
+        <v>2</v>
+      </c>
+      <c r="M326" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N326" s="14">
+        <v>39000</v>
+      </c>
+      <c r="O326" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P326" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="327" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A327" s="11">
+        <v>46130</v>
+      </c>
+      <c r="B327" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C327" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D327" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E327" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="F327" s="13">
+        <v>774993694</v>
+      </c>
+      <c r="G327" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H327" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I327" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J327" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="K327" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="L327" s="12">
+        <v>50</v>
+      </c>
+      <c r="M327" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N327" s="14">
+        <v>1300000</v>
+      </c>
+      <c r="O327" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P327" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="328" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A328" s="11">
+        <v>46130</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C328" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D328" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E328" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F328" s="13">
+        <v>762951288</v>
+      </c>
+      <c r="G328" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H328" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I328" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J328" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K328" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L328" s="12">
+        <v>37</v>
+      </c>
+      <c r="M328" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N328" s="14">
+        <v>1961000</v>
+      </c>
+      <c r="O328" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P328" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="329" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A329" s="11">
+        <v>46130</v>
+      </c>
+      <c r="B329" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C329" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D329" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="E329" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F329" s="13">
+        <v>762951288</v>
+      </c>
+      <c r="G329" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H329" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I329" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J329" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K329" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="L329" s="12">
+        <v>1</v>
+      </c>
+      <c r="M329" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N329" s="14">
+        <v>9000</v>
+      </c>
+      <c r="O329" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S16</v>
+      </c>
+      <c r="P329" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F39375-4229-4139-892F-2CA51F4F8D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AAF419-9509-4A52-A7D9-C06F1249943B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3248" uniqueCount="327">
   <si>
     <t>Date</t>
   </si>
@@ -934,6 +934,87 @@
   </si>
   <si>
     <t>Supermarché</t>
+  </si>
+  <si>
+    <t>MAME MAREME NDIAYE</t>
+  </si>
+  <si>
+    <t>Yarakh</t>
+  </si>
+  <si>
+    <t>Khalil Diallo (Hann Village)</t>
+  </si>
+  <si>
+    <t>Mamadou Diallo (Hann Village)</t>
+  </si>
+  <si>
+    <t>Ibrahima BALDE</t>
+  </si>
+  <si>
+    <t>SEYNABOU SOW</t>
+  </si>
+  <si>
+    <t>Stapro.com SARL n1</t>
+  </si>
+  <si>
+    <t>Il dit que la rotation du produit est lente</t>
+  </si>
+  <si>
+    <t>Mouhamed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vais essayer avec les 2 </t>
+  </si>
+  <si>
+    <t>Mbaye</t>
+  </si>
+  <si>
+    <t>Mamadou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vais essayer avec les 15 sacs </t>
+  </si>
+  <si>
+    <t>Café Refraish 100g</t>
+  </si>
+  <si>
+    <t>AMADOU SOW</t>
+  </si>
+  <si>
+    <t>FATOUMATA TRAORE</t>
+  </si>
+  <si>
+    <t>El Hadj Cissé</t>
+  </si>
+  <si>
+    <t>Il lui reste le café Altimo stick et le lait évaporé kamlac</t>
+  </si>
+  <si>
+    <t>NDACK NDAO</t>
+  </si>
+  <si>
+    <t>THIERNO GUISSE</t>
+  </si>
+  <si>
+    <t>ABDOU LATIF DIENG</t>
+  </si>
+  <si>
+    <t>El hadj</t>
+  </si>
+  <si>
+    <t>Rad</t>
+  </si>
+  <si>
+    <t>NGOUYE NDIAYE</t>
+  </si>
+  <si>
+    <t>Bambilor</t>
+  </si>
+  <si>
+    <t>Mare Guorom</t>
+  </si>
+  <si>
+    <t>775124616</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1031,13 +1112,13 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1047,6 +1128,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1351,8 +1435,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P329" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P329" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P360" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P360" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1665,7 +1749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P329"/>
+  <dimension ref="A1:P360"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -15984,2809 +16068,4421 @@
       </c>
     </row>
     <row r="276" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A276" s="11">
+      <c r="A276" s="8">
         <v>46125</v>
       </c>
-      <c r="B276" s="12" t="s">
+      <c r="B276" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C276" s="12" t="s">
+      <c r="C276" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D276" s="12" t="s">
+      <c r="D276" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E276" s="12" t="s">
+      <c r="E276" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F276" s="13">
+      <c r="F276" s="11">
         <v>777739323</v>
       </c>
-      <c r="G276" s="12" t="s">
+      <c r="G276" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H276" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I276" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J276" s="12" t="s">
+      <c r="H276" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I276" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J276" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K276" s="12" t="s">
+      <c r="K276" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L276" s="12">
+      <c r="L276" s="9">
         <v>30</v>
       </c>
-      <c r="M276" s="14">
+      <c r="M276" s="10">
         <v>9000</v>
       </c>
-      <c r="N276" s="14">
+      <c r="N276" s="10">
         <v>270000</v>
       </c>
-      <c r="O276" s="15" t="str">
+      <c r="O276" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P276" s="16" t="str">
+      <c r="P276" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="277" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A277" s="11">
+      <c r="A277" s="8">
         <v>46125</v>
       </c>
-      <c r="B277" s="12" t="s">
+      <c r="B277" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C277" s="12" t="s">
+      <c r="C277" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D277" s="12" t="s">
+      <c r="D277" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E277" s="12" t="s">
+      <c r="E277" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F277" s="13">
+      <c r="F277" s="11">
         <v>777739323</v>
       </c>
-      <c r="G277" s="12" t="s">
+      <c r="G277" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H277" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I277" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J277" s="12" t="s">
+      <c r="H277" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I277" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J277" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K277" s="12" t="s">
+      <c r="K277" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L277" s="12">
+      <c r="L277" s="9">
         <v>3</v>
       </c>
-      <c r="M277" s="14">
+      <c r="M277" s="10">
         <v>28000</v>
       </c>
-      <c r="N277" s="14">
+      <c r="N277" s="10">
         <v>84000</v>
       </c>
-      <c r="O277" s="15" t="str">
+      <c r="O277" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P277" s="16" t="str">
+      <c r="P277" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="278" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A278" s="11">
+      <c r="A278" s="8">
         <v>46125</v>
       </c>
-      <c r="B278" s="12" t="s">
+      <c r="B278" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C278" s="12" t="s">
+      <c r="C278" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D278" s="12" t="s">
+      <c r="D278" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E278" s="12" t="s">
+      <c r="E278" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F278" s="13">
+      <c r="F278" s="11">
         <v>779486095</v>
       </c>
-      <c r="G278" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H278" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I278" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J278" s="12" t="s">
+      <c r="G278" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H278" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I278" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J278" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K278" s="12" t="s">
+      <c r="K278" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="L278" s="12">
+      <c r="L278" s="9">
         <v>15</v>
       </c>
-      <c r="M278" s="14">
+      <c r="M278" s="10">
         <v>12500</v>
       </c>
-      <c r="N278" s="14">
+      <c r="N278" s="10">
         <v>187500</v>
       </c>
-      <c r="O278" s="15" t="str">
+      <c r="O278" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P278" s="16" t="str">
+      <c r="P278" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="279" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A279" s="11">
+      <c r="A279" s="8">
         <v>46125</v>
       </c>
-      <c r="B279" s="12" t="s">
+      <c r="B279" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C279" s="12" t="s">
+      <c r="C279" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D279" s="12" t="s">
+      <c r="D279" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E279" s="12" t="s">
+      <c r="E279" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F279" s="13">
+      <c r="F279" s="11">
         <v>779486095</v>
       </c>
-      <c r="G279" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H279" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I279" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J279" s="12" t="s">
+      <c r="G279" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H279" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I279" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J279" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K279" s="12" t="s">
+      <c r="K279" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="L279" s="12">
+      <c r="L279" s="9">
         <v>10</v>
       </c>
-      <c r="M279" s="14">
+      <c r="M279" s="10">
         <v>12500</v>
       </c>
-      <c r="N279" s="14">
+      <c r="N279" s="10">
         <v>125000</v>
       </c>
-      <c r="O279" s="15" t="str">
+      <c r="O279" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P279" s="16" t="str">
+      <c r="P279" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A280" s="11">
+      <c r="A280" s="8">
         <v>46125</v>
       </c>
-      <c r="B280" s="12" t="s">
+      <c r="B280" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C280" s="12" t="s">
+      <c r="C280" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D280" s="12" t="s">
+      <c r="D280" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E280" s="12" t="s">
+      <c r="E280" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F280" s="13">
+      <c r="F280" s="11">
         <v>778356666</v>
       </c>
-      <c r="G280" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H280" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I280" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J280" s="12" t="s">
+      <c r="G280" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H280" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I280" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J280" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K280" s="12" t="s">
+      <c r="K280" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L280" s="12">
+      <c r="L280" s="9">
         <v>25</v>
       </c>
-      <c r="M280" s="14">
+      <c r="M280" s="10">
         <v>26000</v>
       </c>
-      <c r="N280" s="14">
+      <c r="N280" s="10">
         <v>650000</v>
       </c>
-      <c r="O280" s="15" t="str">
+      <c r="O280" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P280" s="16" t="str">
+      <c r="P280" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A281" s="11">
+      <c r="A281" s="8">
         <v>46125</v>
       </c>
-      <c r="B281" s="12" t="s">
+      <c r="B281" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C281" s="12" t="s">
+      <c r="C281" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D281" s="12" t="s">
+      <c r="D281" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E281" s="12" t="s">
+      <c r="E281" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F281" s="13">
+      <c r="F281" s="11">
         <v>774216339</v>
       </c>
-      <c r="G281" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H281" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I281" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J281" s="12" t="s">
+      <c r="G281" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H281" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I281" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J281" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="K281" s="12" t="s">
+      <c r="K281" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L281" s="12">
+      <c r="L281" s="9">
         <v>50</v>
       </c>
-      <c r="M281" s="14">
+      <c r="M281" s="10">
         <v>26000</v>
       </c>
-      <c r="N281" s="14">
+      <c r="N281" s="10">
         <v>1300000</v>
       </c>
-      <c r="O281" s="15" t="str">
+      <c r="O281" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P281" s="16" t="str">
+      <c r="P281" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A282" s="11">
+      <c r="A282" s="8">
         <v>46125</v>
       </c>
-      <c r="B282" s="12" t="s">
+      <c r="B282" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C282" s="12" t="s">
+      <c r="C282" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D282" s="12" t="s">
+      <c r="D282" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E282" s="12" t="s">
+      <c r="E282" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F282" s="13">
+      <c r="F282" s="11">
         <v>774216339</v>
       </c>
-      <c r="G282" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H282" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I282" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J282" s="12" t="s">
+      <c r="G282" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H282" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I282" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J282" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="K282" s="12" t="s">
+      <c r="K282" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L282" s="12">
+      <c r="L282" s="9">
         <v>5</v>
       </c>
-      <c r="M282" s="14">
+      <c r="M282" s="10">
         <v>19500</v>
       </c>
-      <c r="N282" s="14">
+      <c r="N282" s="10">
         <v>97500</v>
       </c>
-      <c r="O282" s="15" t="str">
+      <c r="O282" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P282" s="16" t="str">
+      <c r="P282" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A283" s="11">
+      <c r="A283" s="8">
         <v>46125</v>
       </c>
-      <c r="B283" s="12" t="s">
+      <c r="B283" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C283" s="12" t="s">
+      <c r="C283" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D283" s="12" t="s">
+      <c r="D283" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E283" s="12" t="s">
+      <c r="E283" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="F283" s="13">
+      <c r="F283" s="11">
         <v>776634479</v>
       </c>
-      <c r="G283" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H283" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I283" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J283" s="12" t="s">
+      <c r="G283" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I283" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J283" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K283" s="12" t="s">
+      <c r="K283" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L283" s="12">
+      <c r="L283" s="9">
         <v>25</v>
       </c>
-      <c r="M283" s="14">
+      <c r="M283" s="10">
         <v>53000</v>
       </c>
-      <c r="N283" s="14">
+      <c r="N283" s="10">
         <v>1325000</v>
       </c>
-      <c r="O283" s="15" t="str">
+      <c r="O283" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P283" s="16" t="str">
+      <c r="P283" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A284" s="11">
+      <c r="A284" s="8">
         <v>46125</v>
       </c>
-      <c r="B284" s="12" t="s">
+      <c r="B284" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C284" s="12" t="s">
+      <c r="C284" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D284" s="12" t="s">
+      <c r="D284" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E284" s="12" t="s">
+      <c r="E284" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="F284" s="13">
+      <c r="F284" s="11">
         <v>774624747</v>
       </c>
-      <c r="G284" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H284" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I284" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J284" s="12" t="s">
+      <c r="G284" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H284" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I284" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J284" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K284" s="12" t="s">
+      <c r="K284" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L284" s="12">
+      <c r="L284" s="9">
         <v>20</v>
       </c>
-      <c r="M284" s="14">
+      <c r="M284" s="10">
         <v>9000</v>
       </c>
-      <c r="N284" s="14">
+      <c r="N284" s="10">
         <v>180000</v>
       </c>
-      <c r="O284" s="15" t="str">
+      <c r="O284" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P284" s="16" t="str">
+      <c r="P284" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A285" s="11">
+      <c r="A285" s="8">
         <v>46129</v>
       </c>
-      <c r="B285" s="12" t="s">
+      <c r="B285" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C285" s="12" t="s">
+      <c r="C285" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D285" s="12" t="s">
+      <c r="D285" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E285" s="12" t="s">
+      <c r="E285" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="F285" s="13">
+      <c r="F285" s="11">
         <v>779598695</v>
       </c>
-      <c r="G285" s="12" t="s">
+      <c r="G285" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H285" s="12" t="s">
+      <c r="H285" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I285" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J285" s="12" t="s">
+      <c r="I285" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J285" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="K285" s="12" t="s">
+      <c r="K285" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L285" s="12">
+      <c r="L285" s="9">
         <v>25</v>
       </c>
-      <c r="M285" s="14">
+      <c r="M285" s="10">
         <v>26000</v>
       </c>
-      <c r="N285" s="14">
+      <c r="N285" s="10">
         <v>650000</v>
       </c>
-      <c r="O285" s="15" t="str">
+      <c r="O285" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P285" s="16" t="str">
+      <c r="P285" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A286" s="11">
+      <c r="A286" s="8">
         <v>46129</v>
       </c>
-      <c r="B286" s="12" t="s">
+      <c r="B286" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C286" s="12" t="s">
+      <c r="C286" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D286" s="12" t="s">
+      <c r="D286" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E286" s="12" t="s">
+      <c r="E286" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F286" s="13">
+      <c r="F286" s="11">
         <v>773531341</v>
       </c>
-      <c r="G286" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H286" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I286" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J286" s="12" t="s">
+      <c r="G286" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H286" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I286" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J286" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K286" s="12" t="s">
+      <c r="K286" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L286" s="12">
+      <c r="L286" s="9">
         <v>1</v>
       </c>
-      <c r="M286" s="14">
+      <c r="M286" s="10">
         <v>53000</v>
       </c>
-      <c r="N286" s="14">
+      <c r="N286" s="10">
         <v>53000</v>
       </c>
-      <c r="O286" s="15" t="str">
+      <c r="O286" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P286" s="16" t="str">
+      <c r="P286" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="287" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A287" s="11">
+      <c r="A287" s="8">
         <v>46129</v>
       </c>
-      <c r="B287" s="12" t="s">
+      <c r="B287" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C287" s="12" t="s">
+      <c r="C287" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D287" s="12" t="s">
+      <c r="D287" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E287" s="12" t="s">
+      <c r="E287" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F287" s="13">
+      <c r="F287" s="11">
         <v>775586819</v>
       </c>
-      <c r="G287" s="12" t="s">
+      <c r="G287" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H287" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I287" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J287" s="12" t="s">
+      <c r="H287" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I287" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J287" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K287" s="12" t="s">
+      <c r="K287" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L287" s="12">
+      <c r="L287" s="9">
         <v>25</v>
       </c>
-      <c r="M287" s="14">
+      <c r="M287" s="10">
         <v>26000</v>
       </c>
-      <c r="N287" s="14">
+      <c r="N287" s="10">
         <v>650000</v>
       </c>
-      <c r="O287" s="15" t="str">
+      <c r="O287" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P287" s="16" t="str">
+      <c r="P287" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="288" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A288" s="11">
+      <c r="A288" s="8">
         <v>46129</v>
       </c>
-      <c r="B288" s="12" t="s">
+      <c r="B288" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C288" s="12" t="s">
+      <c r="C288" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D288" s="12" t="s">
+      <c r="D288" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E288" s="12" t="s">
+      <c r="E288" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F288" s="13">
+      <c r="F288" s="11">
         <v>768059355</v>
       </c>
-      <c r="G288" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H288" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I288" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J288" s="12" t="s">
+      <c r="G288" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H288" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I288" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J288" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K288" s="12" t="s">
+      <c r="K288" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L288" s="12">
+      <c r="L288" s="9">
         <v>50</v>
       </c>
-      <c r="M288" s="14">
+      <c r="M288" s="10">
         <v>28000</v>
       </c>
-      <c r="N288" s="14">
+      <c r="N288" s="10">
         <v>1400000</v>
       </c>
-      <c r="O288" s="15" t="str">
+      <c r="O288" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P288" s="16" t="str">
+      <c r="P288" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="289" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A289" s="11">
+      <c r="A289" s="8">
         <v>46127</v>
       </c>
-      <c r="B289" s="12" t="s">
+      <c r="B289" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C289" s="12" t="s">
+      <c r="C289" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D289" s="12" t="s">
+      <c r="D289" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E289" s="12" t="s">
+      <c r="E289" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F289" s="13">
+      <c r="F289" s="11">
         <v>763639555</v>
       </c>
-      <c r="G289" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H289" s="12" t="s">
+      <c r="G289" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H289" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I289" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J289" s="12" t="s">
+      <c r="I289" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J289" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K289" s="12" t="s">
+      <c r="K289" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L289" s="12">
+      <c r="L289" s="9">
         <v>1</v>
       </c>
-      <c r="M289" s="14">
+      <c r="M289" s="10">
         <v>17500</v>
       </c>
-      <c r="N289" s="14">
+      <c r="N289" s="10">
         <v>17500</v>
       </c>
-      <c r="O289" s="15" t="str">
+      <c r="O289" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P289" s="16" t="str">
+      <c r="P289" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="290" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A290" s="11">
+      <c r="A290" s="8">
         <v>46127</v>
       </c>
-      <c r="B290" s="12" t="s">
+      <c r="B290" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C290" s="12" t="s">
+      <c r="C290" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D290" s="12" t="s">
+      <c r="D290" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E290" s="12" t="s">
+      <c r="E290" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F290" s="13">
+      <c r="F290" s="11">
         <v>763639555</v>
       </c>
-      <c r="G290" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H290" s="12" t="s">
+      <c r="G290" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H290" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I290" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J290" s="12" t="s">
+      <c r="I290" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J290" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K290" s="12" t="s">
+      <c r="K290" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L290" s="12">
+      <c r="L290" s="9">
         <v>26</v>
       </c>
-      <c r="M290" s="14">
+      <c r="M290" s="10">
         <v>9000</v>
       </c>
-      <c r="N290" s="14">
+      <c r="N290" s="10">
         <v>234000</v>
       </c>
-      <c r="O290" s="15" t="str">
+      <c r="O290" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P290" s="16" t="str">
+      <c r="P290" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="291" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A291" s="11">
+      <c r="A291" s="8">
         <v>46127</v>
       </c>
-      <c r="B291" s="12" t="s">
+      <c r="B291" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C291" s="12" t="s">
+      <c r="C291" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D291" s="12" t="s">
+      <c r="D291" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E291" s="12" t="s">
+      <c r="E291" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F291" s="13">
+      <c r="F291" s="11">
         <v>763639555</v>
       </c>
-      <c r="G291" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H291" s="12" t="s">
+      <c r="G291" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H291" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I291" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J291" s="12" t="s">
+      <c r="I291" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J291" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K291" s="12" t="s">
+      <c r="K291" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L291" s="12">
+      <c r="L291" s="9">
         <v>9</v>
       </c>
-      <c r="M291" s="14">
+      <c r="M291" s="10">
         <v>26000</v>
       </c>
-      <c r="N291" s="14">
+      <c r="N291" s="10">
         <v>234000</v>
       </c>
-      <c r="O291" s="15" t="str">
+      <c r="O291" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P291" s="16" t="str">
+      <c r="P291" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="292" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A292" s="11">
+      <c r="A292" s="8">
         <v>46127</v>
       </c>
-      <c r="B292" s="12" t="s">
+      <c r="B292" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C292" s="12" t="s">
+      <c r="C292" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D292" s="12" t="s">
+      <c r="D292" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E292" s="12" t="s">
+      <c r="E292" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="F292" s="13">
+      <c r="F292" s="11">
         <v>778650281</v>
       </c>
-      <c r="G292" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H292" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I292" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J292" s="12" t="s">
+      <c r="G292" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H292" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I292" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J292" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K292" s="12" t="s">
+      <c r="K292" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L292" s="12">
+      <c r="L292" s="9">
         <v>25</v>
       </c>
-      <c r="M292" s="14">
+      <c r="M292" s="10">
         <v>26000</v>
       </c>
-      <c r="N292" s="14">
+      <c r="N292" s="10">
         <v>650000</v>
       </c>
-      <c r="O292" s="15" t="str">
+      <c r="O292" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P292" s="16" t="str">
+      <c r="P292" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="293" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A293" s="11">
+      <c r="A293" s="8">
         <v>46127</v>
       </c>
-      <c r="B293" s="12" t="s">
+      <c r="B293" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C293" s="12" t="s">
+      <c r="C293" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D293" s="12" t="s">
+      <c r="D293" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="E293" s="12" t="s">
+      <c r="E293" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F293" s="13">
+      <c r="F293" s="11">
         <v>773340367</v>
       </c>
-      <c r="G293" s="12" t="s">
+      <c r="G293" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H293" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I293" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J293" s="12" t="s">
+      <c r="H293" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I293" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J293" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K293" s="12" t="s">
+      <c r="K293" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L293" s="12">
+      <c r="L293" s="9">
         <v>12</v>
       </c>
-      <c r="M293" s="14">
+      <c r="M293" s="10">
         <v>26000</v>
       </c>
-      <c r="N293" s="14">
+      <c r="N293" s="10">
         <v>312000</v>
       </c>
-      <c r="O293" s="15" t="str">
+      <c r="O293" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P293" s="16" t="str">
+      <c r="P293" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="294" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A294" s="11">
+      <c r="A294" s="8">
         <v>46127</v>
       </c>
-      <c r="B294" s="12" t="s">
+      <c r="B294" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C294" s="12" t="s">
+      <c r="C294" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D294" s="12" t="s">
+      <c r="D294" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E294" s="12" t="s">
+      <c r="E294" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="F294" s="13">
+      <c r="F294" s="11">
         <v>779420909</v>
       </c>
-      <c r="G294" s="12" t="s">
+      <c r="G294" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H294" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I294" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J294" s="12" t="s">
+      <c r="H294" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I294" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J294" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K294" s="12" t="s">
+      <c r="K294" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L294" s="12">
-        <v>13</v>
-      </c>
-      <c r="M294" s="14">
+      <c r="L294" s="9">
+        <v>13</v>
+      </c>
+      <c r="M294" s="10">
         <v>26000</v>
       </c>
-      <c r="N294" s="14">
+      <c r="N294" s="10">
         <v>338000</v>
       </c>
-      <c r="O294" s="15" t="str">
+      <c r="O294" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P294" s="16" t="str">
+      <c r="P294" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="295" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A295" s="11">
+      <c r="A295" s="8">
         <v>46127</v>
       </c>
-      <c r="B295" s="12" t="s">
+      <c r="B295" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C295" s="12" t="s">
+      <c r="C295" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D295" s="12" t="s">
+      <c r="D295" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E295" s="12" t="s">
+      <c r="E295" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F295" s="13">
+      <c r="F295" s="11">
         <v>768059355</v>
       </c>
-      <c r="G295" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H295" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I295" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J295" s="12" t="s">
+      <c r="G295" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H295" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I295" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J295" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K295" s="12" t="s">
+      <c r="K295" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L295" s="12">
+      <c r="L295" s="9">
         <v>50</v>
       </c>
-      <c r="M295" s="14">
+      <c r="M295" s="10">
         <v>28000</v>
       </c>
-      <c r="N295" s="14">
+      <c r="N295" s="10">
         <v>1400000</v>
       </c>
-      <c r="O295" s="15" t="str">
+      <c r="O295" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P295" s="16" t="str">
+      <c r="P295" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A296" s="11">
+      <c r="A296" s="8">
         <v>46129</v>
       </c>
-      <c r="B296" s="12" t="s">
+      <c r="B296" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C296" s="12" t="s">
+      <c r="C296" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D296" s="12" t="s">
+      <c r="D296" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E296" s="12" t="s">
+      <c r="E296" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F296" s="13">
+      <c r="F296" s="11">
         <v>771165277</v>
       </c>
-      <c r="G296" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H296" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I296" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J296" s="12" t="s">
+      <c r="G296" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H296" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I296" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J296" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K296" s="12" t="s">
+      <c r="K296" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L296" s="12">
+      <c r="L296" s="9">
         <v>2</v>
       </c>
-      <c r="M296" s="14">
+      <c r="M296" s="10">
         <v>53000</v>
       </c>
-      <c r="N296" s="14">
+      <c r="N296" s="10">
         <v>106000</v>
       </c>
-      <c r="O296" s="15" t="str">
+      <c r="O296" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P296" s="16" t="str">
+      <c r="P296" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="297" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A297" s="11">
+      <c r="A297" s="8">
         <v>46129</v>
       </c>
-      <c r="B297" s="12" t="s">
+      <c r="B297" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C297" s="12" t="s">
+      <c r="C297" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D297" s="12" t="s">
+      <c r="D297" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E297" s="12" t="s">
+      <c r="E297" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F297" s="13">
+      <c r="F297" s="11">
         <v>763469670</v>
       </c>
-      <c r="G297" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H297" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I297" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J297" s="12" t="s">
+      <c r="G297" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H297" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I297" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J297" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K297" s="12" t="s">
+      <c r="K297" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L297" s="12">
+      <c r="L297" s="9">
         <v>100</v>
       </c>
-      <c r="M297" s="14">
+      <c r="M297" s="10">
         <v>53000</v>
       </c>
-      <c r="N297" s="14">
+      <c r="N297" s="10">
         <v>5300000</v>
       </c>
-      <c r="O297" s="15" t="str">
+      <c r="O297" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P297" s="16" t="str">
+      <c r="P297" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="298" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A298" s="11">
+      <c r="A298" s="8">
         <v>46129</v>
       </c>
-      <c r="B298" s="12" t="s">
+      <c r="B298" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C298" s="12" t="s">
+      <c r="C298" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D298" s="12" t="s">
+      <c r="D298" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E298" s="12" t="s">
+      <c r="E298" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F298" s="13">
+      <c r="F298" s="11">
         <v>771786135</v>
       </c>
-      <c r="G298" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H298" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I298" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J298" s="12" t="s">
+      <c r="G298" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H298" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I298" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J298" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K298" s="12" t="s">
+      <c r="K298" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="L298" s="12">
+      <c r="L298" s="9">
         <v>2</v>
       </c>
-      <c r="M298" s="14">
+      <c r="M298" s="10">
         <v>12500</v>
       </c>
-      <c r="N298" s="14">
+      <c r="N298" s="10">
         <v>25000</v>
       </c>
-      <c r="O298" s="15" t="str">
+      <c r="O298" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P298" s="16" t="str">
+      <c r="P298" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A299" s="11">
+      <c r="A299" s="8">
         <v>46129</v>
       </c>
-      <c r="B299" s="12" t="s">
+      <c r="B299" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C299" s="12" t="s">
+      <c r="C299" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D299" s="12" t="s">
+      <c r="D299" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E299" s="12" t="s">
+      <c r="E299" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="F299" s="13">
+      <c r="F299" s="11">
         <v>771786135</v>
       </c>
-      <c r="G299" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H299" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I299" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J299" s="12" t="s">
+      <c r="G299" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H299" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I299" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J299" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K299" s="12" t="s">
+      <c r="K299" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="L299" s="12">
+      <c r="L299" s="9">
         <v>2</v>
       </c>
-      <c r="M299" s="14">
+      <c r="M299" s="10">
         <v>15500</v>
       </c>
-      <c r="N299" s="14">
+      <c r="N299" s="10">
         <v>31000</v>
       </c>
-      <c r="O299" s="15" t="str">
+      <c r="O299" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P299" s="16" t="str">
+      <c r="P299" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="300" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A300" s="11">
+      <c r="A300" s="8">
         <v>46129</v>
       </c>
-      <c r="B300" s="12" t="s">
+      <c r="B300" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C300" s="12" t="s">
+      <c r="C300" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D300" s="12" t="s">
+      <c r="D300" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E300" s="12" t="s">
+      <c r="E300" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="F300" s="13">
+      <c r="F300" s="11">
         <v>778852859</v>
       </c>
-      <c r="G300" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H300" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I300" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J300" s="12" t="s">
+      <c r="G300" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H300" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I300" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J300" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K300" s="12" t="s">
+      <c r="K300" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L300" s="12">
+      <c r="L300" s="9">
         <v>25</v>
       </c>
-      <c r="M300" s="14">
+      <c r="M300" s="10">
         <v>26000</v>
       </c>
-      <c r="N300" s="14">
+      <c r="N300" s="10">
         <v>650000</v>
       </c>
-      <c r="O300" s="15" t="str">
+      <c r="O300" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P300" s="16" t="str">
+      <c r="P300" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A301" s="11">
+      <c r="A301" s="8">
         <v>46129</v>
       </c>
-      <c r="B301" s="12" t="s">
+      <c r="B301" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C301" s="12" t="s">
+      <c r="C301" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D301" s="12" t="s">
+      <c r="D301" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E301" s="12" t="s">
+      <c r="E301" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="F301" s="13">
+      <c r="F301" s="11">
         <v>708015391</v>
       </c>
-      <c r="G301" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H301" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I301" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J301" s="12" t="s">
+      <c r="G301" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H301" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I301" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J301" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K301" s="12" t="s">
+      <c r="K301" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L301" s="12">
+      <c r="L301" s="9">
         <v>1</v>
       </c>
-      <c r="M301" s="14">
+      <c r="M301" s="10">
         <v>53000</v>
       </c>
-      <c r="N301" s="14">
+      <c r="N301" s="10">
         <v>53000</v>
       </c>
-      <c r="O301" s="15" t="str">
+      <c r="O301" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P301" s="16" t="str">
+      <c r="P301" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A302" s="11">
+      <c r="A302" s="8">
         <v>46129</v>
       </c>
-      <c r="B302" s="12" t="s">
+      <c r="B302" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C302" s="12" t="s">
+      <c r="C302" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D302" s="12" t="s">
+      <c r="D302" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E302" s="12" t="s">
+      <c r="E302" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="F302" s="13">
+      <c r="F302" s="11">
         <v>772131614</v>
       </c>
-      <c r="G302" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H302" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I302" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J302" s="12" t="s">
+      <c r="G302" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H302" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I302" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J302" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K302" s="12" t="s">
+      <c r="K302" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L302" s="12">
+      <c r="L302" s="9">
         <v>10</v>
       </c>
-      <c r="M302" s="14">
+      <c r="M302" s="10">
         <v>9000</v>
       </c>
-      <c r="N302" s="14">
+      <c r="N302" s="10">
         <v>90000</v>
       </c>
-      <c r="O302" s="15" t="str">
+      <c r="O302" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P302" s="16" t="str">
+      <c r="P302" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A303" s="11">
+      <c r="A303" s="8">
         <v>46129</v>
       </c>
-      <c r="B303" s="12" t="s">
+      <c r="B303" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C303" s="12" t="s">
+      <c r="C303" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D303" s="12" t="s">
+      <c r="D303" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E303" s="12" t="s">
+      <c r="E303" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="F303" s="13">
+      <c r="F303" s="11">
         <v>778276533</v>
       </c>
-      <c r="G303" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H303" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I303" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J303" s="12" t="s">
+      <c r="G303" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H303" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I303" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J303" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K303" s="12" t="s">
+      <c r="K303" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L303" s="12">
+      <c r="L303" s="9">
         <v>1</v>
       </c>
-      <c r="M303" s="14">
+      <c r="M303" s="10">
         <v>26000</v>
       </c>
-      <c r="N303" s="14">
+      <c r="N303" s="10">
         <v>26000</v>
       </c>
-      <c r="O303" s="15" t="str">
+      <c r="O303" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P303" s="16" t="str">
+      <c r="P303" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A304" s="11">
+      <c r="A304" s="8">
         <v>46129</v>
       </c>
-      <c r="B304" s="12" t="s">
+      <c r="B304" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C304" s="12" t="s">
+      <c r="C304" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D304" s="12" t="s">
+      <c r="D304" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E304" s="12" t="s">
+      <c r="E304" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F304" s="13">
+      <c r="F304" s="11">
         <v>775544532</v>
       </c>
-      <c r="G304" s="12" t="s">
+      <c r="G304" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H304" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I304" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J304" s="12" t="s">
+      <c r="H304" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I304" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J304" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K304" s="12" t="s">
+      <c r="K304" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L304" s="12">
+      <c r="L304" s="9">
         <v>24</v>
       </c>
-      <c r="M304" s="14">
+      <c r="M304" s="10">
         <v>26000</v>
       </c>
-      <c r="N304" s="14">
+      <c r="N304" s="10">
         <v>624000</v>
       </c>
-      <c r="O304" s="15" t="str">
+      <c r="O304" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P304" s="16" t="str">
+      <c r="P304" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A305" s="11">
+      <c r="A305" s="8">
         <v>46129</v>
       </c>
-      <c r="B305" s="12" t="s">
+      <c r="B305" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C305" s="12" t="s">
+      <c r="C305" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D305" s="12" t="s">
+      <c r="D305" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E305" s="12" t="s">
+      <c r="E305" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="F305" s="13">
+      <c r="F305" s="11">
         <v>772131614</v>
       </c>
-      <c r="G305" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H305" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I305" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J305" s="12" t="s">
+      <c r="G305" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H305" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I305" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J305" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K305" s="12" t="s">
+      <c r="K305" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L305" s="12">
+      <c r="L305" s="9">
         <v>1</v>
       </c>
-      <c r="M305" s="14">
+      <c r="M305" s="10">
         <v>53000</v>
       </c>
-      <c r="N305" s="14">
+      <c r="N305" s="10">
         <v>53000</v>
       </c>
-      <c r="O305" s="15" t="str">
+      <c r="O305" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P305" s="16" t="str">
+      <c r="P305" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A306" s="11">
+      <c r="A306" s="8">
         <v>46127</v>
       </c>
-      <c r="B306" s="12" t="s">
+      <c r="B306" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C306" s="12" t="s">
+      <c r="C306" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D306" s="12" t="s">
+      <c r="D306" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E306" s="12" t="s">
+      <c r="E306" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="F306" s="13">
+      <c r="F306" s="11">
         <v>779865100</v>
       </c>
-      <c r="G306" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H306" s="12" t="s">
+      <c r="G306" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H306" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I306" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J306" s="12" t="s">
+      <c r="I306" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J306" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K306" s="12" t="s">
+      <c r="K306" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L306" s="12">
+      <c r="L306" s="9">
         <v>10</v>
       </c>
-      <c r="M306" s="14">
+      <c r="M306" s="10">
         <v>19500</v>
       </c>
-      <c r="N306" s="14">
+      <c r="N306" s="10">
         <v>195000</v>
       </c>
-      <c r="O306" s="15" t="str">
+      <c r="O306" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P306" s="16" t="str">
+      <c r="P306" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="307" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A307" s="11">
+      <c r="A307" s="8">
         <v>46127</v>
       </c>
-      <c r="B307" s="12" t="s">
+      <c r="B307" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C307" s="12" t="s">
+      <c r="C307" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D307" s="12" t="s">
+      <c r="D307" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E307" s="12" t="s">
+      <c r="E307" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="F307" s="13">
+      <c r="F307" s="11">
         <v>779865100</v>
       </c>
-      <c r="G307" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H307" s="12" t="s">
+      <c r="G307" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H307" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I307" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J307" s="12" t="s">
+      <c r="I307" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J307" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K307" s="12" t="s">
+      <c r="K307" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L307" s="12">
+      <c r="L307" s="9">
         <v>20</v>
       </c>
-      <c r="M307" s="14">
+      <c r="M307" s="10">
         <v>9000</v>
       </c>
-      <c r="N307" s="14">
+      <c r="N307" s="10">
         <v>180000</v>
       </c>
-      <c r="O307" s="15" t="str">
+      <c r="O307" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P307" s="16" t="str">
+      <c r="P307" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="308" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A308" s="11">
+      <c r="A308" s="8">
         <v>46127</v>
       </c>
-      <c r="B308" s="12" t="s">
+      <c r="B308" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C308" s="12" t="s">
+      <c r="C308" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D308" s="12" t="s">
+      <c r="D308" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E308" s="12" t="s">
+      <c r="E308" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="F308" s="13">
+      <c r="F308" s="11">
         <v>771871533</v>
       </c>
-      <c r="G308" s="12" t="s">
+      <c r="G308" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H308" s="12" t="s">
+      <c r="H308" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I308" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J308" s="12" t="s">
+      <c r="I308" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J308" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K308" s="12" t="s">
+      <c r="K308" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L308" s="12">
+      <c r="L308" s="9">
         <v>1</v>
       </c>
-      <c r="M308" s="14">
+      <c r="M308" s="10">
         <v>9000</v>
       </c>
-      <c r="N308" s="14">
+      <c r="N308" s="10">
         <v>9000</v>
       </c>
-      <c r="O308" s="15" t="str">
+      <c r="O308" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P308" s="16" t="str">
+      <c r="P308" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="309" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A309" s="11">
+      <c r="A309" s="8">
         <v>46127</v>
       </c>
-      <c r="B309" s="12" t="s">
+      <c r="B309" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C309" s="12" t="s">
+      <c r="C309" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D309" s="12" t="s">
+      <c r="D309" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E309" s="12" t="s">
+      <c r="E309" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="F309" s="13">
+      <c r="F309" s="11">
         <v>771871533</v>
       </c>
-      <c r="G309" s="12" t="s">
+      <c r="G309" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H309" s="12" t="s">
+      <c r="H309" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I309" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J309" s="12" t="s">
+      <c r="I309" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J309" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K309" s="12" t="s">
+      <c r="K309" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L309" s="12">
+      <c r="L309" s="9">
         <v>5</v>
       </c>
-      <c r="M309" s="14">
+      <c r="M309" s="10">
         <v>26000</v>
       </c>
-      <c r="N309" s="14">
+      <c r="N309" s="10">
         <v>130000</v>
       </c>
-      <c r="O309" s="15" t="str">
+      <c r="O309" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P309" s="16" t="str">
+      <c r="P309" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="310" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A310" s="11">
+      <c r="A310" s="8">
         <v>46127</v>
       </c>
-      <c r="B310" s="12" t="s">
+      <c r="B310" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C310" s="12" t="s">
+      <c r="C310" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D310" s="12" t="s">
+      <c r="D310" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E310" s="12" t="s">
+      <c r="E310" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="F310" s="13">
+      <c r="F310" s="11">
         <v>773501029</v>
       </c>
-      <c r="G310" s="12" t="s">
+      <c r="G310" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H310" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I310" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J310" s="12" t="s">
+      <c r="H310" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I310" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J310" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K310" s="12" t="s">
+      <c r="K310" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L310" s="12">
+      <c r="L310" s="9">
         <v>1</v>
       </c>
-      <c r="M310" s="14">
+      <c r="M310" s="10">
         <v>9000</v>
       </c>
-      <c r="N310" s="14">
+      <c r="N310" s="10">
         <v>9000</v>
       </c>
-      <c r="O310" s="15" t="str">
+      <c r="O310" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P310" s="16" t="str">
+      <c r="P310" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="311" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A311" s="11">
+      <c r="A311" s="8">
         <v>46127</v>
       </c>
-      <c r="B311" s="12" t="s">
+      <c r="B311" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C311" s="12" t="s">
+      <c r="C311" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D311" s="12" t="s">
+      <c r="D311" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E311" s="12" t="s">
+      <c r="E311" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="F311" s="13">
+      <c r="F311" s="11">
         <v>773501029</v>
       </c>
-      <c r="G311" s="12" t="s">
+      <c r="G311" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H311" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I311" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J311" s="12" t="s">
+      <c r="H311" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I311" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J311" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K311" s="12" t="s">
+      <c r="K311" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L311" s="12">
+      <c r="L311" s="9">
         <v>5</v>
       </c>
-      <c r="M311" s="14">
+      <c r="M311" s="10">
         <v>26000</v>
       </c>
-      <c r="N311" s="14">
+      <c r="N311" s="10">
         <v>130000</v>
       </c>
-      <c r="O311" s="15" t="str">
+      <c r="O311" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P311" s="16" t="str">
+      <c r="P311" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="312" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A312" s="11">
+      <c r="A312" s="8">
         <v>46127</v>
       </c>
-      <c r="B312" s="12" t="s">
+      <c r="B312" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C312" s="12" t="s">
+      <c r="C312" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D312" s="12" t="s">
+      <c r="D312" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E312" s="12" t="s">
+      <c r="E312" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="F312" s="13">
+      <c r="F312" s="11">
         <v>784464768</v>
       </c>
-      <c r="G312" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H312" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I312" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J312" s="12" t="s">
+      <c r="G312" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H312" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I312" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J312" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K312" s="12" t="s">
+      <c r="K312" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L312" s="12">
-        <v>16</v>
-      </c>
-      <c r="M312" s="14">
+      <c r="L312" s="9">
+        <v>16</v>
+      </c>
+      <c r="M312" s="10">
         <v>26000</v>
       </c>
-      <c r="N312" s="14">
+      <c r="N312" s="10">
         <v>416000</v>
       </c>
-      <c r="O312" s="15" t="str">
+      <c r="O312" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P312" s="16" t="str">
+      <c r="P312" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="313" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A313" s="11">
+      <c r="A313" s="8">
         <v>46126</v>
       </c>
-      <c r="B313" s="12" t="s">
+      <c r="B313" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C313" s="12" t="s">
+      <c r="C313" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D313" s="12" t="s">
+      <c r="D313" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E313" s="12" t="s">
+      <c r="E313" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="F313" s="13">
+      <c r="F313" s="11">
         <v>781316258</v>
       </c>
-      <c r="G313" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H313" s="12" t="s">
+      <c r="G313" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H313" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I313" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J313" s="12" t="s">
+      <c r="I313" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J313" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K313" s="12" t="s">
+      <c r="K313" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L313" s="12">
+      <c r="L313" s="9">
         <v>5</v>
       </c>
-      <c r="M313" s="14">
+      <c r="M313" s="10">
         <v>26000</v>
       </c>
-      <c r="N313" s="14">
+      <c r="N313" s="10">
         <v>130000</v>
       </c>
-      <c r="O313" s="15" t="str">
+      <c r="O313" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P313" s="16" t="str">
+      <c r="P313" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="314" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A314" s="11">
+      <c r="A314" s="8">
         <v>46126</v>
       </c>
-      <c r="B314" s="12" t="s">
+      <c r="B314" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C314" s="12" t="s">
+      <c r="C314" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D314" s="12" t="s">
+      <c r="D314" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E314" s="12" t="s">
+      <c r="E314" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F314" s="13">
+      <c r="F314" s="11">
         <v>775378651</v>
       </c>
-      <c r="G314" s="12" t="s">
+      <c r="G314" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H314" s="12" t="s">
+      <c r="H314" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I314" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J314" s="12" t="s">
+      <c r="I314" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J314" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K314" s="12" t="s">
+      <c r="K314" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L314" s="12">
+      <c r="L314" s="9">
         <v>25</v>
       </c>
-      <c r="M314" s="14">
+      <c r="M314" s="10">
         <v>26000</v>
       </c>
-      <c r="N314" s="14">
+      <c r="N314" s="10">
         <v>650000</v>
       </c>
-      <c r="O314" s="15" t="str">
+      <c r="O314" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P314" s="16" t="str">
+      <c r="P314" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="315" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A315" s="11">
+      <c r="A315" s="8">
         <v>46126</v>
       </c>
-      <c r="B315" s="12" t="s">
+      <c r="B315" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C315" s="12" t="s">
+      <c r="C315" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D315" s="12" t="s">
+      <c r="D315" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E315" s="12" t="s">
+      <c r="E315" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="F315" s="13">
+      <c r="F315" s="11">
         <v>781316258</v>
       </c>
-      <c r="G315" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H315" s="12" t="s">
+      <c r="G315" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H315" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I315" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J315" s="12" t="s">
+      <c r="I315" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J315" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K315" s="12" t="s">
+      <c r="K315" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L315" s="12">
+      <c r="L315" s="9">
         <v>5</v>
       </c>
-      <c r="M315" s="14">
+      <c r="M315" s="10">
         <v>19500</v>
       </c>
-      <c r="N315" s="14">
+      <c r="N315" s="10">
         <v>97500</v>
       </c>
-      <c r="O315" s="15" t="str">
+      <c r="O315" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P315" s="16" t="str">
+      <c r="P315" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="316" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A316" s="11">
+      <c r="A316" s="8">
         <v>46126</v>
       </c>
-      <c r="B316" s="12" t="s">
+      <c r="B316" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C316" s="12" t="s">
+      <c r="C316" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D316" s="12" t="s">
+      <c r="D316" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E316" s="12" t="s">
+      <c r="E316" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="F316" s="13">
+      <c r="F316" s="11">
         <v>781316258</v>
       </c>
-      <c r="G316" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H316" s="12" t="s">
+      <c r="G316" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H316" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I316" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J316" s="12" t="s">
+      <c r="I316" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J316" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K316" s="12" t="s">
+      <c r="K316" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L316" s="12">
+      <c r="L316" s="9">
         <v>10</v>
       </c>
-      <c r="M316" s="14">
+      <c r="M316" s="10">
         <v>28000</v>
       </c>
-      <c r="N316" s="14">
+      <c r="N316" s="10">
         <v>280000</v>
       </c>
-      <c r="O316" s="15" t="str">
+      <c r="O316" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P316" s="16" t="str">
+      <c r="P316" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="317" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A317" s="11">
+      <c r="A317" s="8">
         <v>46126</v>
       </c>
-      <c r="B317" s="12" t="s">
+      <c r="B317" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C317" s="12" t="s">
+      <c r="C317" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D317" s="12" t="s">
+      <c r="D317" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E317" s="12" t="s">
+      <c r="E317" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F317" s="13">
+      <c r="F317" s="11">
         <v>775378651</v>
       </c>
-      <c r="G317" s="12" t="s">
+      <c r="G317" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H317" s="12" t="s">
+      <c r="H317" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I317" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J317" s="12" t="s">
+      <c r="I317" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J317" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K317" s="12" t="s">
+      <c r="K317" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L317" s="12">
+      <c r="L317" s="9">
         <v>3</v>
       </c>
-      <c r="M317" s="14">
+      <c r="M317" s="10">
         <v>19500</v>
       </c>
-      <c r="N317" s="14">
+      <c r="N317" s="10">
         <v>58500</v>
       </c>
-      <c r="O317" s="15" t="str">
+      <c r="O317" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P317" s="16" t="str">
+      <c r="P317" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="318" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A318" s="11">
+      <c r="A318" s="8">
         <v>46126</v>
       </c>
-      <c r="B318" s="12" t="s">
+      <c r="B318" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C318" s="12" t="s">
+      <c r="C318" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D318" s="12" t="s">
+      <c r="D318" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E318" s="12" t="s">
+      <c r="E318" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F318" s="13">
+      <c r="F318" s="11">
         <v>775378651</v>
       </c>
-      <c r="G318" s="12" t="s">
+      <c r="G318" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H318" s="12" t="s">
+      <c r="H318" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I318" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J318" s="12" t="s">
+      <c r="I318" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J318" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K318" s="12" t="s">
+      <c r="K318" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L318" s="12">
+      <c r="L318" s="9">
         <v>5</v>
       </c>
-      <c r="M318" s="14">
+      <c r="M318" s="10">
         <v>9000</v>
       </c>
-      <c r="N318" s="14">
+      <c r="N318" s="10">
         <v>45000</v>
       </c>
-      <c r="O318" s="15" t="str">
+      <c r="O318" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P318" s="16" t="str">
+      <c r="P318" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="319" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A319" s="11">
+      <c r="A319" s="8">
         <v>46126</v>
       </c>
-      <c r="B319" s="12" t="s">
+      <c r="B319" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="C319" s="12" t="s">
+      <c r="C319" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D319" s="12" t="s">
+      <c r="D319" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E319" s="12" t="s">
+      <c r="E319" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F319" s="13">
+      <c r="F319" s="11">
         <v>775378651</v>
       </c>
-      <c r="G319" s="12" t="s">
+      <c r="G319" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H319" s="12" t="s">
+      <c r="H319" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I319" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J319" s="12" t="s">
+      <c r="I319" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J319" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="K319" s="12" t="s">
+      <c r="K319" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L319" s="12">
+      <c r="L319" s="9">
         <v>10</v>
       </c>
-      <c r="M319" s="14">
+      <c r="M319" s="10">
         <v>9000</v>
       </c>
-      <c r="N319" s="14">
+      <c r="N319" s="10">
         <v>90000</v>
       </c>
-      <c r="O319" s="15" t="str">
+      <c r="O319" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P319" s="16" t="str">
+      <c r="P319" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A320" s="11">
+      <c r="A320" s="8">
         <v>46126</v>
       </c>
-      <c r="B320" s="12" t="s">
+      <c r="B320" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C320" s="12" t="s">
+      <c r="C320" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D320" s="12" t="s">
+      <c r="D320" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E320" s="12" t="s">
+      <c r="E320" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="F320" s="13">
+      <c r="F320" s="11">
         <v>776367168</v>
       </c>
-      <c r="G320" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H320" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I320" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J320" s="12" t="s">
+      <c r="G320" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H320" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I320" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J320" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K320" s="12" t="s">
+      <c r="K320" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L320" s="12">
+      <c r="L320" s="9">
         <v>25</v>
       </c>
-      <c r="M320" s="14">
+      <c r="M320" s="10">
         <v>26000</v>
       </c>
-      <c r="N320" s="14">
+      <c r="N320" s="10">
         <v>650000</v>
       </c>
-      <c r="O320" s="15" t="str">
+      <c r="O320" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P320" s="16" t="str">
+      <c r="P320" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="321" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A321" s="11">
+      <c r="A321" s="8">
         <v>46126</v>
       </c>
-      <c r="B321" s="12" t="s">
+      <c r="B321" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C321" s="12" t="s">
+      <c r="C321" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D321" s="12" t="s">
+      <c r="D321" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E321" s="12" t="s">
+      <c r="E321" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="F321" s="13">
+      <c r="F321" s="11">
         <v>773248259</v>
       </c>
-      <c r="G321" s="12" t="s">
+      <c r="G321" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="H321" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I321" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J321" s="12" t="s">
+      <c r="H321" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I321" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J321" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="K321" s="12" t="s">
+      <c r="K321" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L321" s="12">
+      <c r="L321" s="9">
         <v>2</v>
       </c>
-      <c r="M321" s="14">
+      <c r="M321" s="10">
         <v>19500</v>
       </c>
-      <c r="N321" s="14">
+      <c r="N321" s="10">
         <v>39000</v>
       </c>
-      <c r="O321" s="15" t="str">
+      <c r="O321" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P321" s="16" t="str">
+      <c r="P321" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="322" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A322" s="11">
+      <c r="A322" s="8">
         <v>46126</v>
       </c>
-      <c r="B322" s="12" t="s">
+      <c r="B322" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C322" s="12" t="s">
+      <c r="C322" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D322" s="12" t="s">
+      <c r="D322" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E322" s="12" t="s">
+      <c r="E322" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="F322" s="13">
+      <c r="F322" s="11">
         <v>774446616</v>
       </c>
-      <c r="G322" s="12" t="s">
+      <c r="G322" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="H322" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I322" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J322" s="12" t="s">
+      <c r="H322" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I322" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J322" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K322" s="12" t="s">
+      <c r="K322" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="L322" s="12">
+      <c r="L322" s="9">
         <v>4</v>
       </c>
-      <c r="M322" s="14">
+      <c r="M322" s="10">
         <v>12500</v>
       </c>
-      <c r="N322" s="14">
+      <c r="N322" s="10">
         <v>50000</v>
       </c>
-      <c r="O322" s="15" t="str">
+      <c r="O322" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P322" s="16" t="str">
+      <c r="P322" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A323" s="11">
+      <c r="A323" s="8">
         <v>46126</v>
       </c>
-      <c r="B323" s="12" t="s">
+      <c r="B323" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C323" s="12" t="s">
+      <c r="C323" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D323" s="12" t="s">
+      <c r="D323" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E323" s="12" t="s">
+      <c r="E323" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="F323" s="13">
+      <c r="F323" s="11">
         <v>774446616</v>
       </c>
-      <c r="G323" s="12" t="s">
+      <c r="G323" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="H323" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I323" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J323" s="12" t="s">
+      <c r="H323" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I323" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J323" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K323" s="12" t="s">
+      <c r="K323" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="L323" s="12">
+      <c r="L323" s="9">
         <v>1</v>
       </c>
-      <c r="M323" s="14">
+      <c r="M323" s="10">
         <v>15500</v>
       </c>
-      <c r="N323" s="14">
+      <c r="N323" s="10">
         <v>15500</v>
       </c>
-      <c r="O323" s="15" t="str">
+      <c r="O323" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P323" s="16" t="str">
+      <c r="P323" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="324" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A324" s="11">
+      <c r="A324" s="8">
         <v>46130</v>
       </c>
-      <c r="B324" s="12" t="s">
+      <c r="B324" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C324" s="12" t="s">
+      <c r="C324" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D324" s="12" t="s">
+      <c r="D324" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E324" s="12" t="s">
+      <c r="E324" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F324" s="13">
+      <c r="F324" s="11">
         <v>762951288</v>
       </c>
-      <c r="G324" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H324" s="12" t="s">
+      <c r="G324" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H324" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I324" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J324" s="12" t="s">
+      <c r="I324" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J324" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K324" s="12" t="s">
+      <c r="K324" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L324" s="12">
+      <c r="L324" s="9">
         <v>1</v>
       </c>
-      <c r="M324" s="14">
+      <c r="M324" s="10">
         <v>26000</v>
       </c>
-      <c r="N324" s="14">
+      <c r="N324" s="10">
         <v>26000</v>
       </c>
-      <c r="O324" s="15" t="str">
+      <c r="O324" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P324" s="16" t="str">
+      <c r="P324" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A325" s="11">
+      <c r="A325" s="8">
         <v>46130</v>
       </c>
-      <c r="B325" s="12" t="s">
+      <c r="B325" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C325" s="12" t="s">
+      <c r="C325" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D325" s="12" t="s">
+      <c r="D325" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E325" s="12" t="s">
+      <c r="E325" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F325" s="13">
+      <c r="F325" s="11">
         <v>772038792</v>
       </c>
-      <c r="G325" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H325" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I325" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J325" s="12" t="s">
+      <c r="G325" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H325" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I325" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J325" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K325" s="12" t="s">
+      <c r="K325" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L325" s="12">
+      <c r="L325" s="9">
         <v>1</v>
       </c>
-      <c r="M325" s="14">
+      <c r="M325" s="10">
         <v>53000</v>
       </c>
-      <c r="N325" s="14">
+      <c r="N325" s="10">
         <v>53000</v>
       </c>
-      <c r="O325" s="15" t="str">
+      <c r="O325" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P325" s="16" t="str">
+      <c r="P325" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A326" s="11">
+      <c r="A326" s="8">
         <v>46130</v>
       </c>
-      <c r="B326" s="12" t="s">
+      <c r="B326" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C326" s="12" t="s">
+      <c r="C326" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D326" s="12" t="s">
+      <c r="D326" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E326" s="12" t="s">
+      <c r="E326" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F326" s="13">
+      <c r="F326" s="11">
         <v>772038792</v>
       </c>
-      <c r="G326" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H326" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I326" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J326" s="12" t="s">
+      <c r="G326" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H326" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I326" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J326" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="K326" s="12" t="s">
+      <c r="K326" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L326" s="12">
+      <c r="L326" s="9">
         <v>2</v>
       </c>
-      <c r="M326" s="14">
+      <c r="M326" s="10">
         <v>19500</v>
       </c>
-      <c r="N326" s="14">
+      <c r="N326" s="10">
         <v>39000</v>
       </c>
-      <c r="O326" s="15" t="str">
+      <c r="O326" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P326" s="16" t="str">
+      <c r="P326" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A327" s="11">
+      <c r="A327" s="8">
         <v>46130</v>
       </c>
-      <c r="B327" s="12" t="s">
+      <c r="B327" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C327" s="12" t="s">
+      <c r="C327" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D327" s="12" t="s">
+      <c r="D327" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E327" s="12" t="s">
+      <c r="E327" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="F327" s="13">
+      <c r="F327" s="11">
         <v>774993694</v>
       </c>
-      <c r="G327" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H327" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="I327" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J327" s="12" t="s">
+      <c r="G327" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H327" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I327" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J327" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K327" s="12" t="s">
+      <c r="K327" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L327" s="12">
+      <c r="L327" s="9">
         <v>50</v>
       </c>
-      <c r="M327" s="14">
+      <c r="M327" s="10">
         <v>26000</v>
       </c>
-      <c r="N327" s="14">
+      <c r="N327" s="10">
         <v>1300000</v>
       </c>
-      <c r="O327" s="15" t="str">
+      <c r="O327" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P327" s="16" t="str">
+      <c r="P327" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="328" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A328" s="11">
+      <c r="A328" s="8">
         <v>46130</v>
       </c>
-      <c r="B328" s="12" t="s">
+      <c r="B328" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C328" s="12" t="s">
+      <c r="C328" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D328" s="12" t="s">
+      <c r="D328" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E328" s="12" t="s">
+      <c r="E328" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F328" s="13">
+      <c r="F328" s="11">
         <v>762951288</v>
       </c>
-      <c r="G328" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H328" s="12" t="s">
+      <c r="G328" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H328" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I328" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J328" s="12" t="s">
+      <c r="I328" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J328" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K328" s="12" t="s">
+      <c r="K328" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="L328" s="12">
+      <c r="L328" s="9">
         <v>37</v>
       </c>
-      <c r="M328" s="14">
+      <c r="M328" s="10">
         <v>53000</v>
       </c>
-      <c r="N328" s="14">
+      <c r="N328" s="10">
         <v>1961000</v>
       </c>
-      <c r="O328" s="15" t="str">
+      <c r="O328" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P328" s="16" t="str">
+      <c r="P328" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A329" s="11">
+      <c r="A329" s="8">
         <v>46130</v>
       </c>
-      <c r="B329" s="12" t="s">
+      <c r="B329" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C329" s="12" t="s">
+      <c r="C329" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D329" s="12" t="s">
+      <c r="D329" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E329" s="12" t="s">
+      <c r="E329" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F329" s="13">
+      <c r="F329" s="11">
         <v>762951288</v>
       </c>
-      <c r="G329" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H329" s="12" t="s">
+      <c r="G329" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H329" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I329" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J329" s="12" t="s">
+      <c r="I329" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J329" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K329" s="12" t="s">
+      <c r="K329" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="L329" s="12">
+      <c r="L329" s="9">
         <v>1</v>
       </c>
-      <c r="M329" s="14">
+      <c r="M329" s="10">
         <v>9000</v>
       </c>
-      <c r="N329" s="14">
+      <c r="N329" s="10">
         <v>9000</v>
       </c>
-      <c r="O329" s="15" t="str">
+      <c r="O329" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S16</v>
       </c>
-      <c r="P329" s="16" t="str">
+      <c r="P329" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="330" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A330" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B330" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C330" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D330" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E330" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F330" s="13">
+        <v>770933492</v>
+      </c>
+      <c r="G330" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H330" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I330" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J330" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K330" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="L330" s="13">
+        <v>1</v>
+      </c>
+      <c r="M330" s="14">
+        <v>17500</v>
+      </c>
+      <c r="N330" s="14">
+        <v>17500</v>
+      </c>
+      <c r="O330" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P330" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="331" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A331" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B331" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C331" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D331" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E331" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F331" s="13">
+        <v>770933492</v>
+      </c>
+      <c r="G331" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H331" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I331" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J331" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K331" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L331" s="13">
+        <v>2</v>
+      </c>
+      <c r="M331" s="14">
+        <v>12000</v>
+      </c>
+      <c r="N331" s="14">
+        <v>24000</v>
+      </c>
+      <c r="O331" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P331" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A332" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B332" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C332" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D332" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E332" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F332" s="13">
+        <v>770933492</v>
+      </c>
+      <c r="G332" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H332" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I332" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J332" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K332" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L332" s="13">
+        <v>15</v>
+      </c>
+      <c r="M332" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N332" s="14">
+        <v>795000</v>
+      </c>
+      <c r="O332" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P332" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A333" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B333" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C333" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D333" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E333" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="F333" s="13">
+        <v>778487159</v>
+      </c>
+      <c r="G333" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="H333" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I333" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J333" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K333" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="L333" s="13">
+        <v>2</v>
+      </c>
+      <c r="M333" s="14">
+        <v>15500</v>
+      </c>
+      <c r="N333" s="14">
+        <v>31000</v>
+      </c>
+      <c r="O333" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P333" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A334" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B334" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C334" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D334" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E334" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="F334" s="13">
+        <v>777013132</v>
+      </c>
+      <c r="G334" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H334" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I334" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J334" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K334" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L334" s="13">
+        <v>5</v>
+      </c>
+      <c r="M334" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N334" s="14">
+        <v>265000</v>
+      </c>
+      <c r="O334" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P334" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A335" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B335" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C335" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D335" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E335" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F335" s="17">
+        <v>776634479</v>
+      </c>
+      <c r="G335" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H335" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I335" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J335" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K335" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L335" s="13">
+        <v>10</v>
+      </c>
+      <c r="M335" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N335" s="14">
+        <v>530000</v>
+      </c>
+      <c r="O335" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P335" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A336" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B336" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C336" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D336" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E336" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F336" s="17">
+        <v>770712599</v>
+      </c>
+      <c r="G336" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H336" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I336" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J336" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="K336" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L336" s="13">
+        <v>300</v>
+      </c>
+      <c r="M336" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N336" s="14">
+        <v>15900000</v>
+      </c>
+      <c r="O336" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P336" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="337" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A337" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B337" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C337" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D337" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E337" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F337" s="17">
+        <v>780172121</v>
+      </c>
+      <c r="G337" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H337" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I337" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J337" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K337" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="L337" s="13">
+        <v>1</v>
+      </c>
+      <c r="M337" s="14">
+        <v>12500</v>
+      </c>
+      <c r="N337" s="14">
+        <v>12500</v>
+      </c>
+      <c r="O337" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P337" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="338" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A338" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B338" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="C338" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D338" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E338" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F338" s="17">
+        <v>779676016</v>
+      </c>
+      <c r="G338" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H338" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I338" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J338" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K338" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="L338" s="13">
+        <v>25</v>
+      </c>
+      <c r="M338" s="14">
+        <v>12500</v>
+      </c>
+      <c r="N338" s="14">
+        <v>312500</v>
+      </c>
+      <c r="O338" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P338" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="339" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A339" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B339" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C339" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D339" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E339" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F339" s="17">
+        <v>770712599</v>
+      </c>
+      <c r="G339" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H339" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I339" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J339" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="K339" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="L339" s="13">
+        <v>2</v>
+      </c>
+      <c r="M339" s="14">
+        <v>10500</v>
+      </c>
+      <c r="N339" s="14">
+        <v>21000</v>
+      </c>
+      <c r="O339" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P339" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="340" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A340" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B340" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C340" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D340" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E340" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F340" s="17">
+        <v>770712599</v>
+      </c>
+      <c r="G340" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H340" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I340" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J340" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="K340" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L340" s="13">
+        <v>25</v>
+      </c>
+      <c r="M340" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N340" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O340" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P340" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="341" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A341" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B341" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C341" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D341" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E341" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F341" s="17">
+        <v>772957336</v>
+      </c>
+      <c r="G341" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H341" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I341" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J341" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="K341" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L341" s="13">
+        <v>2</v>
+      </c>
+      <c r="M341" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N341" s="14">
+        <v>106000</v>
+      </c>
+      <c r="O341" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P341" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="342" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A342" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B342" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C342" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D342" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="F342" s="17">
+        <v>773040043</v>
+      </c>
+      <c r="G342" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H342" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I342" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J342" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K342" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L342" s="13">
+        <v>2</v>
+      </c>
+      <c r="M342" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N342" s="14">
+        <v>106000</v>
+      </c>
+      <c r="O342" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P342" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="343" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A343" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B343" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C343" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D343" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E343" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F343" s="17">
+        <v>776548448</v>
+      </c>
+      <c r="G343" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H343" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I343" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J343" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="K343" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L343" s="13">
+        <v>15</v>
+      </c>
+      <c r="M343" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N343" s="14">
+        <v>795000</v>
+      </c>
+      <c r="O343" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P343" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="344" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A344" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B344" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C344" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D344" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F344" s="17">
+        <v>775544532</v>
+      </c>
+      <c r="G344" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H344" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I344" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J344" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="K344" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="L344" s="13">
+        <v>25</v>
+      </c>
+      <c r="M344" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N344" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O344" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P344" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="345" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A345" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B345" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C345" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D345" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E345" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F345" s="17">
+        <v>777972938</v>
+      </c>
+      <c r="G345" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H345" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I345" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J345" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="K345" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L345" s="13">
+        <v>2</v>
+      </c>
+      <c r="M345" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N345" s="14">
+        <v>106000</v>
+      </c>
+      <c r="O345" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P345" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="346" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A346" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B346" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C346" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D346" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E346" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F346" s="17">
+        <v>774245132</v>
+      </c>
+      <c r="G346" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H346" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I346" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J346" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K346" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="L346" s="13">
+        <v>2</v>
+      </c>
+      <c r="M346" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N346" s="14">
+        <v>52000</v>
+      </c>
+      <c r="O346" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P346" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="347" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A347" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B347" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C347" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D347" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E347" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F347" s="17">
+        <v>774245132</v>
+      </c>
+      <c r="G347" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H347" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I347" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J347" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K347" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="L347" s="13">
+        <v>10</v>
+      </c>
+      <c r="M347" s="14">
+        <v>14000</v>
+      </c>
+      <c r="N347" s="14">
+        <v>140000</v>
+      </c>
+      <c r="O347" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P347" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="348" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A348" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B348" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C348" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D348" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E348" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F348" s="17">
+        <v>774245132</v>
+      </c>
+      <c r="G348" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H348" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I348" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J348" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K348" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="L348" s="13">
+        <v>5</v>
+      </c>
+      <c r="M348" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N348" s="14">
+        <v>97500</v>
+      </c>
+      <c r="O348" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P348" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="349" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A349" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B349" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C349" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D349" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E349" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F349" s="17">
+        <v>775582583</v>
+      </c>
+      <c r="G349" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H349" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I349" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J349" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K349" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L349" s="13">
+        <v>25</v>
+      </c>
+      <c r="M349" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N349" s="14">
+        <v>700000</v>
+      </c>
+      <c r="O349" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P349" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="350" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A350" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B350" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C350" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D350" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E350" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="F350" s="17">
+        <v>776294949</v>
+      </c>
+      <c r="G350" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H350" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I350" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J350" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="K350" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L350" s="13">
+        <v>50</v>
+      </c>
+      <c r="M350" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N350" s="14">
+        <v>2650000</v>
+      </c>
+      <c r="O350" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P350" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="351" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A351" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B351" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C351" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D351" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E351" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F351" s="17">
+        <v>776428218</v>
+      </c>
+      <c r="G351" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H351" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I351" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J351" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K351" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L351" s="13">
+        <v>2</v>
+      </c>
+      <c r="M351" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N351" s="14">
+        <v>106000</v>
+      </c>
+      <c r="O351" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P351" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="352" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A352" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B352" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C352" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D352" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E352" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F352" s="17">
+        <v>771952687</v>
+      </c>
+      <c r="G352" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H352" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I352" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J352" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K352" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L352" s="13">
+        <v>6</v>
+      </c>
+      <c r="M352" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N352" s="14">
+        <v>318000</v>
+      </c>
+      <c r="O352" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P352" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="353" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A353" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B353" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C353" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D353" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E353" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F353" s="17">
+        <v>774061052</v>
+      </c>
+      <c r="G353" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H353" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I353" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J353" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K353" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L353" s="13">
+        <v>2</v>
+      </c>
+      <c r="M353" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N353" s="14">
+        <v>106000</v>
+      </c>
+      <c r="O353" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P353" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="354" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A354" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B354" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C354" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D354" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E354" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="F354" s="17">
+        <v>777132186</v>
+      </c>
+      <c r="G354" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H354" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I354" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J354" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K354" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L354" s="13">
+        <v>5</v>
+      </c>
+      <c r="M354" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N354" s="14">
+        <v>265000</v>
+      </c>
+      <c r="O354" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P354" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="355" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A355" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B355" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C355" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D355" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E355" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="F355" s="17">
+        <v>776149093</v>
+      </c>
+      <c r="G355" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H355" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="I355" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J355" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K355" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L355" s="13">
+        <v>25</v>
+      </c>
+      <c r="M355" s="14">
+        <v>6000</v>
+      </c>
+      <c r="N355" s="14">
+        <v>150000</v>
+      </c>
+      <c r="O355" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P355" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="356" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A356" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B356" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="C356" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D356" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E356" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F356" s="17">
+        <v>774245132</v>
+      </c>
+      <c r="G356" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H356" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I356" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J356" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K356" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L356" s="13">
+        <v>5</v>
+      </c>
+      <c r="M356" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N356" s="14">
+        <v>265000</v>
+      </c>
+      <c r="O356" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P356" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="357" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A357" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B357" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C357" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D357" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E357" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="F357" s="17">
+        <v>771987678</v>
+      </c>
+      <c r="G357" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H357" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I357" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J357" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="K357" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="L357" s="13">
+        <v>25</v>
+      </c>
+      <c r="M357" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N357" s="14">
+        <v>225000</v>
+      </c>
+      <c r="O357" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P357" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A358" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B358" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C358" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D358" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E358" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F358" s="17">
+        <v>784426640</v>
+      </c>
+      <c r="G358" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H358" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I358" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J358" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="K358" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L358" s="13">
+        <v>10</v>
+      </c>
+      <c r="M358" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N358" s="14">
+        <v>530000</v>
+      </c>
+      <c r="O358" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P358" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="359" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A359" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B359" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C359" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D359" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E359" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F359" s="17">
+        <v>775273147</v>
+      </c>
+      <c r="G359" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H359" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I359" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J359" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K359" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L359" s="13">
+        <v>100</v>
+      </c>
+      <c r="M359" s="14">
+        <v>5750</v>
+      </c>
+      <c r="N359" s="14">
+        <v>575000</v>
+      </c>
+      <c r="O359" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P359" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A360" s="12">
+        <v>46137</v>
+      </c>
+      <c r="B360" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="C360" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="D360" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="E360" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="F360" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="G360" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H360" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I360" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J360" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K360" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L360" s="13">
+        <v>35</v>
+      </c>
+      <c r="M360" s="14">
+        <v>53000</v>
+      </c>
+      <c r="N360" s="14">
+        <v>1855000</v>
+      </c>
+      <c r="O360" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S17</v>
+      </c>
+      <c r="P360" s="16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18762915-CCC8-48A0-A53C-954A8BD33FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D77436-BBDE-442E-986A-5F34D781D01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="86">
   <si>
     <t>Date</t>
   </si>
@@ -213,12 +213,6 @@
   </si>
   <si>
     <t>Keur Massar Sotrac</t>
-  </si>
-  <si>
-    <t>Zac Mbao</t>
-  </si>
-  <si>
-    <t>Ibrahima Tahirou</t>
   </si>
   <si>
     <t>Ablaye</t>
@@ -364,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -385,22 +379,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,8 +695,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P32" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P32" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P31" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P31" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1019,7 +1009,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -1094,7 +1084,7 @@
         <v>46139</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>14</v>
@@ -1103,7 +1093,7 @@
         <v>36</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F2" s="9">
         <v>777128516</v>
@@ -1132,11 +1122,11 @@
       <c r="N2" s="11">
         <v>3000000</v>
       </c>
-      <c r="O2" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P2" s="13" t="str">
+      <c r="O2" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P2" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1146,7 +1136,7 @@
         <v>46139</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>31</v>
@@ -1155,7 +1145,7 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F3" s="10">
         <v>777132186</v>
@@ -1173,7 +1163,7 @@
         <v>20</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L3" s="9">
         <v>21</v>
@@ -1184,11 +1174,11 @@
       <c r="N3" s="11">
         <v>1113000</v>
       </c>
-      <c r="O3" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P3" s="13" t="str">
+      <c r="O3" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P3" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1198,7 +1188,7 @@
         <v>46139</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>31</v>
@@ -1207,7 +1197,7 @@
         <v>32</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="10">
         <v>776149093</v>
@@ -1236,11 +1226,11 @@
       <c r="N4" s="11">
         <v>150000</v>
       </c>
-      <c r="O4" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P4" s="13" t="str">
+      <c r="O4" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P4" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1250,7 +1240,7 @@
         <v>46139</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>23</v>
@@ -1259,7 +1249,7 @@
         <v>59</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5" s="10">
         <v>774249189</v>
@@ -1288,11 +1278,11 @@
       <c r="N5" s="11">
         <v>650000</v>
       </c>
-      <c r="O5" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P5" s="13" t="str">
+      <c r="O5" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P5" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1302,16 +1292,16 @@
         <v>46140</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F6" s="10">
         <v>776528748</v>
@@ -1329,7 +1319,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L6" s="9">
         <v>1</v>
@@ -1340,11 +1330,11 @@
       <c r="N6" s="11">
         <v>15500</v>
       </c>
-      <c r="O6" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P6" s="13" t="str">
+      <c r="O6" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P6" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1354,16 +1344,16 @@
         <v>46140</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F7" s="10">
         <v>776528748</v>
@@ -1381,7 +1371,7 @@
         <v>20</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L7" s="9">
         <v>66</v>
@@ -1392,11 +1382,11 @@
       <c r="N7" s="11">
         <v>3498000</v>
       </c>
-      <c r="O7" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P7" s="13" t="str">
+      <c r="O7" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P7" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1406,16 +1396,16 @@
         <v>46140</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F8" s="10">
         <v>776528748</v>
@@ -1444,11 +1434,11 @@
       <c r="N8" s="11">
         <v>234000</v>
       </c>
-      <c r="O8" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P8" s="13" t="str">
+      <c r="O8" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P8" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1458,7 +1448,7 @@
         <v>46140</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>31</v>
@@ -1496,11 +1486,11 @@
       <c r="N9" s="11">
         <v>5200000</v>
       </c>
-      <c r="O9" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P9" s="13" t="str">
+      <c r="O9" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P9" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1510,7 +1500,7 @@
         <v>46140</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>31</v>
@@ -1548,11 +1538,11 @@
       <c r="N10" s="11">
         <v>1800000</v>
       </c>
-      <c r="O10" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P10" s="13" t="str">
+      <c r="O10" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P10" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1562,7 +1552,7 @@
         <v>46140</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>23</v>
@@ -1571,7 +1561,7 @@
         <v>40</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F11" s="10">
         <v>761490227</v>
@@ -1589,7 +1579,7 @@
         <v>45</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L11" s="9">
         <v>25</v>
@@ -1600,11 +1590,11 @@
       <c r="N11" s="11">
         <v>1325000</v>
       </c>
-      <c r="O11" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P11" s="13" t="str">
+      <c r="O11" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P11" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1614,7 +1604,7 @@
         <v>46140</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>23</v>
@@ -1623,7 +1613,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F12" s="10">
         <v>772625989</v>
@@ -1641,7 +1631,7 @@
         <v>45</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L12" s="9">
         <v>10</v>
@@ -1652,11 +1642,11 @@
       <c r="N12" s="11">
         <v>530000</v>
       </c>
-      <c r="O12" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P12" s="13" t="str">
+      <c r="O12" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P12" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1675,7 +1665,7 @@
         <v>39</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10">
         <v>773122246</v>
@@ -1693,7 +1683,7 @@
         <v>48</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L13" s="9">
         <v>25</v>
@@ -1704,11 +1694,11 @@
       <c r="N13" s="11">
         <v>225000</v>
       </c>
-      <c r="O13" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P13" s="13" t="str">
+      <c r="O13" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P13" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1718,7 +1708,7 @@
         <v>46141</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>25</v>
@@ -1745,7 +1735,7 @@
         <v>26</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L14" s="9">
         <v>2</v>
@@ -1756,11 +1746,11 @@
       <c r="N14" s="11">
         <v>18000</v>
       </c>
-      <c r="O14" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P14" s="13" t="str">
+      <c r="O14" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P14" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1770,7 +1760,7 @@
         <v>46141</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>25</v>
@@ -1808,11 +1798,11 @@
       <c r="N15" s="11">
         <v>12000</v>
       </c>
-      <c r="O15" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P15" s="13" t="str">
+      <c r="O15" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1822,7 +1812,7 @@
         <v>46141</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>25</v>
@@ -1860,11 +1850,11 @@
       <c r="N16" s="11">
         <v>39000</v>
       </c>
-      <c r="O16" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P16" s="13" t="str">
+      <c r="O16" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1874,7 +1864,7 @@
         <v>46141</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>25</v>
@@ -1901,7 +1891,7 @@
         <v>26</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L17" s="9">
         <v>10</v>
@@ -1912,11 +1902,11 @@
       <c r="N17" s="11">
         <v>530000</v>
       </c>
-      <c r="O17" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P17" s="13" t="str">
+      <c r="O17" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P17" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1926,7 +1916,7 @@
         <v>46141</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>25</v>
@@ -1964,11 +1954,11 @@
       <c r="N18" s="11">
         <v>650000</v>
       </c>
-      <c r="O18" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P18" s="13" t="str">
+      <c r="O18" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P18" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -1978,7 +1968,7 @@
         <v>46140</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>25</v>
@@ -1987,7 +1977,7 @@
         <v>33</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F19" s="10">
         <v>772131614</v>
@@ -2016,11 +2006,11 @@
       <c r="N19" s="11">
         <v>19500</v>
       </c>
-      <c r="O19" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P19" s="13" t="str">
+      <c r="O19" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2030,7 +2020,7 @@
         <v>46140</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>25</v>
@@ -2039,7 +2029,7 @@
         <v>33</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F20" s="10">
         <v>778291515</v>
@@ -2068,11 +2058,11 @@
       <c r="N20" s="11">
         <v>84000</v>
       </c>
-      <c r="O20" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P20" s="13" t="str">
+      <c r="O20" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2082,7 +2072,7 @@
         <v>46140</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>25</v>
@@ -2091,7 +2081,7 @@
         <v>33</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F21" s="10">
         <v>772131614</v>
@@ -2120,11 +2110,11 @@
       <c r="N21" s="11">
         <v>26000</v>
       </c>
-      <c r="O21" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P21" s="13" t="str">
+      <c r="O21" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P21" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2134,7 +2124,7 @@
         <v>46140</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>25</v>
@@ -2143,7 +2133,7 @@
         <v>33</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F22" s="10">
         <v>708015391</v>
@@ -2161,7 +2151,7 @@
         <v>26</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L22" s="9">
         <v>6</v>
@@ -2172,11 +2162,11 @@
       <c r="N22" s="11">
         <v>318000</v>
       </c>
-      <c r="O22" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P22" s="13" t="str">
+      <c r="O22" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P22" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2186,7 +2176,7 @@
         <v>46140</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>25</v>
@@ -2195,7 +2185,7 @@
         <v>33</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F23" s="10">
         <v>708015391</v>
@@ -2213,7 +2203,7 @@
         <v>26</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L23" s="9">
         <v>5</v>
@@ -2224,11 +2214,11 @@
       <c r="N23" s="11">
         <v>45000</v>
       </c>
-      <c r="O23" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P23" s="13" t="str">
+      <c r="O23" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P23" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2238,7 +2228,7 @@
         <v>46141</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>31</v>
@@ -2276,11 +2266,11 @@
       <c r="N24" s="11">
         <v>7500000</v>
       </c>
-      <c r="O24" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P24" s="13" t="str">
+      <c r="O24" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P24" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2299,7 +2289,7 @@
         <v>22</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10">
         <v>760169386</v>
@@ -2328,11 +2318,11 @@
       <c r="N25" s="11">
         <v>650000</v>
       </c>
-      <c r="O25" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P25" s="13" t="str">
+      <c r="O25" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P25" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2351,7 +2341,7 @@
         <v>57</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F26" s="10">
         <v>776818022</v>
@@ -2380,11 +2370,11 @@
       <c r="N26" s="11">
         <v>487500</v>
       </c>
-      <c r="O26" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P26" s="13" t="str">
+      <c r="O26" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P26" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2394,7 +2384,7 @@
         <v>46142</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>14</v>
@@ -2421,7 +2411,7 @@
         <v>38</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L27" s="9">
         <v>10</v>
@@ -2432,11 +2422,11 @@
       <c r="N27" s="11">
         <v>125000</v>
       </c>
-      <c r="O27" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P27" s="13" t="str">
+      <c r="O27" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P27" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2446,7 +2436,7 @@
         <v>46142</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>14</v>
@@ -2473,7 +2463,7 @@
         <v>38</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L28" s="9">
         <v>15</v>
@@ -2484,11 +2474,11 @@
       <c r="N28" s="11">
         <v>187500</v>
       </c>
-      <c r="O28" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P28" s="13" t="str">
+      <c r="O28" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P28" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2507,7 +2497,7 @@
         <v>44</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F29" s="10">
         <v>774993694</v>
@@ -2536,11 +2526,11 @@
       <c r="N29" s="11">
         <v>6000</v>
       </c>
-      <c r="O29" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P29" s="13" t="str">
+      <c r="O29" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P29" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2559,7 +2549,7 @@
         <v>44</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F30" s="10">
         <v>774993694</v>
@@ -2588,11 +2578,11 @@
       <c r="N30" s="11">
         <v>975000</v>
       </c>
-      <c r="O30" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P30" s="13" t="str">
+      <c r="O30" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P30" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>
@@ -2602,22 +2592,22 @@
         <v>46142</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="F31" s="10">
-        <v>784785900</v>
+        <v>779724512</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>13</v>
@@ -2626,77 +2616,25 @@
         <v>16</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L31" s="9">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M31" s="11">
-        <v>54000</v>
+        <v>9000</v>
       </c>
       <c r="N31" s="11">
-        <v>810000</v>
-      </c>
-      <c r="O31" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P31" s="13" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>avril</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A32" s="8">
-        <v>46142</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="10">
-        <v>779724512</v>
-      </c>
-      <c r="G32" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L32" s="9">
-        <v>25</v>
-      </c>
-      <c r="M32" s="11">
-        <v>9000</v>
-      </c>
-      <c r="N32" s="11">
         <v>225000</v>
       </c>
-      <c r="O32" s="12" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P32" s="13" t="str">
+      <c r="O31" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P31" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D77436-BBDE-442E-986A-5F34D781D01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BF6D3C-DAF1-4902-9A10-BE368CE1C4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="88">
   <si>
     <t>Date</t>
   </si>
@@ -291,6 +291,12 @@
   </si>
   <si>
     <t>Abdou sow</t>
+  </si>
+  <si>
+    <t>Zac Mbao</t>
+  </si>
+  <si>
+    <t>Ibrahima Tahirou</t>
   </si>
 </sst>
 </file>
@@ -358,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -391,6 +397,22 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,8 +717,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P31" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P31" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P32" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P32" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1009,7 +1031,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -2639,6 +2661,58 @@
         <v>avril</v>
       </c>
     </row>
+    <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A32" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="14">
+        <v>784785900</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" s="13">
+        <v>15</v>
+      </c>
+      <c r="M32" s="15">
+        <v>54000</v>
+      </c>
+      <c r="N32" s="15">
+        <v>810000</v>
+      </c>
+      <c r="O32" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S18</v>
+      </c>
+      <c r="P32" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>avril</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BF6D3C-DAF1-4902-9A10-BE368CE1C4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D8395-2B83-4982-87F9-9FA612822B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="126">
   <si>
     <t>Date</t>
   </si>
@@ -297,6 +297,120 @@
   </si>
   <si>
     <t>Ibrahima Tahirou</t>
+  </si>
+  <si>
+    <t>Grand Dakar</t>
+  </si>
+  <si>
+    <t>Wane</t>
+  </si>
+  <si>
+    <t>Mouhamed CISSE</t>
+  </si>
+  <si>
+    <t>Il n'avait plus de stock</t>
+  </si>
+  <si>
+    <t>Rufisque</t>
+  </si>
+  <si>
+    <t>Bassirou FALL</t>
+  </si>
+  <si>
+    <t>Souhaibou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il dit de repasser la semaine prochaine pour le lait évaporé </t>
+  </si>
+  <si>
+    <t>MACTAR</t>
+  </si>
+  <si>
+    <t>On lui a fait une remise de 14 Cartons (28000) reste à verser 672000f</t>
+  </si>
+  <si>
+    <t>Pikine Sandika</t>
+  </si>
+  <si>
+    <t>Galle GOLLE</t>
+  </si>
+  <si>
+    <t>Marché Bou Bess</t>
+  </si>
+  <si>
+    <t>ABLAYE DIALLO</t>
+  </si>
+  <si>
+    <t>Sodidalo SARL</t>
+  </si>
+  <si>
+    <t>Keur Massar Ainoumady</t>
+  </si>
+  <si>
+    <t>Mouhamed Bâ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il veut essayer </t>
+  </si>
+  <si>
+    <t>Adama Bâ</t>
+  </si>
+  <si>
+    <t>Assane</t>
+  </si>
+  <si>
+    <t>Thierno DIALLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il avait essayer le lait mais il dit que ses clients ont apprécié le lait </t>
+  </si>
+  <si>
+    <t>Ameth</t>
+  </si>
+  <si>
+    <t>Mamodou DIALLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS livré depuis Mercredi </t>
+  </si>
+  <si>
+    <t>Modou Ndiaye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il n'avait plus de stock </t>
+  </si>
+  <si>
+    <t>Mohamed</t>
+  </si>
+  <si>
+    <t>Mbao</t>
+  </si>
+  <si>
+    <t>Abdou Leye</t>
+  </si>
+  <si>
+    <t>Ibrahima Diallo</t>
+  </si>
+  <si>
+    <t>Mamadou BA</t>
+  </si>
+  <si>
+    <t>Il veut essayer le produit mais il veut 100 sac et demande s'il peut avoir une échéance de 10 jours</t>
+  </si>
+  <si>
+    <t>Terminus 54</t>
+  </si>
+  <si>
+    <t>BABACAR Cissé</t>
+  </si>
+  <si>
+    <t>Béckaye</t>
+  </si>
+  <si>
+    <t>Moustapha Baldé</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
   </si>
 </sst>
 </file>
@@ -403,9 +517,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -413,6 +524,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,8 +831,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P32" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P32" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P60" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P60" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1031,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -2662,55 +2776,1511 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A32" s="12">
+      <c r="A32" s="8">
         <v>46142</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="10">
         <v>784785900</v>
       </c>
-      <c r="G32" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="13" t="s">
+      <c r="G32" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="13" t="s">
+      <c r="K32" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="L32" s="13">
-        <v>15</v>
-      </c>
-      <c r="M32" s="15">
+      <c r="L32" s="9">
+        <v>15</v>
+      </c>
+      <c r="M32" s="11">
         <v>54000</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="11">
         <v>810000</v>
       </c>
-      <c r="O32" s="16" t="str">
+      <c r="O32" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S18</v>
       </c>
-      <c r="P32" s="17" t="str">
+      <c r="P32" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>avril</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A33" s="12">
+        <v>46151</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="13">
+        <v>775411988</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="13">
+        <v>6</v>
+      </c>
+      <c r="M33" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N33" s="14">
+        <v>117000</v>
+      </c>
+      <c r="O33" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P33" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A34" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="13">
+        <v>788217757</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" s="13">
+        <v>25</v>
+      </c>
+      <c r="M34" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N34" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O34" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P34" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A35" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" s="13">
+        <v>773914377</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L35" s="13">
+        <v>25</v>
+      </c>
+      <c r="M35" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N35" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O35" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P35" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A36" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="13">
+        <v>779598695</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L36" s="13">
+        <v>5</v>
+      </c>
+      <c r="M36" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N36" s="14">
+        <v>270000</v>
+      </c>
+      <c r="O36" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P36" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A37" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" s="13">
+        <v>775740574</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L37" s="13">
+        <v>25</v>
+      </c>
+      <c r="M37" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N37" s="14">
+        <v>700000</v>
+      </c>
+      <c r="O37" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P37" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A38" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" s="13">
+        <v>775586819</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L38" s="13">
+        <v>25</v>
+      </c>
+      <c r="M38" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N38" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O38" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P38" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A39" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" s="13">
+        <v>775586604</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L39" s="13">
+        <v>50</v>
+      </c>
+      <c r="M39" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N39" s="14">
+        <v>450000</v>
+      </c>
+      <c r="O39" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P39" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A40" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40" s="13">
+        <v>778356666</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L40" s="13">
+        <v>100</v>
+      </c>
+      <c r="M40" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N40" s="14">
+        <v>900000</v>
+      </c>
+      <c r="O40" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P40" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A41" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="13">
+        <v>770706706</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L41" s="13">
+        <v>5</v>
+      </c>
+      <c r="M41" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N41" s="14">
+        <v>270000</v>
+      </c>
+      <c r="O41" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P41" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A42" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42" s="13">
+        <v>766174009</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L42" s="13">
+        <v>10</v>
+      </c>
+      <c r="M42" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N42" s="14">
+        <v>540000</v>
+      </c>
+      <c r="O42" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P42" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A43" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="13">
+        <v>762932950</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L43" s="13">
+        <v>15</v>
+      </c>
+      <c r="M43" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N43" s="14">
+        <v>135000</v>
+      </c>
+      <c r="O43" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P43" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A44" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="13">
+        <v>774004048</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L44" s="13">
+        <v>50</v>
+      </c>
+      <c r="M44" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N44" s="14">
+        <v>2700000</v>
+      </c>
+      <c r="O44" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P44" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A45" s="12">
+        <v>46151</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F45" s="17">
+        <v>775602981</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="13">
+        <v>25</v>
+      </c>
+      <c r="M45" s="14">
+        <v>6000</v>
+      </c>
+      <c r="N45" s="14">
+        <v>150000</v>
+      </c>
+      <c r="O45" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P45" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A46" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="17">
+        <v>781316258</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="K46" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L46" s="13">
+        <v>10</v>
+      </c>
+      <c r="M46" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N46" s="14">
+        <v>540000</v>
+      </c>
+      <c r="O46" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P46" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A47" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="17">
+        <v>774415358</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L47" s="13">
+        <v>25</v>
+      </c>
+      <c r="M47" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N47" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O47" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P47" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A48" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="17">
+        <v>784426640</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K48" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="13">
+        <v>15</v>
+      </c>
+      <c r="M48" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N48" s="14">
+        <v>292500</v>
+      </c>
+      <c r="O48" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P48" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A49" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="17">
+        <v>773122246</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K49" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="13">
+        <v>25</v>
+      </c>
+      <c r="M49" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N49" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O49" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P49" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A50" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="17">
+        <v>775544532</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="13">
+        <v>100</v>
+      </c>
+      <c r="M50" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N50" s="14">
+        <v>2600000</v>
+      </c>
+      <c r="O50" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P50" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A51" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="17">
+        <v>772131614</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="13">
+        <v>10</v>
+      </c>
+      <c r="M51" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N51" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O51" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P51" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A52" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="17">
+        <v>776327767</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L52" s="13">
+        <v>20</v>
+      </c>
+      <c r="M52" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N52" s="14">
+        <v>180000</v>
+      </c>
+      <c r="O52" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P52" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A53" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53" s="17">
+        <v>776327767</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L53" s="13">
+        <v>10</v>
+      </c>
+      <c r="M53" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N53" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O53" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P53" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A54" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="17">
+        <v>773066194</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L54" s="13">
+        <v>25</v>
+      </c>
+      <c r="M54" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N54" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O54" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P54" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A55" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F55" s="17">
+        <v>781091498</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L55" s="13">
+        <v>20</v>
+      </c>
+      <c r="M55" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N55" s="14">
+        <v>1080000</v>
+      </c>
+      <c r="O55" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P55" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A56" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56" s="17">
+        <v>783682649</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K56" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L56" s="13">
+        <v>15</v>
+      </c>
+      <c r="M56" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N56" s="14">
+        <v>135000</v>
+      </c>
+      <c r="O56" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P56" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A57" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="17">
+        <v>783682649</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" s="13">
+        <v>10</v>
+      </c>
+      <c r="M57" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N57" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O57" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P57" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A58" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="17">
+        <v>772038792</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L58" s="13">
+        <v>10</v>
+      </c>
+      <c r="M58" s="14">
+        <v>54000</v>
+      </c>
+      <c r="N58" s="14">
+        <v>540000</v>
+      </c>
+      <c r="O58" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P58" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A59" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F59" s="17">
+        <v>788217757</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L59" s="13">
+        <v>20</v>
+      </c>
+      <c r="M59" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N59" s="14">
+        <v>180000</v>
+      </c>
+      <c r="O59" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P59" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A60" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F60" s="17">
+        <v>772773318</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K60" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L60" s="13">
+        <v>5</v>
+      </c>
+      <c r="M60" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N60" s="14">
+        <v>45000</v>
+      </c>
+      <c r="O60" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P60" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404D8395-2B83-4982-87F9-9FA612822B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D39871-5C73-4D15-B2D0-E97C4F1F3DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -291,12 +291,6 @@
   </si>
   <si>
     <t>Abdou sow</t>
-  </si>
-  <si>
-    <t>Zac Mbao</t>
-  </si>
-  <si>
-    <t>Ibrahima Tahirou</t>
   </si>
   <si>
     <t>Grand Dakar</t>
@@ -478,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -509,22 +503,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -831,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P60" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P60" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P59" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P59" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1145,7 +1123,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -2777,13 +2755,13 @@
     </row>
     <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A32" s="8">
-        <v>46142</v>
+        <v>46151</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>86</v>
@@ -2791,11 +2769,11 @@
       <c r="E32" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="10">
-        <v>784785900</v>
+      <c r="F32" s="9">
+        <v>775411988</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>13</v>
@@ -2804,1481 +2782,1429 @@
         <v>16</v>
       </c>
       <c r="J32" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="9">
+        <v>6</v>
+      </c>
+      <c r="M32" s="11">
+        <v>19500</v>
+      </c>
+      <c r="N32" s="11">
+        <v>117000</v>
+      </c>
+      <c r="O32" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P32" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A33" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="9">
+        <v>788217757</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L33" s="9">
+        <v>25</v>
+      </c>
+      <c r="M33" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N33" s="11">
+        <v>650000</v>
+      </c>
+      <c r="O33" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P33" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A34" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" s="9">
+        <v>773914377</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L34" s="9">
+        <v>25</v>
+      </c>
+      <c r="M34" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N34" s="11">
+        <v>650000</v>
+      </c>
+      <c r="O34" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P34" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A35" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" s="9">
+        <v>779598695</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" s="9">
+        <v>5</v>
+      </c>
+      <c r="M35" s="11">
+        <v>54000</v>
+      </c>
+      <c r="N35" s="11">
+        <v>270000</v>
+      </c>
+      <c r="O35" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P35" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A36" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="9">
+        <v>775740574</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L36" s="9">
+        <v>25</v>
+      </c>
+      <c r="M36" s="11">
+        <v>28000</v>
+      </c>
+      <c r="N36" s="11">
+        <v>700000</v>
+      </c>
+      <c r="O36" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P36" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A37" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F37" s="9">
+        <v>775586819</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="K37" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L37" s="9">
+        <v>25</v>
+      </c>
+      <c r="M37" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N37" s="11">
+        <v>650000</v>
+      </c>
+      <c r="O37" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P37" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A38" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F38" s="9">
+        <v>775586604</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L38" s="9">
+        <v>50</v>
+      </c>
+      <c r="M38" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N38" s="11">
+        <v>450000</v>
+      </c>
+      <c r="O38" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P38" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A39" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" s="9">
+        <v>778356666</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L39" s="9">
+        <v>100</v>
+      </c>
+      <c r="M39" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N39" s="11">
+        <v>900000</v>
+      </c>
+      <c r="O39" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P39" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A40" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40" s="9">
+        <v>770706706</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="L32" s="9">
-        <v>15</v>
-      </c>
-      <c r="M32" s="11">
+      <c r="L40" s="9">
+        <v>5</v>
+      </c>
+      <c r="M40" s="11">
         <v>54000</v>
       </c>
-      <c r="N32" s="11">
-        <v>810000</v>
-      </c>
-      <c r="O32" s="7" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S18</v>
-      </c>
-      <c r="P32" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>avril</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A33" s="12">
+      <c r="N40" s="11">
+        <v>270000</v>
+      </c>
+      <c r="O40" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P40" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A41" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F41" s="9">
+        <v>766174009</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L41" s="9">
+        <v>10</v>
+      </c>
+      <c r="M41" s="11">
+        <v>54000</v>
+      </c>
+      <c r="N41" s="11">
+        <v>540000</v>
+      </c>
+      <c r="O41" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P41" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A42" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F42" s="9">
+        <v>762932950</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L42" s="9">
+        <v>15</v>
+      </c>
+      <c r="M42" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N42" s="11">
+        <v>135000</v>
+      </c>
+      <c r="O42" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P42" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A43" s="8">
+        <v>46148</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="9">
+        <v>774004048</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L43" s="9">
+        <v>50</v>
+      </c>
+      <c r="M43" s="11">
+        <v>54000</v>
+      </c>
+      <c r="N43" s="11">
+        <v>2700000</v>
+      </c>
+      <c r="O43" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P43" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A44" s="8">
         <v>46151</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B44" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C44" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D44" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="10">
+        <v>775602981</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="9">
+        <v>25</v>
+      </c>
+      <c r="M44" s="11">
+        <v>6000</v>
+      </c>
+      <c r="N44" s="11">
+        <v>150000</v>
+      </c>
+      <c r="O44" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P44" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A45" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F45" s="10">
+        <v>781316258</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L45" s="9">
+        <v>10</v>
+      </c>
+      <c r="M45" s="11">
+        <v>54000</v>
+      </c>
+      <c r="N45" s="11">
+        <v>540000</v>
+      </c>
+      <c r="O45" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P45" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A46" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="10">
+        <v>774415358</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="9">
+        <v>25</v>
+      </c>
+      <c r="M46" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N46" s="11">
+        <v>650000</v>
+      </c>
+      <c r="O46" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P46" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A47" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F47" s="10">
+        <v>784426640</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L47" s="9">
+        <v>15</v>
+      </c>
+      <c r="M47" s="11">
+        <v>19500</v>
+      </c>
+      <c r="N47" s="11">
+        <v>292500</v>
+      </c>
+      <c r="O47" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P47" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A48" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="10">
+        <v>773122246</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" s="9">
+        <v>25</v>
+      </c>
+      <c r="M48" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N48" s="11">
+        <v>650000</v>
+      </c>
+      <c r="O48" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P48" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A49" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="10">
+        <v>775544532</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="9">
+        <v>100</v>
+      </c>
+      <c r="M49" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N49" s="11">
+        <v>2600000</v>
+      </c>
+      <c r="O49" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P49" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A50" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F50" s="10">
+        <v>772131614</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L50" s="9">
+        <v>10</v>
+      </c>
+      <c r="M50" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N50" s="11">
+        <v>90000</v>
+      </c>
+      <c r="O50" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P50" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A51" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="10">
+        <v>776327767</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="9">
+        <v>20</v>
+      </c>
+      <c r="M51" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N51" s="11">
+        <v>180000</v>
+      </c>
+      <c r="O51" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P51" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A52" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" s="10">
+        <v>776327767</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" s="9">
+        <v>10</v>
+      </c>
+      <c r="M52" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N52" s="11">
+        <v>90000</v>
+      </c>
+      <c r="O52" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P52" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A53" s="8">
+        <v>46150</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="10">
+        <v>773066194</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" s="9">
+        <v>25</v>
+      </c>
+      <c r="M53" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N53" s="11">
+        <v>650000</v>
+      </c>
+      <c r="O53" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P53" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A54" s="8">
+        <v>46149</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" s="10">
+        <v>781091498</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L54" s="9">
+        <v>20</v>
+      </c>
+      <c r="M54" s="11">
+        <v>54000</v>
+      </c>
+      <c r="N54" s="11">
+        <v>1080000</v>
+      </c>
+      <c r="O54" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P54" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A55" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="10">
+        <v>783682649</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L55" s="9">
+        <v>15</v>
+      </c>
+      <c r="M55" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N55" s="11">
+        <v>135000</v>
+      </c>
+      <c r="O55" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P55" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A56" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F56" s="10">
+        <v>783682649</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L56" s="9">
+        <v>10</v>
+      </c>
+      <c r="M56" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N56" s="11">
+        <v>90000</v>
+      </c>
+      <c r="O56" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P56" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A57" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F57" s="10">
+        <v>772038792</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L57" s="9">
+        <v>10</v>
+      </c>
+      <c r="M57" s="11">
+        <v>54000</v>
+      </c>
+      <c r="N57" s="11">
+        <v>540000</v>
+      </c>
+      <c r="O57" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S19</v>
+      </c>
+      <c r="P57" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A58" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F33" s="13">
-        <v>775411988</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L33" s="13">
-        <v>6</v>
-      </c>
-      <c r="M33" s="14">
-        <v>19500</v>
-      </c>
-      <c r="N33" s="14">
-        <v>117000</v>
-      </c>
-      <c r="O33" s="15" t="str">
+      <c r="F58" s="10">
+        <v>788217757</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L58" s="9">
+        <v>20</v>
+      </c>
+      <c r="M58" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N58" s="11">
+        <v>180000</v>
+      </c>
+      <c r="O58" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S19</v>
       </c>
-      <c r="P33" s="16" t="str">
+      <c r="P58" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A34" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B34" s="13" t="s">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A59" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B59" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C59" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D59" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34" s="13">
-        <v>788217757</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L34" s="13">
-        <v>25</v>
-      </c>
-      <c r="M34" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N34" s="14">
-        <v>650000</v>
-      </c>
-      <c r="O34" s="15" t="str">
+      <c r="E59" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" s="10">
+        <v>772773318</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L59" s="9">
+        <v>5</v>
+      </c>
+      <c r="M59" s="11">
+        <v>9000</v>
+      </c>
+      <c r="N59" s="11">
+        <v>45000</v>
+      </c>
+      <c r="O59" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S19</v>
       </c>
-      <c r="P34" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A35" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F35" s="13">
-        <v>773914377</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L35" s="13">
-        <v>25</v>
-      </c>
-      <c r="M35" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N35" s="14">
-        <v>650000</v>
-      </c>
-      <c r="O35" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P35" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A36" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="13">
-        <v>779598695</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L36" s="13">
-        <v>5</v>
-      </c>
-      <c r="M36" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N36" s="14">
-        <v>270000</v>
-      </c>
-      <c r="O36" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P36" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A37" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F37" s="13">
-        <v>775740574</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" s="13">
-        <v>25</v>
-      </c>
-      <c r="M37" s="14">
-        <v>28000</v>
-      </c>
-      <c r="N37" s="14">
-        <v>700000</v>
-      </c>
-      <c r="O37" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P37" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A38" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F38" s="13">
-        <v>775586819</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L38" s="13">
-        <v>25</v>
-      </c>
-      <c r="M38" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N38" s="14">
-        <v>650000</v>
-      </c>
-      <c r="O38" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P38" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A39" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F39" s="13">
-        <v>775586604</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L39" s="13">
-        <v>50</v>
-      </c>
-      <c r="M39" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N39" s="14">
-        <v>450000</v>
-      </c>
-      <c r="O39" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P39" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A40" s="12">
-        <v>46148</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F40" s="13">
-        <v>778356666</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L40" s="13">
-        <v>100</v>
-      </c>
-      <c r="M40" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N40" s="14">
-        <v>900000</v>
-      </c>
-      <c r="O40" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P40" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A41" s="12">
-        <v>46148</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F41" s="13">
-        <v>770706706</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L41" s="13">
-        <v>5</v>
-      </c>
-      <c r="M41" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N41" s="14">
-        <v>270000</v>
-      </c>
-      <c r="O41" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P41" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A42" s="12">
-        <v>46148</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F42" s="13">
-        <v>766174009</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="K42" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L42" s="13">
-        <v>10</v>
-      </c>
-      <c r="M42" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N42" s="14">
-        <v>540000</v>
-      </c>
-      <c r="O42" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P42" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A43" s="12">
-        <v>46148</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F43" s="13">
-        <v>762932950</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L43" s="13">
-        <v>15</v>
-      </c>
-      <c r="M43" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N43" s="14">
-        <v>135000</v>
-      </c>
-      <c r="O43" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P43" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A44" s="12">
-        <v>46148</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F44" s="13">
-        <v>774004048</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="K44" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L44" s="13">
-        <v>50</v>
-      </c>
-      <c r="M44" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N44" s="14">
-        <v>2700000</v>
-      </c>
-      <c r="O44" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P44" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A45" s="12">
-        <v>46151</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F45" s="17">
-        <v>775602981</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K45" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L45" s="13">
-        <v>25</v>
-      </c>
-      <c r="M45" s="14">
-        <v>6000</v>
-      </c>
-      <c r="N45" s="14">
-        <v>150000</v>
-      </c>
-      <c r="O45" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P45" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A46" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F46" s="17">
-        <v>781316258</v>
-      </c>
-      <c r="G46" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="K46" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L46" s="13">
-        <v>10</v>
-      </c>
-      <c r="M46" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N46" s="14">
-        <v>540000</v>
-      </c>
-      <c r="O46" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P46" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A47" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="F47" s="17">
-        <v>774415358</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L47" s="13">
-        <v>25</v>
-      </c>
-      <c r="M47" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N47" s="14">
-        <v>650000</v>
-      </c>
-      <c r="O47" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P47" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A48" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F48" s="17">
-        <v>784426640</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K48" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="L48" s="13">
-        <v>15</v>
-      </c>
-      <c r="M48" s="14">
-        <v>19500</v>
-      </c>
-      <c r="N48" s="14">
-        <v>292500</v>
-      </c>
-      <c r="O48" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P48" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A49" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="17">
-        <v>773122246</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K49" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L49" s="13">
-        <v>25</v>
-      </c>
-      <c r="M49" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N49" s="14">
-        <v>650000</v>
-      </c>
-      <c r="O49" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P49" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A50" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F50" s="17">
-        <v>775544532</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K50" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L50" s="13">
-        <v>100</v>
-      </c>
-      <c r="M50" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N50" s="14">
-        <v>2600000</v>
-      </c>
-      <c r="O50" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P50" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A51" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="F51" s="17">
-        <v>772131614</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="K51" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L51" s="13">
-        <v>10</v>
-      </c>
-      <c r="M51" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N51" s="14">
-        <v>90000</v>
-      </c>
-      <c r="O51" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P51" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A52" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F52" s="17">
-        <v>776327767</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L52" s="13">
-        <v>20</v>
-      </c>
-      <c r="M52" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N52" s="14">
-        <v>180000</v>
-      </c>
-      <c r="O52" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P52" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A53" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F53" s="17">
-        <v>776327767</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L53" s="13">
-        <v>10</v>
-      </c>
-      <c r="M53" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N53" s="14">
-        <v>90000</v>
-      </c>
-      <c r="O53" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P53" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A54" s="12">
-        <v>46150</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F54" s="17">
-        <v>773066194</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J54" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L54" s="13">
-        <v>25</v>
-      </c>
-      <c r="M54" s="14">
-        <v>26000</v>
-      </c>
-      <c r="N54" s="14">
-        <v>650000</v>
-      </c>
-      <c r="O54" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P54" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A55" s="12">
-        <v>46149</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E55" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="F55" s="17">
-        <v>781091498</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="K55" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L55" s="13">
-        <v>20</v>
-      </c>
-      <c r="M55" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N55" s="14">
-        <v>1080000</v>
-      </c>
-      <c r="O55" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P55" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A56" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F56" s="17">
-        <v>783682649</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L56" s="13">
-        <v>15</v>
-      </c>
-      <c r="M56" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N56" s="14">
-        <v>135000</v>
-      </c>
-      <c r="O56" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P56" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A57" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F57" s="17">
-        <v>783682649</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K57" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L57" s="13">
-        <v>10</v>
-      </c>
-      <c r="M57" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N57" s="14">
-        <v>90000</v>
-      </c>
-      <c r="O57" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P57" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A58" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="F58" s="17">
-        <v>772038792</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="L58" s="13">
-        <v>10</v>
-      </c>
-      <c r="M58" s="14">
-        <v>54000</v>
-      </c>
-      <c r="N58" s="14">
-        <v>540000</v>
-      </c>
-      <c r="O58" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P58" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A59" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F59" s="17">
-        <v>788217757</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K59" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L59" s="13">
-        <v>20</v>
-      </c>
-      <c r="M59" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N59" s="14">
-        <v>180000</v>
-      </c>
-      <c r="O59" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P59" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A60" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F60" s="17">
-        <v>772773318</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K60" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="L60" s="13">
-        <v>5</v>
-      </c>
-      <c r="M60" s="14">
-        <v>9000</v>
-      </c>
-      <c r="N60" s="14">
-        <v>45000</v>
-      </c>
-      <c r="O60" s="15" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S19</v>
-      </c>
-      <c r="P60" s="16" t="str">
+      <c r="P59" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D39871-5C73-4D15-B2D0-E97C4F1F3DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B93793-3C0D-40E7-84CB-547EEF2E2EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -405,6 +405,84 @@
   </si>
   <si>
     <t>Alimentation</t>
+  </si>
+  <si>
+    <t>RAS</t>
+  </si>
+  <si>
+    <t>Kayar</t>
+  </si>
+  <si>
+    <t>Babacar</t>
+  </si>
+  <si>
+    <t>Ras</t>
+  </si>
+  <si>
+    <t>Mohamed Ndiaye</t>
+  </si>
+  <si>
+    <t>Gueye et frère</t>
+  </si>
+  <si>
+    <t>Bayakh</t>
+  </si>
+  <si>
+    <t>Bathie</t>
+  </si>
+  <si>
+    <t>TAPAHA GAYE</t>
+  </si>
+  <si>
+    <t>NAFAR BOUTIQUE</t>
+  </si>
+  <si>
+    <t>MOUHAMED DAYEL</t>
+  </si>
+  <si>
+    <t>BALDE</t>
+  </si>
+  <si>
+    <t>Ben Tally</t>
+  </si>
+  <si>
+    <t>El Hadji</t>
+  </si>
+  <si>
+    <t>Lye</t>
+  </si>
+  <si>
+    <t>Stapro.com SARL n1</t>
+  </si>
+  <si>
+    <t>Il apprécie la promotion</t>
+  </si>
+  <si>
+    <t>Sa reste le lait 25kg</t>
+  </si>
+  <si>
+    <t>S.K.L</t>
+  </si>
+  <si>
+    <t>Alpha ba</t>
+  </si>
+  <si>
+    <t>Merci beaucoup</t>
+  </si>
+  <si>
+    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+  </si>
+  <si>
+    <t>Sicap Mbao</t>
+  </si>
+  <si>
+    <t>Madina</t>
+  </si>
+  <si>
+    <t>DJIBRIL laye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livré hier soir </t>
   </si>
 </sst>
 </file>
@@ -472,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -505,6 +583,22 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -809,8 +903,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P59" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P59" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P82" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P82" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1123,7 +1217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -4209,6 +4303,1194 @@
         <v>mai</v>
       </c>
     </row>
+    <row r="60" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A60" s="12">
+        <v>46158</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F60" s="14">
+        <v>781316258</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="K60" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" s="13">
+        <v>60</v>
+      </c>
+      <c r="M60" s="15">
+        <v>9000</v>
+      </c>
+      <c r="N60" s="15">
+        <v>540000</v>
+      </c>
+      <c r="O60" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P60" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A61" s="12">
+        <v>46158</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" s="14">
+        <v>781316258</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="K61" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L61" s="13">
+        <v>10</v>
+      </c>
+      <c r="M61" s="15">
+        <v>9000</v>
+      </c>
+      <c r="N61" s="15">
+        <v>90000</v>
+      </c>
+      <c r="O61" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P61" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A62" s="12">
+        <v>46157</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F62" s="14">
+        <v>776149093</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="13">
+        <v>25</v>
+      </c>
+      <c r="M62" s="15">
+        <v>6000</v>
+      </c>
+      <c r="N62" s="15">
+        <v>150000</v>
+      </c>
+      <c r="O62" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P62" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A63" s="12">
+        <v>46157</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="14">
+        <v>773012416</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L63" s="13">
+        <v>25</v>
+      </c>
+      <c r="M63" s="15">
+        <v>12000</v>
+      </c>
+      <c r="N63" s="15">
+        <v>300000</v>
+      </c>
+      <c r="O63" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P63" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A64" s="12">
+        <v>46157</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="14">
+        <v>773178746</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I64" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L64" s="13">
+        <v>27</v>
+      </c>
+      <c r="M64" s="15">
+        <v>9000</v>
+      </c>
+      <c r="N64" s="15">
+        <v>243000</v>
+      </c>
+      <c r="O64" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P64" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A65" s="12">
+        <v>46157</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C65" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="14">
+        <v>773701528</v>
+      </c>
+      <c r="G65" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K65" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L65" s="13">
+        <v>6</v>
+      </c>
+      <c r="M65" s="15">
+        <v>12000</v>
+      </c>
+      <c r="N65" s="15">
+        <v>72000</v>
+      </c>
+      <c r="O65" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P65" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A66" s="12">
+        <v>46157</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F66" s="14">
+        <v>765956010</v>
+      </c>
+      <c r="G66" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K66" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L66" s="13">
+        <v>10</v>
+      </c>
+      <c r="M66" s="15">
+        <v>9000</v>
+      </c>
+      <c r="N66" s="15">
+        <v>90000</v>
+      </c>
+      <c r="O66" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P66" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A67" s="12">
+        <v>46156</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F67" s="14">
+        <v>781282357</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L67" s="13">
+        <v>50</v>
+      </c>
+      <c r="M67" s="15">
+        <v>26000</v>
+      </c>
+      <c r="N67" s="15">
+        <v>1300000</v>
+      </c>
+      <c r="O67" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P67" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A68" s="12">
+        <v>46156</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="F68" s="14">
+        <v>762974040</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L68" s="13">
+        <v>25</v>
+      </c>
+      <c r="M68" s="15">
+        <v>26000</v>
+      </c>
+      <c r="N68" s="15">
+        <v>650000</v>
+      </c>
+      <c r="O68" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P68" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A69" s="12">
+        <v>46156</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F69" s="14">
+        <v>775411094</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L69" s="13">
+        <v>100</v>
+      </c>
+      <c r="M69" s="15">
+        <v>9000</v>
+      </c>
+      <c r="N69" s="15">
+        <v>900000</v>
+      </c>
+      <c r="O69" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P69" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A70" s="12">
+        <v>46156</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F70" s="14">
+        <v>775264622</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L70" s="13">
+        <v>25</v>
+      </c>
+      <c r="M70" s="15">
+        <v>26000</v>
+      </c>
+      <c r="N70" s="15">
+        <v>650000</v>
+      </c>
+      <c r="O70" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P70" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A71" s="12">
+        <v>46155</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F71" s="14">
+        <v>775987400</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K71" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L71" s="13">
+        <v>2</v>
+      </c>
+      <c r="M71" s="15">
+        <v>9000</v>
+      </c>
+      <c r="N71" s="15">
+        <v>18000</v>
+      </c>
+      <c r="O71" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P71" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A72" s="12">
+        <v>46155</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F72" s="14">
+        <v>775987400</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L72" s="13">
+        <v>4</v>
+      </c>
+      <c r="M72" s="15">
+        <v>19500</v>
+      </c>
+      <c r="N72" s="15">
+        <v>78000</v>
+      </c>
+      <c r="O72" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P72" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A73" s="12">
+        <v>46155</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F73" s="14">
+        <v>775426848</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L73" s="13">
+        <v>8</v>
+      </c>
+      <c r="M73" s="15">
+        <v>19500</v>
+      </c>
+      <c r="N73" s="15">
+        <v>156000</v>
+      </c>
+      <c r="O73" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P73" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A74" s="12">
+        <v>46155</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F74" s="14">
+        <v>770712599</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K74" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L74" s="13">
+        <v>100</v>
+      </c>
+      <c r="M74" s="15">
+        <v>26000</v>
+      </c>
+      <c r="N74" s="15">
+        <v>2600000</v>
+      </c>
+      <c r="O74" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P74" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A75" s="12">
+        <v>46154</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75" s="14">
+        <v>776634479</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L75" s="13">
+        <v>3</v>
+      </c>
+      <c r="M75" s="15">
+        <v>19500</v>
+      </c>
+      <c r="N75" s="15">
+        <v>58500</v>
+      </c>
+      <c r="O75" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P75" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A76" s="12">
+        <v>46154</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F76" s="14">
+        <v>778195274</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K76" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L76" s="13">
+        <v>100</v>
+      </c>
+      <c r="M76" s="15">
+        <v>26000</v>
+      </c>
+      <c r="N76" s="15">
+        <v>2600000</v>
+      </c>
+      <c r="O76" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P76" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A77" s="12">
+        <v>46154</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F77" s="14">
+        <v>773564759</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="K77" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L77" s="13">
+        <v>10</v>
+      </c>
+      <c r="M77" s="15">
+        <v>19500</v>
+      </c>
+      <c r="N77" s="15">
+        <v>195000</v>
+      </c>
+      <c r="O77" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P77" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A78" s="12">
+        <v>46154</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" s="14">
+        <v>776634479</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="L78" s="13">
+        <v>1</v>
+      </c>
+      <c r="M78" s="15">
+        <v>15000</v>
+      </c>
+      <c r="N78" s="15">
+        <v>15000</v>
+      </c>
+      <c r="O78" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P78" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A79" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F79" s="14">
+        <v>785459209</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K79" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L79" s="13">
+        <v>25</v>
+      </c>
+      <c r="M79" s="15">
+        <v>26000</v>
+      </c>
+      <c r="N79" s="15">
+        <v>650000</v>
+      </c>
+      <c r="O79" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P79" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A80" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F80" s="14">
+        <v>776428218</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L80" s="13">
+        <v>778</v>
+      </c>
+      <c r="M80" s="15">
+        <v>7500</v>
+      </c>
+      <c r="N80" s="15">
+        <v>5835000</v>
+      </c>
+      <c r="O80" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P80" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A81" s="12">
+        <v>46153</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="14">
+        <v>776428218</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="L81" s="13">
+        <v>25</v>
+      </c>
+      <c r="M81" s="15">
+        <v>8750</v>
+      </c>
+      <c r="N81" s="15">
+        <v>218750</v>
+      </c>
+      <c r="O81" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P81" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A82" s="12">
+        <v>46158</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F82" s="14">
+        <v>778657940</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="15"/>
+      <c r="N82" s="15"/>
+      <c r="O82" s="16" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S20</v>
+      </c>
+      <c r="P82" s="17" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B93793-3C0D-40E7-84CB-547EEF2E2EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522E29B6-FCCD-4E9F-BF98-8C76FFF81394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="195">
   <si>
     <t>Date</t>
   </si>
@@ -483,6 +483,141 @@
   </si>
   <si>
     <t xml:space="preserve">Livré hier soir </t>
+  </si>
+  <si>
+    <t>Nd</t>
+  </si>
+  <si>
+    <t>Khadim Lo</t>
+  </si>
+  <si>
+    <t>Il a commencé à vendre le café royal raison pour laquelle il a diminué sa commande</t>
+  </si>
+  <si>
+    <t>Asse</t>
+  </si>
+  <si>
+    <t>Abdourahmane</t>
+  </si>
+  <si>
+    <t>Sakina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client satisfait </t>
+  </si>
+  <si>
+    <t>Zac Mbao</t>
+  </si>
+  <si>
+    <t>Ibrahima Tahirou</t>
+  </si>
+  <si>
+    <t>Keur Mbaye Fall</t>
+  </si>
+  <si>
+    <t>Pape</t>
+  </si>
+  <si>
+    <t>Abdou</t>
+  </si>
+  <si>
+    <t>Keur Ndiaye LO</t>
+  </si>
+  <si>
+    <t>Souleymane Diallo</t>
+  </si>
+  <si>
+    <t>Moustapha DIOUF</t>
+  </si>
+  <si>
+    <t>Tidiane Diallo</t>
+  </si>
+  <si>
+    <t>Ndiol NDIAYE</t>
+  </si>
+  <si>
+    <t>Grand Boutique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour essayer </t>
+  </si>
+  <si>
+    <t>Médina</t>
+  </si>
+  <si>
+    <t>Diop et Frères</t>
+  </si>
+  <si>
+    <t>Café Altimo pot 100g x 24 pcs</t>
+  </si>
+  <si>
+    <t>Ouakam</t>
+  </si>
+  <si>
+    <t>Ibrahima Sori Diallo</t>
+  </si>
+  <si>
+    <t>Niang et frère</t>
+  </si>
+  <si>
+    <t>Bala</t>
+  </si>
+  <si>
+    <t>Moustapha Mbaye</t>
+  </si>
+  <si>
+    <t>Grand Yoff</t>
+  </si>
+  <si>
+    <t>Dame DIOP</t>
+  </si>
+  <si>
+    <t>Alune Ndiaye</t>
+  </si>
+  <si>
+    <t>Mouhamed KANTE</t>
+  </si>
+  <si>
+    <t>Zone de captage</t>
+  </si>
+  <si>
+    <t>Ousmane Dramé</t>
+  </si>
+  <si>
+    <t>Raa</t>
+  </si>
+  <si>
+    <t>Kolda</t>
+  </si>
+  <si>
+    <t>Mansour</t>
+  </si>
+  <si>
+    <t>Moustapha  seye</t>
+  </si>
+  <si>
+    <t>Mor seye</t>
+  </si>
+  <si>
+    <t>Mouhamed Diallo</t>
+  </si>
+  <si>
+    <t>Il veut essayer le produit mais il demande de revoir le prix il dit que c'est cher</t>
+  </si>
+  <si>
+    <t>KamLac Lait concentré sucré 24x1kg</t>
+  </si>
+  <si>
+    <t>Abdou Diop</t>
+  </si>
+  <si>
+    <t>Seye et Frère</t>
+  </si>
+  <si>
+    <t>Il dit que le produit est cher c'est pourquoi il ne peut pas prendre en grande quantité</t>
+  </si>
+  <si>
+    <t>Meadow Cup sac 25kg</t>
   </si>
 </sst>
 </file>
@@ -525,7 +660,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -546,11 +681,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -589,9 +759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -599,6 +766,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,8 +1092,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P82" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P82" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P124" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P124" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1217,7 +1406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -4304,1189 +4493,3373 @@
       </c>
     </row>
     <row r="60" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A60" s="12">
+      <c r="A60" s="8">
         <v>46158</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F60" s="14">
+      <c r="F60" s="10">
         <v>781316258</v>
       </c>
-      <c r="G60" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="13" t="s">
+      <c r="G60" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="K60" s="13" t="s">
+      <c r="K60" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L60" s="13">
+      <c r="L60" s="9">
         <v>60</v>
       </c>
-      <c r="M60" s="15">
+      <c r="M60" s="11">
         <v>9000</v>
       </c>
-      <c r="N60" s="15">
+      <c r="N60" s="11">
         <v>540000</v>
       </c>
-      <c r="O60" s="16" t="str">
+      <c r="O60" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P60" s="17" t="str">
+      <c r="P60" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A61" s="12">
+      <c r="A61" s="8">
         <v>46158</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E61" s="13" t="s">
+      <c r="E61" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F61" s="14">
+      <c r="F61" s="10">
         <v>781316258</v>
       </c>
-      <c r="G61" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I61" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="13" t="s">
+      <c r="G61" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="K61" s="13" t="s">
+      <c r="K61" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L61" s="13">
+      <c r="L61" s="9">
         <v>10</v>
       </c>
-      <c r="M61" s="15">
+      <c r="M61" s="11">
         <v>9000</v>
       </c>
-      <c r="N61" s="15">
+      <c r="N61" s="11">
         <v>90000</v>
       </c>
-      <c r="O61" s="16" t="str">
+      <c r="O61" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P61" s="17" t="str">
+      <c r="P61" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A62" s="12">
+      <c r="A62" s="8">
         <v>46157</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F62" s="14">
+      <c r="F62" s="10">
         <v>776149093</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="G62" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" s="13" t="s">
+      <c r="H62" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="13" t="s">
+      <c r="K62" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L62" s="13">
+      <c r="L62" s="9">
         <v>25</v>
       </c>
-      <c r="M62" s="15">
+      <c r="M62" s="11">
         <v>6000</v>
       </c>
-      <c r="N62" s="15">
+      <c r="N62" s="11">
         <v>150000</v>
       </c>
-      <c r="O62" s="16" t="str">
+      <c r="O62" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P62" s="17" t="str">
+      <c r="P62" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A63" s="12">
+      <c r="A63" s="8">
         <v>46157</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E63" s="13" t="s">
+      <c r="E63" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="10">
         <v>773012416</v>
       </c>
-      <c r="G63" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I63" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J63" s="13" t="s">
+      <c r="G63" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="K63" s="13" t="s">
+      <c r="K63" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L63" s="13">
+      <c r="L63" s="9">
         <v>25</v>
       </c>
-      <c r="M63" s="15">
+      <c r="M63" s="11">
         <v>12000</v>
       </c>
-      <c r="N63" s="15">
+      <c r="N63" s="11">
         <v>300000</v>
       </c>
-      <c r="O63" s="16" t="str">
+      <c r="O63" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P63" s="17" t="str">
+      <c r="P63" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A64" s="12">
+      <c r="A64" s="8">
         <v>46157</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F64" s="14">
+      <c r="F64" s="10">
         <v>773178746</v>
       </c>
-      <c r="G64" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H64" s="13" t="s">
+      <c r="G64" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I64" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="13" t="s">
+      <c r="I64" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="K64" s="13" t="s">
+      <c r="K64" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L64" s="13">
+      <c r="L64" s="9">
         <v>27</v>
       </c>
-      <c r="M64" s="15">
+      <c r="M64" s="11">
         <v>9000</v>
       </c>
-      <c r="N64" s="15">
+      <c r="N64" s="11">
         <v>243000</v>
       </c>
-      <c r="O64" s="16" t="str">
+      <c r="O64" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P64" s="17" t="str">
+      <c r="P64" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A65" s="12">
+      <c r="A65" s="8">
         <v>46157</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="13" t="s">
+      <c r="E65" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F65" s="10">
         <v>773701528</v>
       </c>
-      <c r="G65" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="13" t="s">
+      <c r="G65" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="13" t="s">
+      <c r="I65" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="K65" s="13" t="s">
+      <c r="K65" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L65" s="13">
+      <c r="L65" s="9">
         <v>6</v>
       </c>
-      <c r="M65" s="15">
+      <c r="M65" s="11">
         <v>12000</v>
       </c>
-      <c r="N65" s="15">
+      <c r="N65" s="11">
         <v>72000</v>
       </c>
-      <c r="O65" s="16" t="str">
+      <c r="O65" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P65" s="17" t="str">
+      <c r="P65" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A66" s="12">
+      <c r="A66" s="8">
         <v>46157</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="E66" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F66" s="14">
+      <c r="F66" s="10">
         <v>765956010</v>
       </c>
-      <c r="G66" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" s="13" t="s">
+      <c r="G66" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I66" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" s="13" t="s">
+      <c r="I66" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="K66" s="13" t="s">
+      <c r="K66" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L66" s="13">
+      <c r="L66" s="9">
         <v>10</v>
       </c>
-      <c r="M66" s="15">
+      <c r="M66" s="11">
         <v>9000</v>
       </c>
-      <c r="N66" s="15">
+      <c r="N66" s="11">
         <v>90000</v>
       </c>
-      <c r="O66" s="16" t="str">
+      <c r="O66" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P66" s="17" t="str">
+      <c r="P66" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A67" s="12">
+      <c r="A67" s="8">
         <v>46156</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E67" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="F67" s="14">
+      <c r="F67" s="10">
         <v>781282357</v>
       </c>
-      <c r="G67" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I67" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" s="13" t="s">
+      <c r="G67" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K67" s="13" t="s">
+      <c r="K67" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L67" s="13">
+      <c r="L67" s="9">
         <v>50</v>
       </c>
-      <c r="M67" s="15">
+      <c r="M67" s="11">
         <v>26000</v>
       </c>
-      <c r="N67" s="15">
+      <c r="N67" s="11">
         <v>1300000</v>
       </c>
-      <c r="O67" s="16" t="str">
+      <c r="O67" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P67" s="17" t="str">
+      <c r="P67" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A68" s="12">
+      <c r="A68" s="8">
         <v>46156</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F68" s="14">
+      <c r="F68" s="10">
         <v>762974040</v>
       </c>
-      <c r="G68" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I68" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="13" t="s">
+      <c r="G68" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K68" s="13" t="s">
+      <c r="K68" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L68" s="13">
+      <c r="L68" s="9">
         <v>25</v>
       </c>
-      <c r="M68" s="15">
+      <c r="M68" s="11">
         <v>26000</v>
       </c>
-      <c r="N68" s="15">
+      <c r="N68" s="11">
         <v>650000</v>
       </c>
-      <c r="O68" s="16" t="str">
+      <c r="O68" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P68" s="17" t="str">
+      <c r="P68" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A69" s="12">
+      <c r="A69" s="8">
         <v>46156</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="D69" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="10">
         <v>775411094</v>
       </c>
-      <c r="G69" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="13" t="s">
+      <c r="G69" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K69" s="13" t="s">
+      <c r="K69" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L69" s="13">
+      <c r="L69" s="9">
         <v>100</v>
       </c>
-      <c r="M69" s="15">
+      <c r="M69" s="11">
         <v>9000</v>
       </c>
-      <c r="N69" s="15">
+      <c r="N69" s="11">
         <v>900000</v>
       </c>
-      <c r="O69" s="16" t="str">
+      <c r="O69" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P69" s="17" t="str">
+      <c r="P69" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A70" s="12">
+      <c r="A70" s="8">
         <v>46156</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="E70" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F70" s="14">
+      <c r="F70" s="10">
         <v>775264622</v>
       </c>
-      <c r="G70" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="13" t="s">
+      <c r="G70" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K70" s="13" t="s">
+      <c r="K70" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L70" s="13">
+      <c r="L70" s="9">
         <v>25</v>
       </c>
-      <c r="M70" s="15">
+      <c r="M70" s="11">
         <v>26000</v>
       </c>
-      <c r="N70" s="15">
+      <c r="N70" s="11">
         <v>650000</v>
       </c>
-      <c r="O70" s="16" t="str">
+      <c r="O70" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P70" s="17" t="str">
+      <c r="P70" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A71" s="12">
+      <c r="A71" s="8">
         <v>46155</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E71" s="13" t="s">
+      <c r="E71" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F71" s="14">
+      <c r="F71" s="10">
         <v>775987400</v>
       </c>
-      <c r="G71" s="13" t="s">
+      <c r="G71" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="13" t="s">
+      <c r="H71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="13" t="s">
+      <c r="K71" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L71" s="13">
+      <c r="L71" s="9">
         <v>2</v>
       </c>
-      <c r="M71" s="15">
+      <c r="M71" s="11">
         <v>9000</v>
       </c>
-      <c r="N71" s="15">
+      <c r="N71" s="11">
         <v>18000</v>
       </c>
-      <c r="O71" s="16" t="str">
+      <c r="O71" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P71" s="17" t="str">
+      <c r="P71" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A72" s="12">
+      <c r="A72" s="8">
         <v>46155</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E72" s="13" t="s">
+      <c r="E72" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F72" s="14">
+      <c r="F72" s="10">
         <v>775987400</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="G72" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H72" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I72" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="13" t="s">
+      <c r="H72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="13" t="s">
+      <c r="K72" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L72" s="13">
+      <c r="L72" s="9">
         <v>4</v>
       </c>
-      <c r="M72" s="15">
+      <c r="M72" s="11">
         <v>19500</v>
       </c>
-      <c r="N72" s="15">
+      <c r="N72" s="11">
         <v>78000</v>
       </c>
-      <c r="O72" s="16" t="str">
+      <c r="O72" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P72" s="17" t="str">
+      <c r="P72" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A73" s="12">
+      <c r="A73" s="8">
         <v>46155</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D73" s="13" t="s">
+      <c r="D73" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="E73" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="10">
         <v>775426848</v>
       </c>
-      <c r="G73" s="13" t="s">
+      <c r="G73" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H73" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="13" t="s">
+      <c r="H73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="13" t="s">
+      <c r="K73" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L73" s="13">
+      <c r="L73" s="9">
         <v>8</v>
       </c>
-      <c r="M73" s="15">
+      <c r="M73" s="11">
         <v>19500</v>
       </c>
-      <c r="N73" s="15">
+      <c r="N73" s="11">
         <v>156000</v>
       </c>
-      <c r="O73" s="16" t="str">
+      <c r="O73" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P73" s="17" t="str">
+      <c r="P73" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A74" s="12">
+      <c r="A74" s="8">
         <v>46155</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E74" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F74" s="14">
+      <c r="F74" s="10">
         <v>770712599</v>
       </c>
-      <c r="G74" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="13" t="s">
+      <c r="G74" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="K74" s="13" t="s">
+      <c r="K74" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L74" s="13">
+      <c r="L74" s="9">
         <v>100</v>
       </c>
-      <c r="M74" s="15">
+      <c r="M74" s="11">
         <v>26000</v>
       </c>
-      <c r="N74" s="15">
+      <c r="N74" s="11">
         <v>2600000</v>
       </c>
-      <c r="O74" s="16" t="str">
+      <c r="O74" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P74" s="17" t="str">
+      <c r="P74" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A75" s="12">
+      <c r="A75" s="8">
         <v>46154</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E75" s="13" t="s">
+      <c r="E75" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F75" s="14">
+      <c r="F75" s="10">
         <v>776634479</v>
       </c>
-      <c r="G75" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" s="13" t="s">
+      <c r="G75" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="K75" s="13" t="s">
+      <c r="K75" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L75" s="13">
+      <c r="L75" s="9">
         <v>3</v>
       </c>
-      <c r="M75" s="15">
+      <c r="M75" s="11">
         <v>19500</v>
       </c>
-      <c r="N75" s="15">
+      <c r="N75" s="11">
         <v>58500</v>
       </c>
-      <c r="O75" s="16" t="str">
+      <c r="O75" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P75" s="17" t="str">
+      <c r="P75" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A76" s="12">
+      <c r="A76" s="8">
         <v>46154</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F76" s="14">
+      <c r="F76" s="10">
         <v>778195274</v>
       </c>
-      <c r="G76" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" s="13" t="s">
+      <c r="G76" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K76" s="13" t="s">
+      <c r="K76" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L76" s="13">
+      <c r="L76" s="9">
         <v>100</v>
       </c>
-      <c r="M76" s="15">
+      <c r="M76" s="11">
         <v>26000</v>
       </c>
-      <c r="N76" s="15">
+      <c r="N76" s="11">
         <v>2600000</v>
       </c>
-      <c r="O76" s="16" t="str">
+      <c r="O76" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P76" s="17" t="str">
+      <c r="P76" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A77" s="12">
+      <c r="A77" s="8">
         <v>46154</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="10">
         <v>773564759</v>
       </c>
-      <c r="G77" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" s="13" t="s">
+      <c r="G77" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K77" s="13" t="s">
+      <c r="K77" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L77" s="13">
+      <c r="L77" s="9">
         <v>10</v>
       </c>
-      <c r="M77" s="15">
+      <c r="M77" s="11">
         <v>19500</v>
       </c>
-      <c r="N77" s="15">
+      <c r="N77" s="11">
         <v>195000</v>
       </c>
-      <c r="O77" s="16" t="str">
+      <c r="O77" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P77" s="17" t="str">
+      <c r="P77" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A78" s="12">
+      <c r="A78" s="8">
         <v>46154</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F78" s="14">
+      <c r="F78" s="10">
         <v>776634479</v>
       </c>
-      <c r="G78" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J78" s="13" t="s">
+      <c r="G78" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="K78" s="13" t="s">
+      <c r="K78" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="L78" s="13">
+      <c r="L78" s="9">
         <v>1</v>
       </c>
-      <c r="M78" s="15">
+      <c r="M78" s="11">
         <v>15000</v>
       </c>
-      <c r="N78" s="15">
+      <c r="N78" s="11">
         <v>15000</v>
       </c>
-      <c r="O78" s="16" t="str">
+      <c r="O78" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P78" s="17" t="str">
+      <c r="P78" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A79" s="12">
+      <c r="A79" s="8">
         <v>46153</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E79" s="13" t="s">
+      <c r="E79" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F79" s="14">
+      <c r="F79" s="10">
         <v>785459209</v>
       </c>
-      <c r="G79" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J79" s="13" t="s">
+      <c r="G79" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K79" s="13" t="s">
+      <c r="K79" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L79" s="13">
+      <c r="L79" s="9">
         <v>25</v>
       </c>
-      <c r="M79" s="15">
+      <c r="M79" s="11">
         <v>26000</v>
       </c>
-      <c r="N79" s="15">
+      <c r="N79" s="11">
         <v>650000</v>
       </c>
-      <c r="O79" s="16" t="str">
+      <c r="O79" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P79" s="17" t="str">
+      <c r="P79" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A80" s="12">
+      <c r="A80" s="8">
         <v>46153</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="E80" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="10">
         <v>776428218</v>
       </c>
-      <c r="G80" s="13" t="s">
+      <c r="G80" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H80" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I80" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" s="13" t="s">
+      <c r="H80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K80" s="13" t="s">
+      <c r="K80" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L80" s="13">
+      <c r="L80" s="9">
         <v>778</v>
       </c>
-      <c r="M80" s="15">
+      <c r="M80" s="11">
         <v>7500</v>
       </c>
-      <c r="N80" s="15">
+      <c r="N80" s="11">
         <v>5835000</v>
       </c>
-      <c r="O80" s="16" t="str">
+      <c r="O80" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P80" s="17" t="str">
+      <c r="P80" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A81" s="12">
+      <c r="A81" s="8">
         <v>46153</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E81" s="13" t="s">
+      <c r="E81" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F81" s="14">
+      <c r="F81" s="10">
         <v>776428218</v>
       </c>
-      <c r="G81" s="13" t="s">
+      <c r="G81" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H81" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I81" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" s="13" t="s">
+      <c r="H81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K81" s="13" t="s">
+      <c r="K81" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L81" s="13">
+      <c r="L81" s="9">
         <v>25</v>
       </c>
-      <c r="M81" s="15">
+      <c r="M81" s="11">
         <v>8750</v>
       </c>
-      <c r="N81" s="15">
+      <c r="N81" s="11">
         <v>218750</v>
       </c>
-      <c r="O81" s="16" t="str">
+      <c r="O81" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P81" s="17" t="str">
+      <c r="P81" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A82" s="12">
+      <c r="A82" s="8">
         <v>46158</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E82" s="13" t="s">
+      <c r="E82" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F82" s="14">
+      <c r="F82" s="10">
         <v>778657940</v>
       </c>
-      <c r="G82" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" s="13" t="s">
+      <c r="G82" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="K82" s="13"/>
-      <c r="L82" s="13"/>
-      <c r="M82" s="15"/>
-      <c r="N82" s="15"/>
-      <c r="O82" s="16" t="str">
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+      <c r="M82" s="11"/>
+      <c r="N82" s="11"/>
+      <c r="O82" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S20</v>
       </c>
-      <c r="P82" s="17" t="str">
+      <c r="P82" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A83" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F83" s="13">
+        <v>779235028</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L83" s="13">
+        <v>33</v>
+      </c>
+      <c r="M83" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N83" s="14">
+        <v>858000</v>
+      </c>
+      <c r="O83" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P83" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A84" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F84" s="13">
+        <v>770217868</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L84" s="13">
+        <v>25</v>
+      </c>
+      <c r="M84" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N84" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O84" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P84" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A85" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F85" s="13">
+        <v>774289051</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="K85" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L85" s="13">
+        <v>25</v>
+      </c>
+      <c r="M85" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N85" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O85" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P85" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A86" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F86" s="13">
+        <v>771701320</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K86" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L86" s="13">
+        <v>25</v>
+      </c>
+      <c r="M86" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N86" s="14">
+        <v>225000</v>
+      </c>
+      <c r="O86" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P86" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A87" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F87" s="13">
+        <v>771701320</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L87" s="13">
+        <v>25</v>
+      </c>
+      <c r="M87" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N87" s="14">
+        <v>225000</v>
+      </c>
+      <c r="O87" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P87" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A88" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F88" s="13">
+        <v>771619220</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L88" s="13">
+        <v>51</v>
+      </c>
+      <c r="M88" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N88" s="14">
+        <v>1326000</v>
+      </c>
+      <c r="O88" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P88" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A89" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="F89" s="13">
+        <v>784785900</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L89" s="13">
+        <v>100</v>
+      </c>
+      <c r="M89" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N89" s="14">
+        <v>2600000</v>
+      </c>
+      <c r="O89" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P89" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A90" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F90" s="13">
+        <v>779110400</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L90" s="13">
+        <v>34</v>
+      </c>
+      <c r="M90" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N90" s="14">
+        <v>884000</v>
+      </c>
+      <c r="O90" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P90" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A91" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="F91" s="13">
+        <v>763357265</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K91" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L91" s="13">
+        <v>1</v>
+      </c>
+      <c r="M91" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N91" s="14">
+        <v>26000</v>
+      </c>
+      <c r="O91" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P91" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A92" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F92" s="13">
+        <v>771155837</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K92" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L92" s="13">
+        <v>3</v>
+      </c>
+      <c r="M92" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N92" s="14">
+        <v>78000</v>
+      </c>
+      <c r="O92" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P92" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A93" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F93" s="13">
+        <v>763030898</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K93" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L93" s="13">
+        <v>2</v>
+      </c>
+      <c r="M93" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N93" s="14">
+        <v>52000</v>
+      </c>
+      <c r="O93" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P93" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A94" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F94" s="13">
+        <v>785852626</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K94" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L94" s="13">
+        <v>33</v>
+      </c>
+      <c r="M94" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N94" s="14">
+        <v>858000</v>
+      </c>
+      <c r="O94" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P94" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A95" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F95" s="13">
+        <v>776874747</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K95" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L95" s="13">
+        <v>25</v>
+      </c>
+      <c r="M95" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N95" s="14">
+        <v>225000</v>
+      </c>
+      <c r="O95" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P95" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A96" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F96" s="13">
+        <v>764883712</v>
+      </c>
+      <c r="G96" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="K96" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L96" s="13">
+        <v>5</v>
+      </c>
+      <c r="M96" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N96" s="14">
+        <v>45000</v>
+      </c>
+      <c r="O96" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P96" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A97" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F97" s="13">
+        <v>776347177</v>
+      </c>
+      <c r="G97" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K97" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L97" s="13">
+        <v>5</v>
+      </c>
+      <c r="M97" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N97" s="14">
+        <v>130000</v>
+      </c>
+      <c r="O97" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P97" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A98" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F98" s="13">
+        <v>776347177</v>
+      </c>
+      <c r="G98" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K98" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="L98" s="13">
+        <v>1</v>
+      </c>
+      <c r="M98" s="14">
+        <v>33500</v>
+      </c>
+      <c r="N98" s="14">
+        <v>33500</v>
+      </c>
+      <c r="O98" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P98" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A99" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F99" s="13">
+        <v>775623289</v>
+      </c>
+      <c r="G99" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K99" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L99" s="13">
+        <v>20</v>
+      </c>
+      <c r="M99" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N99" s="14">
+        <v>520000</v>
+      </c>
+      <c r="O99" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P99" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A100" s="12">
+        <v>46161</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F100" s="13">
+        <v>775623289</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L100" s="13">
+        <v>25</v>
+      </c>
+      <c r="M100" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N100" s="14">
+        <v>487500</v>
+      </c>
+      <c r="O100" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P100" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A101" s="12">
+        <v>46160</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F101" s="13">
+        <v>776536527</v>
+      </c>
+      <c r="G101" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K101" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L101" s="13">
+        <v>15</v>
+      </c>
+      <c r="M101" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N101" s="14">
+        <v>135000</v>
+      </c>
+      <c r="O101" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P101" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A102" s="12">
+        <v>46160</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F102" s="13">
+        <v>776175166</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K102" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L102" s="13">
+        <v>100</v>
+      </c>
+      <c r="M102" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N102" s="14">
+        <v>2600000</v>
+      </c>
+      <c r="O102" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P102" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A103" s="12">
+        <v>46160</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F103" s="13">
+        <v>776536527</v>
+      </c>
+      <c r="G103" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K103" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L103" s="13">
+        <v>15</v>
+      </c>
+      <c r="M103" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N103" s="14">
+        <v>135000</v>
+      </c>
+      <c r="O103" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P103" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A104" s="12">
+        <v>46160</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E104" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F104" s="13">
+        <v>772899294</v>
+      </c>
+      <c r="G104" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K104" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L104" s="13">
+        <v>25</v>
+      </c>
+      <c r="M104" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N104" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O104" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P104" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A105" s="17">
+        <v>46161</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F105" s="19">
+        <v>774216339</v>
+      </c>
+      <c r="G105" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="K105" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L105" s="18">
+        <v>25</v>
+      </c>
+      <c r="M105" s="20">
+        <v>26000</v>
+      </c>
+      <c r="N105" s="21">
+        <v>650000</v>
+      </c>
+      <c r="O105" s="22" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P105" s="23" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A106" s="12">
+        <v>46162</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C106" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F106" s="24">
+        <v>775273147</v>
+      </c>
+      <c r="G106" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K106" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L106" s="13">
+        <v>100</v>
+      </c>
+      <c r="M106" s="14">
+        <v>5750</v>
+      </c>
+      <c r="N106" s="14">
+        <v>575000</v>
+      </c>
+      <c r="O106" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P106" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A107" s="12">
+        <v>46165</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F107" s="24">
+        <v>777096402</v>
+      </c>
+      <c r="G107" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J107" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K107" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L107" s="13">
+        <v>50</v>
+      </c>
+      <c r="M107" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N107" s="14">
+        <v>450000</v>
+      </c>
+      <c r="O107" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P107" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A108" s="12">
+        <v>46165</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E108" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F108" s="24">
+        <v>775544532</v>
+      </c>
+      <c r="G108" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K108" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L108" s="13">
+        <v>25</v>
+      </c>
+      <c r="M108" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N108" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O108" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P108" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A109" s="12">
+        <v>46165</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F109" s="24">
+        <v>773739328</v>
+      </c>
+      <c r="G109" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H109" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K109" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L109" s="13">
+        <v>10</v>
+      </c>
+      <c r="M109" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N109" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O109" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P109" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A110" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F110" s="24">
+        <v>779414699</v>
+      </c>
+      <c r="G110" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I110" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J110" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K110" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L110" s="13">
+        <v>15</v>
+      </c>
+      <c r="M110" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N110" s="14">
+        <v>135000</v>
+      </c>
+      <c r="O110" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P110" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A111" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C111" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F111" s="24">
+        <v>779414699</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H111" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I111" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K111" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L111" s="13">
+        <v>10</v>
+      </c>
+      <c r="M111" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N111" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O111" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P111" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A112" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F112" s="24">
+        <v>772252177</v>
+      </c>
+      <c r="G112" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H112" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="K112" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L112" s="13">
+        <v>50</v>
+      </c>
+      <c r="M112" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N112" s="14">
+        <v>1300000</v>
+      </c>
+      <c r="O112" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P112" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A113" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F113" s="24">
+        <v>775284696</v>
+      </c>
+      <c r="G113" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K113" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L113" s="13">
+        <v>50</v>
+      </c>
+      <c r="M113" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N113" s="14">
+        <v>1300000</v>
+      </c>
+      <c r="O113" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P113" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A114" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E114" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F114" s="24">
+        <v>765956010</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I114" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J114" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K114" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L114" s="13">
+        <v>5</v>
+      </c>
+      <c r="M114" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N114" s="14">
+        <v>45000</v>
+      </c>
+      <c r="O114" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P114" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A115" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C115" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F115" s="24">
+        <v>765956010</v>
+      </c>
+      <c r="G115" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I115" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="K115" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L115" s="13">
+        <v>20</v>
+      </c>
+      <c r="M115" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N115" s="14">
+        <v>180000</v>
+      </c>
+      <c r="O115" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P115" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A116" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C116" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F116" s="24">
+        <v>775630094</v>
+      </c>
+      <c r="G116" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K116" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L116" s="13">
+        <v>25</v>
+      </c>
+      <c r="M116" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N116" s="14">
+        <v>700000</v>
+      </c>
+      <c r="O116" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P116" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A117" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F117" s="24">
+        <v>774483791</v>
+      </c>
+      <c r="G117" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J117" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K117" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="L117" s="13">
+        <v>5</v>
+      </c>
+      <c r="M117" s="14">
+        <v>28000</v>
+      </c>
+      <c r="N117" s="14">
+        <v>140000</v>
+      </c>
+      <c r="O117" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P117" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A118" s="12">
+        <v>46164</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F118" s="24">
+        <v>777096402</v>
+      </c>
+      <c r="G118" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J118" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K118" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L118" s="13">
+        <v>25</v>
+      </c>
+      <c r="M118" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N118" s="14">
+        <v>487500</v>
+      </c>
+      <c r="O118" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P118" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A119" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B119" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C119" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F119" s="24">
+        <v>783740441</v>
+      </c>
+      <c r="G119" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J119" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K119" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L119" s="13">
+        <v>10</v>
+      </c>
+      <c r="M119" s="14">
+        <v>9000</v>
+      </c>
+      <c r="N119" s="14">
+        <v>90000</v>
+      </c>
+      <c r="O119" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P119" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A120" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F120" s="24">
+        <v>770712599</v>
+      </c>
+      <c r="G120" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J120" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="K120" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="L120" s="13">
+        <v>100</v>
+      </c>
+      <c r="M120" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N120" s="14">
+        <v>2600000</v>
+      </c>
+      <c r="O120" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P120" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A121" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F121" s="24">
+        <v>774216341</v>
+      </c>
+      <c r="G121" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J121" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K121" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L121" s="13">
+        <v>5</v>
+      </c>
+      <c r="M121" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N121" s="14">
+        <v>97500</v>
+      </c>
+      <c r="O121" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P121" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A122" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="F122" s="24">
+        <v>775485563</v>
+      </c>
+      <c r="G122" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J122" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="K122" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L122" s="13">
+        <v>10</v>
+      </c>
+      <c r="M122" s="14">
+        <v>19500</v>
+      </c>
+      <c r="N122" s="14">
+        <v>195000</v>
+      </c>
+      <c r="O122" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P122" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A123" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F123" s="24">
+        <v>775544532</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H123" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J123" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K123" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L123" s="13">
+        <v>25</v>
+      </c>
+      <c r="M123" s="14">
+        <v>26000</v>
+      </c>
+      <c r="N123" s="14">
+        <v>650000</v>
+      </c>
+      <c r="O123" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P123" s="16" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A124" s="12">
+        <v>46163</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F124" s="24">
+        <v>776634479</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J124" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="K124" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="L124" s="13">
+        <v>8</v>
+      </c>
+      <c r="M124" s="14">
+        <v>55000</v>
+      </c>
+      <c r="N124" s="14">
+        <v>440000</v>
+      </c>
+      <c r="O124" s="15" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S21</v>
+      </c>
+      <c r="P124" s="16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522E29B6-FCCD-4E9F-BF98-8C76FFF81394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EF79F7-682A-4271-AEC2-268DCED33FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -720,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -753,39 +753,19 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,7 +1073,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P124" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P124" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+  <autoFilter ref="A1:P124" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="MAMADOU BA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1476,7 +1462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="8">
         <v>46139</v>
       </c>
@@ -1528,7 +1514,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>46139</v>
       </c>
@@ -1580,7 +1566,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>46139</v>
       </c>
@@ -1632,7 +1618,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>46139</v>
       </c>
@@ -1684,7 +1670,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>46140</v>
       </c>
@@ -1736,7 +1722,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8">
         <v>46140</v>
       </c>
@@ -1788,7 +1774,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>46140</v>
       </c>
@@ -1840,7 +1826,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>46140</v>
       </c>
@@ -1892,7 +1878,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>46140</v>
       </c>
@@ -1944,7 +1930,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="8">
         <v>46140</v>
       </c>
@@ -1996,7 +1982,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
         <v>46140</v>
       </c>
@@ -2048,7 +2034,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>46140</v>
       </c>
@@ -2100,7 +2086,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" s="8">
         <v>46141</v>
       </c>
@@ -2152,7 +2138,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>46141</v>
       </c>
@@ -2204,7 +2190,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" s="8">
         <v>46141</v>
       </c>
@@ -2256,7 +2242,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>46141</v>
       </c>
@@ -2308,7 +2294,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" s="8">
         <v>46141</v>
       </c>
@@ -2360,7 +2346,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>46140</v>
       </c>
@@ -2412,7 +2398,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>46140</v>
       </c>
@@ -2464,7 +2450,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
         <v>46140</v>
       </c>
@@ -2516,7 +2502,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>46140</v>
       </c>
@@ -2568,7 +2554,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="8">
         <v>46140</v>
       </c>
@@ -2620,7 +2606,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="8">
         <v>46141</v>
       </c>
@@ -2724,7 +2710,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="8">
         <v>46141</v>
       </c>
@@ -2776,7 +2762,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="8">
         <v>46142</v>
       </c>
@@ -2828,7 +2814,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" s="8">
         <v>46142</v>
       </c>
@@ -2880,7 +2866,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="8">
         <v>46142</v>
       </c>
@@ -2932,7 +2918,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" s="8">
         <v>46142</v>
       </c>
@@ -2984,7 +2970,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" s="8">
         <v>46142</v>
       </c>
@@ -3036,7 +3022,7 @@
         <v>avril</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" s="8">
         <v>46151</v>
       </c>
@@ -3088,7 +3074,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" s="8">
         <v>46150</v>
       </c>
@@ -3140,7 +3126,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="8">
         <v>46150</v>
       </c>
@@ -3192,7 +3178,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" s="8">
         <v>46150</v>
       </c>
@@ -3244,7 +3230,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" s="8">
         <v>46150</v>
       </c>
@@ -3296,7 +3282,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" s="8">
         <v>46150</v>
       </c>
@@ -3348,7 +3334,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" s="8">
         <v>46150</v>
       </c>
@@ -3452,7 +3438,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" s="8">
         <v>46148</v>
       </c>
@@ -3504,7 +3490,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" s="8">
         <v>46148</v>
       </c>
@@ -3556,7 +3542,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" s="8">
         <v>46148</v>
       </c>
@@ -3608,7 +3594,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" s="8">
         <v>46148</v>
       </c>
@@ -3660,7 +3646,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" s="8">
         <v>46151</v>
       </c>
@@ -3712,7 +3698,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" s="8">
         <v>46150</v>
       </c>
@@ -3764,7 +3750,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" s="8">
         <v>46150</v>
       </c>
@@ -3816,7 +3802,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" s="8">
         <v>46150</v>
       </c>
@@ -3868,7 +3854,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" s="8">
         <v>46150</v>
       </c>
@@ -3920,7 +3906,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" s="8">
         <v>46150</v>
       </c>
@@ -3972,7 +3958,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" s="8">
         <v>46150</v>
       </c>
@@ -4024,7 +4010,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" s="8">
         <v>46150</v>
       </c>
@@ -4076,7 +4062,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" s="8">
         <v>46150</v>
       </c>
@@ -4180,7 +4166,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" s="8">
         <v>46149</v>
       </c>
@@ -4232,7 +4218,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" s="8">
         <v>46147</v>
       </c>
@@ -4284,7 +4270,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" s="8">
         <v>46147</v>
       </c>
@@ -4336,7 +4322,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" s="8">
         <v>46147</v>
       </c>
@@ -4388,7 +4374,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" s="8">
         <v>46147</v>
       </c>
@@ -4440,7 +4426,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" s="8">
         <v>46147</v>
       </c>
@@ -4492,7 +4478,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" s="8">
         <v>46158</v>
       </c>
@@ -4544,7 +4530,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" s="8">
         <v>46158</v>
       </c>
@@ -4596,7 +4582,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" s="8">
         <v>46157</v>
       </c>
@@ -4648,7 +4634,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" s="8">
         <v>46157</v>
       </c>
@@ -4700,7 +4686,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" s="8">
         <v>46157</v>
       </c>
@@ -4752,7 +4738,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" s="8">
         <v>46157</v>
       </c>
@@ -4804,7 +4790,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" s="8">
         <v>46157</v>
       </c>
@@ -4856,7 +4842,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" s="8">
         <v>46156</v>
       </c>
@@ -4908,7 +4894,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" s="8">
         <v>46156</v>
       </c>
@@ -4960,7 +4946,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" s="8">
         <v>46156</v>
       </c>
@@ -5012,7 +4998,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" s="8">
         <v>46156</v>
       </c>
@@ -5064,7 +5050,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" s="8">
         <v>46155</v>
       </c>
@@ -5116,7 +5102,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" s="8">
         <v>46155</v>
       </c>
@@ -5168,7 +5154,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" s="8">
         <v>46155</v>
       </c>
@@ -5220,7 +5206,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" s="8">
         <v>46155</v>
       </c>
@@ -5272,7 +5258,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" s="8">
         <v>46154</v>
       </c>
@@ -5324,7 +5310,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" s="8">
         <v>46154</v>
       </c>
@@ -5376,7 +5362,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" s="8">
         <v>46154</v>
       </c>
@@ -5428,7 +5414,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" s="8">
         <v>46154</v>
       </c>
@@ -5480,7 +5466,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" s="8">
         <v>46153</v>
       </c>
@@ -5532,7 +5518,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" s="8">
         <v>46153</v>
       </c>
@@ -5584,7 +5570,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" s="8">
         <v>46153</v>
       </c>
@@ -5636,7 +5622,7 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" s="8">
         <v>46158</v>
       </c>
@@ -5680,2186 +5666,2186 @@
         <v>mai</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A83" s="12">
+    <row r="83" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="8">
         <v>46162</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E83" s="13" t="s">
+      <c r="E83" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F83" s="9">
         <v>779235028</v>
       </c>
-      <c r="G83" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H83" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I83" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="13" t="s">
+      <c r="G83" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K83" s="13" t="s">
+      <c r="K83" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L83" s="13">
+      <c r="L83" s="9">
         <v>33</v>
       </c>
-      <c r="M83" s="14">
+      <c r="M83" s="11">
         <v>26000</v>
       </c>
-      <c r="N83" s="14">
+      <c r="N83" s="11">
         <v>858000</v>
       </c>
-      <c r="O83" s="15" t="str">
+      <c r="O83" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P83" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A84" s="12">
+      <c r="P83" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="8">
         <v>46162</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E84" s="13" t="s">
+      <c r="E84" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="9">
         <v>770217868</v>
       </c>
-      <c r="G84" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I84" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J84" s="13" t="s">
+      <c r="G84" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="K84" s="13" t="s">
+      <c r="K84" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L84" s="13">
+      <c r="L84" s="9">
         <v>25</v>
       </c>
-      <c r="M84" s="14">
+      <c r="M84" s="11">
         <v>26000</v>
       </c>
-      <c r="N84" s="14">
+      <c r="N84" s="11">
         <v>650000</v>
       </c>
-      <c r="O84" s="15" t="str">
+      <c r="O84" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P84" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A85" s="12">
+      <c r="P84" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A85" s="8">
         <v>46162</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D85" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E85" s="13" t="s">
+      <c r="E85" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="9">
         <v>774289051</v>
       </c>
-      <c r="G85" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H85" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I85" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" s="13" t="s">
+      <c r="G85" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="K85" s="13" t="s">
+      <c r="K85" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L85" s="13">
+      <c r="L85" s="9">
         <v>25</v>
       </c>
-      <c r="M85" s="14">
+      <c r="M85" s="11">
         <v>26000</v>
       </c>
-      <c r="N85" s="14">
+      <c r="N85" s="11">
         <v>650000</v>
       </c>
-      <c r="O85" s="15" t="str">
+      <c r="O85" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P85" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A86" s="12">
+      <c r="P85" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="8">
         <v>46162</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E86" s="13" t="s">
+      <c r="E86" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F86" s="13">
+      <c r="F86" s="9">
         <v>771701320</v>
       </c>
-      <c r="G86" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I86" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" s="13" t="s">
+      <c r="G86" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K86" s="13" t="s">
+      <c r="K86" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L86" s="13">
+      <c r="L86" s="9">
         <v>25</v>
       </c>
-      <c r="M86" s="14">
+      <c r="M86" s="11">
         <v>9000</v>
       </c>
-      <c r="N86" s="14">
+      <c r="N86" s="11">
         <v>225000</v>
       </c>
-      <c r="O86" s="15" t="str">
+      <c r="O86" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P86" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A87" s="12">
+      <c r="P86" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="8">
         <v>46162</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E87" s="13" t="s">
+      <c r="E87" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F87" s="13">
+      <c r="F87" s="9">
         <v>771701320</v>
       </c>
-      <c r="G87" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I87" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" s="13" t="s">
+      <c r="G87" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K87" s="13" t="s">
+      <c r="K87" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L87" s="13">
+      <c r="L87" s="9">
         <v>25</v>
       </c>
-      <c r="M87" s="14">
+      <c r="M87" s="11">
         <v>9000</v>
       </c>
-      <c r="N87" s="14">
+      <c r="N87" s="11">
         <v>225000</v>
       </c>
-      <c r="O87" s="15" t="str">
+      <c r="O87" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P87" s="16" t="str">
+      <c r="P87" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A88" s="12">
+      <c r="A88" s="8">
         <v>46162</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E88" s="13" t="s">
+      <c r="E88" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="9">
         <v>771619220</v>
       </c>
-      <c r="G88" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I88" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" s="13" t="s">
+      <c r="G88" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K88" s="13" t="s">
+      <c r="K88" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L88" s="13">
-        <v>51</v>
-      </c>
-      <c r="M88" s="14">
+      <c r="L88" s="9">
+        <v>50</v>
+      </c>
+      <c r="M88" s="11">
         <v>26000</v>
       </c>
-      <c r="N88" s="14">
-        <v>1326000</v>
-      </c>
-      <c r="O88" s="15" t="str">
+      <c r="N88" s="11">
+        <v>1300000</v>
+      </c>
+      <c r="O88" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P88" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A89" s="12">
+      <c r="P88" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="8">
         <v>46162</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="9">
         <v>784785900</v>
       </c>
-      <c r="G89" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I89" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J89" s="13" t="s">
+      <c r="G89" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K89" s="13" t="s">
+      <c r="K89" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L89" s="13">
+      <c r="L89" s="9">
         <v>100</v>
       </c>
-      <c r="M89" s="14">
+      <c r="M89" s="11">
         <v>26000</v>
       </c>
-      <c r="N89" s="14">
+      <c r="N89" s="11">
         <v>2600000</v>
       </c>
-      <c r="O89" s="15" t="str">
+      <c r="O89" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P89" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A90" s="12">
+      <c r="P89" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="8">
         <v>46162</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E90" s="13" t="s">
+      <c r="E90" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="9">
         <v>779110400</v>
       </c>
-      <c r="G90" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" s="13" t="s">
+      <c r="G90" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K90" s="13" t="s">
+      <c r="K90" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L90" s="13">
+      <c r="L90" s="9">
         <v>34</v>
       </c>
-      <c r="M90" s="14">
+      <c r="M90" s="11">
         <v>26000</v>
       </c>
-      <c r="N90" s="14">
+      <c r="N90" s="11">
         <v>884000</v>
       </c>
-      <c r="O90" s="15" t="str">
+      <c r="O90" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P90" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A91" s="12">
+      <c r="P90" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="8">
         <v>46162</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E91" s="13" t="s">
+      <c r="E91" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F91" s="13">
+      <c r="F91" s="9">
         <v>763357265</v>
       </c>
-      <c r="G91" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H91" s="13" t="s">
+      <c r="G91" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I91" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J91" s="13" t="s">
+      <c r="I91" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K91" s="13" t="s">
+      <c r="K91" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L91" s="13">
+      <c r="L91" s="9">
         <v>1</v>
       </c>
-      <c r="M91" s="14">
+      <c r="M91" s="11">
         <v>26000</v>
       </c>
-      <c r="N91" s="14">
+      <c r="N91" s="11">
         <v>26000</v>
       </c>
-      <c r="O91" s="15" t="str">
+      <c r="O91" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P91" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A92" s="12">
+      <c r="P91" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="8">
         <v>46162</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E92" s="13" t="s">
+      <c r="E92" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F92" s="13">
+      <c r="F92" s="9">
         <v>771155837</v>
       </c>
-      <c r="G92" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" s="13" t="s">
+      <c r="G92" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I92" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J92" s="13" t="s">
+      <c r="I92" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K92" s="13" t="s">
+      <c r="K92" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L92" s="13">
+      <c r="L92" s="9">
         <v>3</v>
       </c>
-      <c r="M92" s="14">
+      <c r="M92" s="11">
         <v>26000</v>
       </c>
-      <c r="N92" s="14">
+      <c r="N92" s="11">
         <v>78000</v>
       </c>
-      <c r="O92" s="15" t="str">
+      <c r="O92" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P92" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A93" s="12">
+      <c r="P92" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="8">
         <v>46162</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E93" s="13" t="s">
+      <c r="E93" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F93" s="13">
+      <c r="F93" s="9">
         <v>763030898</v>
       </c>
-      <c r="G93" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H93" s="13" t="s">
+      <c r="G93" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I93" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" s="13" t="s">
+      <c r="I93" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K93" s="13" t="s">
+      <c r="K93" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L93" s="13">
+      <c r="L93" s="9">
         <v>2</v>
       </c>
-      <c r="M93" s="14">
+      <c r="M93" s="11">
         <v>26000</v>
       </c>
-      <c r="N93" s="14">
+      <c r="N93" s="11">
         <v>52000</v>
       </c>
-      <c r="O93" s="15" t="str">
+      <c r="O93" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P93" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A94" s="12">
+      <c r="P93" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="8">
         <v>46162</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E94" s="13" t="s">
+      <c r="E94" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F94" s="13">
+      <c r="F94" s="9">
         <v>785852626</v>
       </c>
-      <c r="G94" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I94" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J94" s="13" t="s">
+      <c r="G94" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K94" s="13" t="s">
+      <c r="K94" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L94" s="13">
+      <c r="L94" s="9">
         <v>33</v>
       </c>
-      <c r="M94" s="14">
+      <c r="M94" s="11">
         <v>26000</v>
       </c>
-      <c r="N94" s="14">
+      <c r="N94" s="11">
         <v>858000</v>
       </c>
-      <c r="O94" s="15" t="str">
+      <c r="O94" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P94" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A95" s="12">
+      <c r="P94" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="8">
         <v>46161</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E95" s="13" t="s">
+      <c r="E95" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F95" s="13">
+      <c r="F95" s="9">
         <v>776874747</v>
       </c>
-      <c r="G95" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="13" t="s">
+      <c r="G95" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I95" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" s="13" t="s">
+      <c r="I95" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K95" s="13" t="s">
+      <c r="K95" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L95" s="13">
+      <c r="L95" s="9">
         <v>25</v>
       </c>
-      <c r="M95" s="14">
+      <c r="M95" s="11">
         <v>9000</v>
       </c>
-      <c r="N95" s="14">
+      <c r="N95" s="11">
         <v>225000</v>
       </c>
-      <c r="O95" s="15" t="str">
+      <c r="O95" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P95" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A96" s="12">
+      <c r="P95" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="8">
         <v>46161</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E96" s="13" t="s">
+      <c r="E96" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F96" s="13">
+      <c r="F96" s="9">
         <v>764883712</v>
       </c>
-      <c r="G96" s="13" t="s">
+      <c r="G96" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="H96" s="13" t="s">
+      <c r="H96" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" s="13" t="s">
+      <c r="I96" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="K96" s="13" t="s">
+      <c r="K96" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L96" s="13">
+      <c r="L96" s="9">
         <v>5</v>
       </c>
-      <c r="M96" s="14">
+      <c r="M96" s="11">
         <v>9000</v>
       </c>
-      <c r="N96" s="14">
+      <c r="N96" s="11">
         <v>45000</v>
       </c>
-      <c r="O96" s="15" t="str">
+      <c r="O96" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P96" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A97" s="12">
+      <c r="P96" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A97" s="8">
         <v>46161</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D97" s="13" t="s">
+      <c r="D97" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E97" s="13" t="s">
+      <c r="E97" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97" s="9">
         <v>776347177</v>
       </c>
-      <c r="G97" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H97" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I97" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J97" s="13" t="s">
+      <c r="G97" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K97" s="13" t="s">
+      <c r="K97" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L97" s="13">
+      <c r="L97" s="9">
         <v>5</v>
       </c>
-      <c r="M97" s="14">
+      <c r="M97" s="11">
         <v>26000</v>
       </c>
-      <c r="N97" s="14">
+      <c r="N97" s="11">
         <v>130000</v>
       </c>
-      <c r="O97" s="15" t="str">
+      <c r="O97" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P97" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A98" s="12">
+      <c r="P97" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="8">
         <v>46161</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E98" s="13" t="s">
+      <c r="E98" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="9">
         <v>776347177</v>
       </c>
-      <c r="G98" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I98" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J98" s="13" t="s">
+      <c r="G98" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K98" s="13" t="s">
+      <c r="K98" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="L98" s="13">
+      <c r="L98" s="9">
         <v>1</v>
       </c>
-      <c r="M98" s="14">
+      <c r="M98" s="11">
         <v>33500</v>
       </c>
-      <c r="N98" s="14">
+      <c r="N98" s="11">
         <v>33500</v>
       </c>
-      <c r="O98" s="15" t="str">
+      <c r="O98" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P98" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A99" s="12">
+      <c r="P98" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="8">
         <v>46161</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D99" s="13" t="s">
+      <c r="D99" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E99" s="13" t="s">
+      <c r="E99" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F99" s="13">
+      <c r="F99" s="9">
         <v>775623289</v>
       </c>
-      <c r="G99" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I99" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J99" s="13" t="s">
+      <c r="G99" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K99" s="13" t="s">
+      <c r="K99" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L99" s="13">
+      <c r="L99" s="9">
         <v>20</v>
       </c>
-      <c r="M99" s="14">
+      <c r="M99" s="11">
         <v>26000</v>
       </c>
-      <c r="N99" s="14">
+      <c r="N99" s="11">
         <v>520000</v>
       </c>
-      <c r="O99" s="15" t="str">
+      <c r="O99" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P99" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A100" s="12">
+      <c r="P99" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="8">
         <v>46161</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C100" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E100" s="13" t="s">
+      <c r="E100" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F100" s="13">
+      <c r="F100" s="9">
         <v>775623289</v>
       </c>
-      <c r="G100" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I100" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J100" s="13" t="s">
+      <c r="G100" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K100" s="13" t="s">
+      <c r="K100" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L100" s="13">
+      <c r="L100" s="9">
         <v>25</v>
       </c>
-      <c r="M100" s="14">
+      <c r="M100" s="11">
         <v>19500</v>
       </c>
-      <c r="N100" s="14">
+      <c r="N100" s="11">
         <v>487500</v>
       </c>
-      <c r="O100" s="15" t="str">
+      <c r="O100" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P100" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A101" s="12">
+      <c r="P100" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="8">
         <v>46160</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E101" s="13" t="s">
+      <c r="E101" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="9">
         <v>776536527</v>
       </c>
-      <c r="G101" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H101" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J101" s="13" t="s">
+      <c r="G101" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K101" s="13" t="s">
+      <c r="K101" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L101" s="13">
-        <v>15</v>
-      </c>
-      <c r="M101" s="14">
+      <c r="L101" s="9">
+        <v>15</v>
+      </c>
+      <c r="M101" s="11">
         <v>9000</v>
       </c>
-      <c r="N101" s="14">
+      <c r="N101" s="11">
         <v>135000</v>
       </c>
-      <c r="O101" s="15" t="str">
+      <c r="O101" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P101" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A102" s="12">
+      <c r="P101" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A102" s="8">
         <v>46160</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D102" s="13" t="s">
+      <c r="D102" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E102" s="13" t="s">
+      <c r="E102" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102" s="9">
         <v>776175166</v>
       </c>
-      <c r="G102" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I102" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J102" s="13" t="s">
+      <c r="G102" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K102" s="13" t="s">
+      <c r="K102" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L102" s="13">
+      <c r="L102" s="9">
         <v>100</v>
       </c>
-      <c r="M102" s="14">
+      <c r="M102" s="11">
         <v>26000</v>
       </c>
-      <c r="N102" s="14">
+      <c r="N102" s="11">
         <v>2600000</v>
       </c>
-      <c r="O102" s="15" t="str">
+      <c r="O102" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P102" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A103" s="12">
+      <c r="P102" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A103" s="8">
         <v>46160</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E103" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F103" s="13">
+      <c r="F103" s="9">
         <v>776536527</v>
       </c>
-      <c r="G103" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I103" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J103" s="13" t="s">
+      <c r="G103" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K103" s="13" t="s">
+      <c r="K103" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L103" s="13">
-        <v>15</v>
-      </c>
-      <c r="M103" s="14">
+      <c r="L103" s="9">
+        <v>15</v>
+      </c>
+      <c r="M103" s="11">
         <v>9000</v>
       </c>
-      <c r="N103" s="14">
+      <c r="N103" s="11">
         <v>135000</v>
       </c>
-      <c r="O103" s="15" t="str">
+      <c r="O103" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P103" s="16" t="str">
+      <c r="P103" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A104" s="12">
+      <c r="A104" s="8">
         <v>46160</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D104" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E104" s="13" t="s">
+      <c r="E104" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="9">
         <v>772899294</v>
       </c>
-      <c r="G104" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I104" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J104" s="13" t="s">
+      <c r="G104" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="K104" s="13" t="s">
+      <c r="K104" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L104" s="13">
+      <c r="L104" s="9">
         <v>25</v>
       </c>
-      <c r="M104" s="14">
+      <c r="M104" s="11">
         <v>26000</v>
       </c>
-      <c r="N104" s="14">
+      <c r="N104" s="11">
         <v>650000</v>
       </c>
-      <c r="O104" s="15" t="str">
+      <c r="O104" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P104" s="16" t="str">
+      <c r="P104" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A105" s="17">
+      <c r="A105" s="12">
         <v>46161</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B105" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C105" s="18" t="s">
+      <c r="C105" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D105" s="18" t="s">
+      <c r="D105" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="E105" s="18" t="s">
+      <c r="E105" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="F105" s="19">
+      <c r="F105" s="14">
         <v>774216339</v>
       </c>
-      <c r="G105" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="I105" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J105" s="18" t="s">
+      <c r="G105" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="K105" s="18" t="s">
+      <c r="K105" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="L105" s="18">
+      <c r="L105" s="13">
         <v>25</v>
       </c>
-      <c r="M105" s="20">
+      <c r="M105" s="15">
         <v>26000</v>
       </c>
-      <c r="N105" s="21">
+      <c r="N105" s="16">
         <v>650000</v>
       </c>
-      <c r="O105" s="22" t="str">
+      <c r="O105" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P105" s="23" t="str">
+      <c r="P105" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A106" s="12">
+      <c r="A106" s="8">
         <v>46162</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E106" s="13" t="s">
+      <c r="E106" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F106" s="24">
+      <c r="F106" s="10">
         <v>775273147</v>
       </c>
-      <c r="G106" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I106" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J106" s="13" t="s">
+      <c r="G106" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J106" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K106" s="13" t="s">
+      <c r="K106" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L106" s="13">
+      <c r="L106" s="9">
         <v>100</v>
       </c>
-      <c r="M106" s="14">
+      <c r="M106" s="11">
         <v>5750</v>
       </c>
-      <c r="N106" s="14">
+      <c r="N106" s="11">
         <v>575000</v>
       </c>
-      <c r="O106" s="15" t="str">
+      <c r="O106" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P106" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A107" s="12">
+      <c r="P106" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A107" s="8">
         <v>46165</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D107" s="13" t="s">
+      <c r="D107" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E107" s="13" t="s">
+      <c r="E107" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F107" s="24">
+      <c r="F107" s="10">
         <v>777096402</v>
       </c>
-      <c r="G107" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I107" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J107" s="13" t="s">
+      <c r="G107" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J107" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K107" s="13" t="s">
+      <c r="K107" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L107" s="13">
+      <c r="L107" s="9">
         <v>50</v>
       </c>
-      <c r="M107" s="14">
+      <c r="M107" s="11">
         <v>9000</v>
       </c>
-      <c r="N107" s="14">
+      <c r="N107" s="11">
         <v>450000</v>
       </c>
-      <c r="O107" s="15" t="str">
+      <c r="O107" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P107" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A108" s="12">
+      <c r="P107" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A108" s="8">
         <v>46165</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D108" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E108" s="13" t="s">
+      <c r="E108" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F108" s="24">
+      <c r="F108" s="10">
         <v>775544532</v>
       </c>
-      <c r="G108" s="13" t="s">
+      <c r="G108" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H108" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I108" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J108" s="13" t="s">
+      <c r="H108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K108" s="13" t="s">
+      <c r="K108" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L108" s="13">
+      <c r="L108" s="9">
         <v>25</v>
       </c>
-      <c r="M108" s="14">
+      <c r="M108" s="11">
         <v>26000</v>
       </c>
-      <c r="N108" s="14">
+      <c r="N108" s="11">
         <v>650000</v>
       </c>
-      <c r="O108" s="15" t="str">
+      <c r="O108" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P108" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A109" s="12">
+      <c r="P108" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A109" s="8">
         <v>46165</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E109" s="13" t="s">
+      <c r="E109" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F109" s="24">
+      <c r="F109" s="10">
         <v>773739328</v>
       </c>
-      <c r="G109" s="13" t="s">
+      <c r="G109" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H109" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I109" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J109" s="13" t="s">
+      <c r="H109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K109" s="13" t="s">
+      <c r="K109" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L109" s="13">
+      <c r="L109" s="9">
         <v>10</v>
       </c>
-      <c r="M109" s="14">
+      <c r="M109" s="11">
         <v>9000</v>
       </c>
-      <c r="N109" s="14">
+      <c r="N109" s="11">
         <v>90000</v>
       </c>
-      <c r="O109" s="15" t="str">
+      <c r="O109" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P109" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A110" s="12">
+      <c r="P109" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A110" s="8">
         <v>46164</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="C110" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E110" s="13" t="s">
+      <c r="E110" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F110" s="24">
+      <c r="F110" s="10">
         <v>779414699</v>
       </c>
-      <c r="G110" s="13" t="s">
+      <c r="G110" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H110" s="13" t="s">
+      <c r="H110" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I110" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J110" s="13" t="s">
+      <c r="I110" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J110" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K110" s="13" t="s">
+      <c r="K110" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L110" s="13">
-        <v>15</v>
-      </c>
-      <c r="M110" s="14">
+      <c r="L110" s="9">
+        <v>15</v>
+      </c>
+      <c r="M110" s="11">
         <v>9000</v>
       </c>
-      <c r="N110" s="14">
+      <c r="N110" s="11">
         <v>135000</v>
       </c>
-      <c r="O110" s="15" t="str">
+      <c r="O110" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P110" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A111" s="12">
+      <c r="P110" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A111" s="8">
         <v>46164</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E111" s="13" t="s">
+      <c r="E111" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F111" s="24">
+      <c r="F111" s="10">
         <v>779414699</v>
       </c>
-      <c r="G111" s="13" t="s">
+      <c r="G111" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H111" s="13" t="s">
+      <c r="H111" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I111" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J111" s="13" t="s">
+      <c r="I111" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K111" s="13" t="s">
+      <c r="K111" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L111" s="13">
+      <c r="L111" s="9">
         <v>10</v>
       </c>
-      <c r="M111" s="14">
+      <c r="M111" s="11">
         <v>9000</v>
       </c>
-      <c r="N111" s="14">
+      <c r="N111" s="11">
         <v>90000</v>
       </c>
-      <c r="O111" s="15" t="str">
+      <c r="O111" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P111" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A112" s="12">
+      <c r="P111" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A112" s="8">
         <v>46164</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C112" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D112" s="13" t="s">
+      <c r="D112" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E112" s="13" t="s">
+      <c r="E112" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="F112" s="24">
+      <c r="F112" s="10">
         <v>772252177</v>
       </c>
-      <c r="G112" s="13" t="s">
+      <c r="G112" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H112" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I112" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J112" s="13" t="s">
+      <c r="H112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="K112" s="13" t="s">
+      <c r="K112" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L112" s="13">
+      <c r="L112" s="9">
         <v>50</v>
       </c>
-      <c r="M112" s="14">
+      <c r="M112" s="11">
         <v>26000</v>
       </c>
-      <c r="N112" s="14">
+      <c r="N112" s="11">
         <v>1300000</v>
       </c>
-      <c r="O112" s="15" t="str">
+      <c r="O112" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P112" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A113" s="12">
+      <c r="P112" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A113" s="8">
         <v>46164</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D113" s="13" t="s">
+      <c r="D113" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E113" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F113" s="24">
+      <c r="F113" s="10">
         <v>775284696</v>
       </c>
-      <c r="G113" s="13" t="s">
+      <c r="G113" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H113" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I113" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J113" s="13" t="s">
+      <c r="H113" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K113" s="13" t="s">
+      <c r="K113" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L113" s="13">
+      <c r="L113" s="9">
         <v>50</v>
       </c>
-      <c r="M113" s="14">
+      <c r="M113" s="11">
         <v>26000</v>
       </c>
-      <c r="N113" s="14">
+      <c r="N113" s="11">
         <v>1300000</v>
       </c>
-      <c r="O113" s="15" t="str">
+      <c r="O113" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P113" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A114" s="12">
+      <c r="P113" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A114" s="8">
         <v>46164</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E114" s="13" t="s">
+      <c r="E114" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F114" s="24">
+      <c r="F114" s="10">
         <v>765956010</v>
       </c>
-      <c r="G114" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H114" s="13" t="s">
+      <c r="G114" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I114" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J114" s="13" t="s">
+      <c r="I114" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J114" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K114" s="13" t="s">
+      <c r="K114" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L114" s="13">
+      <c r="L114" s="9">
         <v>5</v>
       </c>
-      <c r="M114" s="14">
+      <c r="M114" s="11">
         <v>9000</v>
       </c>
-      <c r="N114" s="14">
+      <c r="N114" s="11">
         <v>45000</v>
       </c>
-      <c r="O114" s="15" t="str">
+      <c r="O114" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P114" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A115" s="12">
+      <c r="P114" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A115" s="8">
         <v>46164</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D115" s="13" t="s">
+      <c r="D115" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="E115" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="F115" s="24">
+      <c r="F115" s="10">
         <v>765956010</v>
       </c>
-      <c r="G115" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H115" s="13" t="s">
+      <c r="G115" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I115" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J115" s="13" t="s">
+      <c r="I115" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="K115" s="13" t="s">
+      <c r="K115" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L115" s="13">
+      <c r="L115" s="9">
         <v>20</v>
       </c>
-      <c r="M115" s="14">
+      <c r="M115" s="11">
         <v>9000</v>
       </c>
-      <c r="N115" s="14">
+      <c r="N115" s="11">
         <v>180000</v>
       </c>
-      <c r="O115" s="15" t="str">
+      <c r="O115" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P115" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A116" s="12">
+      <c r="P115" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A116" s="8">
         <v>46164</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E116" s="13" t="s">
+      <c r="E116" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F116" s="24">
+      <c r="F116" s="10">
         <v>775630094</v>
       </c>
-      <c r="G116" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J116" s="13" t="s">
+      <c r="G116" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K116" s="13" t="s">
+      <c r="K116" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L116" s="13">
+      <c r="L116" s="9">
         <v>25</v>
       </c>
-      <c r="M116" s="14">
+      <c r="M116" s="11">
         <v>28000</v>
       </c>
-      <c r="N116" s="14">
+      <c r="N116" s="11">
         <v>700000</v>
       </c>
-      <c r="O116" s="15" t="str">
+      <c r="O116" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P116" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A117" s="12">
+      <c r="P116" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A117" s="8">
         <v>46164</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D117" s="13" t="s">
+      <c r="D117" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E117" s="13" t="s">
+      <c r="E117" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F117" s="24">
+      <c r="F117" s="10">
         <v>774483791</v>
       </c>
-      <c r="G117" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H117" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I117" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J117" s="13" t="s">
+      <c r="G117" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J117" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K117" s="13" t="s">
+      <c r="K117" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L117" s="13">
+      <c r="L117" s="9">
         <v>5</v>
       </c>
-      <c r="M117" s="14">
+      <c r="M117" s="11">
         <v>28000</v>
       </c>
-      <c r="N117" s="14">
+      <c r="N117" s="11">
         <v>140000</v>
       </c>
-      <c r="O117" s="15" t="str">
+      <c r="O117" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P117" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A118" s="12">
+      <c r="P117" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A118" s="8">
         <v>46164</v>
       </c>
-      <c r="B118" s="13" t="s">
+      <c r="B118" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C118" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E118" s="13" t="s">
+      <c r="E118" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="F118" s="24">
+      <c r="F118" s="10">
         <v>777096402</v>
       </c>
-      <c r="G118" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H118" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I118" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J118" s="13" t="s">
+      <c r="G118" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J118" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K118" s="13" t="s">
+      <c r="K118" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L118" s="13">
+      <c r="L118" s="9">
         <v>25</v>
       </c>
-      <c r="M118" s="14">
+      <c r="M118" s="11">
         <v>19500</v>
       </c>
-      <c r="N118" s="14">
+      <c r="N118" s="11">
         <v>487500</v>
       </c>
-      <c r="O118" s="15" t="str">
+      <c r="O118" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P118" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A119" s="12">
+      <c r="P118" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A119" s="8">
         <v>46163</v>
       </c>
-      <c r="B119" s="13" t="s">
+      <c r="B119" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E119" s="13" t="s">
+      <c r="E119" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F119" s="24">
+      <c r="F119" s="10">
         <v>783740441</v>
       </c>
-      <c r="G119" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H119" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I119" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J119" s="13" t="s">
+      <c r="G119" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J119" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K119" s="13" t="s">
+      <c r="K119" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L119" s="13">
+      <c r="L119" s="9">
         <v>10</v>
       </c>
-      <c r="M119" s="14">
+      <c r="M119" s="11">
         <v>9000</v>
       </c>
-      <c r="N119" s="14">
+      <c r="N119" s="11">
         <v>90000</v>
       </c>
-      <c r="O119" s="15" t="str">
+      <c r="O119" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P119" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A120" s="12">
+      <c r="P119" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A120" s="8">
         <v>46163</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C120" s="13" t="s">
+      <c r="C120" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E120" s="13" t="s">
+      <c r="E120" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F120" s="24">
+      <c r="F120" s="10">
         <v>770712599</v>
       </c>
-      <c r="G120" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H120" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I120" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J120" s="13" t="s">
+      <c r="G120" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J120" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="K120" s="13" t="s">
+      <c r="K120" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="L120" s="13">
+      <c r="L120" s="9">
         <v>100</v>
       </c>
-      <c r="M120" s="14">
+      <c r="M120" s="11">
         <v>26000</v>
       </c>
-      <c r="N120" s="14">
+      <c r="N120" s="11">
         <v>2600000</v>
       </c>
-      <c r="O120" s="15" t="str">
+      <c r="O120" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P120" s="16" t="str">
+      <c r="P120" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A121" s="12">
+      <c r="A121" s="8">
         <v>46163</v>
       </c>
-      <c r="B121" s="13" t="s">
+      <c r="B121" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D121" s="13" t="s">
+      <c r="D121" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E121" s="13" t="s">
+      <c r="E121" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="F121" s="24">
+      <c r="F121" s="10">
         <v>774216341</v>
       </c>
-      <c r="G121" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H121" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I121" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J121" s="13" t="s">
+      <c r="G121" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J121" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K121" s="13" t="s">
+      <c r="K121" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L121" s="13">
+      <c r="L121" s="9">
         <v>5</v>
       </c>
-      <c r="M121" s="14">
+      <c r="M121" s="11">
         <v>19500</v>
       </c>
-      <c r="N121" s="14">
+      <c r="N121" s="11">
         <v>97500</v>
       </c>
-      <c r="O121" s="15" t="str">
+      <c r="O121" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P121" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A122" s="12">
+      <c r="P121" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="28.15" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A122" s="8">
         <v>46163</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C122" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E122" s="13" t="s">
+      <c r="E122" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F122" s="24">
+      <c r="F122" s="10">
         <v>775485563</v>
       </c>
-      <c r="G122" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H122" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I122" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J122" s="13" t="s">
+      <c r="G122" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J122" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="K122" s="13" t="s">
+      <c r="K122" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L122" s="13">
+      <c r="L122" s="9">
         <v>10</v>
       </c>
-      <c r="M122" s="14">
+      <c r="M122" s="11">
         <v>19500</v>
       </c>
-      <c r="N122" s="14">
+      <c r="N122" s="11">
         <v>195000</v>
       </c>
-      <c r="O122" s="15" t="str">
+      <c r="O122" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P122" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A123" s="12">
+      <c r="P122" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A123" s="8">
         <v>46163</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D123" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E123" s="13" t="s">
+      <c r="E123" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F123" s="24">
+      <c r="F123" s="10">
         <v>775544532</v>
       </c>
-      <c r="G123" s="13" t="s">
+      <c r="G123" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H123" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I123" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J123" s="13" t="s">
+      <c r="H123" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J123" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K123" s="13" t="s">
+      <c r="K123" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L123" s="13">
+      <c r="L123" s="9">
         <v>25</v>
       </c>
-      <c r="M123" s="14">
+      <c r="M123" s="11">
         <v>26000</v>
       </c>
-      <c r="N123" s="14">
+      <c r="N123" s="11">
         <v>650000</v>
       </c>
-      <c r="O123" s="15" t="str">
+      <c r="O123" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P123" s="16" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>mai</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A124" s="12">
+      <c r="P123" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>mai</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A124" s="8">
         <v>46163</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C124" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E124" s="13" t="s">
+      <c r="E124" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F124" s="24">
+      <c r="F124" s="10">
         <v>776634479</v>
       </c>
-      <c r="G124" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I124" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J124" s="13" t="s">
+      <c r="G124" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J124" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K124" s="13" t="s">
+      <c r="K124" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="L124" s="13">
+      <c r="L124" s="9">
         <v>8</v>
       </c>
-      <c r="M124" s="14">
+      <c r="M124" s="11">
         <v>55000</v>
       </c>
-      <c r="N124" s="14">
+      <c r="N124" s="11">
         <v>440000</v>
       </c>
-      <c r="O124" s="15" t="str">
+      <c r="O124" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S21</v>
       </c>
-      <c r="P124" s="16" t="str">
+      <c r="P124" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>mai</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF1815B-0F12-4C05-A80A-D8B9E5B5560A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD31C0F-4962-467B-8671-02F962290976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="169">
   <si>
     <t>Date</t>
   </si>
@@ -298,6 +298,249 @@
   </si>
   <si>
     <t>Il dit que nos produits sont  cher raison pour laquelle il achète en petite quantité</t>
+  </si>
+  <si>
+    <t>Kayar</t>
+  </si>
+  <si>
+    <t>Cheikh DIOP</t>
+  </si>
+  <si>
+    <t>Kamlac évaporé 48x160g</t>
+  </si>
+  <si>
+    <t>Pikine Tally Bou Mak</t>
+  </si>
+  <si>
+    <t>Assane</t>
+  </si>
+  <si>
+    <t>Marche Sahm</t>
+  </si>
+  <si>
+    <t>MATAR LY</t>
+  </si>
+  <si>
+    <t>Mohamed Ndiaye</t>
+  </si>
+  <si>
+    <t>Modou GUEYE</t>
+  </si>
+  <si>
+    <t>Ibrahima</t>
+  </si>
+  <si>
+    <t>Cafe au Lait 3-en-1</t>
+  </si>
+  <si>
+    <t>Jus Lido</t>
+  </si>
+  <si>
+    <t>Liberté 1 à 6</t>
+  </si>
+  <si>
+    <t>Makhtar</t>
+  </si>
+  <si>
+    <t>Ndioguou</t>
+  </si>
+  <si>
+    <t>Chocolat jaune 200g x 24 pcs</t>
+  </si>
+  <si>
+    <t>Assane Wade</t>
+  </si>
+  <si>
+    <t>Zone de captage</t>
+  </si>
+  <si>
+    <t>Mamadou Diallo</t>
+  </si>
+  <si>
+    <t>AISSATOU SALL</t>
+  </si>
+  <si>
+    <t>CHERIF DIALLO</t>
+  </si>
+  <si>
+    <t>NDEYE MARÉME DIOP</t>
+  </si>
+  <si>
+    <t>Abdou Gueye</t>
+  </si>
+  <si>
+    <t>Yeumbeul Tally Diallo</t>
+  </si>
+  <si>
+    <t>ABLAYE DIALLO</t>
+  </si>
+  <si>
+    <t>Yeumbeul Mbéde Sass</t>
+  </si>
+  <si>
+    <t>PAPE DIOP</t>
+  </si>
+  <si>
+    <t>MOUHAMED DAYEL</t>
+  </si>
+  <si>
+    <t>Tournal Yeumbeul</t>
+  </si>
+  <si>
+    <t>ALPHA DIALLO</t>
+  </si>
+  <si>
+    <t>SEYNABOU BA</t>
+  </si>
+  <si>
+    <t>Stapro.com SARL n1</t>
+  </si>
+  <si>
+    <t>Il demande de diminuer le prix du produit</t>
+  </si>
+  <si>
+    <t>Keur Mbaye Fall</t>
+  </si>
+  <si>
+    <t>Bargny</t>
+  </si>
+  <si>
+    <t>Wakeur Alpha Thiombane</t>
+  </si>
+  <si>
+    <t>Il apprécie le produit</t>
+  </si>
+  <si>
+    <t>Diamaguene</t>
+  </si>
+  <si>
+    <t>Korka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demain stp </t>
+  </si>
+  <si>
+    <t>Guinaw Rail</t>
+  </si>
+  <si>
+    <t>Khadime FALL</t>
+  </si>
+  <si>
+    <t>Café stick Altimo 1,5gx09boites</t>
+  </si>
+  <si>
+    <t>Amadou</t>
+  </si>
+  <si>
+    <t>Alimentation</t>
+  </si>
+  <si>
+    <t>Merci beaucoup</t>
+  </si>
+  <si>
+    <t>Kamlac Junior mais cereal 50g x 10 x 8 sachet</t>
+  </si>
+  <si>
+    <t>Baye Diouf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je vais essayer avec </t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Supermarché</t>
+  </si>
+  <si>
+    <t>Mouhamed Diallo</t>
+  </si>
+  <si>
+    <t>MOUSTAPHA DIALLO</t>
+  </si>
+  <si>
+    <t>SEYDOU TALL</t>
+  </si>
+  <si>
+    <t>Modou boye</t>
+  </si>
+  <si>
+    <t>Baye Modou</t>
+  </si>
+  <si>
+    <t>Djily</t>
+  </si>
+  <si>
+    <t>Il apprécie la promotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livraison </t>
+  </si>
+  <si>
+    <t>Terminus 54</t>
+  </si>
+  <si>
+    <t>Idrissa</t>
+  </si>
+  <si>
+    <t>RAS</t>
+  </si>
+  <si>
+    <t>Yéne</t>
+  </si>
+  <si>
+    <t>Il n'achète plus notre café stick il dit que c'est chère</t>
+  </si>
+  <si>
+    <t>Abdoulakhate SAMB</t>
+  </si>
+  <si>
+    <t>Il n'avait plus de stock</t>
+  </si>
+  <si>
+    <t>Médina</t>
+  </si>
+  <si>
+    <t>Samba</t>
+  </si>
+  <si>
+    <t>Amadou BAH</t>
+  </si>
+  <si>
+    <t>Keur Massar Gouygui</t>
+  </si>
+  <si>
+    <t>Groupe Agricole commercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dit qu'il veut le lait évaporé kamlac mais la date est proche </t>
+  </si>
+  <si>
+    <t>Mouhamed CISSE</t>
+  </si>
+  <si>
+    <t>Il demande d'être remboursé pour le café stick altimo qu'il avait acheté à 30000</t>
+  </si>
+  <si>
+    <t>Tivaouane Peulh</t>
+  </si>
+  <si>
+    <t>El Hadj Cissé</t>
+  </si>
+  <si>
+    <t>Ras</t>
+  </si>
+  <si>
+    <t>CPm</t>
+  </si>
+  <si>
+    <t>Kosso</t>
+  </si>
+  <si>
+    <t>Bass</t>
+  </si>
+  <si>
+    <t>Il veut essayer le produit</t>
   </si>
 </sst>
 </file>
@@ -365,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -386,12 +629,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -404,41 +655,15 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <font>
-        <color auto="1"/>
-        <name val="TIMES"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-        <name val="TIMES"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -578,6 +803,21 @@
         <name val="TIMES"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+        <name val="TIMES"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -649,6 +889,21 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+        <name val="TIMES"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
@@ -709,27 +964,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P25" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P25" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P85" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P85" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{72E50CE0-52B1-4C49-9D23-C97154D649A5}" name="zone" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{E26577ED-9647-48EE-BE53-9D2F344CB36B}" name="secteur" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{43164A48-AFB0-417D-94C4-5347A67ACD14}" name="Nom_du_magasin" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{66D926A0-8C65-4D89-BA92-AA9653C7DE06}" name="Telephone_Client" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{8D4D921E-310A-44FC-AA1D-F30B627C5984}" name="Type" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{636AF8A9-C9D0-49B6-94C8-FFB87B44FA47}" name="Point_de_Vente" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{35E41B20-D7EB-4025-A9CC-62B85956ABCD}" name="Operation" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{AB905DE1-CC5E-4C11-8318-9C04B6D96EC3}" name="Commentaire" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{9BC88C3B-EEBD-4156-81CB-075746F3F057}" name="Produit" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{8DD706C4-BCF7-47C0-9913-F482F7A2F321}" name="Quantites" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{D96EE09E-B22B-4D75-AABE-AEBF7CE286A6}" name="Prix_Unitaire" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{B1727D51-96B6-4015-83C5-EBCAD96E9834}" name="Prix Total" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{72E50CE0-52B1-4C49-9D23-C97154D649A5}" name="zone" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{E26577ED-9647-48EE-BE53-9D2F344CB36B}" name="secteur" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{43164A48-AFB0-417D-94C4-5347A67ACD14}" name="Nom_du_magasin" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{66D926A0-8C65-4D89-BA92-AA9653C7DE06}" name="Telephone_Client" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{8D4D921E-310A-44FC-AA1D-F30B627C5984}" name="Type" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{636AF8A9-C9D0-49B6-94C8-FFB87B44FA47}" name="Point_de_Vente" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{35E41B20-D7EB-4025-A9CC-62B85956ABCD}" name="Operation" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{AB905DE1-CC5E-4C11-8318-9C04B6D96EC3}" name="Commentaire" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{9BC88C3B-EEBD-4156-81CB-075746F3F057}" name="Produit" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{8DD706C4-BCF7-47C0-9913-F482F7A2F321}" name="Quantites" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{D96EE09E-B22B-4D75-AABE-AEBF7CE286A6}" name="Prix_Unitaire" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{B1727D51-96B6-4015-83C5-EBCAD96E9834}" name="Prix Total" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{9A2C6D78-CE06-4E13-B8E1-0CB92B201156}" name="Semaine" dataDxfId="1">
       <calculatedColumnFormula>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="2">
+    <tableColumn id="18" xr3:uid="{83F3E9A5-7911-47C6-B543-07173CE7D4B5}" name="Mois" dataDxfId="0">
       <calculatedColumnFormula>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1023,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -1094,7 +1349,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A2" s="10">
+      <c r="A2" s="8">
         <v>46180</v>
       </c>
       <c r="B2" t="s">
@@ -1109,7 +1364,7 @@
       <c r="E2" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="9">
         <v>763198632</v>
       </c>
       <c r="G2" t="s">
@@ -1136,17 +1391,17 @@
       <c r="N2">
         <v>53000</v>
       </c>
-      <c r="O2" s="8" t="str">
+      <c r="O2" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P2" s="9" t="str">
+      <c r="P2" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A3" s="10">
+      <c r="A3" s="8">
         <v>46180</v>
       </c>
       <c r="B3" t="s">
@@ -1161,7 +1416,7 @@
       <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <v>776327767</v>
       </c>
       <c r="G3" t="s">
@@ -1188,17 +1443,17 @@
       <c r="N3">
         <v>650000</v>
       </c>
-      <c r="O3" s="8" t="str">
+      <c r="O3" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P3" s="9" t="str">
+      <c r="P3" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A4" s="10">
+      <c r="A4" s="8">
         <v>46180</v>
       </c>
       <c r="B4" t="s">
@@ -1213,7 +1468,7 @@
       <c r="E4" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>776528748</v>
       </c>
       <c r="G4" t="s">
@@ -1240,17 +1495,17 @@
       <c r="N4">
         <v>650000</v>
       </c>
-      <c r="O4" s="8" t="str">
+      <c r="O4" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P4" s="9" t="str">
+      <c r="P4" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A5" s="10">
+      <c r="A5" s="8">
         <v>46180</v>
       </c>
       <c r="B5" t="s">
@@ -1265,7 +1520,7 @@
       <c r="E5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <v>766919353</v>
       </c>
       <c r="G5" t="s">
@@ -1292,17 +1547,17 @@
       <c r="N5">
         <v>135000</v>
       </c>
-      <c r="O5" s="8" t="str">
+      <c r="O5" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P5" s="9" t="str">
+      <c r="P5" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A6" s="10">
+      <c r="A6" s="8">
         <v>46180</v>
       </c>
       <c r="B6" t="s">
@@ -1317,7 +1572,7 @@
       <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <v>779235028</v>
       </c>
       <c r="G6" t="s">
@@ -1344,999 +1599,4119 @@
       <c r="N6">
         <v>270000</v>
       </c>
-      <c r="O6" s="8" t="str">
+      <c r="O6" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P6" s="9" t="str">
+      <c r="P6" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>46179</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <v>764924460</v>
       </c>
-      <c r="G7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="13" t="s">
+      <c r="G7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="11">
         <v>1</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="13">
         <v>33500</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="13">
         <v>33500</v>
       </c>
-      <c r="O7" s="8" t="str">
+      <c r="O7" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P7" s="9" t="str">
+      <c r="P7" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>46179</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <v>776874747</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="13" t="s">
+      <c r="G8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="11">
         <v>25</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="13">
         <v>26000</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="13">
         <v>650000</v>
       </c>
-      <c r="O8" s="8" t="str">
+      <c r="O8" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P8" s="9" t="str">
+      <c r="P8" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>46178</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>784464768</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="13" t="s">
+      <c r="G9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="11">
         <v>100</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="13">
         <v>26000</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="13">
         <v>2600000</v>
       </c>
-      <c r="O9" s="8" t="str">
+      <c r="O9" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P9" s="9" t="str">
+      <c r="P9" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>46177</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <v>774333344</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="13" t="s">
+      <c r="G10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="11">
         <v>30</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="13">
         <v>9000</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="13">
         <v>270000</v>
       </c>
-      <c r="O10" s="8" t="str">
+      <c r="O10" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P10" s="9" t="str">
+      <c r="P10" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>46177</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="12">
         <v>775586819</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="13" t="s">
+      <c r="H11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="11">
         <v>25</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="13">
         <v>26000</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="13">
         <v>650000</v>
       </c>
-      <c r="O11" s="8" t="str">
+      <c r="O11" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P11" s="9" t="str">
+      <c r="P11" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>46177</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="12">
         <v>776180875</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="13" t="s">
+      <c r="G12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="11">
         <v>25</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="13">
         <v>26000</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="13">
         <v>650000</v>
       </c>
-      <c r="O12" s="8" t="str">
+      <c r="O12" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P12" s="9" t="str">
+      <c r="P12" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>46177</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>776149093</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="13" t="s">
+      <c r="H13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="11">
         <v>25</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="13">
         <v>6000</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="13">
         <v>150000</v>
       </c>
-      <c r="O13" s="8" t="str">
+      <c r="O13" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P13" s="9" t="str">
+      <c r="P13" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A14" s="12">
+      <c r="A14" s="10">
         <v>46176</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="12">
         <v>775894235</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="13" t="s">
+      <c r="G14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="11">
         <v>3</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="13">
         <v>15000</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="13">
         <v>45000</v>
       </c>
-      <c r="O14" s="8" t="str">
+      <c r="O14" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P14" s="9" t="str">
+      <c r="P14" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>46176</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="12">
         <v>776885310</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="13" t="s">
+      <c r="G15" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="11">
         <v>25</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="13">
         <v>26000</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="13">
         <v>650000</v>
       </c>
-      <c r="O15" s="8" t="str">
+      <c r="O15" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P15" s="9" t="str">
+      <c r="P15" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A16" s="12">
+      <c r="A16" s="10">
         <v>46176</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <v>773128315</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="13" t="s">
+      <c r="H16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="11">
         <v>25</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="13">
         <v>5750</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="13">
         <v>143750</v>
       </c>
-      <c r="O16" s="8" t="str">
+      <c r="O16" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P16" s="9" t="str">
+      <c r="P16" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>46176</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="12">
         <v>770242093</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="13" t="s">
+      <c r="G17" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="11">
         <v>10</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="13">
         <v>26000</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="13">
         <v>260000</v>
       </c>
-      <c r="O17" s="8" t="str">
+      <c r="O17" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P17" s="9" t="str">
+      <c r="P17" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A18" s="12">
+      <c r="A18" s="10">
         <v>46176</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="12">
         <v>774216341</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="13" t="s">
+      <c r="G18" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="13">
-        <v>15</v>
-      </c>
-      <c r="M18" s="15">
+      <c r="L18" s="11">
+        <v>15</v>
+      </c>
+      <c r="M18" s="13">
         <v>26000</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="13">
         <v>390000</v>
       </c>
-      <c r="O18" s="8" t="str">
+      <c r="O18" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P18" s="9" t="str">
+      <c r="P18" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>46176</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="12">
         <v>776862787</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="13" t="s">
+      <c r="I19" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="11">
         <v>5</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="13">
         <v>19500</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="13">
         <v>97500</v>
       </c>
-      <c r="O19" s="8" t="str">
+      <c r="O19" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P19" s="9" t="str">
+      <c r="P19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A20" s="12">
+      <c r="A20" s="10">
         <v>46175</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <v>775544532</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="13" t="s">
+      <c r="H20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="11">
         <v>100</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="13">
         <v>26000</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="13">
         <v>2600000</v>
       </c>
-      <c r="O20" s="8" t="str">
+      <c r="O20" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P20" s="9" t="str">
+      <c r="P20" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>46177</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <v>775740574</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="13" t="s">
+      <c r="G21" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="11">
         <v>100</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="13">
         <v>9000</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21" s="13">
         <v>900000</v>
       </c>
-      <c r="O21" s="8" t="str">
+      <c r="O21" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P21" s="9" t="str">
+      <c r="P21" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A22" s="12">
+      <c r="A22" s="10">
         <v>46177</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="12">
         <v>776227120</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="13" t="s">
+      <c r="G22" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="13">
-        <v>15</v>
-      </c>
-      <c r="M22" s="15">
+      <c r="L22" s="11">
+        <v>15</v>
+      </c>
+      <c r="M22" s="13">
         <v>26000</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="13">
         <v>390000</v>
       </c>
-      <c r="O22" s="8" t="str">
+      <c r="O22" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P22" s="9" t="str">
+      <c r="P22" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>46177</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="12">
         <v>776328716</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="G23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="K23" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="11">
         <v>25</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="13">
         <v>26000</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="13">
         <v>650000</v>
       </c>
-      <c r="O23" s="8" t="str">
+      <c r="O23" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P23" s="9" t="str">
+      <c r="P23" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A24" s="12">
+      <c r="A24" s="10">
         <v>46177</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="12">
         <v>774624747</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="13" t="s">
+      <c r="G24" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="11">
         <v>10</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24" s="13">
         <v>26000</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="13">
         <v>260000</v>
       </c>
-      <c r="O24" s="8" t="str">
+      <c r="O24" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P24" s="9" t="str">
+      <c r="P24" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A25" s="12">
+      <c r="A25" s="10">
         <v>46177</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="12">
         <v>774624747</v>
       </c>
-      <c r="G25" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="13" t="s">
+      <c r="G25" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K25" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="13">
-        <v>15</v>
-      </c>
-      <c r="M25" s="15">
+      <c r="L25" s="11">
+        <v>15</v>
+      </c>
+      <c r="M25" s="13">
         <v>9000</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="13">
         <v>135000</v>
       </c>
-      <c r="O25" s="8" t="str">
+      <c r="O25" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S23</v>
       </c>
-      <c r="P25" s="9" t="str">
+      <c r="P25" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A26" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="16">
+        <v>777854561</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L26" s="15">
+        <v>17</v>
+      </c>
+      <c r="M26" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N26" s="17">
+        <v>153000</v>
+      </c>
+      <c r="O26" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P26" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A27" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" s="16">
+        <v>774580822</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="15">
+        <v>25</v>
+      </c>
+      <c r="M27" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N27" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O27" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P27" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A28" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="16">
+        <v>773531341</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="15">
+        <v>100</v>
+      </c>
+      <c r="M28" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N28" s="17">
+        <v>2600000</v>
+      </c>
+      <c r="O28" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P28" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A29" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="16">
+        <v>773178746</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L29" s="15">
+        <v>13</v>
+      </c>
+      <c r="M29" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N29" s="17">
+        <v>344500</v>
+      </c>
+      <c r="O29" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P29" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A30" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="16">
+        <v>771495907</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L30" s="15">
+        <v>13</v>
+      </c>
+      <c r="M30" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N30" s="17">
+        <v>344500</v>
+      </c>
+      <c r="O30" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P30" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A31" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="16">
+        <v>774091250</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L31" s="15">
+        <v>1</v>
+      </c>
+      <c r="M31" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N31" s="17">
+        <v>26500</v>
+      </c>
+      <c r="O31" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P31" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A32" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="16">
+        <v>777854561</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L32" s="15">
+        <v>1</v>
+      </c>
+      <c r="M32" s="17">
+        <v>4500</v>
+      </c>
+      <c r="N32" s="17">
+        <v>4500</v>
+      </c>
+      <c r="O32" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P32" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A33" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F33" s="16">
+        <v>777854561</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L33" s="15">
+        <v>10</v>
+      </c>
+      <c r="M33" s="17">
+        <v>11000</v>
+      </c>
+      <c r="N33" s="17">
+        <v>110000</v>
+      </c>
+      <c r="O33" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P33" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A34" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="16">
+        <v>771078008</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L34" s="15">
+        <v>10</v>
+      </c>
+      <c r="M34" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N34" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O34" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P34" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A35" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" s="16">
+        <v>776634479</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L35" s="15">
+        <v>3</v>
+      </c>
+      <c r="M35" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N35" s="17">
+        <v>58500</v>
+      </c>
+      <c r="O35" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P35" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A36" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="16">
+        <v>776634479</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L36" s="15">
+        <v>1</v>
+      </c>
+      <c r="M36" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N36" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O36" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P36" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A37" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="16">
+        <v>775884054</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L37" s="15">
+        <v>2</v>
+      </c>
+      <c r="M37" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N37" s="17">
+        <v>39000</v>
+      </c>
+      <c r="O37" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P37" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A38" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="16">
+        <v>781681995</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L38" s="15">
+        <v>1</v>
+      </c>
+      <c r="M38" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N38" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O38" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P38" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A39" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="16">
+        <v>781681995</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L39" s="15">
+        <v>1</v>
+      </c>
+      <c r="M39" s="17">
+        <v>4500</v>
+      </c>
+      <c r="N39" s="17">
+        <v>4500</v>
+      </c>
+      <c r="O39" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P39" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A40" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="16">
+        <v>776428218</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="15">
+        <v>25</v>
+      </c>
+      <c r="M40" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N40" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O40" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P40" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A41" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="16">
+        <v>774245132</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="15">
+        <v>50</v>
+      </c>
+      <c r="M41" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N41" s="17">
+        <v>1300000</v>
+      </c>
+      <c r="O41" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P41" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A42" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" s="16">
+        <v>775541532</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42" s="15">
+        <v>25</v>
+      </c>
+      <c r="M42" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N42" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O42" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P42" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A43" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="16">
+        <v>771207041</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L43" s="15">
+        <v>25</v>
+      </c>
+      <c r="M43" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N43" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O43" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P43" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A44" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="16">
+        <v>778056161</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L44" s="15">
+        <v>25</v>
+      </c>
+      <c r="M44" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N44" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O44" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P44" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A45" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F45" s="16">
+        <v>775213948</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L45" s="15">
+        <v>25</v>
+      </c>
+      <c r="M45" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N45" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O45" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P45" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A46" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46" s="16">
+        <v>775411094</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L46" s="15">
+        <v>50</v>
+      </c>
+      <c r="M46" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N46" s="17">
+        <v>1300000</v>
+      </c>
+      <c r="O46" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P46" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A47" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="16">
+        <v>773531341</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L47" s="15">
+        <v>100</v>
+      </c>
+      <c r="M47" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N47" s="17">
+        <v>2600000</v>
+      </c>
+      <c r="O47" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P47" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A48" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F48" s="16">
+        <v>773340367</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L48" s="15">
+        <v>10</v>
+      </c>
+      <c r="M48" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N48" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O48" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P48" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A49" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" s="16">
+        <v>773340367</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L49" s="15">
+        <v>10</v>
+      </c>
+      <c r="M49" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N49" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O49" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P49" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A50" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F50" s="16">
+        <v>779420909</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L50" s="15">
+        <v>10</v>
+      </c>
+      <c r="M50" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N50" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O50" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P50" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A51" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F51" s="16">
+        <v>770712599</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L51" s="15">
+        <v>100</v>
+      </c>
+      <c r="M51" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N51" s="17">
+        <v>2600000</v>
+      </c>
+      <c r="O51" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P51" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A52" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F52" s="16">
+        <v>772403781</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="15">
+        <v>25</v>
+      </c>
+      <c r="M52" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N52" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O52" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P52" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A53" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" s="16">
+        <v>783758073</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L53" s="15">
+        <v>25</v>
+      </c>
+      <c r="M53" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N53" s="17">
+        <v>487500</v>
+      </c>
+      <c r="O53" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P53" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A54" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" s="16">
+        <v>772131614</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L54" s="15">
+        <v>10</v>
+      </c>
+      <c r="M54" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N54" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O54" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P54" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A55" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55" s="16">
+        <v>771952687</v>
+      </c>
+      <c r="G55" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L55" s="15">
+        <v>100</v>
+      </c>
+      <c r="M55" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N55" s="17">
+        <v>2800000</v>
+      </c>
+      <c r="O55" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P55" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A56" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F56" s="16">
+        <v>783844775</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I56" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L56" s="15">
+        <v>1</v>
+      </c>
+      <c r="M56" s="17">
+        <v>15000</v>
+      </c>
+      <c r="N56" s="17">
+        <v>15000</v>
+      </c>
+      <c r="O56" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P56" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A57" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F57" s="16">
+        <v>783844997</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L57" s="15">
+        <v>1</v>
+      </c>
+      <c r="M57" s="17">
+        <v>15000</v>
+      </c>
+      <c r="N57" s="17">
+        <v>15000</v>
+      </c>
+      <c r="O57" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P57" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A58" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" s="16">
+        <v>778420348</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L58" s="15">
+        <v>1</v>
+      </c>
+      <c r="M58" s="17">
+        <v>15000</v>
+      </c>
+      <c r="N58" s="17">
+        <v>15000</v>
+      </c>
+      <c r="O58" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P58" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A59" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F59" s="16">
+        <v>783844775</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L59" s="15">
+        <v>1</v>
+      </c>
+      <c r="M59" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N59" s="17">
+        <v>26500</v>
+      </c>
+      <c r="O59" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P59" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A60" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F60" s="16">
+        <v>783740441</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L60" s="15">
+        <v>10</v>
+      </c>
+      <c r="M60" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N60" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O60" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P60" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A61" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F61" s="16">
+        <v>775411094</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61" s="15">
+        <v>100</v>
+      </c>
+      <c r="M61" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N61" s="17">
+        <v>900000</v>
+      </c>
+      <c r="O61" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P61" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A62" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="16">
+        <v>784537895</v>
+      </c>
+      <c r="G62" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L62" s="15">
+        <v>25</v>
+      </c>
+      <c r="M62" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N62" s="17">
+        <v>487500</v>
+      </c>
+      <c r="O62" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P62" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A63" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F63" s="16">
+        <v>786323232</v>
+      </c>
+      <c r="G63" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L63" s="15">
+        <v>20</v>
+      </c>
+      <c r="M63" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N63" s="17">
+        <v>180000</v>
+      </c>
+      <c r="O63" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P63" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A64" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="16">
+        <v>767379110</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64" s="15">
+        <v>25</v>
+      </c>
+      <c r="M64" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N64" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O64" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P64" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A65" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F65" s="16">
+        <v>760169386</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65" s="15">
+        <v>25</v>
+      </c>
+      <c r="M65" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N65" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O65" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P65" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A66" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" s="16">
+        <v>776677566</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="15">
+        <v>100</v>
+      </c>
+      <c r="M66" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N66" s="17">
+        <v>2600000</v>
+      </c>
+      <c r="O66" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P66" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A67" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F67" s="16">
+        <v>779865100</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L67" s="15">
+        <v>2</v>
+      </c>
+      <c r="M67" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N67" s="17">
+        <v>56000</v>
+      </c>
+      <c r="O67" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P67" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A68" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F68" s="16">
+        <v>779865100</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L68" s="15">
+        <v>25</v>
+      </c>
+      <c r="M68" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N68" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O68" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P68" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A69" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F69" s="16">
+        <v>776194586</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L69" s="15">
+        <v>25</v>
+      </c>
+      <c r="M69" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N69" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O69" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P69" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A70" s="14">
+        <v>46183</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F70" s="16">
+        <v>760169386</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L70" s="15">
+        <v>25</v>
+      </c>
+      <c r="M70" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N70" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O70" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P70" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A71" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F71" s="16">
+        <v>772990477</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L71" s="15">
+        <v>25</v>
+      </c>
+      <c r="M71" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N71" s="17">
+        <v>700000</v>
+      </c>
+      <c r="O71" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P71" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A72" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F72" s="16">
+        <v>772990477</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L72" s="15">
+        <v>25</v>
+      </c>
+      <c r="M72" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N72" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O72" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P72" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A73" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F73" s="16">
+        <v>775742357</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K73" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L73" s="15">
+        <v>25</v>
+      </c>
+      <c r="M73" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N73" s="17">
+        <v>487500</v>
+      </c>
+      <c r="O73" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P73" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A74" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F74" s="16">
+        <v>775742357</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K74" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L74" s="15">
+        <v>1</v>
+      </c>
+      <c r="M74" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N74" s="17">
+        <v>28000</v>
+      </c>
+      <c r="O74" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P74" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A75" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F75" s="16">
+        <v>775742357</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="L75" s="15">
+        <v>2</v>
+      </c>
+      <c r="M75" s="17">
+        <v>33500</v>
+      </c>
+      <c r="N75" s="17">
+        <v>67000</v>
+      </c>
+      <c r="O75" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P75" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A76" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F76" s="16">
+        <v>776750178</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L76" s="15">
+        <v>10</v>
+      </c>
+      <c r="M76" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N76" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O76" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P76" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A77" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="16">
+        <v>776750178</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L77" s="15">
+        <v>15</v>
+      </c>
+      <c r="M77" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N77" s="17">
+        <v>135000</v>
+      </c>
+      <c r="O77" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P77" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A78" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F78" s="16">
+        <v>778823579</v>
+      </c>
+      <c r="G78" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="K78" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L78" s="15">
+        <v>10</v>
+      </c>
+      <c r="M78" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N78" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O78" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P78" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A79" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F79" s="16">
+        <v>788217757</v>
+      </c>
+      <c r="G79" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L79" s="15">
+        <v>25</v>
+      </c>
+      <c r="M79" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N79" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O79" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P79" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A80" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F80" s="16">
+        <v>776294949</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L80" s="15">
+        <v>65</v>
+      </c>
+      <c r="M80" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N80" s="17">
+        <v>585000</v>
+      </c>
+      <c r="O80" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P80" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A81" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" s="16">
+        <v>776294949</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L81" s="15">
+        <v>35</v>
+      </c>
+      <c r="M81" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N81" s="17">
+        <v>315000</v>
+      </c>
+      <c r="O81" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P81" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A82" s="14">
+        <v>46181</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F82" s="16">
+        <v>778003741</v>
+      </c>
+      <c r="G82" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K82" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L82" s="15">
+        <v>5</v>
+      </c>
+      <c r="M82" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N82" s="17">
+        <v>132500</v>
+      </c>
+      <c r="O82" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P82" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A83" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F83" s="16">
+        <v>766923118</v>
+      </c>
+      <c r="G83" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L83" s="15">
+        <v>10</v>
+      </c>
+      <c r="M83" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N83" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O83" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P83" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A84" s="14">
+        <v>46184</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F84" s="16">
+        <v>766923118</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L84" s="15">
+        <v>15</v>
+      </c>
+      <c r="M84" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N84" s="17">
+        <v>135000</v>
+      </c>
+      <c r="O84" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P84" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A85" s="14">
+        <v>46182</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F85" s="16">
+        <v>767267003</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L85" s="15">
+        <v>25</v>
+      </c>
+      <c r="M85" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N85" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O85" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P85" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD31C0F-4962-467B-8671-02F962290976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01DB893-53F7-4F0F-A43D-C867BF8FB14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -2943,13 +2943,13 @@
         <v>98</v>
       </c>
       <c r="L32" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M32" s="17">
         <v>4500</v>
       </c>
       <c r="N32" s="17">
-        <v>4500</v>
+        <v>27000</v>
       </c>
       <c r="O32" s="18" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01DB893-53F7-4F0F-A43D-C867BF8FB14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F80A980-A248-4D47-979B-1910FBE71F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="173">
   <si>
     <t>Date</t>
   </si>
@@ -541,6 +541,18 @@
   </si>
   <si>
     <t>Il veut essayer le produit</t>
+  </si>
+  <si>
+    <t>Yarakh</t>
+  </si>
+  <si>
+    <t>Tonton  Bathie (Kappa)</t>
+  </si>
+  <si>
+    <t>Grand Boutique</t>
+  </si>
+  <si>
+    <t>Meadow Cup sac 25kg</t>
   </si>
 </sst>
 </file>
@@ -964,8 +976,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P85" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P85" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P86" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P86" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1278,7 +1290,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -2597,3121 +2609,3173 @@
       </c>
     </row>
     <row r="26" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A26" s="14">
+      <c r="A26" s="10">
         <v>46185</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="12">
         <v>777854561</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I26" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="15" t="s">
+      <c r="I26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K26" s="15" t="s">
+      <c r="K26" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="11">
         <v>17</v>
       </c>
-      <c r="M26" s="17">
+      <c r="M26" s="13">
         <v>9000</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="13">
         <v>153000</v>
       </c>
-      <c r="O26" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P26" s="19" t="str">
+      <c r="O26" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P26" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A27" s="14">
+      <c r="A27" s="10">
         <v>46185</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="12">
         <v>774580822</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="15" t="s">
+      <c r="G27" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="11">
         <v>25</v>
       </c>
-      <c r="M27" s="17">
+      <c r="M27" s="13">
         <v>9000</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="13">
         <v>225000</v>
       </c>
-      <c r="O27" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P27" s="19" t="str">
+      <c r="O27" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P27" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A28" s="14">
+      <c r="A28" s="10">
         <v>46185</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="12">
         <v>773531341</v>
       </c>
-      <c r="G28" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="15" t="s">
+      <c r="G28" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="11">
         <v>100</v>
       </c>
-      <c r="M28" s="17">
+      <c r="M28" s="13">
         <v>26000</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="13">
         <v>2600000</v>
       </c>
-      <c r="O28" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P28" s="19" t="str">
+      <c r="O28" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P28" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A29" s="14">
+      <c r="A29" s="10">
         <v>46185</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="12">
         <v>773178746</v>
       </c>
-      <c r="G29" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="15" t="s">
+      <c r="G29" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L29" s="15">
-        <v>13</v>
-      </c>
-      <c r="M29" s="17">
+      <c r="L29" s="11">
+        <v>13</v>
+      </c>
+      <c r="M29" s="13">
         <v>26500</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="13">
         <v>344500</v>
       </c>
-      <c r="O29" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P29" s="19" t="str">
+      <c r="O29" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P29" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A30" s="14">
+      <c r="A30" s="10">
         <v>46185</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="12">
         <v>771495907</v>
       </c>
-      <c r="G30" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="15" t="s">
+      <c r="G30" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I30" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="15" t="s">
+      <c r="I30" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="15" t="s">
+      <c r="K30" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L30" s="15">
-        <v>13</v>
-      </c>
-      <c r="M30" s="17">
+      <c r="L30" s="11">
+        <v>13</v>
+      </c>
+      <c r="M30" s="13">
         <v>26500</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="13">
         <v>344500</v>
       </c>
-      <c r="O30" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P30" s="19" t="str">
+      <c r="O30" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P30" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A31" s="14">
+      <c r="A31" s="10">
         <v>46185</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="12">
         <v>774091250</v>
       </c>
-      <c r="G31" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" s="15" t="s">
+      <c r="G31" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="15" t="s">
+      <c r="I31" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K31" s="15" t="s">
+      <c r="K31" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="11">
         <v>1</v>
       </c>
-      <c r="M31" s="17">
+      <c r="M31" s="13">
         <v>26500</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="13">
         <v>26500</v>
       </c>
-      <c r="O31" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P31" s="19" t="str">
+      <c r="O31" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P31" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A32" s="14">
+      <c r="A32" s="10">
         <v>46185</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="12">
         <v>777854561</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I32" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="15" t="s">
+      <c r="I32" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K32" s="15" t="s">
+      <c r="K32" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="11">
         <v>6</v>
       </c>
-      <c r="M32" s="17">
+      <c r="M32" s="13">
         <v>4500</v>
       </c>
-      <c r="N32" s="17">
+      <c r="N32" s="13">
         <v>27000</v>
       </c>
-      <c r="O32" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P32" s="19" t="str">
+      <c r="O32" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P32" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A33" s="14">
+      <c r="A33" s="10">
         <v>46185</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="12">
         <v>777854561</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="15" t="s">
+      <c r="H33" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="15" t="s">
+      <c r="I33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K33" s="15" t="s">
+      <c r="K33" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="11">
         <v>10</v>
       </c>
-      <c r="M33" s="17">
+      <c r="M33" s="13">
         <v>11000</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="13">
         <v>110000</v>
       </c>
-      <c r="O33" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P33" s="19" t="str">
+      <c r="O33" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P33" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A34" s="14">
+      <c r="A34" s="10">
         <v>46185</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="12">
         <v>771078008</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="15" t="s">
+      <c r="G34" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="15" t="s">
+      <c r="K34" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L34" s="15">
+      <c r="L34" s="11">
         <v>10</v>
       </c>
-      <c r="M34" s="17">
+      <c r="M34" s="13">
         <v>9000</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="13">
         <v>90000</v>
       </c>
-      <c r="O34" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P34" s="19" t="str">
+      <c r="O34" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P34" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A35" s="14">
+      <c r="A35" s="10">
         <v>46185</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="12">
         <v>776634479</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="15" t="s">
+      <c r="G35" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="K35" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L35" s="15">
+      <c r="L35" s="11">
         <v>3</v>
       </c>
-      <c r="M35" s="17">
+      <c r="M35" s="13">
         <v>19500</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="13">
         <v>58500</v>
       </c>
-      <c r="O35" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P35" s="19" t="str">
+      <c r="O35" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P35" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A36" s="14">
+      <c r="A36" s="10">
         <v>46185</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="12">
         <v>776634479</v>
       </c>
-      <c r="G36" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="15" t="s">
+      <c r="G36" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="15" t="s">
+      <c r="K36" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L36" s="15">
+      <c r="L36" s="11">
         <v>1</v>
       </c>
-      <c r="M36" s="17">
+      <c r="M36" s="13">
         <v>15500</v>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="13">
         <v>15500</v>
       </c>
-      <c r="O36" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P36" s="19" t="str">
+      <c r="O36" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P36" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A37" s="14">
+      <c r="A37" s="10">
         <v>46185</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="12">
         <v>775884054</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H37" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="15" t="s">
+      <c r="H37" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="15" t="s">
+      <c r="K37" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L37" s="15">
+      <c r="L37" s="11">
         <v>2</v>
       </c>
-      <c r="M37" s="17">
+      <c r="M37" s="13">
         <v>19500</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="13">
         <v>39000</v>
       </c>
-      <c r="O37" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P37" s="19" t="str">
+      <c r="O37" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P37" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A38" s="14">
+      <c r="A38" s="10">
         <v>46185</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="12">
         <v>781681995</v>
       </c>
-      <c r="G38" s="15" t="s">
+      <c r="G38" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="15" t="s">
+      <c r="H38" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="15" t="s">
+      <c r="K38" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L38" s="15">
+      <c r="L38" s="11">
         <v>1</v>
       </c>
-      <c r="M38" s="17">
+      <c r="M38" s="13">
         <v>15500</v>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="13">
         <v>15500</v>
       </c>
-      <c r="O38" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P38" s="19" t="str">
+      <c r="O38" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P38" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A39" s="14">
+      <c r="A39" s="10">
         <v>46185</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="12">
         <v>781681995</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" s="15" t="s">
+      <c r="H39" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="15" t="s">
+      <c r="K39" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L39" s="15">
+      <c r="L39" s="11">
         <v>1</v>
       </c>
-      <c r="M39" s="17">
+      <c r="M39" s="13">
         <v>4500</v>
       </c>
-      <c r="N39" s="17">
+      <c r="N39" s="13">
         <v>4500</v>
       </c>
-      <c r="O39" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P39" s="19" t="str">
+      <c r="O39" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P39" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A40" s="14">
+      <c r="A40" s="10">
         <v>46184</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="12">
         <v>776428218</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H40" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="15" t="s">
+      <c r="H40" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="15" t="s">
+      <c r="K40" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="11">
         <v>25</v>
       </c>
-      <c r="M40" s="17">
+      <c r="M40" s="13">
         <v>26000</v>
       </c>
-      <c r="N40" s="17">
+      <c r="N40" s="13">
         <v>650000</v>
       </c>
-      <c r="O40" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P40" s="19" t="str">
+      <c r="O40" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P40" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A41" s="14">
+      <c r="A41" s="10">
         <v>46184</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="12">
         <v>774245132</v>
       </c>
-      <c r="G41" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="15" t="s">
+      <c r="G41" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K41" s="15" t="s">
+      <c r="K41" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="11">
         <v>50</v>
       </c>
-      <c r="M41" s="17">
+      <c r="M41" s="13">
         <v>26000</v>
       </c>
-      <c r="N41" s="17">
+      <c r="N41" s="13">
         <v>1300000</v>
       </c>
-      <c r="O41" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P41" s="19" t="str">
+      <c r="O41" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P41" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A42" s="14">
+      <c r="A42" s="10">
         <v>46184</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="12">
         <v>775541532</v>
       </c>
-      <c r="G42" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="15" t="s">
+      <c r="G42" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K42" s="15" t="s">
+      <c r="K42" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="11">
         <v>25</v>
       </c>
-      <c r="M42" s="17">
+      <c r="M42" s="13">
         <v>26000</v>
       </c>
-      <c r="N42" s="17">
+      <c r="N42" s="13">
         <v>650000</v>
       </c>
-      <c r="O42" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P42" s="19" t="str">
+      <c r="O42" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P42" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A43" s="14">
+      <c r="A43" s="10">
         <v>46184</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="12">
         <v>771207041</v>
       </c>
-      <c r="G43" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="15" t="s">
+      <c r="G43" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K43" s="15" t="s">
+      <c r="K43" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="11">
         <v>25</v>
       </c>
-      <c r="M43" s="17">
+      <c r="M43" s="13">
         <v>26000</v>
       </c>
-      <c r="N43" s="17">
+      <c r="N43" s="13">
         <v>650000</v>
       </c>
-      <c r="O43" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P43" s="19" t="str">
+      <c r="O43" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P43" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A44" s="14">
+      <c r="A44" s="10">
         <v>46184</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="12">
         <v>778056161</v>
       </c>
-      <c r="G44" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="15" t="s">
+      <c r="G44" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K44" s="15" t="s">
+      <c r="K44" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="11">
         <v>25</v>
       </c>
-      <c r="M44" s="17">
+      <c r="M44" s="13">
         <v>26000</v>
       </c>
-      <c r="N44" s="17">
+      <c r="N44" s="13">
         <v>650000</v>
       </c>
-      <c r="O44" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P44" s="19" t="str">
+      <c r="O44" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P44" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A45" s="14">
+      <c r="A45" s="10">
         <v>46184</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="12">
         <v>775213948</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="15" t="s">
+      <c r="H45" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K45" s="15" t="s">
+      <c r="K45" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="11">
         <v>25</v>
       </c>
-      <c r="M45" s="17">
+      <c r="M45" s="13">
         <v>26000</v>
       </c>
-      <c r="N45" s="17">
+      <c r="N45" s="13">
         <v>650000</v>
       </c>
-      <c r="O45" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P45" s="19" t="str">
+      <c r="O45" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P45" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A46" s="14">
+      <c r="A46" s="10">
         <v>46183</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="12">
         <v>775411094</v>
       </c>
-      <c r="G46" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="15" t="s">
+      <c r="G46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K46" s="15" t="s">
+      <c r="K46" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="15">
+      <c r="L46" s="11">
         <v>50</v>
       </c>
-      <c r="M46" s="17">
+      <c r="M46" s="13">
         <v>26000</v>
       </c>
-      <c r="N46" s="17">
+      <c r="N46" s="13">
         <v>1300000</v>
       </c>
-      <c r="O46" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P46" s="19" t="str">
+      <c r="O46" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P46" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A47" s="14">
+      <c r="A47" s="10">
         <v>46183</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="12">
         <v>773531341</v>
       </c>
-      <c r="G47" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="15" t="s">
+      <c r="G47" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K47" s="15" t="s">
+      <c r="K47" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L47" s="15">
+      <c r="L47" s="11">
         <v>100</v>
       </c>
-      <c r="M47" s="17">
+      <c r="M47" s="13">
         <v>26000</v>
       </c>
-      <c r="N47" s="17">
+      <c r="N47" s="13">
         <v>2600000</v>
       </c>
-      <c r="O47" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P47" s="19" t="str">
+      <c r="O47" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P47" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A48" s="14">
+      <c r="A48" s="10">
         <v>46183</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="12">
         <v>773340367</v>
       </c>
-      <c r="G48" s="15" t="s">
+      <c r="G48" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H48" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="15" t="s">
+      <c r="H48" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="15" t="s">
+      <c r="K48" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L48" s="15">
+      <c r="L48" s="11">
         <v>10</v>
       </c>
-      <c r="M48" s="17">
+      <c r="M48" s="13">
         <v>9000</v>
       </c>
-      <c r="N48" s="17">
+      <c r="N48" s="13">
         <v>90000</v>
       </c>
-      <c r="O48" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P48" s="19" t="str">
+      <c r="O48" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P48" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A49" s="14">
+      <c r="A49" s="10">
         <v>46183</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="12">
         <v>773340367</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H49" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="15" t="s">
+      <c r="H49" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K49" s="15" t="s">
+      <c r="K49" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L49" s="15">
+      <c r="L49" s="11">
         <v>10</v>
       </c>
-      <c r="M49" s="17">
+      <c r="M49" s="13">
         <v>9000</v>
       </c>
-      <c r="N49" s="17">
+      <c r="N49" s="13">
         <v>90000</v>
       </c>
-      <c r="O49" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P49" s="19" t="str">
+      <c r="O49" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P49" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A50" s="14">
+      <c r="A50" s="10">
         <v>46183</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="12">
         <v>779420909</v>
       </c>
-      <c r="G50" s="15" t="s">
+      <c r="G50" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H50" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" s="15" t="s">
+      <c r="H50" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K50" s="15" t="s">
+      <c r="K50" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L50" s="15">
+      <c r="L50" s="11">
         <v>10</v>
       </c>
-      <c r="M50" s="17">
+      <c r="M50" s="13">
         <v>9000</v>
       </c>
-      <c r="N50" s="17">
+      <c r="N50" s="13">
         <v>90000</v>
       </c>
-      <c r="O50" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P50" s="19" t="str">
+      <c r="O50" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P50" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A51" s="14">
+      <c r="A51" s="10">
         <v>46183</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="12">
         <v>770712599</v>
       </c>
-      <c r="G51" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" s="15" t="s">
+      <c r="G51" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="K51" s="15" t="s">
+      <c r="K51" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L51" s="15">
+      <c r="L51" s="11">
         <v>100</v>
       </c>
-      <c r="M51" s="17">
+      <c r="M51" s="13">
         <v>26000</v>
       </c>
-      <c r="N51" s="17">
+      <c r="N51" s="13">
         <v>2600000</v>
       </c>
-      <c r="O51" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P51" s="19" t="str">
+      <c r="O51" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P51" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A52" s="14">
+      <c r="A52" s="10">
         <v>46183</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="12">
         <v>772403781</v>
       </c>
-      <c r="G52" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" s="15" t="s">
+      <c r="G52" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K52" s="15" t="s">
+      <c r="K52" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L52" s="15">
+      <c r="L52" s="11">
         <v>25</v>
       </c>
-      <c r="M52" s="17">
+      <c r="M52" s="13">
         <v>26000</v>
       </c>
-      <c r="N52" s="17">
+      <c r="N52" s="13">
         <v>650000</v>
       </c>
-      <c r="O52" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P52" s="19" t="str">
+      <c r="O52" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P52" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A53" s="14">
+      <c r="A53" s="10">
         <v>46182</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="12">
         <v>783758073</v>
       </c>
-      <c r="G53" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" s="15" t="s">
+      <c r="G53" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="K53" s="15" t="s">
+      <c r="K53" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L53" s="15">
+      <c r="L53" s="11">
         <v>25</v>
       </c>
-      <c r="M53" s="17">
+      <c r="M53" s="13">
         <v>19500</v>
       </c>
-      <c r="N53" s="17">
+      <c r="N53" s="13">
         <v>487500</v>
       </c>
-      <c r="O53" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P53" s="19" t="str">
+      <c r="O53" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P53" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A54" s="14">
+      <c r="A54" s="10">
         <v>46182</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="12">
         <v>772131614</v>
       </c>
-      <c r="G54" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H54" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I54" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J54" s="15" t="s">
+      <c r="G54" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="K54" s="15" t="s">
+      <c r="K54" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L54" s="15">
+      <c r="L54" s="11">
         <v>10</v>
       </c>
-      <c r="M54" s="17">
+      <c r="M54" s="13">
         <v>9000</v>
       </c>
-      <c r="N54" s="17">
+      <c r="N54" s="13">
         <v>90000</v>
       </c>
-      <c r="O54" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P54" s="19" t="str">
+      <c r="O54" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P54" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A55" s="14">
+      <c r="A55" s="10">
         <v>46182</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="12">
         <v>771952687</v>
       </c>
-      <c r="G55" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I55" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J55" s="15" t="s">
+      <c r="G55" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K55" s="15" t="s">
+      <c r="K55" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L55" s="15">
+      <c r="L55" s="11">
         <v>100</v>
       </c>
-      <c r="M55" s="17">
+      <c r="M55" s="13">
         <v>28000</v>
       </c>
-      <c r="N55" s="17">
+      <c r="N55" s="13">
         <v>2800000</v>
       </c>
-      <c r="O55" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P55" s="19" t="str">
+      <c r="O55" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P55" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A56" s="14">
+      <c r="A56" s="10">
         <v>46182</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="12">
         <v>783844775</v>
       </c>
-      <c r="G56" s="15" t="s">
+      <c r="G56" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="H56" s="15" t="s">
+      <c r="H56" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I56" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J56" s="15" t="s">
+      <c r="I56" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="K56" s="15" t="s">
+      <c r="K56" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="L56" s="15">
+      <c r="L56" s="11">
         <v>1</v>
       </c>
-      <c r="M56" s="17">
+      <c r="M56" s="13">
         <v>15000</v>
       </c>
-      <c r="N56" s="17">
+      <c r="N56" s="13">
         <v>15000</v>
       </c>
-      <c r="O56" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P56" s="19" t="str">
+      <c r="O56" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P56" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A57" s="14">
+      <c r="A57" s="10">
         <v>46182</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="12">
         <v>783844997</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H57" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I57" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J57" s="15" t="s">
+      <c r="H57" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="K57" s="15" t="s">
+      <c r="K57" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="L57" s="15">
+      <c r="L57" s="11">
         <v>1</v>
       </c>
-      <c r="M57" s="17">
+      <c r="M57" s="13">
         <v>15000</v>
       </c>
-      <c r="N57" s="17">
+      <c r="N57" s="13">
         <v>15000</v>
       </c>
-      <c r="O57" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P57" s="19" t="str">
+      <c r="O57" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P57" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A58" s="14">
+      <c r="A58" s="10">
         <v>46182</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="12">
         <v>778420348</v>
       </c>
-      <c r="G58" s="15" t="s">
+      <c r="G58" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="H58" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="15" t="s">
+      <c r="H58" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="15" t="s">
+      <c r="K58" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="L58" s="15">
+      <c r="L58" s="11">
         <v>1</v>
       </c>
-      <c r="M58" s="17">
+      <c r="M58" s="13">
         <v>15000</v>
       </c>
-      <c r="N58" s="17">
+      <c r="N58" s="13">
         <v>15000</v>
       </c>
-      <c r="O58" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P58" s="19" t="str">
+      <c r="O58" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P58" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A59" s="14">
+      <c r="A59" s="10">
         <v>46182</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E59" s="15" t="s">
+      <c r="E59" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="12">
         <v>783844775</v>
       </c>
-      <c r="G59" s="15" t="s">
+      <c r="G59" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="H59" s="15" t="s">
+      <c r="H59" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I59" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="15" t="s">
+      <c r="I59" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="K59" s="15" t="s">
+      <c r="K59" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L59" s="15">
+      <c r="L59" s="11">
         <v>1</v>
       </c>
-      <c r="M59" s="17">
+      <c r="M59" s="13">
         <v>26500</v>
       </c>
-      <c r="N59" s="17">
+      <c r="N59" s="13">
         <v>26500</v>
       </c>
-      <c r="O59" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P59" s="19" t="str">
+      <c r="O59" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P59" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A60" s="14">
+      <c r="A60" s="10">
         <v>46182</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="12">
         <v>783740441</v>
       </c>
-      <c r="G60" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J60" s="15" t="s">
+      <c r="G60" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="15" t="s">
+      <c r="K60" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L60" s="15">
+      <c r="L60" s="11">
         <v>10</v>
       </c>
-      <c r="M60" s="17">
+      <c r="M60" s="13">
         <v>9000</v>
       </c>
-      <c r="N60" s="17">
+      <c r="N60" s="13">
         <v>90000</v>
       </c>
-      <c r="O60" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P60" s="19" t="str">
+      <c r="O60" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P60" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A61" s="14">
+      <c r="A61" s="10">
         <v>46182</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="12">
         <v>775411094</v>
       </c>
-      <c r="G61" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I61" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="15" t="s">
+      <c r="G61" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J61" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K61" s="15" t="s">
+      <c r="K61" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L61" s="15">
+      <c r="L61" s="11">
         <v>100</v>
       </c>
-      <c r="M61" s="17">
+      <c r="M61" s="13">
         <v>9000</v>
       </c>
-      <c r="N61" s="17">
+      <c r="N61" s="13">
         <v>900000</v>
       </c>
-      <c r="O61" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P61" s="19" t="str">
+      <c r="O61" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P61" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A62" s="14">
+      <c r="A62" s="10">
         <v>46182</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D62" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="12">
         <v>784537895</v>
       </c>
-      <c r="G62" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I62" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" s="15" t="s">
+      <c r="G62" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="15" t="s">
+      <c r="K62" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L62" s="15">
+      <c r="L62" s="11">
         <v>25</v>
       </c>
-      <c r="M62" s="17">
+      <c r="M62" s="13">
         <v>19500</v>
       </c>
-      <c r="N62" s="17">
+      <c r="N62" s="13">
         <v>487500</v>
       </c>
-      <c r="O62" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P62" s="19" t="str">
+      <c r="O62" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P62" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A63" s="14">
+      <c r="A63" s="10">
         <v>46182</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="12">
         <v>786323232</v>
       </c>
-      <c r="G63" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I63" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J63" s="15" t="s">
+      <c r="G63" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J63" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K63" s="15" t="s">
+      <c r="K63" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L63" s="15">
+      <c r="L63" s="11">
         <v>20</v>
       </c>
-      <c r="M63" s="17">
+      <c r="M63" s="13">
         <v>9000</v>
       </c>
-      <c r="N63" s="17">
+      <c r="N63" s="13">
         <v>180000</v>
       </c>
-      <c r="O63" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P63" s="19" t="str">
+      <c r="O63" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P63" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A64" s="14">
+      <c r="A64" s="10">
         <v>46181</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="12">
         <v>767379110</v>
       </c>
-      <c r="G64" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H64" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="15" t="s">
+      <c r="G64" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K64" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L64" s="15">
+      <c r="L64" s="11">
         <v>25</v>
       </c>
-      <c r="M64" s="17">
+      <c r="M64" s="13">
         <v>26000</v>
       </c>
-      <c r="N64" s="17">
+      <c r="N64" s="13">
         <v>650000</v>
       </c>
-      <c r="O64" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P64" s="19" t="str">
+      <c r="O64" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P64" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A65" s="14">
+      <c r="A65" s="10">
         <v>46181</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="12">
         <v>760169386</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J65" s="15" t="s">
+      <c r="G65" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K65" s="15" t="s">
+      <c r="K65" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L65" s="15">
+      <c r="L65" s="11">
         <v>25</v>
       </c>
-      <c r="M65" s="17">
+      <c r="M65" s="13">
         <v>9000</v>
       </c>
-      <c r="N65" s="17">
+      <c r="N65" s="13">
         <v>225000</v>
       </c>
-      <c r="O65" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P65" s="19" t="str">
+      <c r="O65" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P65" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A66" s="14">
+      <c r="A66" s="10">
         <v>46181</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="12">
         <v>776677566</v>
       </c>
-      <c r="G66" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H66" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I66" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J66" s="15" t="s">
+      <c r="G66" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="K66" s="15" t="s">
+      <c r="K66" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L66" s="15">
+      <c r="L66" s="11">
         <v>100</v>
       </c>
-      <c r="M66" s="17">
+      <c r="M66" s="13">
         <v>26000</v>
       </c>
-      <c r="N66" s="17">
+      <c r="N66" s="13">
         <v>2600000</v>
       </c>
-      <c r="O66" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P66" s="19" t="str">
+      <c r="O66" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P66" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A67" s="14">
+      <c r="A67" s="10">
         <v>46183</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E67" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="12">
         <v>779865100</v>
       </c>
-      <c r="G67" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I67" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J67" s="15" t="s">
+      <c r="G67" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="K67" s="15" t="s">
+      <c r="K67" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L67" s="15">
+      <c r="L67" s="11">
         <v>2</v>
       </c>
-      <c r="M67" s="17">
+      <c r="M67" s="13">
         <v>28000</v>
       </c>
-      <c r="N67" s="17">
+      <c r="N67" s="13">
         <v>56000</v>
       </c>
-      <c r="O67" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P67" s="19" t="str">
+      <c r="O67" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P67" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A68" s="14">
+      <c r="A68" s="10">
         <v>46183</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E68" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="12">
         <v>779865100</v>
       </c>
-      <c r="G68" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I68" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" s="15" t="s">
+      <c r="G68" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="K68" s="15" t="s">
+      <c r="K68" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L68" s="15">
+      <c r="L68" s="11">
         <v>25</v>
       </c>
-      <c r="M68" s="17">
+      <c r="M68" s="13">
         <v>9000</v>
       </c>
-      <c r="N68" s="17">
+      <c r="N68" s="13">
         <v>225000</v>
       </c>
-      <c r="O68" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P68" s="19" t="str">
+      <c r="O68" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P68" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A69" s="14">
+      <c r="A69" s="10">
         <v>46183</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D69" s="15" t="s">
+      <c r="D69" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E69" s="15" t="s">
+      <c r="E69" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="12">
         <v>776194586</v>
       </c>
-      <c r="G69" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I69" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="15" t="s">
+      <c r="G69" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="K69" s="15" t="s">
+      <c r="K69" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L69" s="15">
+      <c r="L69" s="11">
         <v>25</v>
       </c>
-      <c r="M69" s="17">
+      <c r="M69" s="13">
         <v>9000</v>
       </c>
-      <c r="N69" s="17">
+      <c r="N69" s="13">
         <v>225000</v>
       </c>
-      <c r="O69" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P69" s="19" t="str">
+      <c r="O69" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P69" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A70" s="14">
+      <c r="A70" s="10">
         <v>46183</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="D70" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="12">
         <v>760169386</v>
       </c>
-      <c r="G70" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J70" s="15" t="s">
+      <c r="G70" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J70" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K70" s="15" t="s">
+      <c r="K70" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L70" s="15">
+      <c r="L70" s="11">
         <v>25</v>
       </c>
-      <c r="M70" s="17">
+      <c r="M70" s="13">
         <v>26000</v>
       </c>
-      <c r="N70" s="17">
+      <c r="N70" s="13">
         <v>650000</v>
       </c>
-      <c r="O70" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P70" s="19" t="str">
+      <c r="O70" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P70" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A71" s="14">
+      <c r="A71" s="10">
         <v>46182</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D71" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E71" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="12">
         <v>772990477</v>
       </c>
-      <c r="G71" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="15" t="s">
+      <c r="G71" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="K71" s="15" t="s">
+      <c r="K71" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L71" s="15">
+      <c r="L71" s="11">
         <v>25</v>
       </c>
-      <c r="M71" s="17">
+      <c r="M71" s="13">
         <v>28000</v>
       </c>
-      <c r="N71" s="17">
+      <c r="N71" s="13">
         <v>700000</v>
       </c>
-      <c r="O71" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P71" s="19" t="str">
+      <c r="O71" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P71" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A72" s="14">
+      <c r="A72" s="10">
         <v>46182</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="D72" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="12">
         <v>772990477</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I72" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="15" t="s">
+      <c r="G72" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="K72" s="15" t="s">
+      <c r="K72" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L72" s="15">
+      <c r="L72" s="11">
         <v>25</v>
       </c>
-      <c r="M72" s="17">
+      <c r="M72" s="13">
         <v>26000</v>
       </c>
-      <c r="N72" s="17">
+      <c r="N72" s="13">
         <v>650000</v>
       </c>
-      <c r="O72" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P72" s="19" t="str">
+      <c r="O72" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P72" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A73" s="14">
+      <c r="A73" s="10">
         <v>46182</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="15" t="s">
+      <c r="D73" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="12">
         <v>775742357</v>
       </c>
-      <c r="G73" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I73" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J73" s="15" t="s">
+      <c r="G73" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K73" s="15" t="s">
+      <c r="K73" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L73" s="15">
+      <c r="L73" s="11">
         <v>25</v>
       </c>
-      <c r="M73" s="17">
+      <c r="M73" s="13">
         <v>19500</v>
       </c>
-      <c r="N73" s="17">
+      <c r="N73" s="13">
         <v>487500</v>
       </c>
-      <c r="O73" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P73" s="19" t="str">
+      <c r="O73" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P73" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A74" s="14">
+      <c r="A74" s="10">
         <v>46182</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="12">
         <v>775742357</v>
       </c>
-      <c r="G74" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I74" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="15" t="s">
+      <c r="G74" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I74" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K74" s="15" t="s">
+      <c r="K74" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L74" s="15">
+      <c r="L74" s="11">
         <v>1</v>
       </c>
-      <c r="M74" s="17">
+      <c r="M74" s="13">
         <v>28000</v>
       </c>
-      <c r="N74" s="17">
+      <c r="N74" s="13">
         <v>28000</v>
       </c>
-      <c r="O74" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P74" s="19" t="str">
+      <c r="O74" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P74" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A75" s="14">
+      <c r="A75" s="10">
         <v>46182</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="15" t="s">
+      <c r="D75" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="12">
         <v>775742357</v>
       </c>
-      <c r="G75" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I75" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J75" s="15" t="s">
+      <c r="G75" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K75" s="15" t="s">
+      <c r="K75" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="L75" s="15">
+      <c r="L75" s="11">
         <v>2</v>
       </c>
-      <c r="M75" s="17">
+      <c r="M75" s="13">
         <v>33500</v>
       </c>
-      <c r="N75" s="17">
+      <c r="N75" s="13">
         <v>67000</v>
       </c>
-      <c r="O75" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P75" s="19" t="str">
+      <c r="O75" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P75" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A76" s="14">
+      <c r="A76" s="10">
         <v>46181</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="12">
         <v>776750178</v>
       </c>
-      <c r="G76" s="15" t="s">
+      <c r="G76" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H76" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I76" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J76" s="15" t="s">
+      <c r="H76" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I76" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K76" s="15" t="s">
+      <c r="K76" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L76" s="15">
+      <c r="L76" s="11">
         <v>10</v>
       </c>
-      <c r="M76" s="17">
+      <c r="M76" s="13">
         <v>9000</v>
       </c>
-      <c r="N76" s="17">
+      <c r="N76" s="13">
         <v>90000</v>
       </c>
-      <c r="O76" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P76" s="19" t="str">
+      <c r="O76" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P76" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A77" s="14">
+      <c r="A77" s="10">
         <v>46181</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="E77" s="15" t="s">
+      <c r="E77" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="12">
         <v>776750178</v>
       </c>
-      <c r="G77" s="15" t="s">
+      <c r="G77" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H77" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I77" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" s="15" t="s">
+      <c r="H77" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K77" s="15" t="s">
+      <c r="K77" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L77" s="15">
-        <v>15</v>
-      </c>
-      <c r="M77" s="17">
+      <c r="L77" s="11">
+        <v>15</v>
+      </c>
+      <c r="M77" s="13">
         <v>9000</v>
       </c>
-      <c r="N77" s="17">
+      <c r="N77" s="13">
         <v>135000</v>
       </c>
-      <c r="O77" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P77" s="19" t="str">
+      <c r="O77" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P77" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A78" s="14">
+      <c r="A78" s="10">
         <v>46181</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="15" t="s">
+      <c r="D78" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E78" s="15" t="s">
+      <c r="E78" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="12">
         <v>778823579</v>
       </c>
-      <c r="G78" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I78" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J78" s="15" t="s">
+      <c r="G78" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="K78" s="15" t="s">
+      <c r="K78" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L78" s="15">
+      <c r="L78" s="11">
         <v>10</v>
       </c>
-      <c r="M78" s="17">
+      <c r="M78" s="13">
         <v>9000</v>
       </c>
-      <c r="N78" s="17">
+      <c r="N78" s="13">
         <v>90000</v>
       </c>
-      <c r="O78" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P78" s="19" t="str">
+      <c r="O78" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P78" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A79" s="14">
+      <c r="A79" s="10">
         <v>46181</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D79" s="15" t="s">
+      <c r="D79" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E79" s="15" t="s">
+      <c r="E79" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="12">
         <v>788217757</v>
       </c>
-      <c r="G79" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I79" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J79" s="15" t="s">
+      <c r="G79" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="K79" s="15" t="s">
+      <c r="K79" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L79" s="15">
+      <c r="L79" s="11">
         <v>25</v>
       </c>
-      <c r="M79" s="17">
+      <c r="M79" s="13">
         <v>9000</v>
       </c>
-      <c r="N79" s="17">
+      <c r="N79" s="13">
         <v>225000</v>
       </c>
-      <c r="O79" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P79" s="19" t="str">
+      <c r="O79" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P79" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A80" s="14">
+      <c r="A80" s="10">
         <v>46181</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D80" s="15" t="s">
+      <c r="D80" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E80" s="15" t="s">
+      <c r="E80" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="12">
         <v>776294949</v>
       </c>
-      <c r="G80" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I80" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" s="15" t="s">
+      <c r="G80" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="K80" s="15" t="s">
+      <c r="K80" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L80" s="15">
+      <c r="L80" s="11">
         <v>65</v>
       </c>
-      <c r="M80" s="17">
+      <c r="M80" s="13">
         <v>9000</v>
       </c>
-      <c r="N80" s="17">
+      <c r="N80" s="13">
         <v>585000</v>
       </c>
-      <c r="O80" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P80" s="19" t="str">
+      <c r="O80" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P80" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A81" s="14">
+      <c r="A81" s="10">
         <v>46181</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D81" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E81" s="15" t="s">
+      <c r="E81" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F81" s="16">
+      <c r="F81" s="12">
         <v>776294949</v>
       </c>
-      <c r="G81" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I81" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" s="15" t="s">
+      <c r="G81" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="K81" s="15" t="s">
+      <c r="K81" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L81" s="15">
+      <c r="L81" s="11">
         <v>35</v>
       </c>
-      <c r="M81" s="17">
+      <c r="M81" s="13">
         <v>9000</v>
       </c>
-      <c r="N81" s="17">
+      <c r="N81" s="13">
         <v>315000</v>
       </c>
-      <c r="O81" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P81" s="19" t="str">
+      <c r="O81" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P81" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A82" s="14">
+      <c r="A82" s="10">
         <v>46181</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="12">
         <v>778003741</v>
       </c>
-      <c r="G82" s="15" t="s">
+      <c r="G82" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="H82" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I82" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" s="15" t="s">
+      <c r="H82" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I82" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K82" s="15" t="s">
+      <c r="K82" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L82" s="15">
+      <c r="L82" s="11">
         <v>5</v>
       </c>
-      <c r="M82" s="17">
+      <c r="M82" s="13">
         <v>26500</v>
       </c>
-      <c r="N82" s="17">
+      <c r="N82" s="13">
         <v>132500</v>
       </c>
-      <c r="O82" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P82" s="19" t="str">
+      <c r="O82" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P82" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A83" s="14">
+      <c r="A83" s="10">
         <v>46184</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D83" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E83" s="15" t="s">
+      <c r="E83" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="F83" s="16">
+      <c r="F83" s="12">
         <v>766923118</v>
       </c>
-      <c r="G83" s="15" t="s">
+      <c r="G83" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H83" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I83" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="15" t="s">
+      <c r="H83" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K83" s="15" t="s">
+      <c r="K83" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L83" s="15">
+      <c r="L83" s="11">
         <v>10</v>
       </c>
-      <c r="M83" s="17">
+      <c r="M83" s="13">
         <v>9000</v>
       </c>
-      <c r="N83" s="17">
+      <c r="N83" s="13">
         <v>90000</v>
       </c>
-      <c r="O83" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P83" s="19" t="str">
+      <c r="O83" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P83" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A84" s="14">
+      <c r="A84" s="10">
         <v>46184</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="D84" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E84" s="15" t="s">
+      <c r="E84" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="F84" s="16">
+      <c r="F84" s="12">
         <v>766923118</v>
       </c>
-      <c r="G84" s="15" t="s">
+      <c r="G84" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H84" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I84" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J84" s="15" t="s">
+      <c r="H84" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K84" s="15" t="s">
+      <c r="K84" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L84" s="15">
-        <v>15</v>
-      </c>
-      <c r="M84" s="17">
+      <c r="L84" s="11">
+        <v>15</v>
+      </c>
+      <c r="M84" s="13">
         <v>9000</v>
       </c>
-      <c r="N84" s="17">
+      <c r="N84" s="13">
         <v>135000</v>
       </c>
-      <c r="O84" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P84" s="19" t="str">
+      <c r="O84" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P84" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A85" s="14">
+      <c r="A85" s="10">
         <v>46182</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D85" s="15" t="s">
+      <c r="D85" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E85" s="15" t="s">
+      <c r="E85" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="F85" s="16">
+      <c r="F85" s="12">
         <v>767267003</v>
       </c>
-      <c r="G85" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H85" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I85" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" s="15" t="s">
+      <c r="G85" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="K85" s="15" t="s">
+      <c r="K85" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L85" s="15">
+      <c r="L85" s="11">
         <v>25</v>
       </c>
-      <c r="M85" s="17">
+      <c r="M85" s="13">
         <v>26000</v>
       </c>
-      <c r="N85" s="17">
+      <c r="N85" s="13">
         <v>650000</v>
       </c>
-      <c r="O85" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S24</v>
-      </c>
-      <c r="P85" s="19" t="str">
+      <c r="O85" s="7" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P85" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A86" s="14">
+        <v>46185</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F86" s="16">
+        <v>775151637</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I86" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K86" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="L86" s="15">
+        <v>2</v>
+      </c>
+      <c r="M86" s="17">
+        <v>55000</v>
+      </c>
+      <c r="N86" s="17">
+        <v>110000</v>
+      </c>
+      <c r="O86" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S24</v>
+      </c>
+      <c r="P86" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F80A980-A248-4D47-979B-1910FBE71F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FDD95C-100E-4789-A306-4411FEBFE394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="187">
   <si>
     <t>Date</t>
   </si>
@@ -553,6 +553,48 @@
   </si>
   <si>
     <t>Meadow Cup sac 25kg</t>
+  </si>
+  <si>
+    <t>Mountagua</t>
+  </si>
+  <si>
+    <t>Chocolat jaune 400g x 12 pcs</t>
+  </si>
+  <si>
+    <t>Pape</t>
+  </si>
+  <si>
+    <t>Mame Serigne</t>
+  </si>
+  <si>
+    <t>Moustapha  seye</t>
+  </si>
+  <si>
+    <t>Lait Janus 400gx10</t>
+  </si>
+  <si>
+    <t>Serigne khadim Ndiaye</t>
+  </si>
+  <si>
+    <t>Il dit que la date de péremption est proche</t>
+  </si>
+  <si>
+    <t>Grand Dakar</t>
+  </si>
+  <si>
+    <t>Babacar Thiam</t>
+  </si>
+  <si>
+    <t>Elhadj Ly</t>
+  </si>
+  <si>
+    <t>Abdou Diallo</t>
+  </si>
+  <si>
+    <t>DKR Plateau</t>
+  </si>
+  <si>
+    <t>Bacary</t>
   </si>
 </sst>
 </file>
@@ -976,8 +1018,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P86" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P86" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P108" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P108" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1290,7 +1332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -5729,53 +5771,1197 @@
       </c>
     </row>
     <row r="86" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A86" s="14">
+      <c r="A86" s="10">
         <v>46185</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D86" s="15" t="s">
+      <c r="D86" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E86" s="15" t="s">
+      <c r="E86" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="F86" s="16">
+      <c r="F86" s="12">
         <v>775151637</v>
       </c>
-      <c r="G86" s="15" t="s">
+      <c r="G86" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="H86" s="15" t="s">
+      <c r="H86" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I86" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J86" s="15" t="s">
+      <c r="I86" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J86" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K86" s="15" t="s">
+      <c r="K86" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="L86" s="15">
+      <c r="L86" s="11">
         <v>2</v>
       </c>
-      <c r="M86" s="17">
+      <c r="M86" s="13">
         <v>55000</v>
       </c>
-      <c r="N86" s="17">
+      <c r="N86" s="13">
         <v>110000</v>
       </c>
-      <c r="O86" s="18" t="str">
+      <c r="O86" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S24</v>
       </c>
-      <c r="P86" s="19" t="str">
+      <c r="P86" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A87" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" s="16">
+        <v>776149093</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L87" s="15">
+        <v>25</v>
+      </c>
+      <c r="M87" s="17">
+        <v>6000</v>
+      </c>
+      <c r="N87" s="17">
+        <v>150000</v>
+      </c>
+      <c r="O87" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P87" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A88" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F88" s="16">
+        <v>777847210</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I88" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="L88" s="15">
+        <v>1</v>
+      </c>
+      <c r="M88" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N88" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O88" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P88" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A89" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F89" s="16">
+        <v>777847210</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I89" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L89" s="15">
+        <v>1</v>
+      </c>
+      <c r="M89" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N89" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O89" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P89" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A90" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F90" s="16">
+        <v>777847210</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I90" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K90" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L90" s="15">
+        <v>3</v>
+      </c>
+      <c r="M90" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N90" s="17">
+        <v>78000</v>
+      </c>
+      <c r="O90" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P90" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A91" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F91" s="16">
+        <v>777847210</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I91" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L91" s="15">
+        <v>29</v>
+      </c>
+      <c r="M91" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N91" s="17">
+        <v>261000</v>
+      </c>
+      <c r="O91" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P91" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A92" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F92" s="16">
+        <v>767379110</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L92" s="15">
+        <v>25</v>
+      </c>
+      <c r="M92" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N92" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O92" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P92" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A93" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="F93" s="16">
+        <v>775884054</v>
+      </c>
+      <c r="G93" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K93" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L93" s="15">
+        <v>3</v>
+      </c>
+      <c r="M93" s="17">
+        <v>4500</v>
+      </c>
+      <c r="N93" s="17">
+        <v>13500</v>
+      </c>
+      <c r="O93" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P93" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A94" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="F94" s="16">
+        <v>777972938</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K94" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L94" s="15">
+        <v>5</v>
+      </c>
+      <c r="M94" s="17">
+        <v>4500</v>
+      </c>
+      <c r="N94" s="17">
+        <v>22500</v>
+      </c>
+      <c r="O94" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P94" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A95" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F95" s="16">
+        <v>777772248</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K95" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L95" s="15">
+        <v>2</v>
+      </c>
+      <c r="M95" s="17">
+        <v>4500</v>
+      </c>
+      <c r="N95" s="17">
+        <v>9000</v>
+      </c>
+      <c r="O95" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P95" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A96" s="14">
+        <v>46189</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" s="16">
+        <v>775630094</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K96" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L96" s="15">
+        <v>5</v>
+      </c>
+      <c r="M96" s="17">
+        <v>12000</v>
+      </c>
+      <c r="N96" s="17">
+        <v>60000</v>
+      </c>
+      <c r="O96" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P96" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A97" s="14">
+        <v>46188</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F97" s="16">
+        <v>765118157</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="K97" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L97" s="15">
+        <v>10</v>
+      </c>
+      <c r="M97" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N97" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O97" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P97" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A98" s="14">
+        <v>46188</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F98" s="16">
+        <v>765118157</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="K98" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L98" s="15">
+        <v>1</v>
+      </c>
+      <c r="M98" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N98" s="17">
+        <v>19500</v>
+      </c>
+      <c r="O98" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P98" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A99" s="14">
+        <v>46188</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E99" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" s="16">
+        <v>773122246</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="K99" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L99" s="15">
+        <v>25</v>
+      </c>
+      <c r="M99" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N99" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O99" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P99" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A100" s="14">
+        <v>46188</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F100" s="16">
+        <v>770589198</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K100" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L100" s="15">
+        <v>10</v>
+      </c>
+      <c r="M100" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N100" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O100" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P100" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A101" s="14">
+        <v>46188</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F101" s="16">
+        <v>772873297</v>
+      </c>
+      <c r="G101" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L101" s="15">
+        <v>25</v>
+      </c>
+      <c r="M101" s="17">
+        <v>6000</v>
+      </c>
+      <c r="N101" s="17">
+        <v>150000</v>
+      </c>
+      <c r="O101" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P101" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A102" s="14">
+        <v>46188</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="F102" s="16">
+        <v>772873297</v>
+      </c>
+      <c r="G102" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K102" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L102" s="15">
+        <v>15</v>
+      </c>
+      <c r="M102" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N102" s="17">
+        <v>135000</v>
+      </c>
+      <c r="O102" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P102" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A103" s="14">
+        <v>46190</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F103" s="16">
+        <v>775250570</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K103" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L103" s="15">
+        <v>10</v>
+      </c>
+      <c r="M103" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N103" s="17">
+        <v>195000</v>
+      </c>
+      <c r="O103" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P103" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A104" s="14">
+        <v>46191</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F104" s="16">
+        <v>773178746</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K104" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L104" s="15">
+        <v>2</v>
+      </c>
+      <c r="M104" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N104" s="17">
+        <v>39000</v>
+      </c>
+      <c r="O104" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P104" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A105" s="14">
+        <v>46191</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F105" s="16">
+        <v>773178746</v>
+      </c>
+      <c r="G105" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K105" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L105" s="15">
+        <v>45</v>
+      </c>
+      <c r="M105" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N105" s="17">
+        <v>405000</v>
+      </c>
+      <c r="O105" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P105" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A106" s="14">
+        <v>46192</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F106" s="16">
+        <v>770158721</v>
+      </c>
+      <c r="G106" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J106" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K106" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L106" s="15">
+        <v>15</v>
+      </c>
+      <c r="M106" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N106" s="17">
+        <v>232500</v>
+      </c>
+      <c r="O106" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P106" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A107" s="14">
+        <v>46192</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F107" s="16">
+        <v>770158721</v>
+      </c>
+      <c r="G107" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K107" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="L107" s="15">
+        <v>10</v>
+      </c>
+      <c r="M107" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N107" s="17">
+        <v>155000</v>
+      </c>
+      <c r="O107" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P107" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A108" s="14">
+        <v>46192</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F108" s="16">
+        <v>770158721</v>
+      </c>
+      <c r="G108" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="K108" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L108" s="15">
+        <v>2</v>
+      </c>
+      <c r="M108" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N108" s="17">
+        <v>56000</v>
+      </c>
+      <c r="O108" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P108" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FDD95C-100E-4789-A306-4411FEBFE394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18B358B-B217-473C-BF20-DFBDA5A34E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="186">
   <si>
     <t>Date</t>
   </si>
@@ -586,9 +586,6 @@
   </si>
   <si>
     <t>Elhadj Ly</t>
-  </si>
-  <si>
-    <t>Abdou Diallo</t>
   </si>
   <si>
     <t>DKR Plateau</t>
@@ -1018,8 +1015,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P108" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P108" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P107" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P107" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1332,7 +1329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -6656,22 +6653,22 @@
     </row>
     <row r="103" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A103" s="14">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>184</v>
+        <v>95</v>
       </c>
       <c r="F103" s="16">
-        <v>775250570</v>
+        <v>773178746</v>
       </c>
       <c r="G103" s="15" t="s">
         <v>15</v>
@@ -6689,13 +6686,13 @@
         <v>40</v>
       </c>
       <c r="L103" s="15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M103" s="17">
         <v>19500</v>
       </c>
       <c r="N103" s="17">
-        <v>195000</v>
+        <v>39000</v>
       </c>
       <c r="O103" s="18" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6738,16 +6735,16 @@
         <v>20</v>
       </c>
       <c r="K104" s="15" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L104" s="15">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="M104" s="17">
-        <v>19500</v>
+        <v>9000</v>
       </c>
       <c r="N104" s="17">
-        <v>39000</v>
+        <v>405000</v>
       </c>
       <c r="O104" s="18" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6760,22 +6757,22 @@
     </row>
     <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A105" s="14">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="F105" s="16">
-        <v>773178746</v>
+        <v>770158721</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>15</v>
@@ -6787,19 +6784,19 @@
         <v>16</v>
       </c>
       <c r="J105" s="15" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="K105" s="15" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="L105" s="15">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="M105" s="17">
-        <v>9000</v>
+        <v>15500</v>
       </c>
       <c r="N105" s="17">
-        <v>405000</v>
+        <v>232500</v>
       </c>
       <c r="O105" s="18" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6821,10 +6818,10 @@
         <v>14</v>
       </c>
       <c r="D106" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E106" s="15" t="s">
         <v>185</v>
-      </c>
-      <c r="E106" s="15" t="s">
-        <v>186</v>
       </c>
       <c r="F106" s="16">
         <v>770158721</v>
@@ -6842,16 +6839,16 @@
         <v>146</v>
       </c>
       <c r="K106" s="15" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="L106" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M106" s="17">
         <v>15500</v>
       </c>
       <c r="N106" s="17">
-        <v>232500</v>
+        <v>155000</v>
       </c>
       <c r="O106" s="18" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
@@ -6873,10 +6870,10 @@
         <v>14</v>
       </c>
       <c r="D107" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E107" s="15" t="s">
         <v>185</v>
-      </c>
-      <c r="E107" s="15" t="s">
-        <v>186</v>
       </c>
       <c r="F107" s="16">
         <v>770158721</v>
@@ -6894,74 +6891,22 @@
         <v>146</v>
       </c>
       <c r="K107" s="15" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="L107" s="15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M107" s="17">
-        <v>15500</v>
+        <v>28000</v>
       </c>
       <c r="N107" s="17">
-        <v>155000</v>
+        <v>56000</v>
       </c>
       <c r="O107" s="18" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
       <c r="P107" s="19" t="str">
-        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
-        <v>juin</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A108" s="14">
-        <v>46192</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C108" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E108" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F108" s="16">
-        <v>770158721</v>
-      </c>
-      <c r="G108" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I108" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J108" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="K108" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="L108" s="15">
-        <v>2</v>
-      </c>
-      <c r="M108" s="17">
-        <v>28000</v>
-      </c>
-      <c r="N108" s="17">
-        <v>56000</v>
-      </c>
-      <c r="O108" s="18" t="str">
-        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S25</v>
-      </c>
-      <c r="P108" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18B358B-B217-473C-BF20-DFBDA5A34E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF7A31A-0878-4CFE-A8F5-E0F4252FFA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="187">
   <si>
     <t>Date</t>
   </si>
@@ -592,6 +592,9 @@
   </si>
   <si>
     <t>Bacary</t>
+  </si>
+  <si>
+    <t>Abdou Diallo</t>
   </si>
 </sst>
 </file>
@@ -1015,8 +1018,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P107" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P107" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P108" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P108" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1329,7 +1332,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -5820,1093 +5823,1145 @@
       </c>
     </row>
     <row r="87" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A87" s="14">
+      <c r="A87" s="10">
         <v>46189</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D87" s="15" t="s">
+      <c r="D87" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="E87" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F87" s="16">
+      <c r="F87" s="12">
         <v>776149093</v>
       </c>
-      <c r="G87" s="15" t="s">
+      <c r="G87" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H87" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I87" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J87" s="15" t="s">
+      <c r="H87" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I87" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K87" s="15" t="s">
+      <c r="K87" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L87" s="15">
+      <c r="L87" s="11">
         <v>25</v>
       </c>
-      <c r="M87" s="17">
+      <c r="M87" s="13">
         <v>6000</v>
       </c>
-      <c r="N87" s="17">
+      <c r="N87" s="13">
         <v>150000</v>
       </c>
-      <c r="O87" s="18" t="str">
+      <c r="O87" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P87" s="19" t="str">
+      <c r="P87" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A88" s="14">
+      <c r="A88" s="10">
         <v>46189</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D88" s="15" t="s">
+      <c r="D88" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E88" s="15" t="s">
+      <c r="E88" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F88" s="16">
+      <c r="F88" s="12">
         <v>777847210</v>
       </c>
-      <c r="G88" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="15" t="s">
+      <c r="G88" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I88" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J88" s="15" t="s">
+      <c r="I88" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J88" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K88" s="15" t="s">
+      <c r="K88" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="L88" s="15">
+      <c r="L88" s="11">
         <v>1</v>
       </c>
-      <c r="M88" s="17">
+      <c r="M88" s="13">
         <v>15500</v>
       </c>
-      <c r="N88" s="17">
+      <c r="N88" s="13">
         <v>15500</v>
       </c>
-      <c r="O88" s="18" t="str">
+      <c r="O88" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P88" s="19" t="str">
+      <c r="P88" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A89" s="14">
+      <c r="A89" s="10">
         <v>46189</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D89" s="15" t="s">
+      <c r="D89" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E89" s="15" t="s">
+      <c r="E89" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F89" s="16">
+      <c r="F89" s="12">
         <v>777847210</v>
       </c>
-      <c r="G89" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H89" s="15" t="s">
+      <c r="G89" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I89" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J89" s="15" t="s">
+      <c r="I89" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K89" s="15" t="s">
+      <c r="K89" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L89" s="15">
+      <c r="L89" s="11">
         <v>1</v>
       </c>
-      <c r="M89" s="17">
+      <c r="M89" s="13">
         <v>15500</v>
       </c>
-      <c r="N89" s="17">
+      <c r="N89" s="13">
         <v>15500</v>
       </c>
-      <c r="O89" s="18" t="str">
+      <c r="O89" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P89" s="19" t="str">
+      <c r="P89" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A90" s="14">
+      <c r="A90" s="10">
         <v>46189</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D90" s="15" t="s">
+      <c r="D90" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E90" s="15" t="s">
+      <c r="E90" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F90" s="16">
+      <c r="F90" s="12">
         <v>777847210</v>
       </c>
-      <c r="G90" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="15" t="s">
+      <c r="G90" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I90" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" s="15" t="s">
+      <c r="I90" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K90" s="15" t="s">
+      <c r="K90" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L90" s="15">
+      <c r="L90" s="11">
         <v>3</v>
       </c>
-      <c r="M90" s="17">
+      <c r="M90" s="13">
         <v>26000</v>
       </c>
-      <c r="N90" s="17">
+      <c r="N90" s="13">
         <v>78000</v>
       </c>
-      <c r="O90" s="18" t="str">
+      <c r="O90" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P90" s="19" t="str">
+      <c r="P90" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A91" s="14">
+      <c r="A91" s="10">
         <v>46189</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D91" s="15" t="s">
+      <c r="D91" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E91" s="15" t="s">
+      <c r="E91" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F91" s="16">
+      <c r="F91" s="12">
         <v>777847210</v>
       </c>
-      <c r="G91" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H91" s="15" t="s">
+      <c r="G91" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I91" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J91" s="15" t="s">
+      <c r="I91" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K91" s="15" t="s">
+      <c r="K91" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L91" s="15">
+      <c r="L91" s="11">
         <v>29</v>
       </c>
-      <c r="M91" s="17">
+      <c r="M91" s="13">
         <v>9000</v>
       </c>
-      <c r="N91" s="17">
+      <c r="N91" s="13">
         <v>261000</v>
       </c>
-      <c r="O91" s="18" t="str">
+      <c r="O91" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P91" s="19" t="str">
+      <c r="P91" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A92" s="14">
+      <c r="A92" s="10">
         <v>46189</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B92" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D92" s="15" t="s">
+      <c r="D92" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E92" s="15" t="s">
+      <c r="E92" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F92" s="16">
+      <c r="F92" s="12">
         <v>767379110</v>
       </c>
-      <c r="G92" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I92" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J92" s="15" t="s">
+      <c r="G92" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K92" s="15" t="s">
+      <c r="K92" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L92" s="15">
+      <c r="L92" s="11">
         <v>25</v>
       </c>
-      <c r="M92" s="17">
+      <c r="M92" s="13">
         <v>9000</v>
       </c>
-      <c r="N92" s="17">
+      <c r="N92" s="13">
         <v>225000</v>
       </c>
-      <c r="O92" s="18" t="str">
+      <c r="O92" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P92" s="19" t="str">
+      <c r="P92" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A93" s="14">
+      <c r="A93" s="10">
         <v>46189</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D93" s="15" t="s">
+      <c r="D93" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E93" s="15" t="s">
+      <c r="E93" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F93" s="16">
+      <c r="F93" s="12">
         <v>775884054</v>
       </c>
-      <c r="G93" s="15" t="s">
+      <c r="G93" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H93" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I93" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" s="15" t="s">
+      <c r="H93" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="K93" s="15" t="s">
+      <c r="K93" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L93" s="15">
+      <c r="L93" s="11">
         <v>3</v>
       </c>
-      <c r="M93" s="17">
+      <c r="M93" s="13">
         <v>4500</v>
       </c>
-      <c r="N93" s="17">
+      <c r="N93" s="13">
         <v>13500</v>
       </c>
-      <c r="O93" s="18" t="str">
+      <c r="O93" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P93" s="19" t="str">
+      <c r="P93" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A94" s="14">
+      <c r="A94" s="10">
         <v>46189</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C94" s="15" t="s">
+      <c r="C94" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D94" s="15" t="s">
+      <c r="D94" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E94" s="15" t="s">
+      <c r="E94" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="F94" s="16">
+      <c r="F94" s="12">
         <v>777972938</v>
       </c>
-      <c r="G94" s="15" t="s">
+      <c r="G94" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H94" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I94" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J94" s="15" t="s">
+      <c r="H94" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K94" s="15" t="s">
+      <c r="K94" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L94" s="15">
+      <c r="L94" s="11">
         <v>5</v>
       </c>
-      <c r="M94" s="17">
+      <c r="M94" s="13">
         <v>4500</v>
       </c>
-      <c r="N94" s="17">
+      <c r="N94" s="13">
         <v>22500</v>
       </c>
-      <c r="O94" s="18" t="str">
+      <c r="O94" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P94" s="19" t="str">
+      <c r="P94" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A95" s="14">
+      <c r="A95" s="10">
         <v>46189</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E95" s="15" t="s">
+      <c r="E95" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="F95" s="16">
+      <c r="F95" s="12">
         <v>777772248</v>
       </c>
-      <c r="G95" s="15" t="s">
+      <c r="G95" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H95" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I95" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" s="15" t="s">
+      <c r="H95" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="K95" s="15" t="s">
+      <c r="K95" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L95" s="15">
+      <c r="L95" s="11">
         <v>2</v>
       </c>
-      <c r="M95" s="17">
+      <c r="M95" s="13">
         <v>4500</v>
       </c>
-      <c r="N95" s="17">
+      <c r="N95" s="13">
         <v>9000</v>
       </c>
-      <c r="O95" s="18" t="str">
+      <c r="O95" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P95" s="19" t="str">
+      <c r="P95" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A96" s="14">
+      <c r="A96" s="10">
         <v>46189</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D96" s="15" t="s">
+      <c r="D96" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E96" s="15" t="s">
+      <c r="E96" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F96" s="16">
+      <c r="F96" s="12">
         <v>775630094</v>
       </c>
-      <c r="G96" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H96" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I96" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J96" s="15" t="s">
+      <c r="G96" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H96" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I96" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K96" s="15" t="s">
+      <c r="K96" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="L96" s="15">
+      <c r="L96" s="11">
         <v>5</v>
       </c>
-      <c r="M96" s="17">
+      <c r="M96" s="13">
         <v>12000</v>
       </c>
-      <c r="N96" s="17">
+      <c r="N96" s="13">
         <v>60000</v>
       </c>
-      <c r="O96" s="18" t="str">
+      <c r="O96" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P96" s="19" t="str">
+      <c r="P96" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A97" s="14">
+      <c r="A97" s="10">
         <v>46188</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D97" s="15" t="s">
+      <c r="D97" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E97" s="15" t="s">
+      <c r="E97" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="F97" s="16">
+      <c r="F97" s="12">
         <v>765118157</v>
       </c>
-      <c r="G97" s="15" t="s">
+      <c r="G97" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H97" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I97" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J97" s="15" t="s">
+      <c r="H97" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I97" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="K97" s="15" t="s">
+      <c r="K97" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L97" s="15">
+      <c r="L97" s="11">
         <v>10</v>
       </c>
-      <c r="M97" s="17">
+      <c r="M97" s="13">
         <v>9000</v>
       </c>
-      <c r="N97" s="17">
+      <c r="N97" s="13">
         <v>90000</v>
       </c>
-      <c r="O97" s="18" t="str">
+      <c r="O97" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P97" s="19" t="str">
+      <c r="P97" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A98" s="14">
+      <c r="A98" s="10">
         <v>46188</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D98" s="15" t="s">
+      <c r="D98" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="F98" s="16">
+      <c r="F98" s="12">
         <v>765118157</v>
       </c>
-      <c r="G98" s="15" t="s">
+      <c r="G98" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H98" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I98" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J98" s="15" t="s">
+      <c r="H98" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I98" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J98" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="K98" s="15" t="s">
+      <c r="K98" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L98" s="15">
+      <c r="L98" s="11">
         <v>1</v>
       </c>
-      <c r="M98" s="17">
+      <c r="M98" s="13">
         <v>19500</v>
       </c>
-      <c r="N98" s="17">
+      <c r="N98" s="13">
         <v>19500</v>
       </c>
-      <c r="O98" s="18" t="str">
+      <c r="O98" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P98" s="19" t="str">
+      <c r="P98" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A99" s="14">
+      <c r="A99" s="10">
         <v>46188</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D99" s="15" t="s">
+      <c r="D99" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E99" s="15" t="s">
+      <c r="E99" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F99" s="16">
+      <c r="F99" s="12">
         <v>773122246</v>
       </c>
-      <c r="G99" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I99" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J99" s="15" t="s">
+      <c r="G99" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I99" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="K99" s="15" t="s">
+      <c r="K99" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L99" s="15">
+      <c r="L99" s="11">
         <v>25</v>
       </c>
-      <c r="M99" s="17">
+      <c r="M99" s="13">
         <v>9000</v>
       </c>
-      <c r="N99" s="17">
+      <c r="N99" s="13">
         <v>225000</v>
       </c>
-      <c r="O99" s="18" t="str">
+      <c r="O99" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P99" s="19" t="str">
+      <c r="P99" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A100" s="14">
+      <c r="A100" s="10">
         <v>46188</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D100" s="15" t="s">
+      <c r="D100" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="E100" s="15" t="s">
+      <c r="E100" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F100" s="16">
+      <c r="F100" s="12">
         <v>770589198</v>
       </c>
-      <c r="G100" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I100" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J100" s="15" t="s">
+      <c r="G100" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I100" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K100" s="15" t="s">
+      <c r="K100" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L100" s="15">
+      <c r="L100" s="11">
         <v>10</v>
       </c>
-      <c r="M100" s="17">
+      <c r="M100" s="13">
         <v>9000</v>
       </c>
-      <c r="N100" s="17">
+      <c r="N100" s="13">
         <v>90000</v>
       </c>
-      <c r="O100" s="18" t="str">
+      <c r="O100" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P100" s="19" t="str">
+      <c r="P100" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A101" s="14">
+      <c r="A101" s="10">
         <v>46188</v>
       </c>
-      <c r="B101" s="15" t="s">
+      <c r="B101" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C101" s="15" t="s">
+      <c r="C101" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D101" s="15" t="s">
+      <c r="D101" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E101" s="15" t="s">
+      <c r="E101" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F101" s="16">
+      <c r="F101" s="12">
         <v>772873297</v>
       </c>
-      <c r="G101" s="15" t="s">
+      <c r="G101" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H101" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I101" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J101" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="15" t="s">
+      <c r="H101" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I101" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L101" s="15">
+      <c r="L101" s="11">
         <v>25</v>
       </c>
-      <c r="M101" s="17">
+      <c r="M101" s="13">
         <v>6000</v>
       </c>
-      <c r="N101" s="17">
+      <c r="N101" s="13">
         <v>150000</v>
       </c>
-      <c r="O101" s="18" t="str">
+      <c r="O101" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P101" s="19" t="str">
+      <c r="P101" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A102" s="14">
+      <c r="A102" s="10">
         <v>46188</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B102" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C102" s="15" t="s">
+      <c r="C102" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D102" s="15" t="s">
+      <c r="D102" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E102" s="15" t="s">
+      <c r="E102" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="F102" s="16">
+      <c r="F102" s="12">
         <v>772873297</v>
       </c>
-      <c r="G102" s="15" t="s">
+      <c r="G102" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H102" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I102" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J102" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="K102" s="15" t="s">
+      <c r="H102" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I102" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K102" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L102" s="15">
-        <v>15</v>
-      </c>
-      <c r="M102" s="17">
+      <c r="L102" s="11">
+        <v>15</v>
+      </c>
+      <c r="M102" s="13">
         <v>9000</v>
       </c>
-      <c r="N102" s="17">
+      <c r="N102" s="13">
         <v>135000</v>
       </c>
-      <c r="O102" s="18" t="str">
+      <c r="O102" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P102" s="19" t="str">
+      <c r="P102" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A103" s="14">
+      <c r="A103" s="10">
         <v>46191</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D103" s="15" t="s">
+      <c r="D103" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E103" s="15" t="s">
+      <c r="E103" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F103" s="16">
+      <c r="F103" s="12">
         <v>773178746</v>
       </c>
-      <c r="G103" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I103" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J103" s="15" t="s">
+      <c r="G103" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I103" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J103" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K103" s="15" t="s">
+      <c r="K103" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L103" s="15">
+      <c r="L103" s="11">
         <v>2</v>
       </c>
-      <c r="M103" s="17">
+      <c r="M103" s="13">
         <v>19500</v>
       </c>
-      <c r="N103" s="17">
+      <c r="N103" s="13">
         <v>39000</v>
       </c>
-      <c r="O103" s="18" t="str">
+      <c r="O103" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P103" s="19" t="str">
+      <c r="P103" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A104" s="14">
+      <c r="A104" s="10">
         <v>46191</v>
       </c>
-      <c r="B104" s="15" t="s">
+      <c r="B104" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D104" s="15" t="s">
+      <c r="D104" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E104" s="15" t="s">
+      <c r="E104" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F104" s="16">
+      <c r="F104" s="12">
         <v>773178746</v>
       </c>
-      <c r="G104" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I104" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J104" s="15" t="s">
+      <c r="G104" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I104" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J104" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K104" s="15" t="s">
+      <c r="K104" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L104" s="15">
+      <c r="L104" s="11">
         <v>45</v>
       </c>
-      <c r="M104" s="17">
+      <c r="M104" s="13">
         <v>9000</v>
       </c>
-      <c r="N104" s="17">
+      <c r="N104" s="13">
         <v>405000</v>
       </c>
-      <c r="O104" s="18" t="str">
+      <c r="O104" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P104" s="19" t="str">
+      <c r="P104" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A105" s="14">
+      <c r="A105" s="10">
         <v>46192</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D105" s="15" t="s">
+      <c r="D105" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E105" s="15" t="s">
+      <c r="E105" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F105" s="16">
+      <c r="F105" s="12">
         <v>770158721</v>
       </c>
-      <c r="G105" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I105" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J105" s="15" t="s">
+      <c r="G105" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J105" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K105" s="15" t="s">
+      <c r="K105" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L105" s="15">
-        <v>15</v>
-      </c>
-      <c r="M105" s="17">
+      <c r="L105" s="11">
+        <v>15</v>
+      </c>
+      <c r="M105" s="13">
         <v>15500</v>
       </c>
-      <c r="N105" s="17">
+      <c r="N105" s="13">
         <v>232500</v>
       </c>
-      <c r="O105" s="18" t="str">
+      <c r="O105" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P105" s="19" t="str">
+      <c r="P105" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A106" s="14">
+      <c r="A106" s="10">
         <v>46192</v>
       </c>
-      <c r="B106" s="15" t="s">
+      <c r="B106" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D106" s="15" t="s">
+      <c r="D106" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E106" s="15" t="s">
+      <c r="E106" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F106" s="16">
+      <c r="F106" s="12">
         <v>770158721</v>
       </c>
-      <c r="G106" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I106" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J106" s="15" t="s">
+      <c r="G106" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J106" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K106" s="15" t="s">
+      <c r="K106" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="L106" s="15">
+      <c r="L106" s="11">
         <v>10</v>
       </c>
-      <c r="M106" s="17">
+      <c r="M106" s="13">
         <v>15500</v>
       </c>
-      <c r="N106" s="17">
+      <c r="N106" s="13">
         <v>155000</v>
       </c>
-      <c r="O106" s="18" t="str">
+      <c r="O106" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P106" s="19" t="str">
+      <c r="P106" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A107" s="14">
+      <c r="A107" s="10">
         <v>46192</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D107" s="15" t="s">
+      <c r="D107" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="E107" s="15" t="s">
+      <c r="E107" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F107" s="16">
+      <c r="F107" s="12">
         <v>770158721</v>
       </c>
-      <c r="G107" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I107" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J107" s="15" t="s">
+      <c r="G107" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I107" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J107" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="K107" s="15" t="s">
+      <c r="K107" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L107" s="15">
+      <c r="L107" s="11">
         <v>2</v>
       </c>
-      <c r="M107" s="17">
+      <c r="M107" s="13">
         <v>28000</v>
       </c>
-      <c r="N107" s="17">
+      <c r="N107" s="13">
         <v>56000</v>
       </c>
-      <c r="O107" s="18" t="str">
+      <c r="O107" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P107" s="19" t="str">
+      <c r="P107" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A108" s="14">
+        <v>46190</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F108" s="16">
+        <v>775250570</v>
+      </c>
+      <c r="G108" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K108" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L108" s="15">
+        <v>10</v>
+      </c>
+      <c r="M108" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N108" s="17">
+        <v>195000</v>
+      </c>
+      <c r="O108" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S25</v>
+      </c>
+      <c r="P108" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF7A31A-0878-4CFE-A8F5-E0F4252FFA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FD1EBB-E3E0-44CF-8711-B332127A8F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="220">
   <si>
     <t>Date</t>
   </si>
@@ -595,6 +595,105 @@
   </si>
   <si>
     <t>Abdou Diallo</t>
+  </si>
+  <si>
+    <t>Matar Ndaiye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depuis l'or sa fait longtemps </t>
+  </si>
+  <si>
+    <t>Mouhamed</t>
+  </si>
+  <si>
+    <t>Sodidalo SARL</t>
+  </si>
+  <si>
+    <t>Keur Massar Ainoumady</t>
+  </si>
+  <si>
+    <t>Wa keur Darou Khoudous</t>
+  </si>
+  <si>
+    <t>Fallou</t>
+  </si>
+  <si>
+    <t>Modou Ndiaye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ras </t>
+  </si>
+  <si>
+    <t>Abdou sow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il dit que la date est très proche </t>
+  </si>
+  <si>
+    <t>El Hadji</t>
+  </si>
+  <si>
+    <t>Livraison hors point de vente</t>
+  </si>
+  <si>
+    <t>HLM</t>
+  </si>
+  <si>
+    <t>Baye sy</t>
+  </si>
+  <si>
+    <t>Sow</t>
+  </si>
+  <si>
+    <t>Ndongo</t>
+  </si>
+  <si>
+    <t>Café Altimo pot 50g x 24 pcs</t>
+  </si>
+  <si>
+    <t>MAMDOU DIA</t>
+  </si>
+  <si>
+    <t>Moustapha BA</t>
+  </si>
+  <si>
+    <t>hors_pdvl</t>
+  </si>
+  <si>
+    <t>Saloum saloum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK </t>
+  </si>
+  <si>
+    <t>Café Altimo pot 100g x 24 pcs</t>
+  </si>
+  <si>
+    <t>Sidi</t>
+  </si>
+  <si>
+    <t>Keur Ndiaye LO</t>
+  </si>
+  <si>
+    <t>Djiby</t>
+  </si>
+  <si>
+    <t>Il a bénéficie d'une remise de 17000</t>
+  </si>
+  <si>
+    <t>Abdou Rakhmane Baldé</t>
+  </si>
+  <si>
+    <t>THIERNO KANTE</t>
+  </si>
+  <si>
+    <t>Jaxaay</t>
+  </si>
+  <si>
+    <t>YaYa Dia</t>
+  </si>
+  <si>
+    <t>Il veut  essayer le produit</t>
   </si>
 </sst>
 </file>
@@ -1018,8 +1117,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P108" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P108" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P141" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P141" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1332,7 +1431,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -6915,53 +7014,1767 @@
       </c>
     </row>
     <row r="108" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A108" s="14">
+      <c r="A108" s="10">
         <v>46190</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C108" s="15" t="s">
+      <c r="C108" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D108" s="15" t="s">
+      <c r="D108" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E108" s="15" t="s">
+      <c r="E108" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="F108" s="16">
+      <c r="F108" s="12">
         <v>775250570</v>
       </c>
-      <c r="G108" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I108" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J108" s="15" t="s">
+      <c r="G108" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J108" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K108" s="15" t="s">
+      <c r="K108" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L108" s="15">
+      <c r="L108" s="11">
         <v>10</v>
       </c>
-      <c r="M108" s="17">
+      <c r="M108" s="13">
         <v>19500</v>
       </c>
-      <c r="N108" s="17">
+      <c r="N108" s="13">
         <v>195000</v>
       </c>
-      <c r="O108" s="18" t="str">
+      <c r="O108" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S25</v>
       </c>
-      <c r="P108" s="19" t="str">
+      <c r="P108" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A109" s="14">
+        <v>46198</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C109" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F109" s="16">
+        <v>771165277</v>
+      </c>
+      <c r="G109" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="K109" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L109" s="15">
+        <v>3</v>
+      </c>
+      <c r="M109" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N109" s="17">
+        <v>46500</v>
+      </c>
+      <c r="O109" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P109" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A110" s="14">
+        <v>46198</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F110" s="16">
+        <v>772131614</v>
+      </c>
+      <c r="G110" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J110" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K110" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L110" s="15">
+        <v>1</v>
+      </c>
+      <c r="M110" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N110" s="17">
+        <v>26000</v>
+      </c>
+      <c r="O110" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P110" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A111" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F111" s="16">
+        <v>772957336</v>
+      </c>
+      <c r="G111" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="K111" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L111" s="15">
+        <v>5</v>
+      </c>
+      <c r="M111" s="17">
+        <v>6000</v>
+      </c>
+      <c r="N111" s="17">
+        <v>30000</v>
+      </c>
+      <c r="O111" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P111" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A112" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C112" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="F112" s="16">
+        <v>778356666</v>
+      </c>
+      <c r="G112" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K112" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L112" s="15">
+        <v>100</v>
+      </c>
+      <c r="M112" s="17">
+        <v>8750</v>
+      </c>
+      <c r="N112" s="17">
+        <v>875000</v>
+      </c>
+      <c r="O112" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P112" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A113" s="14">
+        <v>46196</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F113" s="16">
+        <v>783864321</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="K113" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L113" s="15">
+        <v>25</v>
+      </c>
+      <c r="M113" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N113" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O113" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P113" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A114" s="14">
+        <v>46196</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F114" s="16">
+        <v>783864321</v>
+      </c>
+      <c r="G114" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I114" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J114" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="K114" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L114" s="15">
+        <v>10</v>
+      </c>
+      <c r="M114" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N114" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O114" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P114" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A115" s="14">
+        <v>46195</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C115" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F115" s="16">
+        <v>774187389</v>
+      </c>
+      <c r="G115" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K115" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L115" s="15">
+        <v>30</v>
+      </c>
+      <c r="M115" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N115" s="17">
+        <v>270000</v>
+      </c>
+      <c r="O115" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P115" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A116" s="14">
+        <v>46195</v>
+      </c>
+      <c r="B116" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F116" s="16">
+        <v>776212473</v>
+      </c>
+      <c r="G116" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H116" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="K116" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L116" s="15">
+        <v>10</v>
+      </c>
+      <c r="M116" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N116" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O116" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P116" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A117" s="14">
+        <v>46195</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C117" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E117" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="F117" s="16">
+        <v>779724512</v>
+      </c>
+      <c r="G117" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H117" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J117" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="K117" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L117" s="15">
+        <v>25</v>
+      </c>
+      <c r="M117" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N117" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O117" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P117" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A118" s="14">
+        <v>46200</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="F118" s="16">
+        <v>773739328</v>
+      </c>
+      <c r="G118" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J118" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K118" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L118" s="15">
+        <v>3</v>
+      </c>
+      <c r="M118" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N118" s="17">
+        <v>58500</v>
+      </c>
+      <c r="O118" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P118" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A119" s="14">
+        <v>46200</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C119" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E119" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F119" s="16">
+        <v>775630094</v>
+      </c>
+      <c r="G119" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J119" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K119" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L119" s="15">
+        <v>1</v>
+      </c>
+      <c r="M119" s="17">
+        <v>12000</v>
+      </c>
+      <c r="N119" s="17">
+        <v>12000</v>
+      </c>
+      <c r="O119" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P119" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A120" s="14">
+        <v>46200</v>
+      </c>
+      <c r="B120" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C120" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E120" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F120" s="16">
+        <v>775014335</v>
+      </c>
+      <c r="G120" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J120" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K120" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L120" s="15">
+        <v>25</v>
+      </c>
+      <c r="M120" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N120" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O120" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P120" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A121" s="14">
+        <v>46200</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E121" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F121" s="16">
+        <v>772788635</v>
+      </c>
+      <c r="G121" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H121" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J121" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K121" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L121" s="15">
+        <v>2</v>
+      </c>
+      <c r="M121" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N121" s="17">
+        <v>31000</v>
+      </c>
+      <c r="O121" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P121" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A122" s="14">
+        <v>46200</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C122" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E122" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F122" s="16">
+        <v>775197108</v>
+      </c>
+      <c r="G122" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J122" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K122" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L122" s="15">
+        <v>5</v>
+      </c>
+      <c r="M122" s="17">
+        <v>17500</v>
+      </c>
+      <c r="N122" s="17">
+        <v>87500</v>
+      </c>
+      <c r="O122" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P122" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A123" s="14">
+        <v>46198</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C123" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E123" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F123" s="16">
+        <v>768059355</v>
+      </c>
+      <c r="G123" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J123" s="15"/>
+      <c r="K123" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L123" s="15">
+        <v>100</v>
+      </c>
+      <c r="M123" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N123" s="17">
+        <v>2800000</v>
+      </c>
+      <c r="O123" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P123" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A124" s="14">
+        <v>46198</v>
+      </c>
+      <c r="B124" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E124" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F124" s="16">
+        <v>774414059</v>
+      </c>
+      <c r="G124" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J124" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K124" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L124" s="15">
+        <v>1</v>
+      </c>
+      <c r="M124" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N124" s="17">
+        <v>19500</v>
+      </c>
+      <c r="O124" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P124" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A125" s="14">
+        <v>46198</v>
+      </c>
+      <c r="B125" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C125" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E125" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F125" s="16">
+        <v>774414059</v>
+      </c>
+      <c r="G125" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J125" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K125" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L125" s="15">
+        <v>30</v>
+      </c>
+      <c r="M125" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N125" s="17">
+        <v>270000</v>
+      </c>
+      <c r="O125" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P125" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A126" s="14">
+        <v>46198</v>
+      </c>
+      <c r="B126" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F126" s="16">
+        <v>774414059</v>
+      </c>
+      <c r="G126" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J126" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K126" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L126" s="15">
+        <v>30</v>
+      </c>
+      <c r="M126" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N126" s="17">
+        <v>270000</v>
+      </c>
+      <c r="O126" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P126" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A127" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B127" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C127" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E127" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F127" s="16">
+        <v>777854561</v>
+      </c>
+      <c r="G127" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I127" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J127" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K127" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L127" s="15">
+        <v>1</v>
+      </c>
+      <c r="M127" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N127" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O127" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P127" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A128" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B128" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C128" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E128" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="F128" s="16">
+        <v>775539595</v>
+      </c>
+      <c r="G128" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="H128" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J128" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K128" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L128" s="15">
+        <v>1</v>
+      </c>
+      <c r="M128" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N128" s="17">
+        <v>19500</v>
+      </c>
+      <c r="O128" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P128" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A129" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C129" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E129" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F129" s="16">
+        <v>773178746</v>
+      </c>
+      <c r="G129" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J129" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="K129" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L129" s="15">
+        <v>5</v>
+      </c>
+      <c r="M129" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N129" s="17">
+        <v>132500</v>
+      </c>
+      <c r="O129" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P129" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A130" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B130" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E130" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F130" s="16">
+        <v>773178746</v>
+      </c>
+      <c r="G130" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I130" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J130" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="K130" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L130" s="15">
+        <v>1</v>
+      </c>
+      <c r="M130" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N130" s="17">
+        <v>26000</v>
+      </c>
+      <c r="O130" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P130" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A131" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B131" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C131" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E131" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F131" s="16">
+        <v>777854561</v>
+      </c>
+      <c r="G131" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H131" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I131" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J131" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K131" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L131" s="15">
+        <v>5</v>
+      </c>
+      <c r="M131" s="17">
+        <v>26500</v>
+      </c>
+      <c r="N131" s="17">
+        <v>132500</v>
+      </c>
+      <c r="O131" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P131" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A132" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B132" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C132" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E132" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F132" s="16">
+        <v>773178746</v>
+      </c>
+      <c r="G132" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I132" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J132" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="K132" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="L132" s="15">
+        <v>1</v>
+      </c>
+      <c r="M132" s="17">
+        <v>33500</v>
+      </c>
+      <c r="N132" s="17">
+        <v>33500</v>
+      </c>
+      <c r="O132" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P132" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A133" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B133" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E133" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F133" s="16">
+        <v>777854561</v>
+      </c>
+      <c r="G133" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H133" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I133" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J133" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K133" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="L133" s="15">
+        <v>1</v>
+      </c>
+      <c r="M133" s="17">
+        <v>15500</v>
+      </c>
+      <c r="N133" s="17">
+        <v>15500</v>
+      </c>
+      <c r="O133" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P133" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A134" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B134" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C134" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E134" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="F134" s="16">
+        <v>774091250</v>
+      </c>
+      <c r="G134" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I134" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J134" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K134" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L134" s="15">
+        <v>13</v>
+      </c>
+      <c r="M134" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N134" s="17">
+        <v>117000</v>
+      </c>
+      <c r="O134" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P134" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A135" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B135" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E135" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F135" s="16">
+        <v>783942599</v>
+      </c>
+      <c r="G135" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J135" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K135" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L135" s="15">
+        <v>10</v>
+      </c>
+      <c r="M135" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N135" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O135" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P135" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A136" s="14">
+        <v>46197</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E136" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="F136" s="16">
+        <v>773231589</v>
+      </c>
+      <c r="G136" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I136" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J136" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K136" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L136" s="15">
+        <v>5</v>
+      </c>
+      <c r="M136" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N136" s="17">
+        <v>45000</v>
+      </c>
+      <c r="O136" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P136" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A137" s="14">
+        <v>46196</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D137" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E137" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F137" s="16">
+        <v>788217757</v>
+      </c>
+      <c r="G137" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J137" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="K137" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="L137" s="15">
+        <v>25</v>
+      </c>
+      <c r="M137" s="17">
+        <v>28000</v>
+      </c>
+      <c r="N137" s="17">
+        <v>700000</v>
+      </c>
+      <c r="O137" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P137" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A138" s="14">
+        <v>46196</v>
+      </c>
+      <c r="B138" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E138" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="F138" s="16">
+        <v>774993694</v>
+      </c>
+      <c r="G138" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J138" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="K138" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L138" s="15">
+        <v>50</v>
+      </c>
+      <c r="M138" s="17">
+        <v>12000</v>
+      </c>
+      <c r="N138" s="17">
+        <v>600000</v>
+      </c>
+      <c r="O138" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P138" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A139" s="14">
+        <v>46196</v>
+      </c>
+      <c r="B139" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C139" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D139" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F139" s="16">
+        <v>775171537</v>
+      </c>
+      <c r="G139" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J139" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K139" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L139" s="15">
+        <v>25</v>
+      </c>
+      <c r="M139" s="17">
+        <v>12000</v>
+      </c>
+      <c r="N139" s="17">
+        <v>300000</v>
+      </c>
+      <c r="O139" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P139" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A140" s="14">
+        <v>46196</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C140" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E140" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F140" s="16">
+        <v>768059355</v>
+      </c>
+      <c r="G140" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I140" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J140" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K140" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L140" s="15">
+        <v>50</v>
+      </c>
+      <c r="M140" s="17">
+        <v>12000</v>
+      </c>
+      <c r="N140" s="17">
+        <v>600000</v>
+      </c>
+      <c r="O140" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P140" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A141" s="14">
+        <v>46195</v>
+      </c>
+      <c r="B141" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C141" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="E141" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F141" s="16">
+        <v>784494590</v>
+      </c>
+      <c r="G141" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J141" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="K141" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L141" s="15">
+        <v>15</v>
+      </c>
+      <c r="M141" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N141" s="17">
+        <v>135000</v>
+      </c>
+      <c r="O141" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S26</v>
+      </c>
+      <c r="P141" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FD1EBB-E3E0-44CF-8711-B332127A8F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E8FE75-8E90-48E7-B159-42A559072D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="10785" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semaine 1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="239">
   <si>
     <t>Date</t>
   </si>
@@ -694,6 +694,63 @@
   </si>
   <si>
     <t>Il veut  essayer le produit</t>
+  </si>
+  <si>
+    <t>Aliou Ba</t>
+  </si>
+  <si>
+    <t>774031052</t>
+  </si>
+  <si>
+    <t>Baldé et frère</t>
+  </si>
+  <si>
+    <t>Ngor</t>
+  </si>
+  <si>
+    <t>Mouhamed ba</t>
+  </si>
+  <si>
+    <t>Serigne Fallou GAYE</t>
+  </si>
+  <si>
+    <t>NAFAR BOUTIQUE</t>
+  </si>
+  <si>
+    <t>Asse</t>
+  </si>
+  <si>
+    <t>DJIBRIL laye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il lui reste le café Altimo pots de 200 g 18 cartons et dit qu' on lui avait promis de faire un stockage il lui reste le café refraich stick que je lui est livré le lundi matin </t>
+  </si>
+  <si>
+    <t>Bayakh</t>
+  </si>
+  <si>
+    <t>Mame GOR</t>
+  </si>
+  <si>
+    <t>775903069</t>
+  </si>
+  <si>
+    <t>Bathie</t>
+  </si>
+  <si>
+    <t>Zac Mbao</t>
+  </si>
+  <si>
+    <t>AMADOU Diallo</t>
+  </si>
+  <si>
+    <t>Khadim Lo</t>
+  </si>
+  <si>
+    <t>Il demande de diminuer le prix des produits car c'est cher selon lui,je lui ai parlé du dépôt vente de nouveaux produits mais il demande de voir des échantillons d'abord</t>
+  </si>
+  <si>
+    <t>Dame DIOP</t>
   </si>
 </sst>
 </file>
@@ -1117,8 +1174,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P141" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P141" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P166" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P166" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1431,7 +1488,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P141"/>
+  <dimension ref="A1:P166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -7066,1715 +7123,3005 @@
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A109" s="14">
+      <c r="A109" s="10">
         <v>46198</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D109" s="15" t="s">
+      <c r="D109" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E109" s="15" t="s">
+      <c r="E109" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="F109" s="16">
+      <c r="F109" s="12">
         <v>771165277</v>
       </c>
-      <c r="G109" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I109" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J109" s="15" t="s">
+      <c r="G109" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J109" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="K109" s="15" t="s">
+      <c r="K109" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L109" s="15">
+      <c r="L109" s="11">
         <v>3</v>
       </c>
-      <c r="M109" s="17">
+      <c r="M109" s="13">
         <v>15500</v>
       </c>
-      <c r="N109" s="17">
+      <c r="N109" s="13">
         <v>46500</v>
       </c>
-      <c r="O109" s="18" t="str">
+      <c r="O109" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P109" s="19" t="str">
+      <c r="P109" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A110" s="14">
+      <c r="A110" s="10">
         <v>46198</v>
       </c>
-      <c r="B110" s="15" t="s">
+      <c r="B110" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C110" s="15" t="s">
+      <c r="C110" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D110" s="15" t="s">
+      <c r="D110" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E110" s="15" t="s">
+      <c r="E110" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F110" s="16">
+      <c r="F110" s="12">
         <v>772131614</v>
       </c>
-      <c r="G110" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H110" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I110" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J110" s="15" t="s">
+      <c r="G110" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I110" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J110" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K110" s="15" t="s">
+      <c r="K110" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L110" s="15">
+      <c r="L110" s="11">
         <v>1</v>
       </c>
-      <c r="M110" s="17">
+      <c r="M110" s="13">
         <v>26000</v>
       </c>
-      <c r="N110" s="17">
+      <c r="N110" s="13">
         <v>26000</v>
       </c>
-      <c r="O110" s="18" t="str">
+      <c r="O110" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P110" s="19" t="str">
+      <c r="P110" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A111" s="14">
+      <c r="A111" s="10">
         <v>46197</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C111" s="15" t="s">
+      <c r="C111" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D111" s="15" t="s">
+      <c r="D111" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E111" s="15" t="s">
+      <c r="E111" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="F111" s="16">
+      <c r="F111" s="12">
         <v>772957336</v>
       </c>
-      <c r="G111" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H111" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I111" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J111" s="15" t="s">
+      <c r="G111" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I111" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="K111" s="15" t="s">
+      <c r="K111" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L111" s="15">
+      <c r="L111" s="11">
         <v>5</v>
       </c>
-      <c r="M111" s="17">
+      <c r="M111" s="13">
         <v>6000</v>
       </c>
-      <c r="N111" s="17">
+      <c r="N111" s="13">
         <v>30000</v>
       </c>
-      <c r="O111" s="18" t="str">
+      <c r="O111" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P111" s="19" t="str">
+      <c r="P111" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A112" s="14">
+      <c r="A112" s="10">
         <v>46197</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C112" s="15" t="s">
+      <c r="C112" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D112" s="15" t="s">
+      <c r="D112" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E112" s="15" t="s">
+      <c r="E112" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="F112" s="16">
+      <c r="F112" s="12">
         <v>778356666</v>
       </c>
-      <c r="G112" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H112" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I112" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J112" s="15" t="s">
+      <c r="G112" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I112" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J112" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K112" s="15" t="s">
+      <c r="K112" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L112" s="15">
+      <c r="L112" s="11">
         <v>100</v>
       </c>
-      <c r="M112" s="17">
+      <c r="M112" s="13">
         <v>8750</v>
       </c>
-      <c r="N112" s="17">
+      <c r="N112" s="13">
         <v>875000</v>
       </c>
-      <c r="O112" s="18" t="str">
+      <c r="O112" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P112" s="19" t="str">
+      <c r="P112" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A113" s="14">
+      <c r="A113" s="10">
         <v>46196</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D113" s="15" t="s">
+      <c r="D113" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="E113" s="15" t="s">
+      <c r="E113" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F113" s="16">
+      <c r="F113" s="12">
         <v>783864321</v>
       </c>
-      <c r="G113" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H113" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I113" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J113" s="15" t="s">
+      <c r="G113" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I113" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J113" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="K113" s="15" t="s">
+      <c r="K113" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L113" s="15">
+      <c r="L113" s="11">
         <v>25</v>
       </c>
-      <c r="M113" s="17">
+      <c r="M113" s="13">
         <v>26000</v>
       </c>
-      <c r="N113" s="17">
+      <c r="N113" s="13">
         <v>650000</v>
       </c>
-      <c r="O113" s="18" t="str">
+      <c r="O113" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P113" s="19" t="str">
+      <c r="P113" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A114" s="14">
+      <c r="A114" s="10">
         <v>46196</v>
       </c>
-      <c r="B114" s="15" t="s">
+      <c r="B114" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C114" s="15" t="s">
+      <c r="C114" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D114" s="15" t="s">
+      <c r="D114" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="E114" s="15" t="s">
+      <c r="E114" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F114" s="16">
+      <c r="F114" s="12">
         <v>783864321</v>
       </c>
-      <c r="G114" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I114" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J114" s="15" t="s">
+      <c r="G114" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I114" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J114" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="K114" s="15" t="s">
+      <c r="K114" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L114" s="15">
+      <c r="L114" s="11">
         <v>10</v>
       </c>
-      <c r="M114" s="17">
+      <c r="M114" s="13">
         <v>9000</v>
       </c>
-      <c r="N114" s="17">
+      <c r="N114" s="13">
         <v>90000</v>
       </c>
-      <c r="O114" s="18" t="str">
+      <c r="O114" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P114" s="19" t="str">
+      <c r="P114" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A115" s="14">
+      <c r="A115" s="10">
         <v>46195</v>
       </c>
-      <c r="B115" s="15" t="s">
+      <c r="B115" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D115" s="15" t="s">
+      <c r="D115" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E115" s="15" t="s">
+      <c r="E115" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="F115" s="16">
+      <c r="F115" s="12">
         <v>774187389</v>
       </c>
-      <c r="G115" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H115" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I115" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J115" s="15" t="s">
+      <c r="G115" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J115" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K115" s="15" t="s">
+      <c r="K115" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L115" s="15">
+      <c r="L115" s="11">
         <v>30</v>
       </c>
-      <c r="M115" s="17">
+      <c r="M115" s="13">
         <v>9000</v>
       </c>
-      <c r="N115" s="17">
+      <c r="N115" s="13">
         <v>270000</v>
       </c>
-      <c r="O115" s="18" t="str">
+      <c r="O115" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P115" s="19" t="str">
+      <c r="P115" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A116" s="14">
+      <c r="A116" s="10">
         <v>46195</v>
       </c>
-      <c r="B116" s="15" t="s">
+      <c r="B116" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C116" s="15" t="s">
+      <c r="C116" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D116" s="15" t="s">
+      <c r="D116" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E116" s="15" t="s">
+      <c r="E116" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="F116" s="16">
+      <c r="F116" s="12">
         <v>776212473</v>
       </c>
-      <c r="G116" s="15" t="s">
+      <c r="G116" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H116" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I116" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J116" s="15" t="s">
+      <c r="H116" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I116" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J116" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="K116" s="15" t="s">
+      <c r="K116" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L116" s="15">
+      <c r="L116" s="11">
         <v>10</v>
       </c>
-      <c r="M116" s="17">
+      <c r="M116" s="13">
         <v>9000</v>
       </c>
-      <c r="N116" s="17">
+      <c r="N116" s="13">
         <v>90000</v>
       </c>
-      <c r="O116" s="18" t="str">
+      <c r="O116" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P116" s="19" t="str">
+      <c r="P116" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A117" s="14">
+      <c r="A117" s="10">
         <v>46195</v>
       </c>
-      <c r="B117" s="15" t="s">
+      <c r="B117" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D117" s="15" t="s">
+      <c r="D117" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E117" s="15" t="s">
+      <c r="E117" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="F117" s="16">
+      <c r="F117" s="12">
         <v>779724512</v>
       </c>
-      <c r="G117" s="15" t="s">
+      <c r="G117" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H117" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I117" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J117" s="15" t="s">
+      <c r="H117" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I117" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J117" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="K117" s="15" t="s">
+      <c r="K117" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L117" s="15">
+      <c r="L117" s="11">
         <v>25</v>
       </c>
-      <c r="M117" s="17">
+      <c r="M117" s="13">
         <v>9000</v>
       </c>
-      <c r="N117" s="17">
+      <c r="N117" s="13">
         <v>225000</v>
       </c>
-      <c r="O117" s="18" t="str">
+      <c r="O117" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P117" s="19" t="str">
+      <c r="P117" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A118" s="14">
+      <c r="A118" s="10">
         <v>46200</v>
       </c>
-      <c r="B118" s="15" t="s">
+      <c r="B118" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C118" s="15" t="s">
+      <c r="C118" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D118" s="15" t="s">
+      <c r="D118" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E118" s="15" t="s">
+      <c r="E118" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="F118" s="16">
+      <c r="F118" s="12">
         <v>773739328</v>
       </c>
-      <c r="G118" s="15" t="s">
+      <c r="G118" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H118" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I118" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J118" s="15" t="s">
+      <c r="H118" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I118" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J118" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K118" s="15" t="s">
+      <c r="K118" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L118" s="15">
+      <c r="L118" s="11">
         <v>3</v>
       </c>
-      <c r="M118" s="17">
+      <c r="M118" s="13">
         <v>19500</v>
       </c>
-      <c r="N118" s="17">
+      <c r="N118" s="13">
         <v>58500</v>
       </c>
-      <c r="O118" s="18" t="str">
+      <c r="O118" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P118" s="19" t="str">
+      <c r="P118" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A119" s="14">
+      <c r="A119" s="10">
         <v>46200</v>
       </c>
-      <c r="B119" s="15" t="s">
+      <c r="B119" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C119" s="15" t="s">
+      <c r="C119" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D119" s="15" t="s">
+      <c r="D119" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E119" s="15" t="s">
+      <c r="E119" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="F119" s="16">
+      <c r="F119" s="12">
         <v>775630094</v>
       </c>
-      <c r="G119" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H119" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I119" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J119" s="15" t="s">
+      <c r="G119" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I119" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J119" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K119" s="15" t="s">
+      <c r="K119" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L119" s="11">
         <v>1</v>
       </c>
-      <c r="M119" s="17">
+      <c r="M119" s="13">
         <v>12000</v>
       </c>
-      <c r="N119" s="17">
+      <c r="N119" s="13">
         <v>12000</v>
       </c>
-      <c r="O119" s="18" t="str">
+      <c r="O119" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P119" s="19" t="str">
+      <c r="P119" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A120" s="14">
+      <c r="A120" s="10">
         <v>46200</v>
       </c>
-      <c r="B120" s="15" t="s">
+      <c r="B120" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C120" s="15" t="s">
+      <c r="C120" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D120" s="15" t="s">
+      <c r="D120" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E120" s="15" t="s">
+      <c r="E120" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F120" s="16">
+      <c r="F120" s="12">
         <v>775014335</v>
       </c>
-      <c r="G120" s="15" t="s">
+      <c r="G120" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H120" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I120" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J120" s="15" t="s">
+      <c r="H120" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I120" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J120" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K120" s="15" t="s">
+      <c r="K120" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L120" s="15">
+      <c r="L120" s="11">
         <v>25</v>
       </c>
-      <c r="M120" s="17">
+      <c r="M120" s="13">
         <v>26000</v>
       </c>
-      <c r="N120" s="17">
+      <c r="N120" s="13">
         <v>650000</v>
       </c>
-      <c r="O120" s="18" t="str">
+      <c r="O120" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P120" s="19" t="str">
+      <c r="P120" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A121" s="14">
+      <c r="A121" s="10">
         <v>46200</v>
       </c>
-      <c r="B121" s="15" t="s">
+      <c r="B121" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C121" s="15" t="s">
+      <c r="C121" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D121" s="15" t="s">
+      <c r="D121" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E121" s="15" t="s">
+      <c r="E121" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="F121" s="16">
+      <c r="F121" s="12">
         <v>772788635</v>
       </c>
-      <c r="G121" s="15" t="s">
+      <c r="G121" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H121" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I121" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J121" s="15" t="s">
+      <c r="H121" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I121" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J121" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K121" s="15" t="s">
+      <c r="K121" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L121" s="15">
+      <c r="L121" s="11">
         <v>2</v>
       </c>
-      <c r="M121" s="17">
+      <c r="M121" s="13">
         <v>15500</v>
       </c>
-      <c r="N121" s="17">
+      <c r="N121" s="13">
         <v>31000</v>
       </c>
-      <c r="O121" s="18" t="str">
+      <c r="O121" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P121" s="19" t="str">
+      <c r="P121" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A122" s="14">
+      <c r="A122" s="10">
         <v>46200</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C122" s="15" t="s">
+      <c r="C122" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D122" s="15" t="s">
+      <c r="D122" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E122" s="15" t="s">
+      <c r="E122" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F122" s="16">
+      <c r="F122" s="12">
         <v>775197108</v>
       </c>
-      <c r="G122" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H122" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I122" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J122" s="15" t="s">
+      <c r="G122" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I122" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J122" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K122" s="15" t="s">
+      <c r="K122" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="L122" s="15">
+      <c r="L122" s="11">
         <v>5</v>
       </c>
-      <c r="M122" s="17">
+      <c r="M122" s="13">
         <v>17500</v>
       </c>
-      <c r="N122" s="17">
+      <c r="N122" s="13">
         <v>87500</v>
       </c>
-      <c r="O122" s="18" t="str">
+      <c r="O122" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P122" s="19" t="str">
+      <c r="P122" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A123" s="14">
+      <c r="A123" s="10">
         <v>46198</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C123" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D123" s="15" t="s">
+      <c r="D123" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E123" s="15" t="s">
+      <c r="E123" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="F123" s="16">
+      <c r="F123" s="12">
         <v>768059355</v>
       </c>
-      <c r="G123" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H123" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I123" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J123" s="15"/>
-      <c r="K123" s="15" t="s">
+      <c r="G123" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I123" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J123" s="11"/>
+      <c r="K123" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L123" s="15">
+      <c r="L123" s="11">
         <v>100</v>
       </c>
-      <c r="M123" s="17">
+      <c r="M123" s="13">
         <v>28000</v>
       </c>
-      <c r="N123" s="17">
+      <c r="N123" s="13">
         <v>2800000</v>
       </c>
-      <c r="O123" s="18" t="str">
+      <c r="O123" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P123" s="19" t="str">
+      <c r="P123" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A124" s="14">
+      <c r="A124" s="10">
         <v>46198</v>
       </c>
-      <c r="B124" s="15" t="s">
+      <c r="B124" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D124" s="15" t="s">
+      <c r="D124" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E124" s="15" t="s">
+      <c r="E124" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F124" s="16">
+      <c r="F124" s="12">
         <v>774414059</v>
       </c>
-      <c r="G124" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H124" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J124" s="15" t="s">
+      <c r="G124" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J124" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K124" s="15" t="s">
+      <c r="K124" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L124" s="15">
+      <c r="L124" s="11">
         <v>1</v>
       </c>
-      <c r="M124" s="17">
+      <c r="M124" s="13">
         <v>19500</v>
       </c>
-      <c r="N124" s="17">
+      <c r="N124" s="13">
         <v>19500</v>
       </c>
-      <c r="O124" s="18" t="str">
+      <c r="O124" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P124" s="19" t="str">
+      <c r="P124" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A125" s="14">
+      <c r="A125" s="10">
         <v>46198</v>
       </c>
-      <c r="B125" s="15" t="s">
+      <c r="B125" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C125" s="15" t="s">
+      <c r="C125" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D125" s="15" t="s">
+      <c r="D125" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E125" s="15" t="s">
+      <c r="E125" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F125" s="16">
+      <c r="F125" s="12">
         <v>774414059</v>
       </c>
-      <c r="G125" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H125" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I125" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J125" s="15" t="s">
+      <c r="G125" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I125" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J125" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K125" s="15" t="s">
+      <c r="K125" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L125" s="15">
+      <c r="L125" s="11">
         <v>30</v>
       </c>
-      <c r="M125" s="17">
+      <c r="M125" s="13">
         <v>9000</v>
       </c>
-      <c r="N125" s="17">
+      <c r="N125" s="13">
         <v>270000</v>
       </c>
-      <c r="O125" s="18" t="str">
+      <c r="O125" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P125" s="19" t="str">
+      <c r="P125" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A126" s="14">
+      <c r="A126" s="10">
         <v>46198</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B126" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C126" s="15" t="s">
+      <c r="C126" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D126" s="15" t="s">
+      <c r="D126" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="E126" s="15" t="s">
+      <c r="E126" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F126" s="16">
+      <c r="F126" s="12">
         <v>774414059</v>
       </c>
-      <c r="G126" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H126" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I126" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J126" s="15" t="s">
+      <c r="G126" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J126" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="K126" s="15" t="s">
+      <c r="K126" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="L126" s="15">
+      <c r="L126" s="11">
         <v>30</v>
       </c>
-      <c r="M126" s="17">
+      <c r="M126" s="13">
         <v>9000</v>
       </c>
-      <c r="N126" s="17">
+      <c r="N126" s="13">
         <v>270000</v>
       </c>
-      <c r="O126" s="18" t="str">
+      <c r="O126" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P126" s="19" t="str">
+      <c r="P126" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A127" s="14">
+      <c r="A127" s="10">
         <v>46197</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C127" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D127" s="15" t="s">
+      <c r="D127" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E127" s="15" t="s">
+      <c r="E127" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F127" s="16">
+      <c r="F127" s="12">
         <v>777854561</v>
       </c>
-      <c r="G127" s="15" t="s">
+      <c r="G127" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H127" s="15" t="s">
+      <c r="H127" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I127" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J127" s="15" t="s">
+      <c r="I127" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J127" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="K127" s="15" t="s">
+      <c r="K127" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="L127" s="15">
+      <c r="L127" s="11">
         <v>1</v>
       </c>
-      <c r="M127" s="17">
+      <c r="M127" s="13">
         <v>15500</v>
       </c>
-      <c r="N127" s="17">
+      <c r="N127" s="13">
         <v>15500</v>
       </c>
-      <c r="O127" s="18" t="str">
+      <c r="O127" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P127" s="19" t="str">
+      <c r="P127" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A128" s="14">
+      <c r="A128" s="10">
         <v>46197</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B128" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C128" s="15" t="s">
+      <c r="C128" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D128" s="15" t="s">
+      <c r="D128" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E128" s="15" t="s">
+      <c r="E128" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="F128" s="16">
+      <c r="F128" s="12">
         <v>775539595</v>
       </c>
-      <c r="G128" s="15" t="s">
+      <c r="G128" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="H128" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I128" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J128" s="15" t="s">
+      <c r="H128" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J128" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K128" s="15" t="s">
+      <c r="K128" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="L128" s="15">
+      <c r="L128" s="11">
         <v>1</v>
       </c>
-      <c r="M128" s="17">
+      <c r="M128" s="13">
         <v>19500</v>
       </c>
-      <c r="N128" s="17">
+      <c r="N128" s="13">
         <v>19500</v>
       </c>
-      <c r="O128" s="18" t="str">
+      <c r="O128" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P128" s="19" t="str">
+      <c r="P128" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="129" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A129" s="14">
+      <c r="A129" s="10">
         <v>46197</v>
       </c>
-      <c r="B129" s="15" t="s">
+      <c r="B129" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="C129" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D129" s="15" t="s">
+      <c r="D129" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E129" s="15" t="s">
+      <c r="E129" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F129" s="16">
+      <c r="F129" s="12">
         <v>773178746</v>
       </c>
-      <c r="G129" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H129" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I129" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J129" s="15" t="s">
+      <c r="G129" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J129" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="K129" s="15" t="s">
+      <c r="K129" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L129" s="15">
+      <c r="L129" s="11">
         <v>5</v>
       </c>
-      <c r="M129" s="17">
+      <c r="M129" s="13">
         <v>26500</v>
       </c>
-      <c r="N129" s="17">
+      <c r="N129" s="13">
         <v>132500</v>
       </c>
-      <c r="O129" s="18" t="str">
+      <c r="O129" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P129" s="19" t="str">
+      <c r="P129" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A130" s="14">
+      <c r="A130" s="10">
         <v>46197</v>
       </c>
-      <c r="B130" s="15" t="s">
+      <c r="B130" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C130" s="15" t="s">
+      <c r="C130" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D130" s="15" t="s">
+      <c r="D130" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E130" s="15" t="s">
+      <c r="E130" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F130" s="16">
+      <c r="F130" s="12">
         <v>773178746</v>
       </c>
-      <c r="G130" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H130" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I130" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J130" s="15" t="s">
+      <c r="G130" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I130" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J130" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="K130" s="15" t="s">
+      <c r="K130" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L130" s="15">
+      <c r="L130" s="11">
         <v>1</v>
       </c>
-      <c r="M130" s="17">
+      <c r="M130" s="13">
         <v>26000</v>
       </c>
-      <c r="N130" s="17">
+      <c r="N130" s="13">
         <v>26000</v>
       </c>
-      <c r="O130" s="18" t="str">
+      <c r="O130" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P130" s="19" t="str">
+      <c r="P130" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A131" s="14">
+      <c r="A131" s="10">
         <v>46197</v>
       </c>
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D131" s="15" t="s">
+      <c r="D131" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E131" s="15" t="s">
+      <c r="E131" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F131" s="16">
+      <c r="F131" s="12">
         <v>777854561</v>
       </c>
-      <c r="G131" s="15" t="s">
+      <c r="G131" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H131" s="15" t="s">
+      <c r="H131" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I131" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J131" s="15" t="s">
+      <c r="I131" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J131" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="K131" s="15" t="s">
+      <c r="K131" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="L131" s="15">
+      <c r="L131" s="11">
         <v>5</v>
       </c>
-      <c r="M131" s="17">
+      <c r="M131" s="13">
         <v>26500</v>
       </c>
-      <c r="N131" s="17">
+      <c r="N131" s="13">
         <v>132500</v>
       </c>
-      <c r="O131" s="18" t="str">
+      <c r="O131" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P131" s="19" t="str">
+      <c r="P131" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A132" s="14">
+      <c r="A132" s="10">
         <v>46197</v>
       </c>
-      <c r="B132" s="15" t="s">
+      <c r="B132" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C132" s="15" t="s">
+      <c r="C132" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D132" s="15" t="s">
+      <c r="D132" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E132" s="15" t="s">
+      <c r="E132" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F132" s="16">
+      <c r="F132" s="12">
         <v>773178746</v>
       </c>
-      <c r="G132" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H132" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I132" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J132" s="15" t="s">
+      <c r="G132" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I132" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J132" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="K132" s="15" t="s">
+      <c r="K132" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="L132" s="15">
+      <c r="L132" s="11">
         <v>1</v>
       </c>
-      <c r="M132" s="17">
+      <c r="M132" s="13">
         <v>33500</v>
       </c>
-      <c r="N132" s="17">
+      <c r="N132" s="13">
         <v>33500</v>
       </c>
-      <c r="O132" s="18" t="str">
+      <c r="O132" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P132" s="19" t="str">
+      <c r="P132" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A133" s="14">
+      <c r="A133" s="10">
         <v>46197</v>
       </c>
-      <c r="B133" s="15" t="s">
+      <c r="B133" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C133" s="15" t="s">
+      <c r="C133" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D133" s="15" t="s">
+      <c r="D133" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E133" s="15" t="s">
+      <c r="E133" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F133" s="16">
+      <c r="F133" s="12">
         <v>777854561</v>
       </c>
-      <c r="G133" s="15" t="s">
+      <c r="G133" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H133" s="15" t="s">
+      <c r="H133" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I133" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J133" s="15" t="s">
+      <c r="I133" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J133" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="K133" s="15" t="s">
+      <c r="K133" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="L133" s="15">
+      <c r="L133" s="11">
         <v>1</v>
       </c>
-      <c r="M133" s="17">
+      <c r="M133" s="13">
         <v>15500</v>
       </c>
-      <c r="N133" s="17">
+      <c r="N133" s="13">
         <v>15500</v>
       </c>
-      <c r="O133" s="18" t="str">
+      <c r="O133" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P133" s="19" t="str">
+      <c r="P133" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A134" s="14">
+      <c r="A134" s="10">
         <v>46197</v>
       </c>
-      <c r="B134" s="15" t="s">
+      <c r="B134" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C134" s="15" t="s">
+      <c r="C134" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D134" s="15" t="s">
+      <c r="D134" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E134" s="15" t="s">
+      <c r="E134" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F134" s="16">
+      <c r="F134" s="12">
         <v>774091250</v>
       </c>
-      <c r="G134" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H134" s="15" t="s">
+      <c r="G134" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I134" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J134" s="15" t="s">
+      <c r="I134" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J134" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K134" s="15" t="s">
+      <c r="K134" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L134" s="15">
-        <v>13</v>
-      </c>
-      <c r="M134" s="17">
+      <c r="L134" s="11">
+        <v>13</v>
+      </c>
+      <c r="M134" s="13">
         <v>9000</v>
       </c>
-      <c r="N134" s="17">
+      <c r="N134" s="13">
         <v>117000</v>
       </c>
-      <c r="O134" s="18" t="str">
+      <c r="O134" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P134" s="19" t="str">
+      <c r="P134" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A135" s="14">
+      <c r="A135" s="10">
         <v>46197</v>
       </c>
-      <c r="B135" s="15" t="s">
+      <c r="B135" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C135" s="15" t="s">
+      <c r="C135" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="15" t="s">
+      <c r="D135" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E135" s="15" t="s">
+      <c r="E135" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F135" s="16">
+      <c r="F135" s="12">
         <v>783942599</v>
       </c>
-      <c r="G135" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H135" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I135" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J135" s="15" t="s">
+      <c r="G135" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I135" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J135" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K135" s="15" t="s">
+      <c r="K135" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L135" s="15">
+      <c r="L135" s="11">
         <v>10</v>
       </c>
-      <c r="M135" s="17">
+      <c r="M135" s="13">
         <v>9000</v>
       </c>
-      <c r="N135" s="17">
+      <c r="N135" s="13">
         <v>90000</v>
       </c>
-      <c r="O135" s="18" t="str">
+      <c r="O135" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P135" s="19" t="str">
+      <c r="P135" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="136" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A136" s="14">
+      <c r="A136" s="10">
         <v>46197</v>
       </c>
-      <c r="B136" s="15" t="s">
+      <c r="B136" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C136" s="15" t="s">
+      <c r="C136" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D136" s="15" t="s">
+      <c r="D136" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="E136" s="15" t="s">
+      <c r="E136" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="F136" s="16">
+      <c r="F136" s="12">
         <v>773231589</v>
       </c>
-      <c r="G136" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H136" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I136" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J136" s="15" t="s">
+      <c r="G136" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I136" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J136" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K136" s="15" t="s">
+      <c r="K136" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L136" s="15">
+      <c r="L136" s="11">
         <v>5</v>
       </c>
-      <c r="M136" s="17">
+      <c r="M136" s="13">
         <v>9000</v>
       </c>
-      <c r="N136" s="17">
+      <c r="N136" s="13">
         <v>45000</v>
       </c>
-      <c r="O136" s="18" t="str">
+      <c r="O136" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P136" s="19" t="str">
+      <c r="P136" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A137" s="14">
+      <c r="A137" s="10">
         <v>46196</v>
       </c>
-      <c r="B137" s="15" t="s">
+      <c r="B137" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C137" s="15" t="s">
+      <c r="C137" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D137" s="15" t="s">
+      <c r="D137" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E137" s="15" t="s">
+      <c r="E137" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F137" s="16">
+      <c r="F137" s="12">
         <v>788217757</v>
       </c>
-      <c r="G137" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H137" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I137" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J137" s="15" t="s">
+      <c r="G137" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I137" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J137" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="K137" s="15" t="s">
+      <c r="K137" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L137" s="15">
+      <c r="L137" s="11">
         <v>25</v>
       </c>
-      <c r="M137" s="17">
+      <c r="M137" s="13">
         <v>28000</v>
       </c>
-      <c r="N137" s="17">
+      <c r="N137" s="13">
         <v>700000</v>
       </c>
-      <c r="O137" s="18" t="str">
+      <c r="O137" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P137" s="19" t="str">
+      <c r="P137" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A138" s="14">
+      <c r="A138" s="10">
         <v>46196</v>
       </c>
-      <c r="B138" s="15" t="s">
+      <c r="B138" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C138" s="15" t="s">
+      <c r="C138" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D138" s="15" t="s">
+      <c r="D138" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E138" s="15" t="s">
+      <c r="E138" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F138" s="16">
+      <c r="F138" s="12">
         <v>774993694</v>
       </c>
-      <c r="G138" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H138" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I138" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J138" s="15" t="s">
+      <c r="G138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I138" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J138" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="K138" s="15" t="s">
+      <c r="K138" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="L138" s="15">
+      <c r="L138" s="11">
         <v>50</v>
       </c>
-      <c r="M138" s="17">
+      <c r="M138" s="13">
         <v>12000</v>
       </c>
-      <c r="N138" s="17">
+      <c r="N138" s="13">
         <v>600000</v>
       </c>
-      <c r="O138" s="18" t="str">
+      <c r="O138" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P138" s="19" t="str">
+      <c r="P138" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A139" s="14">
+      <c r="A139" s="10">
         <v>46196</v>
       </c>
-      <c r="B139" s="15" t="s">
+      <c r="B139" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C139" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D139" s="15" t="s">
+      <c r="D139" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E139" s="15" t="s">
+      <c r="E139" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="F139" s="16">
+      <c r="F139" s="12">
         <v>775171537</v>
       </c>
-      <c r="G139" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H139" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I139" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J139" s="15" t="s">
+      <c r="G139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J139" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K139" s="15" t="s">
+      <c r="K139" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="L139" s="15">
+      <c r="L139" s="11">
         <v>25</v>
       </c>
-      <c r="M139" s="17">
+      <c r="M139" s="13">
         <v>12000</v>
       </c>
-      <c r="N139" s="17">
+      <c r="N139" s="13">
         <v>300000</v>
       </c>
-      <c r="O139" s="18" t="str">
+      <c r="O139" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P139" s="19" t="str">
+      <c r="P139" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="140" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A140" s="14">
+      <c r="A140" s="10">
         <v>46196</v>
       </c>
-      <c r="B140" s="15" t="s">
+      <c r="B140" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C140" s="15" t="s">
+      <c r="C140" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D140" s="15" t="s">
+      <c r="D140" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E140" s="15" t="s">
+      <c r="E140" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="F140" s="16">
+      <c r="F140" s="12">
         <v>768059355</v>
       </c>
-      <c r="G140" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H140" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I140" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J140" s="15" t="s">
+      <c r="G140" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I140" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J140" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K140" s="15" t="s">
+      <c r="K140" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="L140" s="15">
+      <c r="L140" s="11">
         <v>50</v>
       </c>
-      <c r="M140" s="17">
+      <c r="M140" s="13">
         <v>12000</v>
       </c>
-      <c r="N140" s="17">
+      <c r="N140" s="13">
         <v>600000</v>
       </c>
-      <c r="O140" s="18" t="str">
+      <c r="O140" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P140" s="19" t="str">
+      <c r="P140" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A141" s="14">
+      <c r="A141" s="10">
         <v>46195</v>
       </c>
-      <c r="B141" s="15" t="s">
+      <c r="B141" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C141" s="15" t="s">
+      <c r="C141" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D141" s="15" t="s">
+      <c r="D141" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="E141" s="15" t="s">
+      <c r="E141" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="F141" s="16">
+      <c r="F141" s="12">
         <v>784494590</v>
       </c>
-      <c r="G141" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H141" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I141" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J141" s="15" t="s">
+      <c r="G141" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I141" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J141" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="K141" s="15" t="s">
+      <c r="K141" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L141" s="15">
-        <v>15</v>
-      </c>
-      <c r="M141" s="17">
+      <c r="L141" s="11">
+        <v>15</v>
+      </c>
+      <c r="M141" s="13">
         <v>9000</v>
       </c>
-      <c r="N141" s="17">
+      <c r="N141" s="13">
         <v>135000</v>
       </c>
-      <c r="O141" s="18" t="str">
+      <c r="O141" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S26</v>
       </c>
-      <c r="P141" s="19" t="str">
+      <c r="P141" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A142" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B142" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C142" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E142" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F142" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="G142" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H142" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I142" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J142" s="15"/>
+      <c r="K142" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L142" s="15">
+        <v>50</v>
+      </c>
+      <c r="M142" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N142" s="17">
+        <v>1300000</v>
+      </c>
+      <c r="O142" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P142" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A143" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B143" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C143" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E143" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F143" s="16">
+        <v>775544532</v>
+      </c>
+      <c r="G143" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H143" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J143" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K143" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L143" s="15">
+        <v>25</v>
+      </c>
+      <c r="M143" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N143" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O143" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P143" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A144" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B144" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C144" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E144" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F144" s="16">
+        <v>779235028</v>
+      </c>
+      <c r="G144" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I144" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J144" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K144" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L144" s="15">
+        <v>55</v>
+      </c>
+      <c r="M144" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N144" s="17">
+        <v>495000</v>
+      </c>
+      <c r="O144" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P144" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A145" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B145" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C145" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E145" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F145" s="16">
+        <v>776862787</v>
+      </c>
+      <c r="G145" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H145" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I145" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J145" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K145" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L145" s="15">
+        <v>25</v>
+      </c>
+      <c r="M145" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N145" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O145" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P145" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A146" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B146" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C146" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E146" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="F146" s="16">
+        <v>773482683</v>
+      </c>
+      <c r="G146" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H146" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J146" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K146" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L146" s="15">
+        <v>10</v>
+      </c>
+      <c r="M146" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N146" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O146" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P146" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A147" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B147" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C147" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E147" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F147" s="16">
+        <v>776862787</v>
+      </c>
+      <c r="G147" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H147" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I147" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J147" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K147" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L147" s="15">
+        <v>5</v>
+      </c>
+      <c r="M147" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N147" s="17">
+        <v>97500</v>
+      </c>
+      <c r="O147" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P147" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A148" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B148" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C148" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E148" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="F148" s="16">
+        <v>776058374</v>
+      </c>
+      <c r="G148" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I148" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J148" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K148" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L148" s="15">
+        <v>25</v>
+      </c>
+      <c r="M148" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N148" s="17">
+        <v>225000</v>
+      </c>
+      <c r="O148" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P148" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A149" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E149" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F149" s="16">
+        <v>775586819</v>
+      </c>
+      <c r="G149" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H149" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I149" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J149" s="15"/>
+      <c r="K149" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L149" s="15">
+        <v>25</v>
+      </c>
+      <c r="M149" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N149" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O149" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P149" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A150" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C150" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D150" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F150" s="16">
+        <v>772131614</v>
+      </c>
+      <c r="G150" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I150" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J150" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K150" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L150" s="15">
+        <v>1</v>
+      </c>
+      <c r="M150" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N150" s="17">
+        <v>19500</v>
+      </c>
+      <c r="O150" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P150" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A151" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C151" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D151" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E151" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F151" s="16">
+        <v>772131614</v>
+      </c>
+      <c r="G151" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I151" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J151" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K151" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="L151" s="15">
+        <v>1</v>
+      </c>
+      <c r="M151" s="17">
+        <v>15000</v>
+      </c>
+      <c r="N151" s="17">
+        <v>15000</v>
+      </c>
+      <c r="O151" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P151" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A152" s="14">
+        <v>46203</v>
+      </c>
+      <c r="B152" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D152" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E152" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F152" s="16">
+        <v>775171537</v>
+      </c>
+      <c r="G152" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I152" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J152" s="15"/>
+      <c r="K152" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L152" s="15">
+        <v>100</v>
+      </c>
+      <c r="M152" s="17">
+        <v>19000</v>
+      </c>
+      <c r="N152" s="17">
+        <v>1900000</v>
+      </c>
+      <c r="O152" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P152" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A153" s="14">
+        <v>46202</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E153" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F153" s="16">
+        <v>774927422</v>
+      </c>
+      <c r="G153" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I153" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J153" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="K153" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L153" s="15">
+        <v>25</v>
+      </c>
+      <c r="M153" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N153" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O153" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P153" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A154" s="14">
+        <v>46202</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C154" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E154" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F154" s="16">
+        <v>776149093</v>
+      </c>
+      <c r="G154" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H154" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I154" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J154" s="15"/>
+      <c r="K154" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L154" s="15">
+        <v>30</v>
+      </c>
+      <c r="M154" s="17">
+        <v>6000</v>
+      </c>
+      <c r="N154" s="17">
+        <v>180000</v>
+      </c>
+      <c r="O154" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P154" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A155" s="14">
+        <v>46202</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C155" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E155" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F155" s="16">
+        <v>762974040</v>
+      </c>
+      <c r="G155" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I155" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J155" s="15"/>
+      <c r="K155" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L155" s="15">
+        <v>25</v>
+      </c>
+      <c r="M155" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N155" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O155" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P155" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juin</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A156" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B156" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E156" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F156" s="16">
+        <v>774289051</v>
+      </c>
+      <c r="G156" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I156" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J156" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="K156" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L156" s="15">
+        <v>25</v>
+      </c>
+      <c r="M156" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N156" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O156" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P156" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" ht="55.9" x14ac:dyDescent="0.45">
+      <c r="A157" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B157" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C157" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E157" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F157" s="16">
+        <v>778657940</v>
+      </c>
+      <c r="G157" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I157" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J157" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="K157" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L157" s="15">
+        <v>25</v>
+      </c>
+      <c r="M157" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N157" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O157" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P157" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A158" s="14">
+        <v>46205</v>
+      </c>
+      <c r="B158" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C158" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="E158" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F158" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="G158" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H158" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I158" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J158" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K158" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L158" s="15">
+        <v>5</v>
+      </c>
+      <c r="M158" s="17">
+        <v>12000</v>
+      </c>
+      <c r="N158" s="17">
+        <v>60000</v>
+      </c>
+      <c r="O158" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P158" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A159" s="14">
+        <v>46205</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C159" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D159" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="E159" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F159" s="16">
+        <v>765956010</v>
+      </c>
+      <c r="G159" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I159" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J159" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K159" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L159" s="15">
+        <v>20</v>
+      </c>
+      <c r="M159" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N159" s="17">
+        <v>180000</v>
+      </c>
+      <c r="O159" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P159" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A160" s="14">
+        <v>46205</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C160" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D160" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="E160" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="F160" s="16">
+        <v>772506388</v>
+      </c>
+      <c r="G160" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H160" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I160" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J160" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K160" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L160" s="15">
+        <v>10</v>
+      </c>
+      <c r="M160" s="17">
+        <v>9000</v>
+      </c>
+      <c r="N160" s="17">
+        <v>90000</v>
+      </c>
+      <c r="O160" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P160" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A161" s="14">
+        <v>46205</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C161" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D161" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="E161" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F161" s="16">
+        <v>775903069</v>
+      </c>
+      <c r="G161" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H161" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I161" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J161" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K161" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="L161" s="15">
+        <v>1</v>
+      </c>
+      <c r="M161" s="17">
+        <v>17500</v>
+      </c>
+      <c r="N161" s="17">
+        <v>17500</v>
+      </c>
+      <c r="O161" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P161" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A162" s="14">
+        <v>46205</v>
+      </c>
+      <c r="B162" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C162" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D162" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="E162" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F162" s="16">
+        <v>775903069</v>
+      </c>
+      <c r="G162" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H162" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I162" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J162" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K162" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="L162" s="15">
+        <v>1</v>
+      </c>
+      <c r="M162" s="17">
+        <v>33500</v>
+      </c>
+      <c r="N162" s="17">
+        <v>33500</v>
+      </c>
+      <c r="O162" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P162" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A163" s="14">
+        <v>46205</v>
+      </c>
+      <c r="B163" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C163" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D163" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="E163" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F163" s="16">
+        <v>775903069</v>
+      </c>
+      <c r="G163" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H163" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I163" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J163" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K163" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L163" s="15">
+        <v>10</v>
+      </c>
+      <c r="M163" s="17">
+        <v>6000</v>
+      </c>
+      <c r="N163" s="17">
+        <v>60000</v>
+      </c>
+      <c r="O163" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P163" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" ht="55.9" x14ac:dyDescent="0.45">
+      <c r="A164" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C164" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E164" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F164" s="16">
+        <v>770217868</v>
+      </c>
+      <c r="G164" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I164" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J164" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="K164" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L164" s="15">
+        <v>50</v>
+      </c>
+      <c r="M164" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N164" s="17">
+        <v>1300000</v>
+      </c>
+      <c r="O164" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P164" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" ht="55.9" x14ac:dyDescent="0.45">
+      <c r="A165" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B165" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E165" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F165" s="16">
+        <v>770217868</v>
+      </c>
+      <c r="G165" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I165" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J165" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="K165" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L165" s="15">
+        <v>25</v>
+      </c>
+      <c r="M165" s="17">
+        <v>19500</v>
+      </c>
+      <c r="N165" s="17">
+        <v>487500</v>
+      </c>
+      <c r="O165" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P165" s="19" t="str">
+        <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
+        <v>juillet</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+      <c r="A166" s="14">
+        <v>46203</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C166" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D166" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E166" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F166" s="16">
+        <v>774216339</v>
+      </c>
+      <c r="G166" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I166" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J166" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K166" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L166" s="15">
+        <v>25</v>
+      </c>
+      <c r="M166" s="17">
+        <v>26000</v>
+      </c>
+      <c r="N166" s="17">
+        <v>650000</v>
+      </c>
+      <c r="O166" s="18" t="str">
+        <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
+        <v>S27</v>
+      </c>
+      <c r="P166" s="19" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juin</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057DDBA3-F215-47C8-B986-BF3DB7E5908C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068F7053-C449-4E70-B072-31B36E02F2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -466,22 +466,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2462,1135 +2446,1143 @@
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A27" s="12">
+      <c r="A27" s="8">
         <v>46213</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="10">
         <v>775630094</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="13" t="s">
+      <c r="H27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K27" s="13" t="s">
+      <c r="K27" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="9">
         <v>1</v>
       </c>
-      <c r="M27" s="15">
+      <c r="M27" s="11">
         <v>11500</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="11">
         <v>11500</v>
       </c>
-      <c r="O27" s="16" t="str">
+      <c r="O27" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P27" s="17" t="str">
+      <c r="P27" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A28" s="12">
+      <c r="A28" s="8">
         <v>46213</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="10">
         <v>775630094</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="13" t="s">
+      <c r="H28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K28" s="13" t="s">
+      <c r="K28" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="9">
         <v>2</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28" s="11">
         <v>15500</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28" s="11">
         <v>31000</v>
       </c>
-      <c r="O28" s="16" t="str">
+      <c r="O28" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P28" s="17" t="str">
+      <c r="P28" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A29" s="12">
+      <c r="A29" s="8">
         <v>46213</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="10">
         <v>775630094</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="13" t="s">
+      <c r="H29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="K29" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="9">
         <v>4</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29" s="11">
         <v>19500</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="11">
         <v>78000</v>
       </c>
-      <c r="O29" s="16" t="str">
+      <c r="O29" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P29" s="17" t="str">
+      <c r="P29" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A30" s="12">
+      <c r="A30" s="8">
         <v>46213</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="10">
         <v>775630094</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="13" t="s">
+      <c r="H30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="K30" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="9">
         <v>25</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30" s="11">
         <v>28000</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30" s="11">
         <v>700000</v>
       </c>
-      <c r="O30" s="16" t="str">
+      <c r="O30" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P30" s="17" t="str">
+      <c r="P30" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A31" s="12">
+      <c r="A31" s="8">
         <v>46213</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="10">
         <v>781985160</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="13" t="s">
+      <c r="H31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K31" s="13" t="s">
+      <c r="K31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="9">
         <v>25</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="11">
         <v>26000</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="11">
         <v>650000</v>
       </c>
-      <c r="O31" s="16" t="str">
+      <c r="O31" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P31" s="17" t="str">
+      <c r="P31" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A32" s="12">
+      <c r="A32" s="8">
         <v>46213</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="10">
         <v>775586819</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13" t="s">
+      <c r="H32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="9">
         <v>100</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="11">
         <v>26000</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="11">
         <v>2600000</v>
       </c>
-      <c r="O32" s="16" t="str">
+      <c r="O32" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P32" s="17" t="str">
+      <c r="P32" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A33" s="12">
+      <c r="A33" s="8">
         <v>46212</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="10">
         <v>775661455</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="13" t="s">
+      <c r="H33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K33" s="13" t="s">
+      <c r="K33" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="9">
         <v>25</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33" s="11">
         <v>26000</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33" s="11">
         <v>650000</v>
       </c>
-      <c r="O33" s="16" t="str">
+      <c r="O33" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P33" s="17" t="str">
+      <c r="P33" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A34" s="12">
+      <c r="A34" s="8">
         <v>46212</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="10">
         <v>774993694</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="13" t="s">
+      <c r="H34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K34" s="13" t="s">
+      <c r="K34" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L34" s="13">
+      <c r="L34" s="9">
         <v>100</v>
       </c>
-      <c r="M34" s="15">
+      <c r="M34" s="11">
         <v>26000</v>
       </c>
-      <c r="N34" s="15">
+      <c r="N34" s="11">
         <v>2600000</v>
       </c>
-      <c r="O34" s="16" t="str">
+      <c r="O34" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P34" s="17" t="str">
+      <c r="P34" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A35" s="12">
+      <c r="A35" s="8">
         <v>46212</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="10">
         <v>776175166</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="13" t="s">
+      <c r="H35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="16" t="str">
+      <c r="K35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="9">
+        <v>100</v>
+      </c>
+      <c r="M35" s="11">
+        <v>26000</v>
+      </c>
+      <c r="N35" s="11">
+        <v>2600000</v>
+      </c>
+      <c r="O35" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P35" s="17" t="str">
+      <c r="P35" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A36" s="12">
+      <c r="A36" s="8">
         <v>46212</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="10">
         <v>775177806</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="13" t="s">
+      <c r="H36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="K36" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L36" s="13">
+      <c r="L36" s="9">
         <v>3</v>
       </c>
-      <c r="M36" s="15">
+      <c r="M36" s="11">
         <v>19500</v>
       </c>
-      <c r="N36" s="15">
+      <c r="N36" s="11">
         <v>58500</v>
       </c>
-      <c r="O36" s="16" t="str">
+      <c r="O36" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P36" s="17" t="str">
+      <c r="P36" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A37" s="12">
+      <c r="A37" s="8">
         <v>46212</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="10">
         <v>776345625</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="13" t="s">
+      <c r="H37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K37" s="13" t="s">
+      <c r="K37" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="L37" s="13">
+      <c r="L37" s="9">
         <v>1</v>
       </c>
-      <c r="M37" s="15">
+      <c r="M37" s="11">
         <v>11500</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37" s="11">
         <v>11500</v>
       </c>
-      <c r="O37" s="16" t="str">
+      <c r="O37" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P37" s="17" t="str">
+      <c r="P37" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A38" s="12">
+      <c r="A38" s="8">
         <v>46211</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="10">
         <v>776536527</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="13" t="s">
+      <c r="H38" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K38" s="13" t="s">
+      <c r="K38" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="9">
         <v>30</v>
       </c>
-      <c r="M38" s="15">
+      <c r="M38" s="11">
         <v>9000</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38" s="11">
         <v>270000</v>
       </c>
-      <c r="O38" s="16" t="str">
+      <c r="O38" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P38" s="17" t="str">
+      <c r="P38" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A39" s="12">
+      <c r="A39" s="8">
         <v>46211</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="10">
         <v>779598695</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J39" s="13" t="s">
+      <c r="H39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K39" s="13" t="s">
+      <c r="K39" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="13">
+      <c r="L39" s="9">
         <v>20</v>
       </c>
-      <c r="M39" s="15">
+      <c r="M39" s="11">
         <v>9000</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="11">
         <v>180000</v>
       </c>
-      <c r="O39" s="16" t="str">
+      <c r="O39" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P39" s="17" t="str">
+      <c r="P39" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A40" s="12">
+      <c r="A40" s="8">
         <v>46211</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F40" s="14">
+      <c r="F40" s="10">
         <v>778657940</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="13" t="s">
+      <c r="H40" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J40" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="9">
         <v>50</v>
       </c>
-      <c r="M40" s="15">
+      <c r="M40" s="11">
         <v>9000</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="11">
         <v>450000</v>
       </c>
-      <c r="O40" s="16" t="str">
+      <c r="O40" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P40" s="17" t="str">
+      <c r="P40" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A41" s="12">
+      <c r="A41" s="8">
         <v>46211</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="10">
         <v>770158721</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="13" t="s">
+      <c r="H41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K41" s="13" t="s">
+      <c r="K41" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L41" s="13">
+      <c r="L41" s="9">
         <v>25</v>
       </c>
-      <c r="M41" s="15">
+      <c r="M41" s="11">
         <v>15500</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="11">
         <v>387500</v>
       </c>
-      <c r="O41" s="16" t="str">
+      <c r="O41" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P41" s="17" t="str">
+      <c r="P41" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A42" s="12">
+      <c r="A42" s="8">
         <v>46210</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F42" s="14">
+      <c r="F42" s="10">
         <v>772377240</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H42" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="13" t="s">
+      <c r="H42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K42" s="13" t="s">
+      <c r="K42" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L42" s="13">
+      <c r="L42" s="9">
         <v>25</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="11">
         <v>19500</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="11">
         <v>487500</v>
       </c>
-      <c r="O42" s="16" t="str">
+      <c r="O42" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P42" s="17" t="str">
+      <c r="P42" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A43" s="12">
+      <c r="A43" s="8">
         <v>46209</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="10">
         <v>775602981</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="13" t="s">
+      <c r="H43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="K43" s="13" t="s">
+      <c r="K43" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L43" s="13">
+      <c r="L43" s="9">
         <v>25</v>
       </c>
-      <c r="M43" s="15">
+      <c r="M43" s="11">
         <v>6000</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="11">
         <v>150000</v>
       </c>
-      <c r="O43" s="16" t="str">
+      <c r="O43" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P43" s="17" t="str">
+      <c r="P43" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
-      <c r="A44" s="12">
+      <c r="A44" s="8">
         <v>46212</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="14">
+      <c r="F44" s="10">
         <v>773482683</v>
       </c>
-      <c r="G44" s="13" t="s">
+      <c r="G44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="13" t="s">
+      <c r="H44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="K44" s="13" t="s">
+      <c r="K44" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L44" s="13">
+      <c r="L44" s="9">
         <v>10</v>
       </c>
-      <c r="M44" s="15">
+      <c r="M44" s="11">
         <v>9000</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="11">
         <v>90000</v>
       </c>
-      <c r="O44" s="16" t="str">
+      <c r="O44" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P44" s="17" t="str">
+      <c r="P44" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A45" s="12">
+      <c r="A45" s="8">
         <v>46212</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="14">
+      <c r="F45" s="10">
         <v>773122246</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H45" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="13" t="s">
+      <c r="H45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="K45" s="13" t="s">
+      <c r="K45" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L45" s="13">
+      <c r="L45" s="9">
         <v>25</v>
       </c>
-      <c r="M45" s="15">
+      <c r="M45" s="11">
         <v>26000</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="11">
         <v>650000</v>
       </c>
-      <c r="O45" s="16" t="str">
+      <c r="O45" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P45" s="17" t="str">
+      <c r="P45" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A46" s="12">
+      <c r="A46" s="8">
         <v>46212</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="14">
+      <c r="F46" s="10">
         <v>772131614</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="G46" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I46" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="13" t="s">
+      <c r="H46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="K46" s="13" t="s">
+      <c r="K46" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L46" s="13">
+      <c r="L46" s="9">
         <v>5</v>
       </c>
-      <c r="M46" s="15">
+      <c r="M46" s="11">
         <v>9000</v>
       </c>
-      <c r="N46" s="15">
+      <c r="N46" s="11">
         <v>45000</v>
       </c>
-      <c r="O46" s="16" t="str">
+      <c r="O46" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P46" s="17" t="str">
+      <c r="P46" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A47" s="12">
+      <c r="A47" s="8">
         <v>46210</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F47" s="14">
+      <c r="F47" s="10">
         <v>775894237</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H47" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J47" s="13" t="s">
+      <c r="H47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K47" s="13" t="s">
+      <c r="K47" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="L47" s="13">
+      <c r="L47" s="9">
         <v>5</v>
       </c>
-      <c r="M47" s="15">
+      <c r="M47" s="11">
         <v>9000</v>
       </c>
-      <c r="N47" s="15">
+      <c r="N47" s="11">
         <v>45000</v>
       </c>
-      <c r="O47" s="16" t="str">
+      <c r="O47" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P47" s="17" t="str">
+      <c r="P47" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A48" s="12">
+      <c r="A48" s="8">
         <v>46210</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="14">
+      <c r="F48" s="10">
         <v>775894237</v>
       </c>
-      <c r="G48" s="13" t="s">
+      <c r="G48" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H48" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="13" t="s">
+      <c r="H48" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K48" s="13" t="s">
+      <c r="K48" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L48" s="13">
+      <c r="L48" s="9">
         <v>15</v>
       </c>
-      <c r="M48" s="15">
+      <c r="M48" s="11">
         <v>4500</v>
       </c>
-      <c r="N48" s="15">
+      <c r="N48" s="11">
         <v>67500</v>
       </c>
-      <c r="O48" s="16" t="str">
+      <c r="O48" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
         <v>S28</v>
       </c>
-      <c r="P48" s="17" t="str">
+      <c r="P48" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>

--- a/Donnees_RZ.xlsx
+++ b/Donnees_RZ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NDAO ABDOULAYE\Desktop\AFRIKA LEYRI\Rapport\Promoteur\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068F7053-C449-4E70-B072-31B36E02F2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4154EFAB-4B7A-49DD-BFFD-9247190C2224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10996" tabRatio="470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -366,6 +366,15 @@
   </si>
   <si>
     <t xml:space="preserve">Mogi deme dh </t>
+  </si>
+  <si>
+    <t>BABACAR Cissé</t>
+  </si>
+  <si>
+    <t>Mballo Séye</t>
+  </si>
+  <si>
+    <t>Il demande de diminuer le prix</t>
   </si>
 </sst>
 </file>
@@ -433,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -464,6 +473,31 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -771,8 +805,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P48" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
-  <autoFilter ref="A1:P48" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}" name="Semaine_1" displayName="Semaine_1" ref="A1:P50" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16">
+  <autoFilter ref="A1:P50" xr:uid="{FC757211-1341-459A-BE29-FAC5D7146FA5}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F85C405C-E78B-4DA6-8568-08107D7551E4}" name="Date" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{24A95AD6-D6B8-4864-9451-50BFB3565C62}" name="Prenom_Nom_RZ" dataDxfId="14"/>
@@ -1085,7 +1119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.53125" bestFit="1" customWidth="1"/>
@@ -1155,27 +1189,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="8">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+      <c r="F2" s="10">
+        <v>775630094</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>13</v>
@@ -1183,22 +1217,24 @@
       <c r="I2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="9"/>
+      <c r="J2" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="K2" s="9" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="L2" s="9">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M2" s="11">
-        <v>26000</v>
+        <v>11500</v>
       </c>
       <c r="N2" s="11">
-        <v>1300000</v>
+        <v>11500</v>
       </c>
       <c r="O2" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P2" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1207,7 +1243,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>41</v>
@@ -1216,16 +1252,16 @@
         <v>24</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="F3" s="10">
-        <v>775544532</v>
+        <v>775630094</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>13</v>
@@ -1237,44 +1273,44 @@
         <v>73</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="L3" s="9">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="M3" s="11">
-        <v>26000</v>
+        <v>15500</v>
       </c>
       <c r="N3" s="11">
-        <v>650000</v>
+        <v>31000</v>
       </c>
       <c r="O3" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P3" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="F4" s="10">
-        <v>779235028</v>
+        <v>775630094</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>15</v>
@@ -1289,47 +1325,47 @@
         <v>73</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L4" s="9">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="M4" s="11">
-        <v>9000</v>
+        <v>19500</v>
       </c>
       <c r="N4" s="11">
-        <v>495000</v>
+        <v>78000</v>
       </c>
       <c r="O4" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P4" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F5" s="10">
-        <v>776862787</v>
+        <v>775630094</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>13</v>
@@ -1341,20 +1377,20 @@
         <v>73</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="L5" s="9">
         <v>25</v>
       </c>
       <c r="M5" s="11">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="N5" s="11">
-        <v>650000</v>
+        <v>700000</v>
       </c>
       <c r="O5" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P5" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1363,25 +1399,25 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="F6" s="10">
-        <v>773482683</v>
+        <v>781985160</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>13</v>
@@ -1393,20 +1429,20 @@
         <v>73</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="L6" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M6" s="11">
-        <v>9000</v>
+        <v>26000</v>
       </c>
       <c r="N6" s="11">
-        <v>90000</v>
+        <v>650000</v>
       </c>
       <c r="O6" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P6" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
@@ -1415,22 +1451,22 @@
     </row>
     <row r="7" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A7" s="8">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F7" s="10">
-        <v>776862787</v>
+        <v>775586819</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>23</v>
@@ -1441,48 +1477,46 @@
       <c r="I7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>73</v>
-      </c>
+      <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L7" s="9">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="M7" s="11">
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="N7" s="11">
-        <v>97500</v>
+        <v>2600000</v>
       </c>
       <c r="O7" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P7" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
-        <v>46204</v>
+        <v>46212</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F8" s="10">
-        <v>776058374</v>
+        <v>775661455</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>15</v>
@@ -1497,47 +1531,47 @@
         <v>73</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L8" s="9">
         <v>25</v>
       </c>
       <c r="M8" s="11">
-        <v>9000</v>
+        <v>26000</v>
       </c>
       <c r="N8" s="11">
-        <v>225000</v>
+        <v>650000</v>
       </c>
       <c r="O8" s="7" t="str">
         <f>"S"&amp;_xlfn.ISOWEEKNUM(Semaine_1[[#This Row],[Date]])</f>
-        <v>S27</v>
+        <v>S28</v>
       </c>
       <c r="P8" t="str">
         <f>TEXT(Semaine_1[[#This Row],[Date]],"MMMM")</f>
         <v>juillet</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="28.15" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
-        <v>46204</v>
+        <v>46212</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="F9" s="10">
-        <v>775586819</v>
+        <v>774993694</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H9" s="9" t="s